--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="232">
   <si>
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
   <si>
-    <t>Generated from embedded historical records + saved TEDUH records · 15/10/2026</t>
+    <t>Generated from embedded historical records + saved TEDUH records · 16/10/2026</t>
   </si>
   <si>
     <t>RECORD DETAIL</t>
@@ -102,232 +102,235 @@
     <t>Latest record</t>
   </si>
   <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>Sales Unit · latest</t>
+  </si>
+  <si>
+    <t>74 / 81</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>68 / 113</t>
+  </si>
+  <si>
+    <t>21 / 48</t>
+  </si>
+  <si>
+    <t>71 / 113</t>
+  </si>
+  <si>
+    <t>46 / 46</t>
+  </si>
+  <si>
+    <t>56 / 56</t>
+  </si>
+  <si>
+    <t>24 / 25</t>
+  </si>
+  <si>
+    <t>10 / 25</t>
+  </si>
+  <si>
+    <t>77 / 99</t>
+  </si>
+  <si>
+    <t>111 / 111</t>
+  </si>
+  <si>
+    <t>134 / 138</t>
+  </si>
+  <si>
+    <t>79 / 81</t>
+  </si>
+  <si>
+    <t>23 / 26</t>
+  </si>
+  <si>
+    <t>124 / 126</t>
+  </si>
+  <si>
+    <t>98 / 104</t>
+  </si>
+  <si>
+    <t>29 / 44</t>
+  </si>
+  <si>
+    <t>63 / 85</t>
+  </si>
+  <si>
+    <t>23 / 102</t>
+  </si>
+  <si>
+    <t>45 / 136</t>
+  </si>
+  <si>
+    <t>1 / 27</t>
+  </si>
+  <si>
+    <t>161 / 308</t>
+  </si>
+  <si>
+    <t>34 / 149</t>
+  </si>
+  <si>
+    <t>Sales Status · latest</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>Yet to launch</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>44%</t>
+  </si>
+  <si>
+    <t>63%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>78%</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>98%</t>
+  </si>
+  <si>
+    <t>88%</t>
+  </si>
+  <si>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>66%</t>
+  </si>
+  <si>
+    <t>74%</t>
+  </si>
+  <si>
+    <t>23%</t>
+  </si>
+  <si>
+    <t>Yet to sign</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>4%</t>
+  </si>
+  <si>
+    <t>52%</t>
+  </si>
+  <si>
+    <t>Weekly baseline</t>
+  </si>
+  <si>
+    <t>No record 7–14 days earlier</t>
+  </si>
+  <si>
+    <t>Sales Unit · baseline</t>
+  </si>
+  <si>
+    <t>Sales Status · baseline</t>
+  </si>
+  <si>
+    <t>Weekly Change</t>
+  </si>
+  <si>
+    <t>Insufficient weekly history</t>
+  </si>
+  <si>
+    <t>No signed status yet</t>
+  </si>
+  <si>
+    <t>Record Date</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Unit Group / Layout</t>
+  </si>
+  <si>
+    <t>Status Type</t>
+  </si>
+  <si>
+    <t>Signed Units</t>
+  </si>
+  <si>
+    <t>Total Units</t>
+  </si>
+  <si>
+    <t>Signed %</t>
+  </si>
+  <si>
+    <t>Raw Recorded Status</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>17/03/2025</t>
+  </si>
+  <si>
+    <t>Booked</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>11% Booked (9/81 units)</t>
+  </si>
+  <si>
+    <t>Embedded historical record</t>
+  </si>
+  <si>
+    <t>06/10/2025</t>
+  </si>
+  <si>
+    <t>35% Booked (28/81 units)</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>Signed</t>
+  </si>
+  <si>
+    <t>59% Signed (48/81 units)</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>65% Signed (53/81 units)</t>
+  </si>
+  <si>
+    <t>88% Signed (72/81 units)</t>
+  </si>
+  <si>
     <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>Sales Unit · latest</t>
-  </si>
-  <si>
-    <t>74 / 81</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>68 / 113</t>
-  </si>
-  <si>
-    <t>21 / 48</t>
-  </si>
-  <si>
-    <t>71 / 113</t>
-  </si>
-  <si>
-    <t>46 / 46</t>
-  </si>
-  <si>
-    <t>56 / 56</t>
-  </si>
-  <si>
-    <t>24 / 25</t>
-  </si>
-  <si>
-    <t>10 / 25</t>
-  </si>
-  <si>
-    <t>77 / 99</t>
-  </si>
-  <si>
-    <t>111 / 111</t>
-  </si>
-  <si>
-    <t>134 / 138</t>
-  </si>
-  <si>
-    <t>79 / 81</t>
-  </si>
-  <si>
-    <t>23 / 26</t>
-  </si>
-  <si>
-    <t>124 / 126</t>
-  </si>
-  <si>
-    <t>98 / 104</t>
-  </si>
-  <si>
-    <t>29 / 44</t>
-  </si>
-  <si>
-    <t>63 / 85</t>
-  </si>
-  <si>
-    <t>23 / 102</t>
-  </si>
-  <si>
-    <t>45 / 136</t>
-  </si>
-  <si>
-    <t>1 / 27</t>
-  </si>
-  <si>
-    <t>161 / 308</t>
-  </si>
-  <si>
-    <t>34 / 149</t>
-  </si>
-  <si>
-    <t>Sales Status · latest</t>
-  </si>
-  <si>
-    <t>91%</t>
-  </si>
-  <si>
-    <t>Yet to launch</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>44%</t>
-  </si>
-  <si>
-    <t>63%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>96%</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>78%</t>
-  </si>
-  <si>
-    <t>97%</t>
-  </si>
-  <si>
-    <t>98%</t>
-  </si>
-  <si>
-    <t>88%</t>
-  </si>
-  <si>
-    <t>94%</t>
-  </si>
-  <si>
-    <t>66%</t>
-  </si>
-  <si>
-    <t>74%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>Yet to sign</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>52%</t>
-  </si>
-  <si>
-    <t>Weekly baseline</t>
-  </si>
-  <si>
-    <t>No record 7–14 days earlier</t>
-  </si>
-  <si>
-    <t>Sales Unit · baseline</t>
-  </si>
-  <si>
-    <t>Sales Status · baseline</t>
-  </si>
-  <si>
-    <t>Weekly Change</t>
-  </si>
-  <si>
-    <t>Insufficient weekly history</t>
-  </si>
-  <si>
-    <t>No signed status yet</t>
-  </si>
-  <si>
-    <t>Record Date</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Unit Group / Layout</t>
-  </si>
-  <si>
-    <t>Status Type</t>
-  </si>
-  <si>
-    <t>Signed Units</t>
-  </si>
-  <si>
-    <t>Total Units</t>
-  </si>
-  <si>
-    <t>Signed %</t>
-  </si>
-  <si>
-    <t>Raw Recorded Status</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>17/03/2025</t>
-  </si>
-  <si>
-    <t>Booked</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>11% Booked (9/81 units)</t>
-  </si>
-  <si>
-    <t>Embedded historical record</t>
-  </si>
-  <si>
-    <t>06/10/2025</t>
-  </si>
-  <si>
-    <t>35% Booked (28/81 units)</t>
-  </si>
-  <si>
-    <t>08/06/2026</t>
-  </si>
-  <si>
-    <t>Signed</t>
-  </si>
-  <si>
-    <t>59% Signed (48/81 units)</t>
-  </si>
-  <si>
-    <t>10/07/2026</t>
-  </si>
-  <si>
-    <t>65% Signed (53/81 units)</t>
-  </si>
-  <si>
-    <t>88% Signed (72/81 units)</t>
   </si>
   <si>
     <t>74/81 signed</t>
@@ -1965,7 +1968,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2149,7 +2152,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>3</v>
@@ -2170,53 +2173,53 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="11">
+        <v>74</v>
+      </c>
+      <c r="F8" s="11">
+        <v>81</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0.9135802469135802</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>94</v>
@@ -2228,7 +2231,7 @@
         <v>94</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>96</v>
@@ -2236,16 +2239,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>94</v>
@@ -2257,7 +2260,7 @@
         <v>94</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>96</v>
@@ -2265,26 +2268,28 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="11">
-        <v>113</v>
-      </c>
-      <c r="G11" s="13"/>
+      <c r="F11" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>94</v>
+      </c>
       <c r="H11" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>96</v>
@@ -2292,7 +2297,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>5</v>
@@ -2311,7 +2316,7 @@
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>96</v>
@@ -2319,7 +2324,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>5</v>
@@ -2338,7 +2343,7 @@
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>96</v>
@@ -2346,7 +2351,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>5</v>
@@ -2373,7 +2378,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>5</v>
@@ -2382,19 +2387,17 @@
         <v>20</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="11">
-        <v>34</v>
+        <v>93</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="F15" s="11">
         <v>113</v>
       </c>
-      <c r="G15" s="14">
-        <v>0.3008849557522124</v>
-      </c>
+      <c r="G15" s="13"/>
       <c r="H15" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>96</v>
@@ -2402,7 +2405,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>5</v>
@@ -2414,16 +2417,16 @@
         <v>100</v>
       </c>
       <c r="E16" s="11">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F16" s="11">
         <v>113</v>
       </c>
       <c r="G16" s="14">
-        <v>0.3274336283185841</v>
+        <v>0.3008849557522124</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>96</v>
@@ -2431,7 +2434,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>5</v>
@@ -2452,7 +2455,7 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>96</v>
@@ -2460,7 +2463,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>5</v>
@@ -2472,16 +2475,16 @@
         <v>100</v>
       </c>
       <c r="E18" s="11">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F18" s="11">
         <v>113</v>
       </c>
       <c r="G18" s="14">
-        <v>0.4778761061946903</v>
+        <v>0.3274336283185841</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>96</v>
@@ -2489,7 +2492,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>5</v>
@@ -2501,13 +2504,13 @@
         <v>100</v>
       </c>
       <c r="E19" s="11">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F19" s="11">
         <v>113</v>
       </c>
       <c r="G19" s="14">
-        <v>0.5575221238938053</v>
+        <v>0.4778761061946903</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>123</v>
@@ -2518,7 +2521,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>5</v>
@@ -2530,13 +2533,13 @@
         <v>100</v>
       </c>
       <c r="E20" s="11">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F20" s="11">
         <v>113</v>
       </c>
       <c r="G20" s="14">
-        <v>0.6017699115044248</v>
+        <v>0.5575221238938053</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>124</v>
@@ -2547,7 +2550,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>5</v>
@@ -2568,7 +2571,7 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>96</v>
@@ -2576,7 +2579,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>5</v>
@@ -2600,66 +2603,70 @@
         <v>125</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="E23" s="11">
+        <v>68</v>
       </c>
       <c r="F23" s="11">
-        <v>48</v>
-      </c>
-      <c r="G23" s="13"/>
+        <v>113</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0.6017699115044248</v>
+      </c>
       <c r="H23" s="12" t="s">
         <v>126</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>114</v>
+        <v>29</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="E24" s="11">
+        <v>68</v>
       </c>
       <c r="F24" s="11">
-        <v>48</v>
-      </c>
-      <c r="G24" s="13"/>
+        <v>113</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0.6017699115044248</v>
+      </c>
       <c r="H24" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>6</v>
@@ -2686,7 +2693,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>6</v>
@@ -2713,7 +2720,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>6</v>
@@ -2732,7 +2739,7 @@
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I27" s="11" t="s">
         <v>96</v>
@@ -2740,7 +2747,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>6</v>
@@ -2767,7 +2774,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>6</v>
@@ -2776,17 +2783,15 @@
         <v>21</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" s="11">
-        <v>15</v>
+        <v>93</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="F29" s="11">
         <v>48</v>
       </c>
-      <c r="G29" s="14">
-        <v>0.3125</v>
-      </c>
+      <c r="G29" s="13"/>
       <c r="H29" s="12" t="s">
         <v>130</v>
       </c>
@@ -2796,7 +2801,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>6</v>
@@ -2805,19 +2810,17 @@
         <v>21</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E30" s="11">
-        <v>19</v>
+        <v>93</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="F30" s="11">
         <v>48</v>
       </c>
-      <c r="G30" s="14">
-        <v>0.3958333333333333</v>
-      </c>
+      <c r="G30" s="13"/>
       <c r="H30" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>96</v>
@@ -2825,7 +2828,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>6</v>
@@ -2837,13 +2840,13 @@
         <v>100</v>
       </c>
       <c r="E31" s="11">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F31" s="11">
         <v>48</v>
       </c>
       <c r="G31" s="14">
-        <v>0.3958333333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>131</v>
@@ -2854,7 +2857,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>6</v>
@@ -2866,13 +2869,13 @@
         <v>100</v>
       </c>
       <c r="E32" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F32" s="11">
         <v>48</v>
       </c>
       <c r="G32" s="14">
-        <v>0.4375</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>132</v>
@@ -2883,7 +2886,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>6</v>
@@ -2895,45 +2898,45 @@
         <v>100</v>
       </c>
       <c r="E33" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F33" s="11">
         <v>48</v>
       </c>
       <c r="G33" s="14">
-        <v>0.4375</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="11">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="F34" s="11">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="G34" s="14">
-        <v>0.8383838383838383</v>
+        <v>0.4375</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>96</v>
@@ -2941,65 +2944,65 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="11">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="F35" s="11">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G35" s="14">
-        <v>0.6194690265486725</v>
+        <v>0.4375</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="11">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="F36" s="11">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G36" s="14">
-        <v>0.6194690265486725</v>
+        <v>0.4375</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>7</v>
@@ -3011,16 +3014,16 @@
         <v>100</v>
       </c>
       <c r="E37" s="11">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F37" s="11">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G37" s="14">
-        <v>0.6283185840707964</v>
+        <v>0.8383838383838383</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I37" s="11" t="s">
         <v>96</v>
@@ -3028,7 +3031,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>7</v>
@@ -3040,45 +3043,45 @@
         <v>100</v>
       </c>
       <c r="E38" s="11">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F38" s="11">
         <v>113</v>
       </c>
       <c r="G38" s="14">
-        <v>0.6283185840707964</v>
+        <v>0.6194690265486725</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="11">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F39" s="11">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="G39" s="14">
-        <v>0.9782608695652174</v>
+        <v>0.6194690265486725</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I39" s="11" t="s">
         <v>96</v>
@@ -3086,10 +3089,10 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>22</v>
@@ -3098,16 +3101,16 @@
         <v>100</v>
       </c>
       <c r="E40" s="11">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F40" s="11">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="G40" s="14">
-        <v>0.8392857142857143</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>96</v>
@@ -3115,65 +3118,65 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="11">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F41" s="11">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G41" s="14">
-        <v>0.52</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="11">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="F42" s="11">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G42" s="14">
-        <v>0.12</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>8</v>
@@ -3185,16 +3188,16 @@
         <v>100</v>
       </c>
       <c r="E43" s="11">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F43" s="11">
         <v>46</v>
       </c>
       <c r="G43" s="14">
-        <v>1</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I43" s="11" t="s">
         <v>96</v>
@@ -3202,7 +3205,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>8</v>
@@ -3214,16 +3217,16 @@
         <v>100</v>
       </c>
       <c r="E44" s="11">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F44" s="11">
         <v>56</v>
       </c>
       <c r="G44" s="14">
-        <v>1</v>
+        <v>0.8392857142857143</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>96</v>
@@ -3231,7 +3234,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>8</v>
@@ -3243,16 +3246,16 @@
         <v>100</v>
       </c>
       <c r="E45" s="11">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F45" s="11">
         <v>25</v>
       </c>
       <c r="G45" s="14">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I45" s="11" t="s">
         <v>96</v>
@@ -3260,7 +3263,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>8</v>
@@ -3272,16 +3275,16 @@
         <v>100</v>
       </c>
       <c r="E46" s="11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F46" s="11">
         <v>25</v>
       </c>
       <c r="G46" s="14">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>96</v>
@@ -3289,7 +3292,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>8</v>
@@ -3310,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I47" s="11" t="s">
         <v>96</v>
@@ -3318,7 +3321,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>8</v>
@@ -3339,7 +3342,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>96</v>
@@ -3347,7 +3350,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>8</v>
@@ -3368,7 +3371,7 @@
         <v>0.96</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I49" s="11" t="s">
         <v>96</v>
@@ -3376,7 +3379,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>8</v>
@@ -3388,13 +3391,13 @@
         <v>100</v>
       </c>
       <c r="E50" s="11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F50" s="11">
         <v>25</v>
       </c>
       <c r="G50" s="14">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H50" s="12" t="s">
         <v>146</v>
@@ -3405,7 +3408,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>8</v>
@@ -3426,7 +3429,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I51" s="11" t="s">
         <v>96</v>
@@ -3434,7 +3437,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>8</v>
@@ -3455,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>96</v>
@@ -3463,7 +3466,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>8</v>
@@ -3484,7 +3487,7 @@
         <v>0.96</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I53" s="11" t="s">
         <v>96</v>
@@ -3492,7 +3495,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>8</v>
@@ -3504,13 +3507,13 @@
         <v>100</v>
       </c>
       <c r="E54" s="11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F54" s="11">
         <v>25</v>
       </c>
       <c r="G54" s="14">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="H54" s="12" t="s">
         <v>147</v>
@@ -3521,7 +3524,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>8</v>
@@ -3542,15 +3545,15 @@
         <v>1</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>8</v>
@@ -3571,15 +3574,15 @@
         <v>1</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>8</v>
@@ -3600,15 +3603,15 @@
         <v>0.96</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>8</v>
@@ -3629,126 +3632,126 @@
         <v>0.4</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E59" s="11">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="F59" s="11">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="G59" s="14">
-        <v>0.8787878787878788</v>
+        <v>1</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E60" s="11">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F60" s="11">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="G60" s="14">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E61" s="11">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="F61" s="11">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G61" s="14">
-        <v>0.7777777777777778</v>
+        <v>0.96</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E62" s="11">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F62" s="11">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G62" s="14">
-        <v>0.7777777777777778</v>
+        <v>0.4</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -3756,141 +3759,141 @@
         <v>29</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E63" s="11">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="F63" s="11">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="G63" s="14">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E64" s="11">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="F64" s="11">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="G64" s="14">
-        <v>0.9099099099099099</v>
+        <v>1</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E65" s="11">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="F65" s="11">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="G65" s="14">
-        <v>0.9492753623188406</v>
+        <v>0.96</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c r="B66" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E66" s="11">
         <v>10</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E66" s="11">
-        <v>78</v>
-      </c>
       <c r="F66" s="11">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="G66" s="14">
-        <v>0.9629629629629629</v>
+        <v>0.4</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E67" s="11">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F67" s="11">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G67" s="14">
-        <v>0.5135135135135135</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="I67" s="11" t="s">
         <v>96</v>
@@ -3898,28 +3901,28 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D68" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E68" s="11">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F68" s="11">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="G68" s="14">
-        <v>0.6739130434782609</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>96</v>
@@ -3927,28 +3930,28 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E69" s="11">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="F69" s="11">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G69" s="14">
-        <v>0.5432098765432098</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I69" s="11" t="s">
         <v>96</v>
@@ -3956,28 +3959,28 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E70" s="11">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F70" s="11">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G70" s="14">
-        <v>0.5585585585585585</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>96</v>
@@ -3985,65 +3988,65 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E71" s="11">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F71" s="11">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="G71" s="14">
-        <v>0.7101449275362319</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E72" s="11">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="F72" s="11">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G72" s="14">
-        <v>0.6419753086419753</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>10</v>
@@ -4055,16 +4058,16 @@
         <v>100</v>
       </c>
       <c r="E73" s="11">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F73" s="11">
         <v>111</v>
       </c>
       <c r="G73" s="14">
-        <v>0.918918918918919</v>
+        <v>0.9099099099099099</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="I73" s="11" t="s">
         <v>96</v>
@@ -4072,7 +4075,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>10</v>
@@ -4093,7 +4096,7 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>96</v>
@@ -4101,7 +4104,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>10</v>
@@ -4122,7 +4125,7 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I75" s="11" t="s">
         <v>96</v>
@@ -4130,7 +4133,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>10</v>
@@ -4142,16 +4145,16 @@
         <v>100</v>
       </c>
       <c r="E76" s="11">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="F76" s="11">
         <v>111</v>
       </c>
       <c r="G76" s="14">
-        <v>0.918918918918919</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>96</v>
@@ -4159,7 +4162,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>10</v>
@@ -4171,16 +4174,16 @@
         <v>100</v>
       </c>
       <c r="E77" s="11">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="F77" s="11">
         <v>138</v>
       </c>
       <c r="G77" s="14">
-        <v>0.9492753623188406</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="I77" s="11" t="s">
         <v>96</v>
@@ -4188,7 +4191,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="B78" s="11" t="s">
         <v>10</v>
@@ -4200,16 +4203,16 @@
         <v>100</v>
       </c>
       <c r="E78" s="11">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F78" s="11">
         <v>81</v>
       </c>
       <c r="G78" s="14">
-        <v>0.9629629629629629</v>
+        <v>0.5432098765432098</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>96</v>
@@ -4217,7 +4220,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>10</v>
@@ -4229,16 +4232,16 @@
         <v>100</v>
       </c>
       <c r="E79" s="11">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="F79" s="11">
         <v>111</v>
       </c>
       <c r="G79" s="14">
-        <v>1</v>
+        <v>0.5585585585585585</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I79" s="11" t="s">
         <v>96</v>
@@ -4246,7 +4249,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>10</v>
@@ -4258,16 +4261,16 @@
         <v>100</v>
       </c>
       <c r="E80" s="11">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="F80" s="11">
         <v>138</v>
       </c>
       <c r="G80" s="14">
-        <v>0.9710144927536232</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>96</v>
@@ -4275,7 +4278,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>10</v>
@@ -4287,16 +4290,16 @@
         <v>100</v>
       </c>
       <c r="E81" s="11">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="F81" s="11">
         <v>81</v>
       </c>
       <c r="G81" s="14">
-        <v>0.9753086419753086</v>
+        <v>0.6419753086419753</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I81" s="11" t="s">
         <v>96</v>
@@ -4304,7 +4307,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>10</v>
@@ -4316,24 +4319,24 @@
         <v>100</v>
       </c>
       <c r="E82" s="11">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F82" s="11">
         <v>111</v>
       </c>
       <c r="G82" s="14">
-        <v>1</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>10</v>
@@ -4345,24 +4348,24 @@
         <v>100</v>
       </c>
       <c r="E83" s="11">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F83" s="11">
         <v>138</v>
       </c>
       <c r="G83" s="14">
-        <v>0.9710144927536232</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>10</v>
@@ -4374,27 +4377,27 @@
         <v>100</v>
       </c>
       <c r="E84" s="11">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F84" s="11">
         <v>81</v>
       </c>
       <c r="G84" s="14">
-        <v>0.9753086419753086</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>20</v>
@@ -4403,16 +4406,16 @@
         <v>100</v>
       </c>
       <c r="E85" s="11">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="F85" s="11">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="G85" s="14">
-        <v>0.11538461538461539</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I85" s="11" t="s">
         <v>96</v>
@@ -4420,10 +4423,10 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>23</v>
@@ -4432,16 +4435,16 @@
         <v>100</v>
       </c>
       <c r="E86" s="11">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="F86" s="11">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="G86" s="14">
-        <v>0.6111111111111112</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>96</v>
@@ -4449,10 +4452,10 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C87" s="12" t="s">
         <v>22</v>
@@ -4461,16 +4464,16 @@
         <v>100</v>
       </c>
       <c r="E87" s="11">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F87" s="11">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="G87" s="14">
-        <v>0.16346153846153846</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="I87" s="11" t="s">
         <v>96</v>
@@ -4478,28 +4481,28 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F88" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G88" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="E88" s="11">
+        <v>111</v>
+      </c>
+      <c r="F88" s="11">
+        <v>111</v>
+      </c>
+      <c r="G88" s="14">
+        <v>1</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>96</v>
@@ -4507,28 +4510,28 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E89" s="11">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="F89" s="11">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G89" s="14">
-        <v>0.6538461538461539</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I89" s="11" t="s">
         <v>96</v>
@@ -4536,28 +4539,28 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E90" s="11">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="F90" s="11">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G90" s="14">
-        <v>0.8809523809523809</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I90" s="11" t="s">
         <v>96</v>
@@ -4565,202 +4568,202 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D91" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E91" s="11">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="F91" s="11">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G91" s="14">
-        <v>0.6826923076923077</v>
+        <v>1</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D92" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E92" s="11">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="F92" s="11">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G92" s="14">
-        <v>0.6538461538461539</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D93" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E93" s="11">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="F93" s="11">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G93" s="14">
-        <v>0.9206349206349206</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E94" s="11">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="F94" s="11">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G94" s="14">
-        <v>0.8557692307692307</v>
+        <v>1</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E95" s="11">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="F95" s="11">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G95" s="14">
-        <v>0.8846153846153846</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E96" s="11">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="F96" s="11">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G96" s="14">
-        <v>0.9841269841269841</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E97" s="11">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="F97" s="11">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G97" s="14">
-        <v>0.9423076923076923</v>
+        <v>0.11538461538461539</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="I97" s="11" t="s">
         <v>96</v>
@@ -4768,97 +4771,97 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D98" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E98" s="11">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="F98" s="11">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="G98" s="14">
-        <v>0.8846153846153846</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D99" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E99" s="11">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="F99" s="11">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="G99" s="14">
-        <v>0.9841269841269841</v>
+        <v>0.16346153846153846</v>
       </c>
       <c r="H99" s="12" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E100" s="11">
-        <v>98</v>
-      </c>
-      <c r="F100" s="11">
-        <v>104</v>
-      </c>
-      <c r="G100" s="14">
-        <v>0.9423076923076923</v>
+        <v>109</v>
+      </c>
+      <c r="E100" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F100" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="G100" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="H100" s="12" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>20</v>
@@ -4867,16 +4870,16 @@
         <v>100</v>
       </c>
       <c r="E101" s="11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F101" s="11">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G101" s="14">
-        <v>0.36363636363636365</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="I101" s="11" t="s">
         <v>96</v>
@@ -4884,10 +4887,10 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>23</v>
@@ -4896,16 +4899,16 @@
         <v>100</v>
       </c>
       <c r="E102" s="11">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="F102" s="11">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G102" s="14">
-        <v>0.4588235294117647</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>96</v>
@@ -4913,10 +4916,10 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>22</v>
@@ -4925,16 +4928,16 @@
         <v>100</v>
       </c>
       <c r="E103" s="11">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F103" s="11">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G103" s="14">
-        <v>0.10784313725490197</v>
+        <v>0.6826923076923077</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I103" s="11" t="s">
         <v>96</v>
@@ -4942,10 +4945,10 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C104" s="12" t="s">
         <v>20</v>
@@ -4954,16 +4957,16 @@
         <v>100</v>
       </c>
       <c r="E104" s="11">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F104" s="11">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G104" s="14">
-        <v>0.6590909090909091</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>96</v>
@@ -4971,10 +4974,10 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>23</v>
@@ -4983,16 +4986,16 @@
         <v>100</v>
       </c>
       <c r="E105" s="11">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="F105" s="11">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G105" s="14">
-        <v>0.7411764705882353</v>
+        <v>0.9206349206349206</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="I105" s="11" t="s">
         <v>96</v>
@@ -5000,10 +5003,10 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>22</v>
@@ -5012,16 +5015,16 @@
         <v>100</v>
       </c>
       <c r="E106" s="11">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="F106" s="11">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G106" s="14">
-        <v>0.21568627450980393</v>
+        <v>0.8557692307692307</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>96</v>
@@ -5029,10 +5032,10 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>20</v>
@@ -5041,27 +5044,27 @@
         <v>100</v>
       </c>
       <c r="E107" s="11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F107" s="11">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G107" s="14">
-        <v>0.6590909090909091</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="I107" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>23</v>
@@ -5070,27 +5073,27 @@
         <v>100</v>
       </c>
       <c r="E108" s="11">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F108" s="11">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G108" s="14">
-        <v>0.7411764705882353</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="I108" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>22</v>
@@ -5099,172 +5102,172 @@
         <v>100</v>
       </c>
       <c r="E109" s="11">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="F109" s="11">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G109" s="14">
-        <v>0.22549019607843138</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="I109" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C110" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E110" s="11">
+        <v>23</v>
+      </c>
+      <c r="F110" s="11">
+        <v>26</v>
+      </c>
+      <c r="G110" s="14">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="H110" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I110" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E110" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F110" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G110" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H110" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I110" s="11" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C111" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E111" s="11">
+        <v>124</v>
+      </c>
+      <c r="F111" s="11">
+        <v>126</v>
+      </c>
+      <c r="G111" s="14">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="H111" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="I111" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E111" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G111" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H111" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I111" s="11" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C112" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E112" s="11">
+        <v>98</v>
+      </c>
+      <c r="F112" s="11">
+        <v>104</v>
+      </c>
+      <c r="G112" s="14">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="H112" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="I112" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E112" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F112" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G112" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H112" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="I112" s="11" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E113" s="11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F113" s="11">
-        <v>136</v>
+        <v>26</v>
       </c>
       <c r="G113" s="14">
-        <v>0.17647058823529413</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="I113" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D114" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E114" s="11">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="F114" s="11">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G114" s="14">
-        <v>0.22058823529411764</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>22</v>
@@ -5273,74 +5276,74 @@
         <v>100</v>
       </c>
       <c r="E115" s="11">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="F115" s="11">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="G115" s="14">
-        <v>0.33088235294117646</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="I115" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D116" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E116" s="11">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F116" s="11">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G116" s="14">
-        <v>0.33088235294117646</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="H116" s="12" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="D117" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E117" s="11">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="F117" s="11">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="G117" s="14">
-        <v>0.42857142857142855</v>
+        <v>0.4588235294117647</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="I117" s="11" t="s">
         <v>96</v>
@@ -5348,28 +5351,28 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D118" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E118" s="11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F118" s="11">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="G118" s="14">
-        <v>0.037037037037037035</v>
+        <v>0.10784313725490197</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>96</v>
@@ -5377,28 +5380,28 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="D119" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E119" s="11">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="F119" s="11">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="G119" s="14">
-        <v>0.4444444444444444</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="I119" s="11" t="s">
         <v>96</v>
@@ -5406,28 +5409,28 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D120" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E120" s="11">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F120" s="11">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="G120" s="14">
-        <v>0</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>96</v>
@@ -5435,28 +5438,28 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>121</v>
+        <v>30</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="D121" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E121" s="11">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="F121" s="11">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="G121" s="14">
-        <v>0.656084656084656</v>
+        <v>0.21568627450980393</v>
       </c>
       <c r="H121" s="12" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="I121" s="11" t="s">
         <v>96</v>
@@ -5464,202 +5467,202 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D122" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E122" s="11">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F122" s="11">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G122" s="14">
-        <v>0</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="I122" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="D123" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E123" s="11">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="F123" s="11">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="G123" s="14">
-        <v>0.783068783068783</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="H123" s="12" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="I123" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D124" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E124" s="11">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F124" s="11">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="G124" s="14">
-        <v>0.037037037037037035</v>
+        <v>0.22549019607843138</v>
       </c>
       <c r="H124" s="12" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="D125" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E125" s="11">
-        <v>154</v>
+        <v>29</v>
       </c>
       <c r="F125" s="11">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="G125" s="14">
-        <v>0.8148148148148148</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H125" s="12" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="I125" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D126" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E126" s="11">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F126" s="11">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="G126" s="14">
-        <v>0.037037037037037035</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="H126" s="12" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D127" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E127" s="11">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="F127" s="11">
-        <v>308</v>
+        <v>102</v>
       </c>
       <c r="G127" s="14">
-        <v>0.5194805194805194</v>
+        <v>0.22549019607843138</v>
       </c>
       <c r="H127" s="12" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E128" s="11">
-        <v>1</v>
-      </c>
-      <c r="F128" s="11">
-        <v>27</v>
-      </c>
-      <c r="G128" s="14">
-        <v>0.037037037037037035</v>
+        <v>109</v>
+      </c>
+      <c r="E128" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F128" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="G128" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="H128" s="12" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>96</v>
@@ -5667,86 +5670,86 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E129" s="11">
-        <v>1</v>
-      </c>
-      <c r="F129" s="11">
-        <v>27</v>
-      </c>
-      <c r="G129" s="14">
-        <v>0.037037037037037035</v>
+        <v>109</v>
+      </c>
+      <c r="E129" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F129" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="G129" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E130" s="11">
-        <v>161</v>
-      </c>
-      <c r="F130" s="11">
-        <v>308</v>
-      </c>
-      <c r="G130" s="14">
-        <v>0.5227272727272727</v>
+        <v>109</v>
+      </c>
+      <c r="E130" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F130" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="G130" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="H130" s="12" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D131" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E131" s="11">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F131" s="11">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="G131" s="14">
-        <v>0.06040268456375839</v>
+        <v>0.17647058823529413</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="I131" s="11" t="s">
         <v>96</v>
@@ -5754,28 +5757,28 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D132" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E132" s="11">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F132" s="11">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="G132" s="14">
-        <v>0.14093959731543623</v>
+        <v>0.22058823529411764</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="I132" s="11" t="s">
         <v>96</v>
@@ -5783,28 +5786,28 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D133" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E133" s="11">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="F133" s="11">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="G133" s="14">
-        <v>0.15436241610738255</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="I133" s="11" t="s">
         <v>96</v>
@@ -5812,86 +5815,86 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D134" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E134" s="11">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F134" s="11">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="G134" s="14">
-        <v>0.2080536912751678</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="I134" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D135" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E135" s="11">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F135" s="11">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="G135" s="14">
-        <v>0.22818791946308725</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="I135" s="11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="D136" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E136" s="11">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="F136" s="11">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="G136" s="14">
-        <v>0.22818791946308725</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="I136" s="11" t="s">
         <v>96</v>
@@ -5899,35 +5902,673 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E137" s="11">
+        <v>1</v>
+      </c>
+      <c r="F137" s="11">
+        <v>27</v>
+      </c>
+      <c r="G137" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H137" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I137" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E138" s="11">
+        <v>84</v>
+      </c>
+      <c r="F138" s="11">
+        <v>189</v>
+      </c>
+      <c r="G138" s="14">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="H138" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="I138" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B139" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E139" s="11">
+        <v>0</v>
+      </c>
+      <c r="F139" s="11">
+        <v>27</v>
+      </c>
+      <c r="G139" s="14">
+        <v>0</v>
+      </c>
+      <c r="H139" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="I139" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E140" s="11">
+        <v>124</v>
+      </c>
+      <c r="F140" s="11">
+        <v>189</v>
+      </c>
+      <c r="G140" s="14">
+        <v>0.656084656084656</v>
+      </c>
+      <c r="H140" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="I140" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E141" s="11">
+        <v>0</v>
+      </c>
+      <c r="F141" s="11">
+        <v>27</v>
+      </c>
+      <c r="G141" s="14">
+        <v>0</v>
+      </c>
+      <c r="H141" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="I141" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B142" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E142" s="11">
+        <v>148</v>
+      </c>
+      <c r="F142" s="11">
+        <v>189</v>
+      </c>
+      <c r="G142" s="14">
+        <v>0.783068783068783</v>
+      </c>
+      <c r="H142" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I142" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B143" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E143" s="11">
+        <v>1</v>
+      </c>
+      <c r="F143" s="11">
+        <v>27</v>
+      </c>
+      <c r="G143" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H143" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I143" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E144" s="11">
+        <v>154</v>
+      </c>
+      <c r="F144" s="11">
+        <v>189</v>
+      </c>
+      <c r="G144" s="14">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="H144" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="I144" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E145" s="11">
+        <v>1</v>
+      </c>
+      <c r="F145" s="11">
+        <v>27</v>
+      </c>
+      <c r="G145" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H145" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I145" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E146" s="11">
+        <v>160</v>
+      </c>
+      <c r="F146" s="11">
+        <v>308</v>
+      </c>
+      <c r="G146" s="14">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="I146" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E147" s="11">
+        <v>1</v>
+      </c>
+      <c r="F147" s="11">
+        <v>27</v>
+      </c>
+      <c r="G147" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H147" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I147" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E148" s="11">
+        <v>1</v>
+      </c>
+      <c r="F148" s="11">
+        <v>27</v>
+      </c>
+      <c r="G148" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H148" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="I148" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E149" s="11">
+        <v>161</v>
+      </c>
+      <c r="F149" s="11">
+        <v>308</v>
+      </c>
+      <c r="G149" s="14">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="H149" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="I149" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B137" s="11" t="s">
+      <c r="B150" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E150" s="11">
+        <v>1</v>
+      </c>
+      <c r="F150" s="11">
+        <v>27</v>
+      </c>
+      <c r="G150" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H150" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="I150" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E151" s="11">
+        <v>161</v>
+      </c>
+      <c r="F151" s="11">
+        <v>308</v>
+      </c>
+      <c r="G151" s="14">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="H151" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="I151" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B152" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C137" s="12" t="s">
+      <c r="C152" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D137" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E137" s="11">
+      <c r="D152" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E152" s="11">
+        <v>9</v>
+      </c>
+      <c r="F152" s="11">
+        <v>149</v>
+      </c>
+      <c r="G152" s="14">
+        <v>0.06040268456375839</v>
+      </c>
+      <c r="H152" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="I152" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B153" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E153" s="11">
+        <v>21</v>
+      </c>
+      <c r="F153" s="11">
+        <v>149</v>
+      </c>
+      <c r="G153" s="14">
+        <v>0.14093959731543623</v>
+      </c>
+      <c r="H153" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="I153" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E154" s="11">
+        <v>23</v>
+      </c>
+      <c r="F154" s="11">
+        <v>149</v>
+      </c>
+      <c r="G154" s="14">
+        <v>0.15436241610738255</v>
+      </c>
+      <c r="H154" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="I154" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E155" s="11">
+        <v>31</v>
+      </c>
+      <c r="F155" s="11">
+        <v>149</v>
+      </c>
+      <c r="G155" s="14">
+        <v>0.2080536912751678</v>
+      </c>
+      <c r="H155" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="I155" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E156" s="11">
         <v>34</v>
       </c>
-      <c r="F137" s="11">
+      <c r="F156" s="11">
         <v>149</v>
       </c>
-      <c r="G137" s="14">
+      <c r="G156" s="14">
         <v>0.22818791946308725</v>
       </c>
-      <c r="H137" s="12" t="s">
+      <c r="H156" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="I137" s="11" t="s">
-        <v>106</v>
+      <c r="I156" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E157" s="11">
+        <v>34</v>
+      </c>
+      <c r="F157" s="11">
+        <v>149</v>
+      </c>
+      <c r="G157" s="14">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H157" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="I157" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E158" s="11">
+        <v>34</v>
+      </c>
+      <c r="F158" s="11">
+        <v>149</v>
+      </c>
+      <c r="G158" s="14">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H158" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="I158" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E159" s="11">
+        <v>34</v>
+      </c>
+      <c r="F159" s="11">
+        <v>149</v>
+      </c>
+      <c r="G159" s="14">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H159" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="I159" s="11" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I137"/>
+  <autoFilter ref="A1:I159"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5944,10 +6585,10 @@
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -5955,23 +6596,23 @@
         <v>76</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -5979,23 +6620,23 @@
         <v>80</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="239">
   <si>
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
   <si>
-    <t>Generated from embedded historical records + saved TEDUH records · 16/10/2026</t>
+    <t>Generated from embedded historical records + saved TEDUH records · 19/10/2026</t>
   </si>
   <si>
     <t>RECORD DETAIL</t>
@@ -102,241 +102,253 @@
     <t>Latest record</t>
   </si>
   <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>Sales Unit · latest</t>
+  </si>
+  <si>
+    <t>74 / 81</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>69 / 113</t>
+  </si>
+  <si>
+    <t>21 / 48</t>
+  </si>
+  <si>
+    <t>71 / 113</t>
+  </si>
+  <si>
+    <t>46 / 46</t>
+  </si>
+  <si>
+    <t>56 / 56</t>
+  </si>
+  <si>
+    <t>24 / 25</t>
+  </si>
+  <si>
+    <t>10 / 25</t>
+  </si>
+  <si>
+    <t>77 / 99</t>
+  </si>
+  <si>
+    <t>111 / 111</t>
+  </si>
+  <si>
+    <t>134 / 138</t>
+  </si>
+  <si>
+    <t>79 / 81</t>
+  </si>
+  <si>
+    <t>23 / 26</t>
+  </si>
+  <si>
+    <t>124 / 126</t>
+  </si>
+  <si>
+    <t>98 / 104</t>
+  </si>
+  <si>
+    <t>29 / 44</t>
+  </si>
+  <si>
+    <t>65 / 85</t>
+  </si>
+  <si>
+    <t>24 / 102</t>
+  </si>
+  <si>
+    <t>45 / 136</t>
+  </si>
+  <si>
+    <t>1 / 27</t>
+  </si>
+  <si>
+    <t>161 / 308</t>
+  </si>
+  <si>
+    <t>34 / 149</t>
+  </si>
+  <si>
+    <t>Sales Status · latest</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>Yet to launch</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>44%</t>
+  </si>
+  <si>
+    <t>63%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>78%</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>98%</t>
+  </si>
+  <si>
+    <t>88%</t>
+  </si>
+  <si>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>66%</t>
+  </si>
+  <si>
+    <t>76%</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>Yet to sign</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>4%</t>
+  </si>
+  <si>
+    <t>52%</t>
+  </si>
+  <si>
+    <t>23%</t>
+  </si>
+  <si>
+    <t>Weekly baseline</t>
+  </si>
+  <si>
+    <t>No record 7–14 days earlier</t>
+  </si>
+  <si>
+    <t>Sales Unit · baseline</t>
+  </si>
+  <si>
+    <t>Sales Status · baseline</t>
+  </si>
+  <si>
+    <t>Weekly Change</t>
+  </si>
+  <si>
+    <t>Insufficient weekly history</t>
+  </si>
+  <si>
+    <t>No signed status yet</t>
+  </si>
+  <si>
+    <t>Record Date</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Unit Group / Layout</t>
+  </si>
+  <si>
+    <t>Status Type</t>
+  </si>
+  <si>
+    <t>Signed Units</t>
+  </si>
+  <si>
+    <t>Total Units</t>
+  </si>
+  <si>
+    <t>Signed %</t>
+  </si>
+  <si>
+    <t>Raw Recorded Status</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>17/03/2025</t>
+  </si>
+  <si>
+    <t>Booked</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>11% Booked (9/81 units)</t>
+  </si>
+  <si>
+    <t>Embedded historical record</t>
+  </si>
+  <si>
+    <t>06/10/2025</t>
+  </si>
+  <si>
+    <t>35% Booked (28/81 units)</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>Signed</t>
+  </si>
+  <si>
+    <t>59% Signed (48/81 units)</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>65% Signed (53/81 units)</t>
+  </si>
+  <si>
+    <t>88% Signed (72/81 units)</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>74/81 signed</t>
+  </si>
+  <si>
+    <t>Saved TEDUH record</t>
+  </si>
+  <si>
     <t>16/10/2026</t>
   </si>
   <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>Sales Unit · latest</t>
-  </si>
-  <si>
-    <t>74 / 81</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>68 / 113</t>
-  </si>
-  <si>
-    <t>21 / 48</t>
-  </si>
-  <si>
-    <t>71 / 113</t>
-  </si>
-  <si>
-    <t>46 / 46</t>
-  </si>
-  <si>
-    <t>56 / 56</t>
-  </si>
-  <si>
-    <t>24 / 25</t>
-  </si>
-  <si>
-    <t>10 / 25</t>
-  </si>
-  <si>
-    <t>77 / 99</t>
-  </si>
-  <si>
-    <t>111 / 111</t>
-  </si>
-  <si>
-    <t>134 / 138</t>
-  </si>
-  <si>
-    <t>79 / 81</t>
-  </si>
-  <si>
-    <t>23 / 26</t>
-  </si>
-  <si>
-    <t>124 / 126</t>
-  </si>
-  <si>
-    <t>98 / 104</t>
-  </si>
-  <si>
-    <t>29 / 44</t>
-  </si>
-  <si>
-    <t>63 / 85</t>
-  </si>
-  <si>
-    <t>23 / 102</t>
-  </si>
-  <si>
-    <t>45 / 136</t>
-  </si>
-  <si>
-    <t>1 / 27</t>
-  </si>
-  <si>
-    <t>161 / 308</t>
-  </si>
-  <si>
-    <t>34 / 149</t>
-  </si>
-  <si>
-    <t>Sales Status · latest</t>
-  </si>
-  <si>
-    <t>91%</t>
-  </si>
-  <si>
-    <t>Yet to launch</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>44%</t>
-  </si>
-  <si>
-    <t>63%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>96%</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>78%</t>
-  </si>
-  <si>
-    <t>97%</t>
-  </si>
-  <si>
-    <t>98%</t>
-  </si>
-  <si>
-    <t>88%</t>
-  </si>
-  <si>
-    <t>94%</t>
-  </si>
-  <si>
-    <t>66%</t>
-  </si>
-  <si>
-    <t>74%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>Yet to sign</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>52%</t>
-  </si>
-  <si>
-    <t>Weekly baseline</t>
-  </si>
-  <si>
-    <t>No record 7–14 days earlier</t>
-  </si>
-  <si>
-    <t>Sales Unit · baseline</t>
-  </si>
-  <si>
-    <t>Sales Status · baseline</t>
-  </si>
-  <si>
-    <t>Weekly Change</t>
-  </si>
-  <si>
-    <t>Insufficient weekly history</t>
-  </si>
-  <si>
-    <t>No signed status yet</t>
-  </si>
-  <si>
-    <t>Record Date</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Unit Group / Layout</t>
-  </si>
-  <si>
-    <t>Status Type</t>
-  </si>
-  <si>
-    <t>Signed Units</t>
-  </si>
-  <si>
-    <t>Total Units</t>
-  </si>
-  <si>
-    <t>Signed %</t>
-  </si>
-  <si>
-    <t>Raw Recorded Status</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>17/03/2025</t>
-  </si>
-  <si>
-    <t>Booked</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>11% Booked (9/81 units)</t>
-  </si>
-  <si>
-    <t>Embedded historical record</t>
-  </si>
-  <si>
-    <t>06/10/2025</t>
-  </si>
-  <si>
-    <t>35% Booked (28/81 units)</t>
-  </si>
-  <si>
-    <t>08/06/2026</t>
-  </si>
-  <si>
-    <t>Signed</t>
-  </si>
-  <si>
-    <t>59% Signed (48/81 units)</t>
-  </si>
-  <si>
-    <t>10/07/2026</t>
-  </si>
-  <si>
-    <t>65% Signed (53/81 units)</t>
-  </si>
-  <si>
-    <t>88% Signed (72/81 units)</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>74/81 signed</t>
-  </si>
-  <si>
-    <t>Saved TEDUH record</t>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>18/10/2026</t>
   </si>
   <si>
     <t>No group details</t>
@@ -396,6 +408,9 @@
     <t>68/113 signed</t>
   </si>
   <si>
+    <t>69/113 signed</t>
+  </si>
+  <si>
     <t>8% Booked (4/48 units)</t>
   </si>
   <si>
@@ -607,6 +622,12 @@
   </si>
   <si>
     <t>23/102 signed</t>
+  </si>
+  <si>
+    <t>65/85 signed</t>
+  </si>
+  <si>
+    <t>24/102 signed</t>
   </si>
   <si>
     <t>No parseable group-level values: Yet to Sign</t>
@@ -1640,89 +1661,89 @@
         <v>75</v>
       </c>
       <c r="Y8" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>33</v>
@@ -1799,7 +1820,7 @@
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>33</v>
@@ -1876,79 +1897,79 @@
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="E12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="V12" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="V12" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="W12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1968,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I159"/>
+  <dimension ref="A1:I225"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1982,36 +2003,36 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>3</v>
@@ -2020,25 +2041,25 @@
         <v>18</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F2" s="11">
         <v>81</v>
       </c>
       <c r="G2" s="13"/>
       <c r="H2" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>3</v>
@@ -2047,25 +2068,25 @@
         <v>18</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F3" s="11">
         <v>81</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>3</v>
@@ -2074,7 +2095,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" s="11">
         <v>48</v>
@@ -2086,15 +2107,15 @@
         <v>0.5925925925925926</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>3</v>
@@ -2103,7 +2124,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E5" s="11">
         <v>53</v>
@@ -2115,10 +2136,10 @@
         <v>0.654320987654321</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -2132,7 +2153,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" s="11">
         <v>72</v>
@@ -2144,15 +2165,15 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>3</v>
@@ -2161,7 +2182,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7" s="11">
         <v>74</v>
@@ -2173,15 +2194,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>3</v>
@@ -2190,7 +2211,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" s="11">
         <v>74</v>
@@ -2202,183 +2223,189 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E9" s="11">
+        <v>74</v>
+      </c>
+      <c r="F9" s="11">
+        <v>81</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0.9135802469135802</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E10" s="11">
+        <v>74</v>
+      </c>
+      <c r="F10" s="11">
+        <v>81</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0.9135802469135802</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E11" s="11">
+        <v>74</v>
+      </c>
+      <c r="F11" s="11">
+        <v>81</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0.9135802469135802</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="11">
-        <v>113</v>
-      </c>
-      <c r="G12" s="13"/>
+        <v>95</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>95</v>
+      </c>
       <c r="H12" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="E13" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="11">
-        <v>113</v>
-      </c>
-      <c r="G13" s="13"/>
+        <v>95</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>95</v>
+      </c>
       <c r="H13" s="12" t="s">
         <v>114</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="11">
-        <v>113</v>
-      </c>
-      <c r="G14" s="13"/>
+        <v>95</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>95</v>
+      </c>
       <c r="H14" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>5</v>
@@ -2387,25 +2414,25 @@
         <v>20</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F15" s="11">
         <v>113</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>5</v>
@@ -2414,27 +2441,25 @@
         <v>20</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="11">
-        <v>34</v>
+        <v>94</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="F16" s="11">
         <v>113</v>
       </c>
-      <c r="G16" s="14">
-        <v>0.3008849557522124</v>
-      </c>
+      <c r="G16" s="13"/>
       <c r="H16" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>5</v>
@@ -2443,27 +2468,25 @@
         <v>20</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="11">
-        <v>37</v>
+        <v>94</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="F17" s="11">
         <v>113</v>
       </c>
-      <c r="G17" s="14">
-        <v>0.3274336283185841</v>
-      </c>
+      <c r="G17" s="13"/>
       <c r="H17" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>5</v>
@@ -2472,22 +2495,20 @@
         <v>20</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="11">
-        <v>37</v>
+        <v>94</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="F18" s="11">
         <v>113</v>
       </c>
-      <c r="G18" s="14">
-        <v>0.3274336283185841</v>
-      </c>
+      <c r="G18" s="13"/>
       <c r="H18" s="12" t="s">
         <v>121</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -2501,27 +2522,27 @@
         <v>20</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E19" s="11">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F19" s="11">
         <v>113</v>
       </c>
       <c r="G19" s="14">
-        <v>0.4778761061946903</v>
+        <v>0.3008849557522124</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>123</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>5</v>
@@ -2530,27 +2551,27 @@
         <v>20</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" s="11">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="F20" s="11">
         <v>113</v>
       </c>
       <c r="G20" s="14">
-        <v>0.5575221238938053</v>
+        <v>0.3274336283185841</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>5</v>
@@ -2559,27 +2580,27 @@
         <v>20</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E21" s="11">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F21" s="11">
         <v>113</v>
       </c>
       <c r="G21" s="14">
-        <v>0.6017699115044248</v>
+        <v>0.3274336283185841</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>125</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>5</v>
@@ -2588,27 +2609,27 @@
         <v>20</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E22" s="11">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F22" s="11">
         <v>113</v>
       </c>
       <c r="G22" s="14">
-        <v>0.6017699115044248</v>
+        <v>0.4778761061946903</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>5</v>
@@ -2617,27 +2638,27 @@
         <v>20</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E23" s="11">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F23" s="11">
         <v>113</v>
       </c>
       <c r="G23" s="14">
-        <v>0.6017699115044248</v>
+        <v>0.5575221238938053</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>5</v>
@@ -2646,7 +2667,7 @@
         <v>20</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E24" s="11">
         <v>68</v>
@@ -2658,177 +2679,189 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="11">
+        <v>68</v>
+      </c>
+      <c r="F25" s="11">
         <v>113</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F25" s="11">
-        <v>48</v>
-      </c>
-      <c r="G25" s="13"/>
+      <c r="G25" s="14">
+        <v>0.6017699115044248</v>
+      </c>
       <c r="H25" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E26" s="11">
+        <v>68</v>
       </c>
       <c r="F26" s="11">
-        <v>48</v>
-      </c>
-      <c r="G26" s="13"/>
+        <v>113</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0.6017699115044248</v>
+      </c>
       <c r="H26" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E27" s="11">
+        <v>68</v>
       </c>
       <c r="F27" s="11">
-        <v>48</v>
-      </c>
-      <c r="G27" s="13"/>
+        <v>113</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0.6017699115044248</v>
+      </c>
       <c r="H27" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E28" s="11">
+        <v>69</v>
       </c>
       <c r="F28" s="11">
-        <v>48</v>
-      </c>
-      <c r="G28" s="13"/>
+        <v>113</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0.6106194690265486</v>
+      </c>
       <c r="H28" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E29" s="11">
+        <v>69</v>
       </c>
       <c r="F29" s="11">
-        <v>48</v>
-      </c>
-      <c r="G29" s="13"/>
+        <v>113</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0.6106194690265486</v>
+      </c>
       <c r="H29" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E30" s="11">
+        <v>69</v>
       </c>
       <c r="F30" s="11">
-        <v>48</v>
-      </c>
-      <c r="G30" s="13"/>
+        <v>113</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0.6106194690265486</v>
+      </c>
       <c r="H30" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>6</v>
@@ -2837,27 +2870,25 @@
         <v>21</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E31" s="11">
-        <v>15</v>
+        <v>94</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="F31" s="11">
         <v>48</v>
       </c>
-      <c r="G31" s="14">
-        <v>0.3125</v>
-      </c>
+      <c r="G31" s="13"/>
       <c r="H31" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>6</v>
@@ -2866,27 +2897,25 @@
         <v>21</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" s="11">
-        <v>19</v>
+        <v>94</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="F32" s="11">
         <v>48</v>
       </c>
-      <c r="G32" s="14">
-        <v>0.3958333333333333</v>
-      </c>
+      <c r="G32" s="13"/>
       <c r="H32" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>6</v>
@@ -2895,27 +2924,25 @@
         <v>21</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" s="11">
-        <v>19</v>
+        <v>94</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="F33" s="11">
         <v>48</v>
       </c>
-      <c r="G33" s="14">
-        <v>0.3958333333333333</v>
-      </c>
+      <c r="G33" s="13"/>
       <c r="H33" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>6</v>
@@ -2924,27 +2951,25 @@
         <v>21</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" s="11">
-        <v>21</v>
+        <v>94</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="F34" s="11">
         <v>48</v>
       </c>
-      <c r="G34" s="14">
-        <v>0.4375</v>
-      </c>
+      <c r="G34" s="13"/>
       <c r="H34" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>6</v>
@@ -2953,27 +2978,25 @@
         <v>21</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E35" s="11">
-        <v>21</v>
+        <v>94</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="F35" s="11">
         <v>48</v>
       </c>
-      <c r="G35" s="14">
-        <v>0.4375</v>
-      </c>
+      <c r="G35" s="13"/>
       <c r="H35" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>6</v>
@@ -2982,109 +3005,107 @@
         <v>21</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E36" s="11">
-        <v>21</v>
+        <v>94</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="F36" s="11">
         <v>48</v>
       </c>
-      <c r="G36" s="14">
-        <v>0.4375</v>
-      </c>
+      <c r="G36" s="13"/>
       <c r="H36" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E37" s="11">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="F37" s="11">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="G37" s="14">
-        <v>0.8383838383838383</v>
+        <v>0.3125</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E38" s="11">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="F38" s="11">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G38" s="14">
-        <v>0.6194690265486725</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E39" s="11">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="F39" s="11">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G39" s="14">
-        <v>0.6194690265486725</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -3092,439 +3113,439 @@
         <v>30</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E40" s="11">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="F40" s="11">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G40" s="14">
-        <v>0.6283185840707964</v>
+        <v>0.4375</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E41" s="11">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="F41" s="11">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G41" s="14">
-        <v>0.6283185840707964</v>
+        <v>0.4375</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E42" s="11">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="F42" s="11">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G42" s="14">
-        <v>0.6283185840707964</v>
+        <v>0.4375</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E43" s="11">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="F43" s="11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G43" s="14">
-        <v>0.9782608695652174</v>
+        <v>0.4375</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>139</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E44" s="11">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="F44" s="11">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G44" s="14">
-        <v>0.8392857142857143</v>
+        <v>0.4375</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E45" s="11">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F45" s="11">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G45" s="14">
-        <v>0.52</v>
+        <v>0.4375</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E46" s="11">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="F46" s="11">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="G46" s="14">
-        <v>0.12</v>
+        <v>0.8383838383838383</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E47" s="11">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="F47" s="11">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="G47" s="14">
-        <v>1</v>
+        <v>0.6194690265486725</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>22</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E48" s="11">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F48" s="11">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="G48" s="14">
-        <v>1</v>
+        <v>0.6194690265486725</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E49" s="11">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="F49" s="11">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G49" s="14">
-        <v>0.96</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E50" s="11">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="F50" s="11">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G50" s="14">
-        <v>0.28</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E51" s="11">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F51" s="11">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="G51" s="14">
-        <v>1</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H51" s="12" t="s">
         <v>143</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>22</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E52" s="11">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F52" s="11">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="G52" s="14">
-        <v>1</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E53" s="11">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="F53" s="11">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G53" s="14">
-        <v>0.96</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E54" s="11">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="F54" s="11">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G54" s="14">
-        <v>0.32</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>8</v>
@@ -3533,27 +3554,27 @@
         <v>23</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E55" s="11">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F55" s="11">
         <v>46</v>
       </c>
       <c r="G55" s="14">
-        <v>1</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>8</v>
@@ -3562,27 +3583,27 @@
         <v>22</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E56" s="11">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F56" s="11">
         <v>56</v>
       </c>
       <c r="G56" s="14">
-        <v>1</v>
+        <v>0.8392857142857143</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>8</v>
@@ -3591,27 +3612,27 @@
         <v>24</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E57" s="11">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F57" s="11">
         <v>25</v>
       </c>
       <c r="G57" s="14">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>8</v>
@@ -3620,27 +3641,27 @@
         <v>25</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E58" s="11">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F58" s="11">
         <v>25</v>
       </c>
       <c r="G58" s="14">
-        <v>0.4</v>
+        <v>0.12</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>8</v>
@@ -3649,7 +3670,7 @@
         <v>23</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E59" s="11">
         <v>46</v>
@@ -3661,15 +3682,15 @@
         <v>1</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>8</v>
@@ -3678,7 +3699,7 @@
         <v>22</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E60" s="11">
         <v>56</v>
@@ -3690,15 +3711,15 @@
         <v>1</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>8</v>
@@ -3707,7 +3728,7 @@
         <v>24</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E61" s="11">
         <v>24</v>
@@ -3719,15 +3740,15 @@
         <v>0.96</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>8</v>
@@ -3736,27 +3757,27 @@
         <v>25</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E62" s="11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F62" s="11">
         <v>25</v>
       </c>
       <c r="G62" s="14">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>8</v>
@@ -3765,7 +3786,7 @@
         <v>23</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E63" s="11">
         <v>46</v>
@@ -3777,15 +3798,15 @@
         <v>1</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>8</v>
@@ -3794,7 +3815,7 @@
         <v>22</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E64" s="11">
         <v>56</v>
@@ -3806,15 +3827,15 @@
         <v>1</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>8</v>
@@ -3823,7 +3844,7 @@
         <v>24</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E65" s="11">
         <v>24</v>
@@ -3835,15 +3856,15 @@
         <v>0.96</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>8</v>
@@ -3852,109 +3873,109 @@
         <v>25</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E66" s="11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F66" s="11">
         <v>25</v>
       </c>
       <c r="G66" s="14">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="H66" s="12" t="s">
         <v>152</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E67" s="11">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="F67" s="11">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="G67" s="14">
-        <v>0.8787878787878788</v>
+        <v>1</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E68" s="11">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F68" s="11">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="G68" s="14">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E69" s="11">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="F69" s="11">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G69" s="14">
-        <v>0.7777777777777778</v>
+        <v>0.96</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -3962,2580 +3983,2580 @@
         <v>30</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E70" s="11">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F70" s="11">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G70" s="14">
-        <v>0.7777777777777778</v>
+        <v>0.4</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E71" s="11">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="F71" s="11">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="G71" s="14">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E72" s="11">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F72" s="11">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="G72" s="14">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>155</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E73" s="11">
+        <v>24</v>
+      </c>
+      <c r="F73" s="11">
+        <v>25</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0.96</v>
+      </c>
+      <c r="H73" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B73" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E73" s="11">
-        <v>101</v>
-      </c>
-      <c r="F73" s="11">
-        <v>111</v>
-      </c>
-      <c r="G73" s="14">
-        <v>0.9099099099099099</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>157</v>
-      </c>
       <c r="I73" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="B74" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E74" s="11">
         <v>10</v>
       </c>
-      <c r="C74" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E74" s="11">
-        <v>131</v>
-      </c>
       <c r="F74" s="11">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="G74" s="14">
-        <v>0.9492753623188406</v>
+        <v>0.4</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E75" s="11">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="F75" s="11">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G75" s="14">
-        <v>0.9629629629629629</v>
+        <v>1</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E76" s="11">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F76" s="11">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="G76" s="14">
-        <v>0.5135135135135135</v>
+        <v>1</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E77" s="11">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="F77" s="11">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="G77" s="14">
-        <v>0.6739130434782609</v>
+        <v>0.96</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="B78" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E78" s="11">
         <v>10</v>
       </c>
-      <c r="C78" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E78" s="11">
-        <v>44</v>
-      </c>
       <c r="F78" s="11">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="G78" s="14">
-        <v>0.5432098765432098</v>
+        <v>0.4</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E79" s="11">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F79" s="11">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="G79" s="14">
-        <v>0.5585585585585585</v>
+        <v>1</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E80" s="11">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="F80" s="11">
-        <v>138</v>
+        <v>56</v>
       </c>
       <c r="G80" s="14">
-        <v>0.7101449275362319</v>
+        <v>1</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E81" s="11">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F81" s="11">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="G81" s="14">
-        <v>0.6419753086419753</v>
+        <v>0.96</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B82" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E82" s="11">
         <v>10</v>
       </c>
-      <c r="C82" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E82" s="11">
-        <v>102</v>
-      </c>
       <c r="F82" s="11">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="G82" s="14">
-        <v>0.918918918918919</v>
+        <v>0.4</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E83" s="11">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="F83" s="11">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c r="G83" s="14">
-        <v>0.9492753623188406</v>
+        <v>1</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>22</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E84" s="11">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="F84" s="11">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="G84" s="14">
-        <v>0.9629629629629629</v>
+        <v>1</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E85" s="11">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="F85" s="11">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="G85" s="14">
-        <v>0.918918918918919</v>
+        <v>0.96</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B86" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E86" s="11">
         <v>10</v>
       </c>
-      <c r="C86" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D86" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E86" s="11">
-        <v>131</v>
-      </c>
       <c r="F86" s="11">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="G86" s="14">
-        <v>0.9492753623188406</v>
+        <v>0.4</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E87" s="11">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="F87" s="11">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G87" s="14">
-        <v>0.9629629629629629</v>
+        <v>1</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E88" s="11">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="F88" s="11">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="G88" s="14">
         <v>1</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E89" s="11">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="F89" s="11">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="G89" s="14">
-        <v>0.9710144927536232</v>
+        <v>0.96</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B90" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E90" s="11">
         <v>10</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E90" s="11">
-        <v>79</v>
-      </c>
       <c r="F90" s="11">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="G90" s="14">
-        <v>0.9753086419753086</v>
+        <v>0.4</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E91" s="11">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="F91" s="11">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G91" s="14">
-        <v>1</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E92" s="11">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="F92" s="11">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="G92" s="14">
-        <v>0.9710144927536232</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E93" s="11">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F93" s="11">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G93" s="14">
-        <v>0.9753086419753086</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E94" s="11">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F94" s="11">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G94" s="14">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E95" s="11">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="F95" s="11">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="G95" s="14">
-        <v>0.9710144927536232</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E96" s="11">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F96" s="11">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G96" s="14">
-        <v>0.9753086419753086</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E97" s="11">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="F97" s="11">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="G97" s="14">
-        <v>0.11538461538461539</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E98" s="11">
         <v>77</v>
       </c>
       <c r="F98" s="11">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="G98" s="14">
-        <v>0.6111111111111112</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E99" s="11">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="F99" s="11">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G99" s="14">
-        <v>0.16346153846153846</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H99" s="12" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E100" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F100" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G100" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E100" s="11">
+        <v>101</v>
+      </c>
+      <c r="F100" s="11">
+        <v>111</v>
+      </c>
+      <c r="G100" s="14">
+        <v>0.9099099099099099</v>
       </c>
       <c r="H100" s="12" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E101" s="11">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="F101" s="11">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G101" s="14">
-        <v>0.6538461538461539</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E102" s="11">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="F102" s="11">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G102" s="14">
-        <v>0.8809523809523809</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E103" s="11">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F103" s="11">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G103" s="14">
-        <v>0.6826923076923077</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E104" s="11">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="F104" s="11">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G104" s="14">
-        <v>0.6538461538461539</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E105" s="11">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="F105" s="11">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G105" s="14">
-        <v>0.9206349206349206</v>
+        <v>0.5432098765432098</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E106" s="11">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="F106" s="11">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G106" s="14">
-        <v>0.8557692307692307</v>
+        <v>0.5585585585585585</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E107" s="11">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="F107" s="11">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G107" s="14">
-        <v>0.8846153846153846</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="I107" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E108" s="11">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="F108" s="11">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G108" s="14">
-        <v>0.9841269841269841</v>
+        <v>0.6419753086419753</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="I108" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E109" s="11">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F109" s="11">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G109" s="14">
-        <v>0.9423076923076923</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="I109" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E110" s="11">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="F110" s="11">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G110" s="14">
-        <v>0.8846153846153846</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="I110" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E111" s="11">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="F111" s="11">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G111" s="14">
-        <v>0.9841269841269841</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="I111" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E112" s="11">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F112" s="11">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G112" s="14">
-        <v>0.9423076923076923</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="H112" s="12" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="I112" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E113" s="11">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="F113" s="11">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G113" s="14">
-        <v>0.8846153846153846</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="I113" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E114" s="11">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="F114" s="11">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G114" s="14">
-        <v>0.9841269841269841</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E115" s="11">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F115" s="11">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G115" s="14">
-        <v>0.9423076923076923</v>
+        <v>1</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I115" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E116" s="11">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="F116" s="11">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="G116" s="14">
-        <v>0.36363636363636365</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H116" s="12" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E117" s="11">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="F117" s="11">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G117" s="14">
-        <v>0.4588235294117647</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="I117" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E118" s="11">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="F118" s="11">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G118" s="14">
-        <v>0.10784313725490197</v>
+        <v>1</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="I118" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E119" s="11">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="F119" s="11">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="G119" s="14">
-        <v>0.6590909090909091</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="I119" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E120" s="11">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F120" s="11">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G120" s="14">
-        <v>0.7411764705882353</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="I120" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E121" s="11">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="F121" s="11">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G121" s="14">
-        <v>0.21568627450980393</v>
+        <v>1</v>
       </c>
       <c r="H121" s="12" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="I121" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E122" s="11">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="F122" s="11">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="G122" s="14">
-        <v>0.6590909090909091</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="I122" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E123" s="11">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F123" s="11">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G123" s="14">
-        <v>0.7411764705882353</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H123" s="12" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="I123" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E124" s="11">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="F124" s="11">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G124" s="14">
-        <v>0.22549019607843138</v>
+        <v>1</v>
       </c>
       <c r="H124" s="12" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E125" s="11">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="F125" s="11">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="G125" s="14">
-        <v>0.6590909090909091</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H125" s="12" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="I125" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E126" s="11">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F126" s="11">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G126" s="14">
-        <v>0.7411764705882353</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H126" s="12" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E127" s="11">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="F127" s="11">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G127" s="14">
-        <v>0.22549019607843138</v>
+        <v>1</v>
       </c>
       <c r="H127" s="12" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E128" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F128" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G128" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E128" s="11">
+        <v>134</v>
+      </c>
+      <c r="F128" s="11">
+        <v>138</v>
+      </c>
+      <c r="G128" s="14">
+        <v>0.9710144927536232</v>
       </c>
       <c r="H128" s="12" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E129" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F129" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G129" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E129" s="11">
+        <v>79</v>
+      </c>
+      <c r="F129" s="11">
+        <v>81</v>
+      </c>
+      <c r="G129" s="14">
+        <v>0.9753086419753086</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E130" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F130" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G130" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E130" s="11">
+        <v>111</v>
+      </c>
+      <c r="F130" s="11">
+        <v>111</v>
+      </c>
+      <c r="G130" s="14">
+        <v>1</v>
       </c>
       <c r="H130" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E131" s="11">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="F131" s="11">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G131" s="14">
-        <v>0.17647058823529413</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="I131" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>22</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E132" s="11">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F132" s="11">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="G132" s="14">
-        <v>0.22058823529411764</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="I132" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E133" s="11">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="F133" s="11">
-        <v>136</v>
+        <v>26</v>
       </c>
       <c r="G133" s="14">
-        <v>0.33088235294117646</v>
+        <v>0.11538461538461539</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="I133" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E134" s="11">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F134" s="11">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G134" s="14">
-        <v>0.33088235294117646</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="I134" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C135" s="12" t="s">
         <v>22</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E135" s="11">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F135" s="11">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="G135" s="14">
-        <v>0.33088235294117646</v>
+        <v>0.16346153846153846</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="I135" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>203</v>
+        <v>112</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E136" s="11">
-        <v>81</v>
-      </c>
-      <c r="F136" s="11">
-        <v>189</v>
-      </c>
-      <c r="G136" s="14">
-        <v>0.42857142857142855</v>
+        <v>113</v>
+      </c>
+      <c r="E136" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F136" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G136" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="I136" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C137" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E137" s="11">
+        <v>17</v>
+      </c>
+      <c r="F137" s="11">
         <v>26</v>
       </c>
-      <c r="D137" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E137" s="11">
-        <v>1</v>
-      </c>
-      <c r="F137" s="11">
-        <v>27</v>
-      </c>
       <c r="G137" s="14">
-        <v>0.037037037037037035</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I137" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>203</v>
+        <v>23</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E138" s="11">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="F138" s="11">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="G138" s="14">
-        <v>0.4444444444444444</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="I138" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E139" s="11">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F139" s="11">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="G139" s="14">
-        <v>0</v>
+        <v>0.6826923076923077</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="I139" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>203</v>
+        <v>20</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E140" s="11">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="F140" s="11">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="G140" s="14">
-        <v>0.656084656084656</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="I140" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E141" s="11">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="F141" s="11">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="G141" s="14">
-        <v>0</v>
+        <v>0.9206349206349206</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="I141" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>203</v>
+        <v>22</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E142" s="11">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="F142" s="11">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="G142" s="14">
-        <v>0.783068783068783</v>
+        <v>0.8557692307692307</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C143" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E143" s="11">
+        <v>23</v>
+      </c>
+      <c r="F143" s="11">
         <v>26</v>
       </c>
-      <c r="D143" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E143" s="11">
-        <v>1</v>
-      </c>
-      <c r="F143" s="11">
-        <v>27</v>
-      </c>
       <c r="G143" s="14">
-        <v>0.037037037037037035</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="I143" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>203</v>
+        <v>23</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E144" s="11">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="F144" s="11">
+        <v>126</v>
+      </c>
+      <c r="G144" s="14">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="H144" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="G144" s="14">
-        <v>0.8148148148148148</v>
-      </c>
-      <c r="H144" s="12" t="s">
-        <v>210</v>
-      </c>
       <c r="I144" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E145" s="11">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F145" s="11">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="G145" s="14">
-        <v>0.037037037037037035</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H145" s="12" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="I145" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E146" s="11">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="F146" s="11">
-        <v>308</v>
+        <v>26</v>
       </c>
       <c r="G146" s="14">
-        <v>0.5194805194805194</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E147" s="11">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="F147" s="11">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="G147" s="14">
-        <v>0.037037037037037035</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H147" s="12" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="I147" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E148" s="11">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F148" s="11">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="G148" s="14">
-        <v>0.037037037037037035</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H148" s="12" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="I148" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E149" s="11">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="F149" s="11">
-        <v>308</v>
+        <v>26</v>
       </c>
       <c r="G149" s="14">
-        <v>0.5227272727272727</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H149" s="12" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="I149" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E150" s="11">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="F150" s="11">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="G150" s="14">
-        <v>0.037037037037037035</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H150" s="12" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="I150" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E151" s="11">
-        <v>161</v>
+        <v>98</v>
       </c>
       <c r="F151" s="11">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="G151" s="14">
-        <v>0.5227272727272727</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H151" s="12" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="I151" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C152" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E152" s="11">
         <v>23</v>
       </c>
-      <c r="D152" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E152" s="11">
-        <v>9</v>
-      </c>
       <c r="F152" s="11">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="G152" s="14">
-        <v>0.06040268456375839</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H152" s="12" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="I152" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C153" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E153" s="11">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="F153" s="11">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="G153" s="14">
-        <v>0.14093959731543623</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H153" s="12" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="I153" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E154" s="11">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="F154" s="11">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="G154" s="14">
-        <v>0.15436241610738255</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H154" s="12" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="I154" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C155" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E155" s="11">
         <v>23</v>
       </c>
-      <c r="D155" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E155" s="11">
-        <v>31</v>
-      </c>
       <c r="F155" s="11">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="G155" s="14">
-        <v>0.2080536912751678</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H155" s="12" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="I155" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C156" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E156" s="11">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="F156" s="11">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="G156" s="14">
-        <v>0.22818791946308725</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H156" s="12" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="I156" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E157" s="11">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="F157" s="11">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="G157" s="14">
-        <v>0.22818791946308725</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H157" s="12" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="I157" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C158" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E158" s="11">
         <v>23</v>
       </c>
-      <c r="D158" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E158" s="11">
-        <v>34</v>
-      </c>
       <c r="F158" s="11">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="G158" s="14">
-        <v>0.22818791946308725</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H158" s="12" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="I158" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
@@ -6543,32 +6564,1946 @@
         <v>29</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C159" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D159" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E159" s="11">
+        <v>124</v>
+      </c>
+      <c r="F159" s="11">
+        <v>126</v>
+      </c>
+      <c r="G159" s="14">
+        <v>0.9841269841269841</v>
+      </c>
+      <c r="H159" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="I159" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E160" s="11">
+        <v>98</v>
+      </c>
+      <c r="F160" s="11">
+        <v>104</v>
+      </c>
+      <c r="G160" s="14">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="H160" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="I160" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E161" s="11">
+        <v>16</v>
+      </c>
+      <c r="F161" s="11">
+        <v>44</v>
+      </c>
+      <c r="G161" s="14">
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="H161" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I161" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B162" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E162" s="11">
+        <v>39</v>
+      </c>
+      <c r="F162" s="11">
+        <v>85</v>
+      </c>
+      <c r="G162" s="14">
+        <v>0.4588235294117647</v>
+      </c>
+      <c r="H162" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="I162" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C163" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E163" s="11">
+        <v>11</v>
+      </c>
+      <c r="F163" s="11">
+        <v>102</v>
+      </c>
+      <c r="G163" s="14">
+        <v>0.10784313725490197</v>
+      </c>
+      <c r="H163" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="I163" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E164" s="11">
+        <v>29</v>
+      </c>
+      <c r="F164" s="11">
+        <v>44</v>
+      </c>
+      <c r="G164" s="14">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="H164" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="I164" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C165" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E165" s="11">
+        <v>63</v>
+      </c>
+      <c r="F165" s="11">
+        <v>85</v>
+      </c>
+      <c r="G165" s="14">
+        <v>0.7411764705882353</v>
+      </c>
+      <c r="H165" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="I165" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E166" s="11">
+        <v>22</v>
+      </c>
+      <c r="F166" s="11">
+        <v>102</v>
+      </c>
+      <c r="G166" s="14">
+        <v>0.21568627450980393</v>
+      </c>
+      <c r="H166" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="I166" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B167" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C167" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E167" s="11">
+        <v>29</v>
+      </c>
+      <c r="F167" s="11">
+        <v>44</v>
+      </c>
+      <c r="G167" s="14">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="H167" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="I167" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B168" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E168" s="11">
+        <v>63</v>
+      </c>
+      <c r="F168" s="11">
+        <v>85</v>
+      </c>
+      <c r="G168" s="14">
+        <v>0.7411764705882353</v>
+      </c>
+      <c r="H168" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="I168" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E169" s="11">
+        <v>23</v>
+      </c>
+      <c r="F169" s="11">
+        <v>102</v>
+      </c>
+      <c r="G169" s="14">
+        <v>0.22549019607843138</v>
+      </c>
+      <c r="H169" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="I169" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B170" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E170" s="11">
+        <v>29</v>
+      </c>
+      <c r="F170" s="11">
+        <v>44</v>
+      </c>
+      <c r="G170" s="14">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="H170" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="I170" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B171" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E171" s="11">
+        <v>63</v>
+      </c>
+      <c r="F171" s="11">
+        <v>85</v>
+      </c>
+      <c r="G171" s="14">
+        <v>0.7411764705882353</v>
+      </c>
+      <c r="H171" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="I171" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E172" s="11">
+        <v>23</v>
+      </c>
+      <c r="F172" s="11">
+        <v>102</v>
+      </c>
+      <c r="G172" s="14">
+        <v>0.22549019607843138</v>
+      </c>
+      <c r="H172" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="I172" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B173" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E173" s="11">
+        <v>29</v>
+      </c>
+      <c r="F173" s="11">
+        <v>44</v>
+      </c>
+      <c r="G173" s="14">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="H173" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="I173" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B174" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E174" s="11">
+        <v>65</v>
+      </c>
+      <c r="F174" s="11">
+        <v>85</v>
+      </c>
+      <c r="G174" s="14">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="I174" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B175" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E175" s="11">
+        <v>24</v>
+      </c>
+      <c r="F175" s="11">
+        <v>102</v>
+      </c>
+      <c r="G175" s="14">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="H175" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I175" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B176" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E176" s="11">
+        <v>29</v>
+      </c>
+      <c r="F176" s="11">
+        <v>44</v>
+      </c>
+      <c r="G176" s="14">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="H176" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="I176" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B177" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D177" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E177" s="11">
+        <v>65</v>
+      </c>
+      <c r="F177" s="11">
+        <v>85</v>
+      </c>
+      <c r="G177" s="14">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="H177" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="I177" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B178" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E178" s="11">
+        <v>24</v>
+      </c>
+      <c r="F178" s="11">
+        <v>102</v>
+      </c>
+      <c r="G178" s="14">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="H178" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I178" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B179" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E179" s="11">
+        <v>29</v>
+      </c>
+      <c r="F179" s="11">
+        <v>44</v>
+      </c>
+      <c r="G179" s="14">
+        <v>0.6590909090909091</v>
+      </c>
+      <c r="H179" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="I179" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B180" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C180" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E180" s="11">
+        <v>65</v>
+      </c>
+      <c r="F180" s="11">
+        <v>85</v>
+      </c>
+      <c r="G180" s="14">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="H180" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="I180" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B181" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D181" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E181" s="11">
+        <v>24</v>
+      </c>
+      <c r="F181" s="11">
+        <v>102</v>
+      </c>
+      <c r="G181" s="14">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="H181" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I181" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B182" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D182" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E182" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F182" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G182" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H182" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I182" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B183" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D183" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E183" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F183" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G183" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H183" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I183" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B184" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E184" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F184" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G184" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H184" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="I184" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E159" s="11">
+      <c r="B185" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D185" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E185" s="11">
+        <v>24</v>
+      </c>
+      <c r="F185" s="11">
+        <v>136</v>
+      </c>
+      <c r="G185" s="14">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="H185" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="I185" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B186" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D186" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E186" s="11">
+        <v>30</v>
+      </c>
+      <c r="F186" s="11">
+        <v>136</v>
+      </c>
+      <c r="G186" s="14">
+        <v>0.22058823529411764</v>
+      </c>
+      <c r="H186" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="I186" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B187" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D187" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E187" s="11">
+        <v>45</v>
+      </c>
+      <c r="F187" s="11">
+        <v>136</v>
+      </c>
+      <c r="G187" s="14">
+        <v>0.33088235294117646</v>
+      </c>
+      <c r="H187" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="I187" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B188" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E188" s="11">
+        <v>45</v>
+      </c>
+      <c r="F188" s="11">
+        <v>136</v>
+      </c>
+      <c r="G188" s="14">
+        <v>0.33088235294117646</v>
+      </c>
+      <c r="H188" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I188" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B189" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D189" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E189" s="11">
+        <v>45</v>
+      </c>
+      <c r="F189" s="11">
+        <v>136</v>
+      </c>
+      <c r="G189" s="14">
+        <v>0.33088235294117646</v>
+      </c>
+      <c r="H189" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I189" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B190" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D190" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E190" s="11">
+        <v>45</v>
+      </c>
+      <c r="F190" s="11">
+        <v>136</v>
+      </c>
+      <c r="G190" s="14">
+        <v>0.33088235294117646</v>
+      </c>
+      <c r="H190" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I190" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B191" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D191" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E191" s="11">
+        <v>45</v>
+      </c>
+      <c r="F191" s="11">
+        <v>136</v>
+      </c>
+      <c r="G191" s="14">
+        <v>0.33088235294117646</v>
+      </c>
+      <c r="H191" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I191" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B192" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D192" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E192" s="11">
+        <v>45</v>
+      </c>
+      <c r="F192" s="11">
+        <v>136</v>
+      </c>
+      <c r="G192" s="14">
+        <v>0.33088235294117646</v>
+      </c>
+      <c r="H192" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I192" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B193" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C193" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D193" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E193" s="11">
+        <v>81</v>
+      </c>
+      <c r="F193" s="11">
+        <v>189</v>
+      </c>
+      <c r="G193" s="14">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="H193" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="I193" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B194" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C194" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D194" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E194" s="11">
+        <v>1</v>
+      </c>
+      <c r="F194" s="11">
+        <v>27</v>
+      </c>
+      <c r="G194" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H194" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="I194" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B195" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D195" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E195" s="11">
+        <v>84</v>
+      </c>
+      <c r="F195" s="11">
+        <v>189</v>
+      </c>
+      <c r="G195" s="14">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="H195" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="I195" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B196" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D196" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E196" s="11">
+        <v>0</v>
+      </c>
+      <c r="F196" s="11">
+        <v>27</v>
+      </c>
+      <c r="G196" s="14">
+        <v>0</v>
+      </c>
+      <c r="H196" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="I196" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B197" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D197" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E197" s="11">
+        <v>124</v>
+      </c>
+      <c r="F197" s="11">
+        <v>189</v>
+      </c>
+      <c r="G197" s="14">
+        <v>0.656084656084656</v>
+      </c>
+      <c r="H197" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="I197" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B198" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D198" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E198" s="11">
+        <v>0</v>
+      </c>
+      <c r="F198" s="11">
+        <v>27</v>
+      </c>
+      <c r="G198" s="14">
+        <v>0</v>
+      </c>
+      <c r="H198" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="I198" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B199" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D199" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E199" s="11">
+        <v>148</v>
+      </c>
+      <c r="F199" s="11">
+        <v>189</v>
+      </c>
+      <c r="G199" s="14">
+        <v>0.783068783068783</v>
+      </c>
+      <c r="H199" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="I199" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B200" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D200" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E200" s="11">
+        <v>1</v>
+      </c>
+      <c r="F200" s="11">
+        <v>27</v>
+      </c>
+      <c r="G200" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H200" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="I200" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B201" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D201" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E201" s="11">
+        <v>154</v>
+      </c>
+      <c r="F201" s="11">
+        <v>189</v>
+      </c>
+      <c r="G201" s="14">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="H201" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="I201" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B202" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D202" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E202" s="11">
+        <v>1</v>
+      </c>
+      <c r="F202" s="11">
+        <v>27</v>
+      </c>
+      <c r="G202" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H202" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="I202" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B203" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D203" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E203" s="11">
+        <v>160</v>
+      </c>
+      <c r="F203" s="11">
+        <v>308</v>
+      </c>
+      <c r="G203" s="14">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="H203" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="I203" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B204" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D204" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E204" s="11">
+        <v>1</v>
+      </c>
+      <c r="F204" s="11">
+        <v>27</v>
+      </c>
+      <c r="G204" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H204" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="I204" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B205" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D205" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E205" s="11">
+        <v>1</v>
+      </c>
+      <c r="F205" s="11">
+        <v>27</v>
+      </c>
+      <c r="G205" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H205" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="I205" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B206" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D206" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E206" s="11">
+        <v>161</v>
+      </c>
+      <c r="F206" s="11">
+        <v>308</v>
+      </c>
+      <c r="G206" s="14">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="H206" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I206" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B207" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D207" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E207" s="11">
+        <v>1</v>
+      </c>
+      <c r="F207" s="11">
+        <v>27</v>
+      </c>
+      <c r="G207" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H207" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="I207" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B208" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C208" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D208" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E208" s="11">
+        <v>161</v>
+      </c>
+      <c r="F208" s="11">
+        <v>308</v>
+      </c>
+      <c r="G208" s="14">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="H208" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I208" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B209" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D209" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E209" s="11">
+        <v>1</v>
+      </c>
+      <c r="F209" s="11">
+        <v>27</v>
+      </c>
+      <c r="G209" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H209" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="I209" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B210" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D210" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E210" s="11">
+        <v>161</v>
+      </c>
+      <c r="F210" s="11">
+        <v>308</v>
+      </c>
+      <c r="G210" s="14">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="H210" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I210" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B211" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D211" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E211" s="11">
+        <v>1</v>
+      </c>
+      <c r="F211" s="11">
+        <v>27</v>
+      </c>
+      <c r="G211" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H211" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="I211" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B212" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D212" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E212" s="11">
+        <v>161</v>
+      </c>
+      <c r="F212" s="11">
+        <v>308</v>
+      </c>
+      <c r="G212" s="14">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="H212" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I212" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B213" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D213" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E213" s="11">
+        <v>1</v>
+      </c>
+      <c r="F213" s="11">
+        <v>27</v>
+      </c>
+      <c r="G213" s="14">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H213" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="I213" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B214" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D214" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E214" s="11">
+        <v>161</v>
+      </c>
+      <c r="F214" s="11">
+        <v>308</v>
+      </c>
+      <c r="G214" s="14">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="H214" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I214" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B215" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D215" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E215" s="11">
+        <v>9</v>
+      </c>
+      <c r="F215" s="11">
+        <v>149</v>
+      </c>
+      <c r="G215" s="14">
+        <v>0.06040268456375839</v>
+      </c>
+      <c r="H215" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="I215" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B216" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D216" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E216" s="11">
+        <v>21</v>
+      </c>
+      <c r="F216" s="11">
+        <v>149</v>
+      </c>
+      <c r="G216" s="14">
+        <v>0.14093959731543623</v>
+      </c>
+      <c r="H216" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="I216" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B217" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D217" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E217" s="11">
+        <v>23</v>
+      </c>
+      <c r="F217" s="11">
+        <v>149</v>
+      </c>
+      <c r="G217" s="14">
+        <v>0.15436241610738255</v>
+      </c>
+      <c r="H217" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="I217" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B218" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D218" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E218" s="11">
+        <v>31</v>
+      </c>
+      <c r="F218" s="11">
+        <v>149</v>
+      </c>
+      <c r="G218" s="14">
+        <v>0.2080536912751678</v>
+      </c>
+      <c r="H218" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I218" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B219" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D219" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E219" s="11">
         <v>34</v>
       </c>
-      <c r="F159" s="11">
+      <c r="F219" s="11">
         <v>149</v>
       </c>
-      <c r="G159" s="14">
+      <c r="G219" s="14">
         <v>0.22818791946308725</v>
       </c>
-      <c r="H159" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="I159" s="11" t="s">
-        <v>107</v>
+      <c r="H219" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I219" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B220" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D220" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E220" s="11">
+        <v>34</v>
+      </c>
+      <c r="F220" s="11">
+        <v>149</v>
+      </c>
+      <c r="G220" s="14">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H220" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="I220" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B221" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D221" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E221" s="11">
+        <v>34</v>
+      </c>
+      <c r="F221" s="11">
+        <v>149</v>
+      </c>
+      <c r="G221" s="14">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H221" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="I221" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B222" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D222" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E222" s="11">
+        <v>34</v>
+      </c>
+      <c r="F222" s="11">
+        <v>149</v>
+      </c>
+      <c r="G222" s="14">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H222" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="I222" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B223" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D223" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E223" s="11">
+        <v>34</v>
+      </c>
+      <c r="F223" s="11">
+        <v>149</v>
+      </c>
+      <c r="G223" s="14">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H223" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="I223" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B224" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D224" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E224" s="11">
+        <v>34</v>
+      </c>
+      <c r="F224" s="11">
+        <v>149</v>
+      </c>
+      <c r="G224" s="14">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H224" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="I224" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B225" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D225" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E225" s="11">
+        <v>34</v>
+      </c>
+      <c r="F225" s="11">
+        <v>149</v>
+      </c>
+      <c r="G225" s="14">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H225" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="I225" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I159"/>
+  <autoFilter ref="A1:I225"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -6585,58 +8520,58 @@
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="240">
   <si>
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Data Quality Alert</t>
   </si>
   <si>
     <t>17/03/2025</t>
@@ -1989,7 +1992,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I225"/>
+  <dimension ref="A1:J225"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1999,9 +2002,10 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="46" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>84</v>
       </c>
@@ -2029,10 +2033,13 @@
       <c r="I1" s="10" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>3</v>
@@ -2041,25 +2048,28 @@
         <v>18</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F2" s="11">
         <v>81</v>
       </c>
       <c r="G2" s="13"/>
       <c r="H2" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>3</v>
@@ -2068,25 +2078,28 @@
         <v>18</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F3" s="11">
         <v>81</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>3</v>
@@ -2095,7 +2108,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E4" s="11">
         <v>48</v>
@@ -2107,15 +2120,18 @@
         <v>0.5925925925925926</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>3</v>
@@ -2124,7 +2140,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E5" s="11">
         <v>53</v>
@@ -2136,13 +2152,16 @@
         <v>0.654320987654321</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>30</v>
       </c>
@@ -2153,7 +2172,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E6" s="11">
         <v>72</v>
@@ -2165,15 +2184,18 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>3</v>
@@ -2182,7 +2204,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7" s="11">
         <v>74</v>
@@ -2194,15 +2216,18 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>3</v>
@@ -2211,7 +2236,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" s="11">
         <v>74</v>
@@ -2223,15 +2248,18 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>3</v>
@@ -2240,7 +2268,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E9" s="11">
         <v>74</v>
@@ -2252,15 +2280,18 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>3</v>
@@ -2269,7 +2300,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E10" s="11">
         <v>74</v>
@@ -2281,13 +2312,16 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2298,7 +2332,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E11" s="11">
         <v>74</v>
@@ -2310,71 +2344,80 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>30</v>
       </c>
@@ -2382,30 +2425,33 @@
         <v>4</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>5</v>
@@ -2414,25 +2460,28 @@
         <v>20</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F15" s="11">
         <v>113</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>5</v>
@@ -2441,25 +2490,28 @@
         <v>20</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F16" s="11">
         <v>113</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>5</v>
@@ -2468,25 +2520,28 @@
         <v>20</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F17" s="11">
         <v>113</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>5</v>
@@ -2495,25 +2550,28 @@
         <v>20</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F18" s="11">
         <v>113</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>5</v>
@@ -2522,7 +2580,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E19" s="11">
         <v>34</v>
@@ -2534,15 +2592,18 @@
         <v>0.3008849557522124</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>5</v>
@@ -2551,7 +2612,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" s="11">
         <v>37</v>
@@ -2563,15 +2624,18 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>5</v>
@@ -2580,7 +2644,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E21" s="11">
         <v>37</v>
@@ -2592,15 +2656,18 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>5</v>
@@ -2609,7 +2676,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E22" s="11">
         <v>54</v>
@@ -2621,15 +2688,18 @@
         <v>0.4778761061946903</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>5</v>
@@ -2638,7 +2708,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E23" s="11">
         <v>63</v>
@@ -2650,15 +2720,18 @@
         <v>0.5575221238938053</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>5</v>
@@ -2667,7 +2740,7 @@
         <v>20</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E24" s="11">
         <v>68</v>
@@ -2679,13 +2752,16 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>30</v>
       </c>
@@ -2696,7 +2772,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E25" s="11">
         <v>68</v>
@@ -2708,15 +2784,18 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>5</v>
@@ -2725,7 +2804,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E26" s="11">
         <v>68</v>
@@ -2737,15 +2816,18 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>5</v>
@@ -2754,7 +2836,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E27" s="11">
         <v>68</v>
@@ -2766,15 +2848,18 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>5</v>
@@ -2783,7 +2868,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E28" s="11">
         <v>69</v>
@@ -2795,15 +2880,18 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>5</v>
@@ -2812,7 +2900,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E29" s="11">
         <v>69</v>
@@ -2824,13 +2912,16 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -2841,7 +2932,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E30" s="11">
         <v>69</v>
@@ -2853,15 +2944,18 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>6</v>
@@ -2870,25 +2964,28 @@
         <v>21</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F31" s="11">
         <v>48</v>
       </c>
       <c r="G31" s="13"/>
       <c r="H31" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>6</v>
@@ -2897,25 +2994,28 @@
         <v>21</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F32" s="11">
         <v>48</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>6</v>
@@ -2924,25 +3024,28 @@
         <v>21</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F33" s="11">
         <v>48</v>
       </c>
       <c r="G33" s="13"/>
       <c r="H33" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>6</v>
@@ -2951,25 +3054,28 @@
         <v>21</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F34" s="11">
         <v>48</v>
       </c>
       <c r="G34" s="13"/>
       <c r="H34" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>6</v>
@@ -2978,25 +3084,28 @@
         <v>21</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F35" s="11">
         <v>48</v>
       </c>
       <c r="G35" s="13"/>
       <c r="H35" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>6</v>
@@ -3005,25 +3114,28 @@
         <v>21</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F36" s="11">
         <v>48</v>
       </c>
       <c r="G36" s="13"/>
       <c r="H36" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>6</v>
@@ -3032,7 +3144,7 @@
         <v>21</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E37" s="11">
         <v>15</v>
@@ -3044,15 +3156,18 @@
         <v>0.3125</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>6</v>
@@ -3061,7 +3176,7 @@
         <v>21</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E38" s="11">
         <v>19</v>
@@ -3073,15 +3188,18 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>6</v>
@@ -3090,7 +3208,7 @@
         <v>21</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E39" s="11">
         <v>19</v>
@@ -3102,13 +3220,16 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>30</v>
       </c>
@@ -3119,7 +3240,7 @@
         <v>21</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E40" s="11">
         <v>21</v>
@@ -3131,15 +3252,18 @@
         <v>0.4375</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>6</v>
@@ -3148,7 +3272,7 @@
         <v>21</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E41" s="11">
         <v>21</v>
@@ -3160,15 +3284,18 @@
         <v>0.4375</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>6</v>
@@ -3177,7 +3304,7 @@
         <v>21</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E42" s="11">
         <v>21</v>
@@ -3189,15 +3316,18 @@
         <v>0.4375</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>6</v>
@@ -3206,7 +3336,7 @@
         <v>21</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E43" s="11">
         <v>21</v>
@@ -3218,15 +3348,18 @@
         <v>0.4375</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>6</v>
@@ -3235,7 +3368,7 @@
         <v>21</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E44" s="11">
         <v>21</v>
@@ -3247,13 +3380,16 @@
         <v>0.4375</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>29</v>
       </c>
@@ -3264,7 +3400,7 @@
         <v>21</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E45" s="11">
         <v>21</v>
@@ -3276,15 +3412,18 @@
         <v>0.4375</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>7</v>
@@ -3293,7 +3432,7 @@
         <v>22</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E46" s="11">
         <v>83</v>
@@ -3305,15 +3444,18 @@
         <v>0.8383838383838383</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>7</v>
@@ -3322,7 +3464,7 @@
         <v>22</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E47" s="11">
         <v>70</v>
@@ -3334,15 +3476,18 @@
         <v>0.6194690265486725</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>7</v>
@@ -3351,7 +3496,7 @@
         <v>22</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E48" s="11">
         <v>70</v>
@@ -3363,13 +3508,16 @@
         <v>0.6194690265486725</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>30</v>
       </c>
@@ -3380,7 +3528,7 @@
         <v>22</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E49" s="11">
         <v>71</v>
@@ -3392,15 +3540,18 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>7</v>
@@ -3409,7 +3560,7 @@
         <v>22</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E50" s="11">
         <v>71</v>
@@ -3421,15 +3572,18 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>7</v>
@@ -3438,7 +3592,7 @@
         <v>22</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E51" s="11">
         <v>71</v>
@@ -3450,15 +3604,18 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>7</v>
@@ -3467,7 +3624,7 @@
         <v>22</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E52" s="11">
         <v>71</v>
@@ -3479,15 +3636,18 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>7</v>
@@ -3496,7 +3656,7 @@
         <v>22</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E53" s="11">
         <v>71</v>
@@ -3508,13 +3668,16 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>29</v>
       </c>
@@ -3525,7 +3688,7 @@
         <v>22</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E54" s="11">
         <v>71</v>
@@ -3537,15 +3700,18 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>8</v>
@@ -3554,7 +3720,7 @@
         <v>23</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E55" s="11">
         <v>45</v>
@@ -3566,15 +3732,18 @@
         <v>0.9782608695652174</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J55" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>8</v>
@@ -3583,7 +3752,7 @@
         <v>22</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E56" s="11">
         <v>47</v>
@@ -3595,15 +3764,18 @@
         <v>0.8392857142857143</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J56" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>8</v>
@@ -3612,7 +3784,7 @@
         <v>24</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E57" s="11">
         <v>13</v>
@@ -3624,15 +3796,18 @@
         <v>0.52</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>8</v>
@@ -3641,7 +3816,7 @@
         <v>25</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E58" s="11">
         <v>3</v>
@@ -3653,15 +3828,18 @@
         <v>0.12</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J58" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>8</v>
@@ -3670,7 +3848,7 @@
         <v>23</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E59" s="11">
         <v>46</v>
@@ -3682,15 +3860,18 @@
         <v>1</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>8</v>
@@ -3699,7 +3880,7 @@
         <v>22</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E60" s="11">
         <v>56</v>
@@ -3711,15 +3892,18 @@
         <v>1</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J60" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>8</v>
@@ -3728,7 +3912,7 @@
         <v>24</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E61" s="11">
         <v>24</v>
@@ -3740,15 +3924,18 @@
         <v>0.96</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J61" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>8</v>
@@ -3757,7 +3944,7 @@
         <v>25</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E62" s="11">
         <v>7</v>
@@ -3769,15 +3956,18 @@
         <v>0.28</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J62" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>8</v>
@@ -3786,7 +3976,7 @@
         <v>23</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E63" s="11">
         <v>46</v>
@@ -3798,15 +3988,18 @@
         <v>1</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>8</v>
@@ -3815,7 +4008,7 @@
         <v>22</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E64" s="11">
         <v>56</v>
@@ -3827,15 +4020,18 @@
         <v>1</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>8</v>
@@ -3844,7 +4040,7 @@
         <v>24</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E65" s="11">
         <v>24</v>
@@ -3856,15 +4052,18 @@
         <v>0.96</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>8</v>
@@ -3873,7 +4072,7 @@
         <v>25</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E66" s="11">
         <v>8</v>
@@ -3885,13 +4084,16 @@
         <v>0.32</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>30</v>
       </c>
@@ -3902,7 +4104,7 @@
         <v>23</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E67" s="11">
         <v>46</v>
@@ -3914,13 +4116,16 @@
         <v>1</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
         <v>30</v>
       </c>
@@ -3931,7 +4136,7 @@
         <v>22</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E68" s="11">
         <v>56</v>
@@ -3943,13 +4148,16 @@
         <v>1</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J68" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
         <v>30</v>
       </c>
@@ -3960,7 +4168,7 @@
         <v>24</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E69" s="11">
         <v>24</v>
@@ -3972,13 +4180,16 @@
         <v>0.96</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>30</v>
       </c>
@@ -3989,7 +4200,7 @@
         <v>25</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E70" s="11">
         <v>10</v>
@@ -4001,15 +4212,18 @@
         <v>0.4</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J70" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>8</v>
@@ -4018,7 +4232,7 @@
         <v>23</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E71" s="11">
         <v>46</v>
@@ -4030,15 +4244,18 @@
         <v>1</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>8</v>
@@ -4047,7 +4264,7 @@
         <v>22</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E72" s="11">
         <v>56</v>
@@ -4059,15 +4276,18 @@
         <v>1</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J72" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>8</v>
@@ -4076,7 +4296,7 @@
         <v>24</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E73" s="11">
         <v>24</v>
@@ -4088,15 +4308,18 @@
         <v>0.96</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J73" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>8</v>
@@ -4105,7 +4328,7 @@
         <v>25</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E74" s="11">
         <v>10</v>
@@ -4117,15 +4340,18 @@
         <v>0.4</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>8</v>
@@ -4134,7 +4360,7 @@
         <v>23</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E75" s="11">
         <v>46</v>
@@ -4146,15 +4372,18 @@
         <v>1</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J75" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>8</v>
@@ -4163,7 +4392,7 @@
         <v>22</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E76" s="11">
         <v>56</v>
@@ -4175,15 +4404,18 @@
         <v>1</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J76" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>8</v>
@@ -4192,7 +4424,7 @@
         <v>24</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E77" s="11">
         <v>24</v>
@@ -4204,15 +4436,18 @@
         <v>0.96</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J77" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B78" s="11" t="s">
         <v>8</v>
@@ -4221,7 +4456,7 @@
         <v>25</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E78" s="11">
         <v>10</v>
@@ -4233,15 +4468,18 @@
         <v>0.4</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>8</v>
@@ -4250,7 +4488,7 @@
         <v>23</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E79" s="11">
         <v>46</v>
@@ -4262,15 +4500,18 @@
         <v>1</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>8</v>
@@ -4279,7 +4520,7 @@
         <v>22</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E80" s="11">
         <v>56</v>
@@ -4291,15 +4532,18 @@
         <v>1</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>8</v>
@@ -4308,7 +4552,7 @@
         <v>24</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E81" s="11">
         <v>24</v>
@@ -4320,15 +4564,18 @@
         <v>0.96</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>8</v>
@@ -4337,7 +4584,7 @@
         <v>25</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E82" s="11">
         <v>10</v>
@@ -4349,15 +4596,18 @@
         <v>0.4</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J82" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>8</v>
@@ -4366,7 +4616,7 @@
         <v>23</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E83" s="11">
         <v>46</v>
@@ -4378,15 +4628,18 @@
         <v>1</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>8</v>
@@ -4395,7 +4648,7 @@
         <v>22</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E84" s="11">
         <v>56</v>
@@ -4407,15 +4660,18 @@
         <v>1</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J84" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>8</v>
@@ -4424,7 +4680,7 @@
         <v>24</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E85" s="11">
         <v>24</v>
@@ -4436,15 +4692,18 @@
         <v>0.96</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J85" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>8</v>
@@ -4453,7 +4712,7 @@
         <v>25</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E86" s="11">
         <v>10</v>
@@ -4465,13 +4724,16 @@
         <v>0.4</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J86" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
         <v>29</v>
       </c>
@@ -4482,7 +4744,7 @@
         <v>23</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E87" s="11">
         <v>46</v>
@@ -4494,13 +4756,16 @@
         <v>1</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>29</v>
       </c>
@@ -4511,7 +4776,7 @@
         <v>22</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E88" s="11">
         <v>56</v>
@@ -4523,13 +4788,16 @@
         <v>1</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J88" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
         <v>29</v>
       </c>
@@ -4540,7 +4808,7 @@
         <v>24</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E89" s="11">
         <v>24</v>
@@ -4552,13 +4820,16 @@
         <v>0.96</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J89" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
         <v>29</v>
       </c>
@@ -4569,7 +4840,7 @@
         <v>25</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E90" s="11">
         <v>10</v>
@@ -4581,15 +4852,18 @@
         <v>0.4</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J90" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>9</v>
@@ -4598,7 +4872,7 @@
         <v>21</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E91" s="11">
         <v>87</v>
@@ -4610,15 +4884,18 @@
         <v>0.8787878787878788</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J91" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>9</v>
@@ -4627,7 +4904,7 @@
         <v>21</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E92" s="11">
         <v>77</v>
@@ -4639,15 +4916,18 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J92" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>9</v>
@@ -4656,7 +4936,7 @@
         <v>21</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E93" s="11">
         <v>77</v>
@@ -4668,13 +4948,16 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J93" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>30</v>
       </c>
@@ -4685,7 +4968,7 @@
         <v>21</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E94" s="11">
         <v>77</v>
@@ -4697,15 +4980,18 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J94" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>9</v>
@@ -4714,7 +5000,7 @@
         <v>21</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E95" s="11">
         <v>77</v>
@@ -4726,15 +5012,18 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J95" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>9</v>
@@ -4743,7 +5032,7 @@
         <v>21</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E96" s="11">
         <v>77</v>
@@ -4755,15 +5044,18 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J96" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>9</v>
@@ -4772,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E97" s="11">
         <v>77</v>
@@ -4784,15 +5076,18 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J97" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>9</v>
@@ -4801,7 +5096,7 @@
         <v>21</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E98" s="11">
         <v>77</v>
@@ -4813,13 +5108,16 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J98" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>29</v>
       </c>
@@ -4830,7 +5128,7 @@
         <v>21</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E99" s="11">
         <v>77</v>
@@ -4842,15 +5140,18 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H99" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J99" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>10</v>
@@ -4859,7 +5160,7 @@
         <v>20</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E100" s="11">
         <v>101</v>
@@ -4871,15 +5172,18 @@
         <v>0.9099099099099099</v>
       </c>
       <c r="H100" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="I100" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="J100" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="11" t="s">
         <v>162</v>
-      </c>
-      <c r="I100" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="11" t="s">
-        <v>161</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>10</v>
@@ -4888,7 +5192,7 @@
         <v>23</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E101" s="11">
         <v>131</v>
@@ -4900,15 +5204,18 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J101" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>10</v>
@@ -4917,7 +5224,7 @@
         <v>22</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E102" s="11">
         <v>78</v>
@@ -4929,15 +5236,18 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J102" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B103" s="11" t="s">
         <v>10</v>
@@ -4946,7 +5256,7 @@
         <v>20</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E103" s="11">
         <v>57</v>
@@ -4958,15 +5268,18 @@
         <v>0.5135135135135135</v>
       </c>
       <c r="H103" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="I103" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="J103" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="11" t="s">
         <v>166</v>
-      </c>
-      <c r="I103" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="11" t="s">
-        <v>165</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>10</v>
@@ -4975,7 +5288,7 @@
         <v>23</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E104" s="11">
         <v>93</v>
@@ -4987,15 +5300,18 @@
         <v>0.6739130434782609</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>10</v>
@@ -5004,7 +5320,7 @@
         <v>22</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E105" s="11">
         <v>44</v>
@@ -5016,15 +5332,18 @@
         <v>0.5432098765432098</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J105" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>10</v>
@@ -5033,7 +5352,7 @@
         <v>20</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E106" s="11">
         <v>62</v>
@@ -5045,15 +5364,18 @@
         <v>0.5585585585585585</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J106" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B107" s="11" t="s">
         <v>10</v>
@@ -5062,7 +5384,7 @@
         <v>23</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E107" s="11">
         <v>98</v>
@@ -5074,15 +5396,18 @@
         <v>0.7101449275362319</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I107" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J107" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>10</v>
@@ -5091,7 +5416,7 @@
         <v>22</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E108" s="11">
         <v>52</v>
@@ -5103,15 +5428,18 @@
         <v>0.6419753086419753</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I108" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J108" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B109" s="11" t="s">
         <v>10</v>
@@ -5120,7 +5448,7 @@
         <v>20</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E109" s="11">
         <v>102</v>
@@ -5132,15 +5460,18 @@
         <v>0.918918918918919</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I109" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J109" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>10</v>
@@ -5149,7 +5480,7 @@
         <v>23</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E110" s="11">
         <v>131</v>
@@ -5161,15 +5492,18 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I110" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J110" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>10</v>
@@ -5178,7 +5512,7 @@
         <v>22</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E111" s="11">
         <v>78</v>
@@ -5190,15 +5524,18 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I111" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J111" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>10</v>
@@ -5207,7 +5544,7 @@
         <v>20</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E112" s="11">
         <v>102</v>
@@ -5219,15 +5556,18 @@
         <v>0.918918918918919</v>
       </c>
       <c r="H112" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I112" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J112" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>10</v>
@@ -5236,7 +5576,7 @@
         <v>23</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E113" s="11">
         <v>131</v>
@@ -5248,15 +5588,18 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I113" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J113" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B114" s="11" t="s">
         <v>10</v>
@@ -5265,7 +5608,7 @@
         <v>22</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E114" s="11">
         <v>78</v>
@@ -5277,13 +5620,16 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J114" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
         <v>30</v>
       </c>
@@ -5294,7 +5640,7 @@
         <v>20</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E115" s="11">
         <v>111</v>
@@ -5306,13 +5652,16 @@
         <v>1</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I115" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J115" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
         <v>30</v>
       </c>
@@ -5323,7 +5672,7 @@
         <v>23</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E116" s="11">
         <v>134</v>
@@ -5335,13 +5684,16 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H116" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J116" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>30</v>
       </c>
@@ -5352,7 +5704,7 @@
         <v>22</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E117" s="11">
         <v>79</v>
@@ -5364,15 +5716,18 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I117" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J117" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>10</v>
@@ -5381,7 +5736,7 @@
         <v>20</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E118" s="11">
         <v>111</v>
@@ -5393,15 +5748,18 @@
         <v>1</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I118" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J118" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>10</v>
@@ -5410,7 +5768,7 @@
         <v>23</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E119" s="11">
         <v>134</v>
@@ -5422,15 +5780,18 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I119" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J119" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B120" s="11" t="s">
         <v>10</v>
@@ -5439,7 +5800,7 @@
         <v>22</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E120" s="11">
         <v>79</v>
@@ -5451,15 +5812,18 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I120" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J120" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>10</v>
@@ -5468,7 +5832,7 @@
         <v>20</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E121" s="11">
         <v>111</v>
@@ -5480,15 +5844,18 @@
         <v>1</v>
       </c>
       <c r="H121" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I121" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J121" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B122" s="11" t="s">
         <v>10</v>
@@ -5497,7 +5864,7 @@
         <v>23</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E122" s="11">
         <v>134</v>
@@ -5509,15 +5876,18 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I122" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J122" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>10</v>
@@ -5526,7 +5896,7 @@
         <v>22</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E123" s="11">
         <v>79</v>
@@ -5538,15 +5908,18 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H123" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I123" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J123" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>10</v>
@@ -5555,7 +5928,7 @@
         <v>20</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E124" s="11">
         <v>111</v>
@@ -5567,15 +5940,18 @@
         <v>1</v>
       </c>
       <c r="H124" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J124" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>10</v>
@@ -5584,7 +5960,7 @@
         <v>23</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E125" s="11">
         <v>134</v>
@@ -5596,15 +5972,18 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H125" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I125" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J125" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>10</v>
@@ -5613,7 +5992,7 @@
         <v>22</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E126" s="11">
         <v>79</v>
@@ -5625,15 +6004,18 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H126" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J126" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>10</v>
@@ -5642,7 +6024,7 @@
         <v>20</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E127" s="11">
         <v>111</v>
@@ -5654,15 +6036,18 @@
         <v>1</v>
       </c>
       <c r="H127" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J127" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B128" s="11" t="s">
         <v>10</v>
@@ -5671,7 +6056,7 @@
         <v>23</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E128" s="11">
         <v>134</v>
@@ -5683,15 +6068,18 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H128" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J128" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>10</v>
@@ -5700,7 +6088,7 @@
         <v>22</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E129" s="11">
         <v>79</v>
@@ -5712,13 +6100,16 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J129" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>29</v>
       </c>
@@ -5729,7 +6120,7 @@
         <v>20</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E130" s="11">
         <v>111</v>
@@ -5741,13 +6132,16 @@
         <v>1</v>
       </c>
       <c r="H130" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J130" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>29</v>
       </c>
@@ -5758,7 +6152,7 @@
         <v>23</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E131" s="11">
         <v>134</v>
@@ -5770,13 +6164,16 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I131" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J131" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
         <v>29</v>
       </c>
@@ -5787,7 +6184,7 @@
         <v>22</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E132" s="11">
         <v>79</v>
@@ -5799,15 +6196,18 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I132" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J132" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B133" s="11" t="s">
         <v>11</v>
@@ -5816,7 +6216,7 @@
         <v>20</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E133" s="11">
         <v>3</v>
@@ -5828,15 +6228,18 @@
         <v>0.11538461538461539</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I133" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J133" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B134" s="11" t="s">
         <v>11</v>
@@ -5845,7 +6248,7 @@
         <v>23</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E134" s="11">
         <v>77</v>
@@ -5857,15 +6260,18 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I134" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J134" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B135" s="11" t="s">
         <v>11</v>
@@ -5874,7 +6280,7 @@
         <v>22</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E135" s="11">
         <v>17</v>
@@ -5886,44 +6292,50 @@
         <v>0.16346153846153846</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I135" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J135" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G136" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I136" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J136" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>11</v>
@@ -5932,7 +6344,7 @@
         <v>20</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E137" s="11">
         <v>17</v>
@@ -5944,15 +6356,18 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I137" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J137" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B138" s="11" t="s">
         <v>11</v>
@@ -5961,7 +6376,7 @@
         <v>23</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E138" s="11">
         <v>111</v>
@@ -5973,15 +6388,18 @@
         <v>0.8809523809523809</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I138" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J138" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>11</v>
@@ -5990,7 +6408,7 @@
         <v>22</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E139" s="11">
         <v>71</v>
@@ -6002,15 +6420,18 @@
         <v>0.6826923076923077</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I139" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J139" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B140" s="11" t="s">
         <v>11</v>
@@ -6019,7 +6440,7 @@
         <v>20</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E140" s="11">
         <v>17</v>
@@ -6031,15 +6452,18 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I140" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J140" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B141" s="11" t="s">
         <v>11</v>
@@ -6048,7 +6472,7 @@
         <v>23</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E141" s="11">
         <v>116</v>
@@ -6060,15 +6484,18 @@
         <v>0.9206349206349206</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I141" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J141" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B142" s="11" t="s">
         <v>11</v>
@@ -6077,7 +6504,7 @@
         <v>22</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E142" s="11">
         <v>89</v>
@@ -6089,13 +6516,16 @@
         <v>0.8557692307692307</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J142" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
         <v>30</v>
       </c>
@@ -6106,7 +6536,7 @@
         <v>20</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E143" s="11">
         <v>23</v>
@@ -6118,13 +6548,16 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I143" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J143" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
         <v>30</v>
       </c>
@@ -6135,7 +6568,7 @@
         <v>23</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E144" s="11">
         <v>124</v>
@@ -6147,13 +6580,16 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H144" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J144" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>30</v>
       </c>
@@ -6164,7 +6600,7 @@
         <v>22</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E145" s="11">
         <v>98</v>
@@ -6176,15 +6612,18 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H145" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I145" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J145" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>11</v>
@@ -6193,7 +6632,7 @@
         <v>20</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E146" s="11">
         <v>23</v>
@@ -6205,15 +6644,18 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J146" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B147" s="11" t="s">
         <v>11</v>
@@ -6222,7 +6664,7 @@
         <v>23</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E147" s="11">
         <v>124</v>
@@ -6234,15 +6676,18 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H147" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I147" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J147" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B148" s="11" t="s">
         <v>11</v>
@@ -6251,7 +6696,7 @@
         <v>22</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E148" s="11">
         <v>98</v>
@@ -6263,15 +6708,18 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H148" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I148" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J148" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>11</v>
@@ -6280,7 +6728,7 @@
         <v>20</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E149" s="11">
         <v>23</v>
@@ -6292,15 +6740,18 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H149" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I149" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J149" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>11</v>
@@ -6309,7 +6760,7 @@
         <v>23</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E150" s="11">
         <v>124</v>
@@ -6321,15 +6772,18 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H150" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I150" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J150" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>11</v>
@@ -6338,7 +6792,7 @@
         <v>22</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E151" s="11">
         <v>98</v>
@@ -6350,15 +6804,18 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H151" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I151" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J151" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B152" s="11" t="s">
         <v>11</v>
@@ -6367,7 +6824,7 @@
         <v>20</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E152" s="11">
         <v>23</v>
@@ -6379,15 +6836,18 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H152" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I152" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J152" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B153" s="11" t="s">
         <v>11</v>
@@ -6396,7 +6856,7 @@
         <v>23</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E153" s="11">
         <v>124</v>
@@ -6408,15 +6868,18 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H153" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I153" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J153" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B154" s="11" t="s">
         <v>11</v>
@@ -6425,7 +6888,7 @@
         <v>22</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E154" s="11">
         <v>98</v>
@@ -6437,15 +6900,18 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H154" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I154" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J154" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>11</v>
@@ -6454,7 +6920,7 @@
         <v>20</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E155" s="11">
         <v>23</v>
@@ -6466,15 +6932,18 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H155" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I155" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J155" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B156" s="11" t="s">
         <v>11</v>
@@ -6483,7 +6952,7 @@
         <v>23</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E156" s="11">
         <v>124</v>
@@ -6495,15 +6964,18 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H156" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I156" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J156" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>11</v>
@@ -6512,7 +6984,7 @@
         <v>22</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E157" s="11">
         <v>98</v>
@@ -6524,13 +6996,16 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H157" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I157" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J157" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>29</v>
       </c>
@@ -6541,7 +7016,7 @@
         <v>20</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E158" s="11">
         <v>23</v>
@@ -6553,13 +7028,16 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H158" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I158" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J158" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>29</v>
       </c>
@@ -6570,7 +7048,7 @@
         <v>23</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E159" s="11">
         <v>124</v>
@@ -6582,13 +7060,16 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H159" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I159" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J159" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
         <v>29</v>
       </c>
@@ -6599,7 +7080,7 @@
         <v>22</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E160" s="11">
         <v>98</v>
@@ -6611,15 +7092,18 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H160" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I160" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J160" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B161" s="11" t="s">
         <v>12</v>
@@ -6628,7 +7112,7 @@
         <v>20</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E161" s="11">
         <v>16</v>
@@ -6640,15 +7124,18 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="H161" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I161" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J161" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B162" s="11" t="s">
         <v>12</v>
@@ -6657,7 +7144,7 @@
         <v>23</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E162" s="11">
         <v>39</v>
@@ -6669,15 +7156,18 @@
         <v>0.4588235294117647</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I162" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J162" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B163" s="11" t="s">
         <v>12</v>
@@ -6686,7 +7176,7 @@
         <v>22</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E163" s="11">
         <v>11</v>
@@ -6698,13 +7188,16 @@
         <v>0.10784313725490197</v>
       </c>
       <c r="H163" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I163" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J163" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
         <v>30</v>
       </c>
@@ -6715,7 +7208,7 @@
         <v>20</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E164" s="11">
         <v>29</v>
@@ -6727,13 +7220,16 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H164" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I164" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J164" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
         <v>30</v>
       </c>
@@ -6744,7 +7240,7 @@
         <v>23</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E165" s="11">
         <v>63</v>
@@ -6756,13 +7252,16 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H165" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I165" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J165" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
         <v>30</v>
       </c>
@@ -6773,7 +7272,7 @@
         <v>22</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E166" s="11">
         <v>22</v>
@@ -6785,15 +7284,18 @@
         <v>0.21568627450980393</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I166" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J166" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B167" s="11" t="s">
         <v>12</v>
@@ -6802,7 +7304,7 @@
         <v>20</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E167" s="11">
         <v>29</v>
@@ -6814,15 +7316,18 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H167" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I167" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J167" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>12</v>
@@ -6831,7 +7336,7 @@
         <v>23</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E168" s="11">
         <v>63</v>
@@ -6843,15 +7348,18 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H168" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I168" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J168" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B169" s="11" t="s">
         <v>12</v>
@@ -6860,7 +7368,7 @@
         <v>22</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E169" s="11">
         <v>23</v>
@@ -6872,15 +7380,18 @@
         <v>0.22549019607843138</v>
       </c>
       <c r="H169" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I169" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J169" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>12</v>
@@ -6889,7 +7400,7 @@
         <v>20</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E170" s="11">
         <v>29</v>
@@ -6901,15 +7412,18 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H170" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I170" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J170" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B171" s="11" t="s">
         <v>12</v>
@@ -6918,7 +7432,7 @@
         <v>23</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E171" s="11">
         <v>63</v>
@@ -6930,15 +7444,18 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H171" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I171" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J171" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B172" s="11" t="s">
         <v>12</v>
@@ -6947,7 +7464,7 @@
         <v>22</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E172" s="11">
         <v>23</v>
@@ -6959,15 +7476,18 @@
         <v>0.22549019607843138</v>
       </c>
       <c r="H172" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I172" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J172" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B173" s="11" t="s">
         <v>12</v>
@@ -6976,7 +7496,7 @@
         <v>20</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E173" s="11">
         <v>29</v>
@@ -6988,15 +7508,18 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H173" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I173" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J173" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B174" s="11" t="s">
         <v>12</v>
@@ -7005,7 +7528,7 @@
         <v>23</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E174" s="11">
         <v>65</v>
@@ -7017,15 +7540,18 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H174" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I174" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J174" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B175" s="11" t="s">
         <v>12</v>
@@ -7034,7 +7560,7 @@
         <v>22</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E175" s="11">
         <v>24</v>
@@ -7046,15 +7572,18 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H175" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I175" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J175" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B176" s="11" t="s">
         <v>12</v>
@@ -7063,7 +7592,7 @@
         <v>20</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E176" s="11">
         <v>29</v>
@@ -7075,15 +7604,18 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H176" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I176" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J176" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B177" s="11" t="s">
         <v>12</v>
@@ -7092,7 +7624,7 @@
         <v>23</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E177" s="11">
         <v>65</v>
@@ -7104,15 +7636,18 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H177" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I177" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J177" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B178" s="11" t="s">
         <v>12</v>
@@ -7121,7 +7656,7 @@
         <v>22</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E178" s="11">
         <v>24</v>
@@ -7133,13 +7668,16 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H178" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I178" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J178" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>29</v>
       </c>
@@ -7150,7 +7688,7 @@
         <v>20</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E179" s="11">
         <v>29</v>
@@ -7162,13 +7700,16 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H179" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I179" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J179" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>29</v>
       </c>
@@ -7179,7 +7720,7 @@
         <v>23</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E180" s="11">
         <v>65</v>
@@ -7191,13 +7732,16 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H180" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I180" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J180" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>29</v>
       </c>
@@ -7208,7 +7752,7 @@
         <v>22</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E181" s="11">
         <v>24</v>
@@ -7220,42 +7764,48 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H181" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I181" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J181" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B182" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E182" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G182" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H182" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I182" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J182" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
         <v>30</v>
       </c>
@@ -7263,59 +7813,65 @@
         <v>13</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E183" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G183" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H183" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I183" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J183" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E184" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G184" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H184" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I184" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J184" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B185" s="11" t="s">
         <v>14</v>
@@ -7324,7 +7880,7 @@
         <v>22</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E185" s="11">
         <v>24</v>
@@ -7336,15 +7892,18 @@
         <v>0.17647058823529413</v>
       </c>
       <c r="H185" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I185" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J185" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B186" s="11" t="s">
         <v>14</v>
@@ -7353,7 +7912,7 @@
         <v>22</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E186" s="11">
         <v>30</v>
@@ -7365,13 +7924,16 @@
         <v>0.22058823529411764</v>
       </c>
       <c r="H186" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I186" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J186" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>30</v>
       </c>
@@ -7382,7 +7944,7 @@
         <v>22</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E187" s="11">
         <v>45</v>
@@ -7394,15 +7956,18 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H187" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I187" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J187" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B188" s="11" t="s">
         <v>14</v>
@@ -7411,7 +7976,7 @@
         <v>22</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E188" s="11">
         <v>45</v>
@@ -7423,15 +7988,18 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H188" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I188" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J188" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B189" s="11" t="s">
         <v>14</v>
@@ -7440,7 +8008,7 @@
         <v>22</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E189" s="11">
         <v>45</v>
@@ -7452,15 +8020,18 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H189" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I189" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J189" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B190" s="11" t="s">
         <v>14</v>
@@ -7469,7 +8040,7 @@
         <v>22</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E190" s="11">
         <v>45</v>
@@ -7481,15 +8052,18 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H190" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I190" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J190" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B191" s="11" t="s">
         <v>14</v>
@@ -7498,7 +8072,7 @@
         <v>22</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E191" s="11">
         <v>45</v>
@@ -7510,13 +8084,16 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H191" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I191" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J191" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="11" t="s">
         <v>29</v>
       </c>
@@ -7527,7 +8104,7 @@
         <v>22</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E192" s="11">
         <v>45</v>
@@ -7539,24 +8116,27 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H192" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I192" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J192" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B193" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E193" s="11">
         <v>81</v>
@@ -7568,15 +8148,18 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="H193" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I193" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J193" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B194" s="11" t="s">
         <v>15</v>
@@ -7585,7 +8168,7 @@
         <v>26</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E194" s="11">
         <v>1</v>
@@ -7597,24 +8180,27 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H194" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I194" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J194" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B195" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E195" s="11">
         <v>84</v>
@@ -7626,15 +8212,18 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="H195" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I195" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J195" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B196" s="11" t="s">
         <v>15</v>
@@ -7643,7 +8232,7 @@
         <v>26</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E196" s="11">
         <v>0</v>
@@ -7655,24 +8244,27 @@
         <v>0</v>
       </c>
       <c r="H196" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I196" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J196" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B197" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E197" s="11">
         <v>124</v>
@@ -7684,15 +8276,18 @@
         <v>0.656084656084656</v>
       </c>
       <c r="H197" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I197" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J197" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B198" s="11" t="s">
         <v>15</v>
@@ -7701,7 +8296,7 @@
         <v>26</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E198" s="11">
         <v>0</v>
@@ -7713,24 +8308,27 @@
         <v>0</v>
       </c>
       <c r="H198" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I198" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J198" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B199" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D199" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E199" s="11">
         <v>148</v>
@@ -7742,15 +8340,18 @@
         <v>0.783068783068783</v>
       </c>
       <c r="H199" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I199" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J199" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B200" s="11" t="s">
         <v>15</v>
@@ -7759,7 +8360,7 @@
         <v>26</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E200" s="11">
         <v>1</v>
@@ -7771,24 +8372,27 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H200" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I200" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J200" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B201" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E201" s="11">
         <v>154</v>
@@ -7800,15 +8404,18 @@
         <v>0.8148148148148148</v>
       </c>
       <c r="H201" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I201" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J201" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B202" s="11" t="s">
         <v>15</v>
@@ -7817,7 +8424,7 @@
         <v>26</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E202" s="11">
         <v>1</v>
@@ -7829,13 +8436,16 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H202" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I202" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J202" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="11" t="s">
         <v>30</v>
       </c>
@@ -7846,7 +8456,7 @@
         <v>27</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E203" s="11">
         <v>160</v>
@@ -7858,13 +8468,16 @@
         <v>0.5194805194805194</v>
       </c>
       <c r="H203" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I203" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J203" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="11" t="s">
         <v>30</v>
       </c>
@@ -7875,7 +8488,7 @@
         <v>26</v>
       </c>
       <c r="D204" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E204" s="11">
         <v>1</v>
@@ -7887,15 +8500,18 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H204" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I204" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J204" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B205" s="11" t="s">
         <v>15</v>
@@ -7904,7 +8520,7 @@
         <v>26</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E205" s="11">
         <v>1</v>
@@ -7916,15 +8532,18 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H205" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I205" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J205" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>15</v>
@@ -7933,7 +8552,7 @@
         <v>27</v>
       </c>
       <c r="D206" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E206" s="11">
         <v>161</v>
@@ -7945,15 +8564,18 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H206" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I206" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J206" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B207" s="11" t="s">
         <v>15</v>
@@ -7962,7 +8584,7 @@
         <v>26</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E207" s="11">
         <v>1</v>
@@ -7974,15 +8596,18 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H207" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I207" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J207" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B208" s="11" t="s">
         <v>15</v>
@@ -7991,7 +8616,7 @@
         <v>27</v>
       </c>
       <c r="D208" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E208" s="11">
         <v>161</v>
@@ -8003,15 +8628,18 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H208" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I208" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J208" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B209" s="11" t="s">
         <v>15</v>
@@ -8020,7 +8648,7 @@
         <v>26</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E209" s="11">
         <v>1</v>
@@ -8032,15 +8660,18 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H209" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I209" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J209" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B210" s="11" t="s">
         <v>15</v>
@@ -8049,7 +8680,7 @@
         <v>27</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E210" s="11">
         <v>161</v>
@@ -8061,15 +8692,18 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H210" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I210" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J210" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B211" s="11" t="s">
         <v>15</v>
@@ -8078,7 +8712,7 @@
         <v>26</v>
       </c>
       <c r="D211" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E211" s="11">
         <v>1</v>
@@ -8090,15 +8724,18 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H211" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I211" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J211" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B212" s="11" t="s">
         <v>15</v>
@@ -8107,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E212" s="11">
         <v>161</v>
@@ -8119,13 +8756,16 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H212" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I212" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J212" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
         <v>29</v>
       </c>
@@ -8136,7 +8776,7 @@
         <v>26</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E213" s="11">
         <v>1</v>
@@ -8148,13 +8788,16 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H213" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I213" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J213" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
         <v>29</v>
       </c>
@@ -8165,7 +8808,7 @@
         <v>27</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E214" s="11">
         <v>161</v>
@@ -8177,15 +8820,18 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H214" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I214" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J214" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B215" s="11" t="s">
         <v>16</v>
@@ -8194,7 +8840,7 @@
         <v>23</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E215" s="11">
         <v>9</v>
@@ -8206,15 +8852,18 @@
         <v>0.06040268456375839</v>
       </c>
       <c r="H215" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I215" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J215" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>16</v>
@@ -8223,7 +8872,7 @@
         <v>23</v>
       </c>
       <c r="D216" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E216" s="11">
         <v>21</v>
@@ -8235,15 +8884,18 @@
         <v>0.14093959731543623</v>
       </c>
       <c r="H216" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I216" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J216" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B217" s="11" t="s">
         <v>16</v>
@@ -8252,7 +8904,7 @@
         <v>23</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E217" s="11">
         <v>23</v>
@@ -8264,15 +8916,18 @@
         <v>0.15436241610738255</v>
       </c>
       <c r="H217" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I217" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J217" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>16</v>
@@ -8281,7 +8936,7 @@
         <v>23</v>
       </c>
       <c r="D218" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E218" s="11">
         <v>31</v>
@@ -8293,15 +8948,18 @@
         <v>0.2080536912751678</v>
       </c>
       <c r="H218" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I218" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J218" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B219" s="11" t="s">
         <v>16</v>
@@ -8310,7 +8968,7 @@
         <v>23</v>
       </c>
       <c r="D219" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E219" s="11">
         <v>34</v>
@@ -8322,13 +8980,16 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H219" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I219" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J219" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>30</v>
       </c>
@@ -8339,7 +9000,7 @@
         <v>23</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E220" s="11">
         <v>34</v>
@@ -8351,15 +9012,18 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H220" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="J220" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B221" s="11" t="s">
         <v>16</v>
@@ -8368,7 +9032,7 @@
         <v>23</v>
       </c>
       <c r="D221" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E221" s="11">
         <v>34</v>
@@ -8380,15 +9044,18 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H221" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I221" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J221" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>16</v>
@@ -8397,7 +9064,7 @@
         <v>23</v>
       </c>
       <c r="D222" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E222" s="11">
         <v>34</v>
@@ -8409,15 +9076,18 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H222" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I222" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J222" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B223" s="11" t="s">
         <v>16</v>
@@ -8426,7 +9096,7 @@
         <v>23</v>
       </c>
       <c r="D223" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E223" s="11">
         <v>34</v>
@@ -8438,15 +9108,18 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H223" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I223" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J223" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>16</v>
@@ -8455,7 +9128,7 @@
         <v>23</v>
       </c>
       <c r="D224" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E224" s="11">
         <v>34</v>
@@ -8467,13 +9140,16 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H224" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I224" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="J224" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
         <v>29</v>
       </c>
@@ -8484,7 +9160,7 @@
         <v>23</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E225" s="11">
         <v>34</v>
@@ -8496,14 +9172,17 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H225" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I225" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="J225" s="12" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I225"/>
+  <autoFilter ref="A1:J225"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -8520,10 +9199,10 @@
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -8531,23 +9210,23 @@
         <v>77</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -8555,23 +9234,23 @@
         <v>81</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="238">
   <si>
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
@@ -294,9 +294,6 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Data Quality Alert</t>
-  </si>
-  <si>
     <t>17/03/2025</t>
   </si>
   <si>
@@ -501,7 +498,25 @@
     <t>77/99 signed</t>
   </si>
   <si>
-    <t>27/02/2025</t>
+    <t>25/08/2025</t>
+  </si>
+  <si>
+    <t>51% Signed (57/111 units)</t>
+  </si>
+  <si>
+    <t>67% Signed (93/138 units)</t>
+  </si>
+  <si>
+    <t>54% Signed (44/81 units)</t>
+  </si>
+  <si>
+    <t>56% Signed (62/111 units)</t>
+  </si>
+  <si>
+    <t>71% Signed (98/138 units)</t>
+  </si>
+  <si>
+    <t>64% Signed (52/81 units)</t>
   </si>
   <si>
     <t>91% Signed (101/111 units)</t>
@@ -513,27 +528,6 @@
     <t>96% Signed (78/81 units)</t>
   </si>
   <si>
-    <t>25/08/2025</t>
-  </si>
-  <si>
-    <t>51% Signed (57/111 units)</t>
-  </si>
-  <si>
-    <t>67% Signed (93/138 units)</t>
-  </si>
-  <si>
-    <t>54% Signed (44/81 units)</t>
-  </si>
-  <si>
-    <t>56% Signed (62/111 units)</t>
-  </si>
-  <si>
-    <t>71% Signed (98/138 units)</t>
-  </si>
-  <si>
-    <t>64% Signed (52/81 units)</t>
-  </si>
-  <si>
     <t>91% Signed (102/111 units)</t>
   </si>
   <si>
@@ -555,6 +549,9 @@
     <t>79/81 signed</t>
   </si>
   <si>
+    <t>No parseable group-level values: Yet to sign</t>
+  </si>
+  <si>
     <t>12% Signed (3/26 units)</t>
   </si>
   <si>
@@ -564,9 +561,6 @@
     <t>16% Signed (17/104 units)</t>
   </si>
   <si>
-    <t>No parseable group-level values: Yet to sign</t>
-  </si>
-  <si>
     <t>65% Signed (17/26 units)</t>
   </si>
   <si>
@@ -648,7 +642,7 @@
     <t>45/136 signed</t>
   </si>
   <si>
-    <t>Group 1</t>
+    <t>Earlier release scope (189 units)</t>
   </si>
   <si>
     <t>25% Signed (81/189 units)</t>
@@ -1992,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J225"/>
+  <dimension ref="A1:I225"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2002,10 +1996,9 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="46" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>84</v>
       </c>
@@ -2033,13 +2026,10 @@
       <c r="I1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>94</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>3</v>
@@ -2048,28 +2038,25 @@
         <v>18</v>
       </c>
       <c r="D2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F2" s="11">
         <v>81</v>
       </c>
       <c r="G2" s="13"/>
       <c r="H2" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I2" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>3</v>
@@ -2078,28 +2065,25 @@
         <v>18</v>
       </c>
       <c r="D3" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F3" s="11">
         <v>81</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>100</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>101</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>3</v>
@@ -2108,7 +2092,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" s="11">
         <v>48</v>
@@ -2120,18 +2104,15 @@
         <v>0.5925925925925926</v>
       </c>
       <c r="H4" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>3</v>
@@ -2140,7 +2121,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E5" s="11">
         <v>53</v>
@@ -2152,16 +2133,13 @@
         <v>0.654320987654321</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>30</v>
       </c>
@@ -2172,7 +2150,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E6" s="11">
         <v>72</v>
@@ -2184,18 +2162,15 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="H6" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>106</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>107</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>3</v>
@@ -2204,7 +2179,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E7" s="11">
         <v>74</v>
@@ -2216,18 +2191,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I7" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>3</v>
@@ -2236,7 +2208,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E8" s="11">
         <v>74</v>
@@ -2248,18 +2220,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>3</v>
@@ -2268,7 +2237,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E9" s="11">
         <v>74</v>
@@ -2280,18 +2249,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>3</v>
@@ -2300,7 +2266,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10" s="11">
         <v>74</v>
@@ -2312,16 +2278,13 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2332,7 +2295,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" s="11">
         <v>74</v>
@@ -2344,80 +2307,71 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>115</v>
-      </c>
       <c r="I12" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>115</v>
-      </c>
       <c r="I13" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>30</v>
       </c>
@@ -2425,33 +2379,30 @@
         <v>4</v>
       </c>
       <c r="C14" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="E14" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" s="12" t="s">
+      <c r="I14" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
         <v>115</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>116</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>5</v>
@@ -2460,28 +2411,25 @@
         <v>20</v>
       </c>
       <c r="D15" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F15" s="11">
         <v>113</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
         <v>117</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>5</v>
@@ -2490,28 +2438,25 @@
         <v>20</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F16" s="11">
         <v>113</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>120</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>5</v>
@@ -2520,28 +2465,25 @@
         <v>20</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F17" s="11">
         <v>113</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>5</v>
@@ -2550,28 +2492,25 @@
         <v>20</v>
       </c>
       <c r="D18" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F18" s="11">
         <v>113</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>123</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>5</v>
@@ -2580,7 +2519,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E19" s="11">
         <v>34</v>
@@ -2592,18 +2531,15 @@
         <v>0.3008849557522124</v>
       </c>
       <c r="H19" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>125</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>5</v>
@@ -2612,7 +2548,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="11">
         <v>37</v>
@@ -2624,18 +2560,15 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I20" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>5</v>
@@ -2644,7 +2577,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E21" s="11">
         <v>37</v>
@@ -2656,18 +2589,15 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H21" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>5</v>
@@ -2676,7 +2606,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E22" s="11">
         <v>54</v>
@@ -2688,18 +2618,15 @@
         <v>0.4778761061946903</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>5</v>
@@ -2708,7 +2635,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E23" s="11">
         <v>63</v>
@@ -2720,18 +2647,15 @@
         <v>0.5575221238938053</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>5</v>
@@ -2740,7 +2664,7 @@
         <v>20</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E24" s="11">
         <v>68</v>
@@ -2752,16 +2676,13 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J24" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>30</v>
       </c>
@@ -2772,7 +2693,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E25" s="11">
         <v>68</v>
@@ -2784,18 +2705,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>5</v>
@@ -2804,7 +2722,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E26" s="11">
         <v>68</v>
@@ -2816,18 +2734,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I26" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>5</v>
@@ -2836,7 +2751,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E27" s="11">
         <v>68</v>
@@ -2848,18 +2763,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>5</v>
@@ -2868,7 +2780,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E28" s="11">
         <v>69</v>
@@ -2880,18 +2792,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>5</v>
@@ -2900,7 +2809,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E29" s="11">
         <v>69</v>
@@ -2912,16 +2821,13 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J29" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -2932,7 +2838,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E30" s="11">
         <v>69</v>
@@ -2944,18 +2850,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>6</v>
@@ -2964,28 +2867,25 @@
         <v>21</v>
       </c>
       <c r="D31" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F31" s="11">
         <v>48</v>
       </c>
       <c r="G31" s="13"/>
       <c r="H31" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>6</v>
@@ -2994,28 +2894,25 @@
         <v>21</v>
       </c>
       <c r="D32" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F32" s="11">
         <v>48</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J32" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>6</v>
@@ -3024,28 +2921,25 @@
         <v>21</v>
       </c>
       <c r="D33" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F33" s="11">
         <v>48</v>
       </c>
       <c r="G33" s="13"/>
       <c r="H33" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J33" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>6</v>
@@ -3054,28 +2948,25 @@
         <v>21</v>
       </c>
       <c r="D34" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F34" s="11">
         <v>48</v>
       </c>
       <c r="G34" s="13"/>
       <c r="H34" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J34" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>6</v>
@@ -3084,28 +2975,25 @@
         <v>21</v>
       </c>
       <c r="D35" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F35" s="11">
         <v>48</v>
       </c>
       <c r="G35" s="13"/>
       <c r="H35" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I35" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>6</v>
@@ -3114,28 +3002,25 @@
         <v>21</v>
       </c>
       <c r="D36" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F36" s="11">
         <v>48</v>
       </c>
       <c r="G36" s="13"/>
       <c r="H36" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>6</v>
@@ -3144,7 +3029,7 @@
         <v>21</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E37" s="11">
         <v>15</v>
@@ -3156,18 +3041,15 @@
         <v>0.3125</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>6</v>
@@ -3176,7 +3058,7 @@
         <v>21</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E38" s="11">
         <v>19</v>
@@ -3188,18 +3070,15 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>6</v>
@@ -3208,7 +3087,7 @@
         <v>21</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E39" s="11">
         <v>19</v>
@@ -3220,16 +3099,13 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>30</v>
       </c>
@@ -3240,7 +3116,7 @@
         <v>21</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E40" s="11">
         <v>21</v>
@@ -3252,18 +3128,15 @@
         <v>0.4375</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J40" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>6</v>
@@ -3272,7 +3145,7 @@
         <v>21</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E41" s="11">
         <v>21</v>
@@ -3284,18 +3157,15 @@
         <v>0.4375</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I41" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>6</v>
@@ -3304,7 +3174,7 @@
         <v>21</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E42" s="11">
         <v>21</v>
@@ -3316,18 +3186,15 @@
         <v>0.4375</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>6</v>
@@ -3336,7 +3203,7 @@
         <v>21</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E43" s="11">
         <v>21</v>
@@ -3348,18 +3215,15 @@
         <v>0.4375</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>6</v>
@@ -3368,7 +3232,7 @@
         <v>21</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E44" s="11">
         <v>21</v>
@@ -3380,16 +3244,13 @@
         <v>0.4375</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J44" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>29</v>
       </c>
@@ -3400,7 +3261,7 @@
         <v>21</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E45" s="11">
         <v>21</v>
@@ -3412,18 +3273,15 @@
         <v>0.4375</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>7</v>
@@ -3432,7 +3290,7 @@
         <v>22</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E46" s="11">
         <v>83</v>
@@ -3444,18 +3302,15 @@
         <v>0.8383838383838383</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J46" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>7</v>
@@ -3464,7 +3319,7 @@
         <v>22</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E47" s="11">
         <v>70</v>
@@ -3476,18 +3331,15 @@
         <v>0.6194690265486725</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>7</v>
@@ -3496,7 +3348,7 @@
         <v>22</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E48" s="11">
         <v>70</v>
@@ -3508,16 +3360,13 @@
         <v>0.6194690265486725</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J48" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>30</v>
       </c>
@@ -3528,7 +3377,7 @@
         <v>22</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E49" s="11">
         <v>71</v>
@@ -3540,18 +3389,15 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>7</v>
@@ -3560,7 +3406,7 @@
         <v>22</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E50" s="11">
         <v>71</v>
@@ -3572,18 +3418,15 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I50" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>7</v>
@@ -3592,7 +3435,7 @@
         <v>22</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E51" s="11">
         <v>71</v>
@@ -3604,18 +3447,15 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>7</v>
@@ -3624,7 +3464,7 @@
         <v>22</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E52" s="11">
         <v>71</v>
@@ -3636,18 +3476,15 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J52" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>7</v>
@@ -3656,7 +3493,7 @@
         <v>22</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E53" s="11">
         <v>71</v>
@@ -3668,16 +3505,13 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>29</v>
       </c>
@@ -3688,7 +3522,7 @@
         <v>22</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E54" s="11">
         <v>71</v>
@@ -3700,18 +3534,15 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>8</v>
@@ -3720,7 +3551,7 @@
         <v>23</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E55" s="11">
         <v>45</v>
@@ -3732,18 +3563,15 @@
         <v>0.9782608695652174</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I55" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J55" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>8</v>
@@ -3752,7 +3580,7 @@
         <v>22</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E56" s="11">
         <v>47</v>
@@ -3764,18 +3592,15 @@
         <v>0.8392857142857143</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I56" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J56" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>8</v>
@@ -3784,7 +3609,7 @@
         <v>24</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E57" s="11">
         <v>13</v>
@@ -3796,18 +3621,15 @@
         <v>0.52</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I57" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J57" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>8</v>
@@ -3816,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E58" s="11">
         <v>3</v>
@@ -3828,18 +3650,15 @@
         <v>0.12</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J58" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>8</v>
@@ -3848,7 +3667,7 @@
         <v>23</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E59" s="11">
         <v>46</v>
@@ -3860,18 +3679,15 @@
         <v>1</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>8</v>
@@ -3880,7 +3696,7 @@
         <v>22</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E60" s="11">
         <v>56</v>
@@ -3892,18 +3708,15 @@
         <v>1</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J60" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>8</v>
@@ -3912,7 +3725,7 @@
         <v>24</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E61" s="11">
         <v>24</v>
@@ -3924,18 +3737,15 @@
         <v>0.96</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J61" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>8</v>
@@ -3944,7 +3754,7 @@
         <v>25</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E62" s="11">
         <v>7</v>
@@ -3956,18 +3766,15 @@
         <v>0.28</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J62" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>8</v>
@@ -3976,7 +3783,7 @@
         <v>23</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E63" s="11">
         <v>46</v>
@@ -3988,18 +3795,15 @@
         <v>1</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>8</v>
@@ -4008,7 +3812,7 @@
         <v>22</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E64" s="11">
         <v>56</v>
@@ -4020,18 +3824,15 @@
         <v>1</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J64" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>8</v>
@@ -4040,7 +3841,7 @@
         <v>24</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E65" s="11">
         <v>24</v>
@@ -4052,18 +3853,15 @@
         <v>0.96</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J65" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>8</v>
@@ -4072,7 +3870,7 @@
         <v>25</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E66" s="11">
         <v>8</v>
@@ -4084,16 +3882,13 @@
         <v>0.32</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J66" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>30</v>
       </c>
@@ -4104,7 +3899,7 @@
         <v>23</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E67" s="11">
         <v>46</v>
@@ -4116,16 +3911,13 @@
         <v>1</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J67" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
         <v>30</v>
       </c>
@@ -4136,7 +3928,7 @@
         <v>22</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E68" s="11">
         <v>56</v>
@@ -4148,16 +3940,13 @@
         <v>1</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J68" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
         <v>30</v>
       </c>
@@ -4168,7 +3957,7 @@
         <v>24</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E69" s="11">
         <v>24</v>
@@ -4180,16 +3969,13 @@
         <v>0.96</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J69" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>30</v>
       </c>
@@ -4200,7 +3986,7 @@
         <v>25</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E70" s="11">
         <v>10</v>
@@ -4212,18 +3998,15 @@
         <v>0.4</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J70" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>8</v>
@@ -4232,7 +4015,7 @@
         <v>23</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E71" s="11">
         <v>46</v>
@@ -4244,18 +4027,15 @@
         <v>1</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J71" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>8</v>
@@ -4264,7 +4044,7 @@
         <v>22</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E72" s="11">
         <v>56</v>
@@ -4276,18 +4056,15 @@
         <v>1</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J72" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>8</v>
@@ -4296,7 +4073,7 @@
         <v>24</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E73" s="11">
         <v>24</v>
@@ -4308,18 +4085,15 @@
         <v>0.96</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J73" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>8</v>
@@ -4328,7 +4102,7 @@
         <v>25</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E74" s="11">
         <v>10</v>
@@ -4340,18 +4114,15 @@
         <v>0.4</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I74" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J74" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>8</v>
@@ -4360,7 +4131,7 @@
         <v>23</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E75" s="11">
         <v>46</v>
@@ -4372,18 +4143,15 @@
         <v>1</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I75" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J75" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>8</v>
@@ -4392,7 +4160,7 @@
         <v>22</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E76" s="11">
         <v>56</v>
@@ -4404,18 +4172,15 @@
         <v>1</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I76" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J76" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>8</v>
@@ -4424,7 +4189,7 @@
         <v>24</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E77" s="11">
         <v>24</v>
@@ -4436,18 +4201,15 @@
         <v>0.96</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I77" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J77" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B78" s="11" t="s">
         <v>8</v>
@@ -4456,7 +4218,7 @@
         <v>25</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E78" s="11">
         <v>10</v>
@@ -4468,18 +4230,15 @@
         <v>0.4</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J78" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>8</v>
@@ -4488,7 +4247,7 @@
         <v>23</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E79" s="11">
         <v>46</v>
@@ -4500,18 +4259,15 @@
         <v>1</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J79" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>8</v>
@@ -4520,7 +4276,7 @@
         <v>22</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E80" s="11">
         <v>56</v>
@@ -4532,18 +4288,15 @@
         <v>1</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J80" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>8</v>
@@ -4552,7 +4305,7 @@
         <v>24</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E81" s="11">
         <v>24</v>
@@ -4564,18 +4317,15 @@
         <v>0.96</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J81" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>8</v>
@@ -4584,7 +4334,7 @@
         <v>25</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E82" s="11">
         <v>10</v>
@@ -4596,18 +4346,15 @@
         <v>0.4</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J82" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>8</v>
@@ -4616,7 +4363,7 @@
         <v>23</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E83" s="11">
         <v>46</v>
@@ -4628,18 +4375,15 @@
         <v>1</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J83" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>8</v>
@@ -4648,7 +4392,7 @@
         <v>22</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E84" s="11">
         <v>56</v>
@@ -4660,18 +4404,15 @@
         <v>1</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J84" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>8</v>
@@ -4680,7 +4421,7 @@
         <v>24</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E85" s="11">
         <v>24</v>
@@ -4692,18 +4433,15 @@
         <v>0.96</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J85" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>8</v>
@@ -4712,7 +4450,7 @@
         <v>25</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E86" s="11">
         <v>10</v>
@@ -4724,16 +4462,13 @@
         <v>0.4</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J86" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
         <v>29</v>
       </c>
@@ -4744,7 +4479,7 @@
         <v>23</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E87" s="11">
         <v>46</v>
@@ -4756,16 +4491,13 @@
         <v>1</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J87" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>29</v>
       </c>
@@ -4776,7 +4508,7 @@
         <v>22</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E88" s="11">
         <v>56</v>
@@ -4788,16 +4520,13 @@
         <v>1</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J88" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
         <v>29</v>
       </c>
@@ -4808,7 +4537,7 @@
         <v>24</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E89" s="11">
         <v>24</v>
@@ -4820,16 +4549,13 @@
         <v>0.96</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J89" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
         <v>29</v>
       </c>
@@ -4840,7 +4566,7 @@
         <v>25</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E90" s="11">
         <v>10</v>
@@ -4852,18 +4578,15 @@
         <v>0.4</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J90" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>9</v>
@@ -4872,7 +4595,7 @@
         <v>21</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E91" s="11">
         <v>87</v>
@@ -4884,18 +4607,15 @@
         <v>0.8787878787878788</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J91" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>9</v>
@@ -4904,7 +4624,7 @@
         <v>21</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E92" s="11">
         <v>77</v>
@@ -4916,18 +4636,15 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J92" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>9</v>
@@ -4936,7 +4653,7 @@
         <v>21</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E93" s="11">
         <v>77</v>
@@ -4948,16 +4665,13 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J93" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>30</v>
       </c>
@@ -4968,7 +4682,7 @@
         <v>21</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E94" s="11">
         <v>77</v>
@@ -4980,18 +4694,15 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J94" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>9</v>
@@ -5000,7 +4711,7 @@
         <v>21</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E95" s="11">
         <v>77</v>
@@ -5012,18 +4723,15 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I95" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J95" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>9</v>
@@ -5032,7 +4740,7 @@
         <v>21</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E96" s="11">
         <v>77</v>
@@ -5044,18 +4752,15 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J96" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>9</v>
@@ -5064,7 +4769,7 @@
         <v>21</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E97" s="11">
         <v>77</v>
@@ -5076,18 +4781,15 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J97" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>9</v>
@@ -5096,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E98" s="11">
         <v>77</v>
@@ -5108,16 +4810,13 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J98" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>29</v>
       </c>
@@ -5128,7 +4827,7 @@
         <v>21</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E99" s="11">
         <v>77</v>
@@ -5140,18 +4839,15 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H99" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="I99" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="I99" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J99" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="11" t="s">
-        <v>162</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>10</v>
@@ -5160,30 +4856,27 @@
         <v>20</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E100" s="11">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="F100" s="11">
         <v>111</v>
       </c>
       <c r="G100" s="14">
-        <v>0.9099099099099099</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="H100" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J100" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>10</v>
@@ -5192,30 +4885,27 @@
         <v>23</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E101" s="11">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="F101" s="11">
         <v>138</v>
       </c>
       <c r="G101" s="14">
-        <v>0.9492753623188406</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J101" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>10</v>
@@ -5224,30 +4914,27 @@
         <v>22</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E102" s="11">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F102" s="11">
         <v>81</v>
       </c>
       <c r="G102" s="14">
-        <v>0.9629629629629629</v>
+        <v>0.5432098765432098</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I102" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J102" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="B103" s="11" t="s">
         <v>10</v>
@@ -5256,30 +4943,27 @@
         <v>20</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E103" s="11">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F103" s="11">
         <v>111</v>
       </c>
       <c r="G103" s="14">
-        <v>0.5135135135135135</v>
+        <v>0.5585585585585585</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I103" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J103" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>10</v>
@@ -5288,30 +4972,27 @@
         <v>23</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E104" s="11">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F104" s="11">
         <v>138</v>
       </c>
       <c r="G104" s="14">
-        <v>0.6739130434782609</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I104" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J104" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>10</v>
@@ -5320,30 +5001,27 @@
         <v>22</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E105" s="11">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F105" s="11">
         <v>81</v>
       </c>
       <c r="G105" s="14">
-        <v>0.5432098765432098</v>
+        <v>0.6419753086419753</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J105" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>10</v>
@@ -5352,30 +5030,27 @@
         <v>20</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E106" s="11">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F106" s="11">
         <v>111</v>
       </c>
       <c r="G106" s="14">
-        <v>0.5585585585585585</v>
+        <v>0.9099099099099099</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J106" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B107" s="11" t="s">
         <v>10</v>
@@ -5384,30 +5059,27 @@
         <v>23</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E107" s="11">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="F107" s="11">
         <v>138</v>
       </c>
       <c r="G107" s="14">
-        <v>0.7101449275362319</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I107" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J107" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>10</v>
@@ -5416,30 +5088,27 @@
         <v>22</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E108" s="11">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F108" s="11">
         <v>81</v>
       </c>
       <c r="G108" s="14">
-        <v>0.6419753086419753</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I108" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J108" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B109" s="11" t="s">
         <v>10</v>
@@ -5448,7 +5117,7 @@
         <v>20</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E109" s="11">
         <v>102</v>
@@ -5460,18 +5129,15 @@
         <v>0.918918918918919</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I109" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J109" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>10</v>
@@ -5480,7 +5146,7 @@
         <v>23</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E110" s="11">
         <v>131</v>
@@ -5492,18 +5158,15 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I110" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J110" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>10</v>
@@ -5512,7 +5175,7 @@
         <v>22</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E111" s="11">
         <v>78</v>
@@ -5524,18 +5187,15 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I111" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J111" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>10</v>
@@ -5544,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E112" s="11">
         <v>102</v>
@@ -5556,18 +5216,15 @@
         <v>0.918918918918919</v>
       </c>
       <c r="H112" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I112" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J112" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>10</v>
@@ -5576,7 +5233,7 @@
         <v>23</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E113" s="11">
         <v>131</v>
@@ -5588,18 +5245,15 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I113" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J113" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B114" s="11" t="s">
         <v>10</v>
@@ -5608,7 +5262,7 @@
         <v>22</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E114" s="11">
         <v>78</v>
@@ -5620,16 +5274,13 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J114" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
         <v>30</v>
       </c>
@@ -5640,7 +5291,7 @@
         <v>20</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E115" s="11">
         <v>111</v>
@@ -5652,16 +5303,13 @@
         <v>1</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I115" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J115" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
         <v>30</v>
       </c>
@@ -5672,7 +5320,7 @@
         <v>23</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E116" s="11">
         <v>134</v>
@@ -5684,16 +5332,13 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H116" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J116" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>30</v>
       </c>
@@ -5704,7 +5349,7 @@
         <v>22</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E117" s="11">
         <v>79</v>
@@ -5716,18 +5361,15 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I117" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J117" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>10</v>
@@ -5736,7 +5378,7 @@
         <v>20</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E118" s="11">
         <v>111</v>
@@ -5748,18 +5390,15 @@
         <v>1</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I118" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J118" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>10</v>
@@ -5768,7 +5407,7 @@
         <v>23</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E119" s="11">
         <v>134</v>
@@ -5780,18 +5419,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I119" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J119" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B120" s="11" t="s">
         <v>10</v>
@@ -5800,7 +5436,7 @@
         <v>22</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E120" s="11">
         <v>79</v>
@@ -5812,18 +5448,15 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I120" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J120" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A121" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>10</v>
@@ -5832,7 +5465,7 @@
         <v>20</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E121" s="11">
         <v>111</v>
@@ -5844,18 +5477,15 @@
         <v>1</v>
       </c>
       <c r="H121" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I121" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J121" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B122" s="11" t="s">
         <v>10</v>
@@ -5864,7 +5494,7 @@
         <v>23</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E122" s="11">
         <v>134</v>
@@ -5876,18 +5506,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I122" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J122" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A123" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>10</v>
@@ -5896,7 +5523,7 @@
         <v>22</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E123" s="11">
         <v>79</v>
@@ -5908,18 +5535,15 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H123" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I123" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J123" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>10</v>
@@ -5928,7 +5552,7 @@
         <v>20</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E124" s="11">
         <v>111</v>
@@ -5940,18 +5564,15 @@
         <v>1</v>
       </c>
       <c r="H124" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J124" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>10</v>
@@ -5960,7 +5581,7 @@
         <v>23</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E125" s="11">
         <v>134</v>
@@ -5972,18 +5593,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H125" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I125" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J125" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>10</v>
@@ -5992,7 +5610,7 @@
         <v>22</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E126" s="11">
         <v>79</v>
@@ -6004,18 +5622,15 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H126" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J126" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>10</v>
@@ -6024,7 +5639,7 @@
         <v>20</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E127" s="11">
         <v>111</v>
@@ -6036,18 +5651,15 @@
         <v>1</v>
       </c>
       <c r="H127" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J127" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B128" s="11" t="s">
         <v>10</v>
@@ -6056,7 +5668,7 @@
         <v>23</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E128" s="11">
         <v>134</v>
@@ -6068,18 +5680,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H128" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J128" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>10</v>
@@ -6088,7 +5697,7 @@
         <v>22</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E129" s="11">
         <v>79</v>
@@ -6100,16 +5709,13 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J129" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>29</v>
       </c>
@@ -6120,7 +5726,7 @@
         <v>20</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E130" s="11">
         <v>111</v>
@@ -6132,16 +5738,13 @@
         <v>1</v>
       </c>
       <c r="H130" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J130" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>29</v>
       </c>
@@ -6152,7 +5755,7 @@
         <v>23</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E131" s="11">
         <v>134</v>
@@ -6164,16 +5767,13 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I131" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J131" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
         <v>29</v>
       </c>
@@ -6184,7 +5784,7 @@
         <v>22</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E132" s="11">
         <v>79</v>
@@ -6196,146 +5796,131 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I132" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J132" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="B133" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E133" s="11">
-        <v>3</v>
-      </c>
-      <c r="F133" s="11">
-        <v>26</v>
-      </c>
-      <c r="G133" s="14">
-        <v>0.11538461538461539</v>
+        <v>113</v>
+      </c>
+      <c r="E133" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F133" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G133" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I133" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J133" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="B134" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E134" s="11">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="F134" s="11">
+        <v>26</v>
+      </c>
+      <c r="G134" s="14">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="H134" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="I134" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="G134" s="14">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="H134" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="I134" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J134" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="11" t="s">
-        <v>162</v>
       </c>
       <c r="B135" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E135" s="11">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="F135" s="11">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="G135" s="14">
-        <v>0.16346153846153846</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I135" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J135" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E136" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="F136" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G136" s="11" t="s">
-        <v>96</v>
+        <v>101</v>
+      </c>
+      <c r="E136" s="11">
+        <v>17</v>
+      </c>
+      <c r="F136" s="11">
+        <v>104</v>
+      </c>
+      <c r="G136" s="14">
+        <v>0.16346153846153846</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I136" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J136" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>11</v>
@@ -6344,7 +5929,7 @@
         <v>20</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E137" s="11">
         <v>17</v>
@@ -6356,18 +5941,15 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I137" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J137" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B138" s="11" t="s">
         <v>11</v>
@@ -6376,7 +5958,7 @@
         <v>23</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E138" s="11">
         <v>111</v>
@@ -6388,18 +5970,15 @@
         <v>0.8809523809523809</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I138" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J138" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>11</v>
@@ -6408,7 +5987,7 @@
         <v>22</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E139" s="11">
         <v>71</v>
@@ -6420,18 +5999,15 @@
         <v>0.6826923076923077</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I139" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J139" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B140" s="11" t="s">
         <v>11</v>
@@ -6440,7 +6016,7 @@
         <v>20</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E140" s="11">
         <v>17</v>
@@ -6452,18 +6028,15 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I140" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J140" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B141" s="11" t="s">
         <v>11</v>
@@ -6472,7 +6045,7 @@
         <v>23</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E141" s="11">
         <v>116</v>
@@ -6484,18 +6057,15 @@
         <v>0.9206349206349206</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I141" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J141" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B142" s="11" t="s">
         <v>11</v>
@@ -6504,7 +6074,7 @@
         <v>22</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E142" s="11">
         <v>89</v>
@@ -6516,16 +6086,13 @@
         <v>0.8557692307692307</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J142" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
         <v>30</v>
       </c>
@@ -6536,7 +6103,7 @@
         <v>20</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E143" s="11">
         <v>23</v>
@@ -6548,16 +6115,13 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I143" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J143" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
         <v>30</v>
       </c>
@@ -6568,7 +6132,7 @@
         <v>23</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E144" s="11">
         <v>124</v>
@@ -6580,16 +6144,13 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H144" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J144" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>30</v>
       </c>
@@ -6600,7 +6161,7 @@
         <v>22</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E145" s="11">
         <v>98</v>
@@ -6612,18 +6173,15 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H145" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I145" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J145" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>11</v>
@@ -6632,7 +6190,7 @@
         <v>20</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E146" s="11">
         <v>23</v>
@@ -6644,18 +6202,15 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J146" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B147" s="11" t="s">
         <v>11</v>
@@ -6664,7 +6219,7 @@
         <v>23</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E147" s="11">
         <v>124</v>
@@ -6676,18 +6231,15 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H147" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I147" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J147" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B148" s="11" t="s">
         <v>11</v>
@@ -6696,7 +6248,7 @@
         <v>22</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E148" s="11">
         <v>98</v>
@@ -6708,18 +6260,15 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H148" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I148" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J148" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>11</v>
@@ -6728,7 +6277,7 @@
         <v>20</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E149" s="11">
         <v>23</v>
@@ -6740,18 +6289,15 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H149" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I149" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J149" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>11</v>
@@ -6760,7 +6306,7 @@
         <v>23</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E150" s="11">
         <v>124</v>
@@ -6772,18 +6318,15 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H150" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I150" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J150" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>11</v>
@@ -6792,7 +6335,7 @@
         <v>22</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E151" s="11">
         <v>98</v>
@@ -6804,18 +6347,15 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H151" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I151" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J151" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B152" s="11" t="s">
         <v>11</v>
@@ -6824,7 +6364,7 @@
         <v>20</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E152" s="11">
         <v>23</v>
@@ -6836,18 +6376,15 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H152" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I152" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J152" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B153" s="11" t="s">
         <v>11</v>
@@ -6856,7 +6393,7 @@
         <v>23</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E153" s="11">
         <v>124</v>
@@ -6868,18 +6405,15 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H153" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I153" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J153" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B154" s="11" t="s">
         <v>11</v>
@@ -6888,7 +6422,7 @@
         <v>22</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E154" s="11">
         <v>98</v>
@@ -6900,18 +6434,15 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H154" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I154" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J154" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>11</v>
@@ -6920,7 +6451,7 @@
         <v>20</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E155" s="11">
         <v>23</v>
@@ -6932,18 +6463,15 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H155" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I155" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J155" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B156" s="11" t="s">
         <v>11</v>
@@ -6952,7 +6480,7 @@
         <v>23</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E156" s="11">
         <v>124</v>
@@ -6964,18 +6492,15 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H156" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I156" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J156" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>11</v>
@@ -6984,7 +6509,7 @@
         <v>22</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E157" s="11">
         <v>98</v>
@@ -6996,16 +6521,13 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H157" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I157" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J157" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>29</v>
       </c>
@@ -7016,7 +6538,7 @@
         <v>20</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E158" s="11">
         <v>23</v>
@@ -7028,16 +6550,13 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H158" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I158" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J158" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>29</v>
       </c>
@@ -7048,7 +6567,7 @@
         <v>23</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E159" s="11">
         <v>124</v>
@@ -7060,16 +6579,13 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H159" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I159" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J159" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
         <v>29</v>
       </c>
@@ -7080,7 +6596,7 @@
         <v>22</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E160" s="11">
         <v>98</v>
@@ -7092,18 +6608,15 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H160" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I160" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J160" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B161" s="11" t="s">
         <v>12</v>
@@ -7112,7 +6625,7 @@
         <v>20</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E161" s="11">
         <v>16</v>
@@ -7124,18 +6637,15 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="H161" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I161" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J161" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B162" s="11" t="s">
         <v>12</v>
@@ -7144,7 +6654,7 @@
         <v>23</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E162" s="11">
         <v>39</v>
@@ -7156,18 +6666,15 @@
         <v>0.4588235294117647</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I162" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J162" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B163" s="11" t="s">
         <v>12</v>
@@ -7176,7 +6683,7 @@
         <v>22</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E163" s="11">
         <v>11</v>
@@ -7188,16 +6695,13 @@
         <v>0.10784313725490197</v>
       </c>
       <c r="H163" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I163" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J163" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
         <v>30</v>
       </c>
@@ -7208,7 +6712,7 @@
         <v>20</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E164" s="11">
         <v>29</v>
@@ -7220,16 +6724,13 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H164" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I164" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J164" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
         <v>30</v>
       </c>
@@ -7240,7 +6741,7 @@
         <v>23</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E165" s="11">
         <v>63</v>
@@ -7252,16 +6753,13 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H165" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I165" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J165" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
         <v>30</v>
       </c>
@@ -7272,7 +6770,7 @@
         <v>22</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E166" s="11">
         <v>22</v>
@@ -7284,18 +6782,15 @@
         <v>0.21568627450980393</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I166" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J166" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B167" s="11" t="s">
         <v>12</v>
@@ -7304,7 +6799,7 @@
         <v>20</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E167" s="11">
         <v>29</v>
@@ -7316,18 +6811,15 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H167" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I167" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J167" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>12</v>
@@ -7336,7 +6828,7 @@
         <v>23</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E168" s="11">
         <v>63</v>
@@ -7348,18 +6840,15 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H168" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I168" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J168" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B169" s="11" t="s">
         <v>12</v>
@@ -7368,7 +6857,7 @@
         <v>22</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E169" s="11">
         <v>23</v>
@@ -7380,18 +6869,15 @@
         <v>0.22549019607843138</v>
       </c>
       <c r="H169" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I169" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J169" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>12</v>
@@ -7400,7 +6886,7 @@
         <v>20</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E170" s="11">
         <v>29</v>
@@ -7412,18 +6898,15 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H170" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I170" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J170" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B171" s="11" t="s">
         <v>12</v>
@@ -7432,7 +6915,7 @@
         <v>23</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E171" s="11">
         <v>63</v>
@@ -7444,18 +6927,15 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H171" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I171" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J171" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B172" s="11" t="s">
         <v>12</v>
@@ -7464,7 +6944,7 @@
         <v>22</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E172" s="11">
         <v>23</v>
@@ -7476,18 +6956,15 @@
         <v>0.22549019607843138</v>
       </c>
       <c r="H172" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I172" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J172" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B173" s="11" t="s">
         <v>12</v>
@@ -7496,7 +6973,7 @@
         <v>20</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E173" s="11">
         <v>29</v>
@@ -7508,18 +6985,15 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H173" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I173" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J173" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B174" s="11" t="s">
         <v>12</v>
@@ -7528,7 +7002,7 @@
         <v>23</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E174" s="11">
         <v>65</v>
@@ -7540,18 +7014,15 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H174" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I174" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J174" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B175" s="11" t="s">
         <v>12</v>
@@ -7560,7 +7031,7 @@
         <v>22</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E175" s="11">
         <v>24</v>
@@ -7572,18 +7043,15 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H175" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I175" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J175" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B176" s="11" t="s">
         <v>12</v>
@@ -7592,7 +7060,7 @@
         <v>20</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E176" s="11">
         <v>29</v>
@@ -7604,18 +7072,15 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H176" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I176" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J176" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B177" s="11" t="s">
         <v>12</v>
@@ -7624,7 +7089,7 @@
         <v>23</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E177" s="11">
         <v>65</v>
@@ -7636,18 +7101,15 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H177" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I177" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J177" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B178" s="11" t="s">
         <v>12</v>
@@ -7656,7 +7118,7 @@
         <v>22</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E178" s="11">
         <v>24</v>
@@ -7668,16 +7130,13 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H178" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I178" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J178" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>29</v>
       </c>
@@ -7688,7 +7147,7 @@
         <v>20</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E179" s="11">
         <v>29</v>
@@ -7700,16 +7159,13 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H179" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I179" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J179" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>29</v>
       </c>
@@ -7720,7 +7176,7 @@
         <v>23</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E180" s="11">
         <v>65</v>
@@ -7732,16 +7188,13 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H180" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I180" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J180" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>29</v>
       </c>
@@ -7752,7 +7205,7 @@
         <v>22</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E181" s="11">
         <v>24</v>
@@ -7764,48 +7217,42 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H181" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I181" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J181" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B182" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C182" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D182" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D182" s="11" t="s">
-        <v>114</v>
-      </c>
       <c r="E182" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G182" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H182" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I182" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J182" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
         <v>30</v>
       </c>
@@ -7813,65 +7260,59 @@
         <v>13</v>
       </c>
       <c r="C183" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D183" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D183" s="11" t="s">
-        <v>114</v>
-      </c>
       <c r="E183" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G183" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H183" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I183" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J183" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A184" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C184" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D184" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D184" s="11" t="s">
-        <v>114</v>
-      </c>
       <c r="E184" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G184" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H184" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I184" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J184" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B185" s="11" t="s">
         <v>14</v>
@@ -7880,7 +7321,7 @@
         <v>22</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E185" s="11">
         <v>24</v>
@@ -7892,18 +7333,15 @@
         <v>0.17647058823529413</v>
       </c>
       <c r="H185" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I185" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J185" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B186" s="11" t="s">
         <v>14</v>
@@ -7912,7 +7350,7 @@
         <v>22</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E186" s="11">
         <v>30</v>
@@ -7924,16 +7362,13 @@
         <v>0.22058823529411764</v>
       </c>
       <c r="H186" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I186" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J186" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>30</v>
       </c>
@@ -7944,7 +7379,7 @@
         <v>22</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E187" s="11">
         <v>45</v>
@@ -7956,18 +7391,15 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H187" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I187" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J187" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B188" s="11" t="s">
         <v>14</v>
@@ -7976,7 +7408,7 @@
         <v>22</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E188" s="11">
         <v>45</v>
@@ -7988,18 +7420,15 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H188" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I188" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J188" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A189" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B189" s="11" t="s">
         <v>14</v>
@@ -8008,7 +7437,7 @@
         <v>22</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E189" s="11">
         <v>45</v>
@@ -8020,18 +7449,15 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H189" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I189" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J189" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B190" s="11" t="s">
         <v>14</v>
@@ -8040,7 +7466,7 @@
         <v>22</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E190" s="11">
         <v>45</v>
@@ -8052,18 +7478,15 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H190" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I190" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J190" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B191" s="11" t="s">
         <v>14</v>
@@ -8072,7 +7495,7 @@
         <v>22</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E191" s="11">
         <v>45</v>
@@ -8084,16 +7507,13 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H191" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I191" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J191" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="11" t="s">
         <v>29</v>
       </c>
@@ -8104,7 +7524,7 @@
         <v>22</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E192" s="11">
         <v>45</v>
@@ -8116,27 +7536,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H192" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I192" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J192" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="11" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B193" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E193" s="11">
         <v>81</v>
@@ -8148,18 +7565,15 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="H193" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I193" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J193" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B194" s="11" t="s">
         <v>15</v>
@@ -8168,7 +7582,7 @@
         <v>26</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E194" s="11">
         <v>1</v>
@@ -8180,27 +7594,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H194" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I194" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J194" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A195" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B195" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E195" s="11">
         <v>84</v>
@@ -8212,18 +7623,15 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="H195" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I195" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J195" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A196" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B196" s="11" t="s">
         <v>15</v>
@@ -8232,7 +7640,7 @@
         <v>26</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E196" s="11">
         <v>0</v>
@@ -8244,27 +7652,24 @@
         <v>0</v>
       </c>
       <c r="H196" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I196" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J196" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B197" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E197" s="11">
         <v>124</v>
@@ -8276,18 +7681,15 @@
         <v>0.656084656084656</v>
       </c>
       <c r="H197" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I197" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J197" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B198" s="11" t="s">
         <v>15</v>
@@ -8296,7 +7698,7 @@
         <v>26</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E198" s="11">
         <v>0</v>
@@ -8308,27 +7710,24 @@
         <v>0</v>
       </c>
       <c r="H198" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I198" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J198" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B199" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D199" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E199" s="11">
         <v>148</v>
@@ -8340,18 +7739,15 @@
         <v>0.783068783068783</v>
       </c>
       <c r="H199" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I199" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J199" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B200" s="11" t="s">
         <v>15</v>
@@ -8360,7 +7756,7 @@
         <v>26</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E200" s="11">
         <v>1</v>
@@ -8372,27 +7768,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H200" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I200" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J200" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B201" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E201" s="11">
         <v>154</v>
@@ -8404,18 +7797,15 @@
         <v>0.8148148148148148</v>
       </c>
       <c r="H201" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I201" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J201" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B202" s="11" t="s">
         <v>15</v>
@@ -8424,7 +7814,7 @@
         <v>26</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E202" s="11">
         <v>1</v>
@@ -8436,16 +7826,13 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H202" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I202" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J202" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="11" t="s">
         <v>30</v>
       </c>
@@ -8456,7 +7843,7 @@
         <v>27</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E203" s="11">
         <v>160</v>
@@ -8468,16 +7855,13 @@
         <v>0.5194805194805194</v>
       </c>
       <c r="H203" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I203" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J203" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="11" t="s">
         <v>30</v>
       </c>
@@ -8488,7 +7872,7 @@
         <v>26</v>
       </c>
       <c r="D204" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E204" s="11">
         <v>1</v>
@@ -8500,18 +7884,15 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H204" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I204" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J204" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B205" s="11" t="s">
         <v>15</v>
@@ -8520,7 +7901,7 @@
         <v>26</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E205" s="11">
         <v>1</v>
@@ -8532,18 +7913,15 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H205" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I205" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J205" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>15</v>
@@ -8552,7 +7930,7 @@
         <v>27</v>
       </c>
       <c r="D206" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E206" s="11">
         <v>161</v>
@@ -8564,18 +7942,15 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H206" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I206" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J206" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A207" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B207" s="11" t="s">
         <v>15</v>
@@ -8584,7 +7959,7 @@
         <v>26</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E207" s="11">
         <v>1</v>
@@ -8596,18 +7971,15 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H207" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I207" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J207" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A208" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B208" s="11" t="s">
         <v>15</v>
@@ -8616,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="D208" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E208" s="11">
         <v>161</v>
@@ -8628,18 +8000,15 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H208" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I208" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J208" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B209" s="11" t="s">
         <v>15</v>
@@ -8648,7 +8017,7 @@
         <v>26</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E209" s="11">
         <v>1</v>
@@ -8660,18 +8029,15 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H209" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I209" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J209" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B210" s="11" t="s">
         <v>15</v>
@@ -8680,7 +8046,7 @@
         <v>27</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E210" s="11">
         <v>161</v>
@@ -8692,18 +8058,15 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H210" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I210" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J210" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B211" s="11" t="s">
         <v>15</v>
@@ -8712,7 +8075,7 @@
         <v>26</v>
       </c>
       <c r="D211" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E211" s="11">
         <v>1</v>
@@ -8724,18 +8087,15 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H211" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I211" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J211" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B212" s="11" t="s">
         <v>15</v>
@@ -8744,7 +8104,7 @@
         <v>27</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E212" s="11">
         <v>161</v>
@@ -8756,16 +8116,13 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H212" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I212" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J212" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
         <v>29</v>
       </c>
@@ -8776,7 +8133,7 @@
         <v>26</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E213" s="11">
         <v>1</v>
@@ -8788,16 +8145,13 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H213" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I213" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J213" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
         <v>29</v>
       </c>
@@ -8808,7 +8162,7 @@
         <v>27</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E214" s="11">
         <v>161</v>
@@ -8820,18 +8174,15 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H214" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I214" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J214" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B215" s="11" t="s">
         <v>16</v>
@@ -8840,7 +8191,7 @@
         <v>23</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E215" s="11">
         <v>9</v>
@@ -8852,18 +8203,15 @@
         <v>0.06040268456375839</v>
       </c>
       <c r="H215" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I215" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J215" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>16</v>
@@ -8872,7 +8220,7 @@
         <v>23</v>
       </c>
       <c r="D216" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E216" s="11">
         <v>21</v>
@@ -8884,18 +8232,15 @@
         <v>0.14093959731543623</v>
       </c>
       <c r="H216" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I216" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J216" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A217" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B217" s="11" t="s">
         <v>16</v>
@@ -8904,7 +8249,7 @@
         <v>23</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E217" s="11">
         <v>23</v>
@@ -8916,18 +8261,15 @@
         <v>0.15436241610738255</v>
       </c>
       <c r="H217" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I217" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J217" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>16</v>
@@ -8936,7 +8278,7 @@
         <v>23</v>
       </c>
       <c r="D218" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E218" s="11">
         <v>31</v>
@@ -8948,18 +8290,15 @@
         <v>0.2080536912751678</v>
       </c>
       <c r="H218" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I218" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J218" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B219" s="11" t="s">
         <v>16</v>
@@ -8968,7 +8307,7 @@
         <v>23</v>
       </c>
       <c r="D219" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E219" s="11">
         <v>34</v>
@@ -8980,16 +8319,13 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H219" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I219" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J219" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>30</v>
       </c>
@@ -9000,7 +8336,7 @@
         <v>23</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E220" s="11">
         <v>34</v>
@@ -9012,18 +8348,15 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H220" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J220" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B221" s="11" t="s">
         <v>16</v>
@@ -9032,7 +8365,7 @@
         <v>23</v>
       </c>
       <c r="D221" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E221" s="11">
         <v>34</v>
@@ -9044,18 +8377,15 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H221" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I221" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="J221" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A222" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>16</v>
@@ -9064,7 +8394,7 @@
         <v>23</v>
       </c>
       <c r="D222" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E222" s="11">
         <v>34</v>
@@ -9076,18 +8406,15 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H222" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I222" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J222" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B223" s="11" t="s">
         <v>16</v>
@@ -9096,7 +8423,7 @@
         <v>23</v>
       </c>
       <c r="D223" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E223" s="11">
         <v>34</v>
@@ -9108,18 +8435,15 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H223" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I223" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J223" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>16</v>
@@ -9128,7 +8452,7 @@
         <v>23</v>
       </c>
       <c r="D224" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E224" s="11">
         <v>34</v>
@@ -9140,16 +8464,13 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H224" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I224" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J224" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
         <v>29</v>
       </c>
@@ -9160,7 +8481,7 @@
         <v>23</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E225" s="11">
         <v>34</v>
@@ -9172,17 +8493,14 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H225" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I225" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J225" s="12" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J225"/>
+  <autoFilter ref="A1:I225"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -9199,10 +8517,10 @@
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9210,23 +8528,23 @@
         <v>77</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9234,23 +8552,23 @@
         <v>81</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="246">
   <si>
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
@@ -81,379 +81,403 @@
     <t>22' x 70'</t>
   </si>
   <si>
+    <t>Group 57513</t>
+  </si>
+  <si>
+    <t>Group 57514</t>
+  </si>
+  <si>
+    <t>Group 57515</t>
+  </si>
+  <si>
+    <t>Group 57516</t>
+  </si>
+  <si>
+    <t>Group 1</t>
+  </si>
+  <si>
+    <t>Group 2</t>
+  </si>
+  <si>
+    <t>Group 3</t>
+  </si>
+  <si>
+    <t>Rumah teres only</t>
+  </si>
+  <si>
+    <t>Group A · front-kitchen layout</t>
+  </si>
+  <si>
+    <t>Group B · rear-kitchen layout</t>
+  </si>
+  <si>
+    <t>20' x 65'</t>
+  </si>
+  <si>
+    <t>Latest record</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>Sales Unit · latest</t>
+  </si>
+  <si>
+    <t>74 / 81</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>69 / 113</t>
+  </si>
+  <si>
+    <t>21 / 48</t>
+  </si>
+  <si>
+    <t>71 / 113</t>
+  </si>
+  <si>
+    <t>46 / 46</t>
+  </si>
+  <si>
+    <t>56 / 56</t>
+  </si>
+  <si>
+    <t>24 / 25</t>
+  </si>
+  <si>
+    <t>10 / 25</t>
+  </si>
+  <si>
+    <t>77 / 99</t>
+  </si>
+  <si>
+    <t>111 / 111</t>
+  </si>
+  <si>
+    <t>134 / 138</t>
+  </si>
+  <si>
+    <t>79 / 81</t>
+  </si>
+  <si>
+    <t>23 / 26</t>
+  </si>
+  <si>
+    <t>124 / 126</t>
+  </si>
+  <si>
+    <t>98 / 104</t>
+  </si>
+  <si>
+    <t>29 / 44</t>
+  </si>
+  <si>
+    <t>65 / 85</t>
+  </si>
+  <si>
+    <t>24 / 102</t>
+  </si>
+  <si>
+    <t>45 / 136</t>
+  </si>
+  <si>
+    <t>1 / 27</t>
+  </si>
+  <si>
+    <t>161 / 308</t>
+  </si>
+  <si>
+    <t>34 / 149</t>
+  </si>
+  <si>
+    <t>Sales Status · latest</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>Yet to launch</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>44%</t>
+  </si>
+  <si>
+    <t>63%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>78%</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>98%</t>
+  </si>
+  <si>
+    <t>88%</t>
+  </si>
+  <si>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>66%</t>
+  </si>
+  <si>
+    <t>76%</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>Yet to sign</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>4%</t>
+  </si>
+  <si>
+    <t>52%</t>
+  </si>
+  <si>
+    <t>23%</t>
+  </si>
+  <si>
+    <t>Weekly baseline</t>
+  </si>
+  <si>
+    <t>No record 7–14 days earlier</t>
+  </si>
+  <si>
+    <t>Sales Unit · baseline</t>
+  </si>
+  <si>
+    <t>Sales Status · baseline</t>
+  </si>
+  <si>
+    <t>Weekly Change</t>
+  </si>
+  <si>
+    <t>Insufficient weekly history</t>
+  </si>
+  <si>
+    <t>No signed status yet</t>
+  </si>
+  <si>
+    <t>Record Date</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Unit Group / Layout</t>
+  </si>
+  <si>
+    <t>Status Type</t>
+  </si>
+  <si>
+    <t>Signed Units</t>
+  </si>
+  <si>
+    <t>Total Units</t>
+  </si>
+  <si>
+    <t>Signed %</t>
+  </si>
+  <si>
+    <t>Raw Recorded Status</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>17/03/2025</t>
+  </si>
+  <si>
+    <t>Booked</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>11% Booked (9/81 units)</t>
+  </si>
+  <si>
+    <t>Embedded historical record</t>
+  </si>
+  <si>
+    <t>06/10/2025</t>
+  </si>
+  <si>
+    <t>35% Booked (28/81 units)</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>Signed</t>
+  </si>
+  <si>
+    <t>59% Signed (48/81 units)</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>65% Signed (53/81 units)</t>
+  </si>
+  <si>
+    <t>88% Signed (72/81 units)</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>74/81 signed</t>
+  </si>
+  <si>
+    <t>Saved TEDUH record</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>18/10/2026</t>
+  </si>
+  <si>
+    <t>No group details</t>
+  </si>
+  <si>
+    <t>Unclassified</t>
+  </si>
+  <si>
+    <t>No parseable group-level values: Yet to Launch</t>
+  </si>
+  <si>
+    <t>01/08/2024</t>
+  </si>
+  <si>
+    <t>33% Booked (37/113 units)</t>
+  </si>
+  <si>
+    <t>17/10/2024</t>
+  </si>
+  <si>
+    <t>31% Booked (35/113 units)</t>
+  </si>
+  <si>
+    <t>29/11/2024</t>
+  </si>
+  <si>
+    <t>19% Booked (21/113 units)</t>
+  </si>
+  <si>
+    <t>25% Booked (28/113 units)</t>
+  </si>
+  <si>
+    <t>20/08/2025</t>
+  </si>
+  <si>
+    <t>30% Signed (34/113 units)</t>
+  </si>
+  <si>
+    <t>11/09/2025</t>
+  </si>
+  <si>
+    <t>33% Signed (37/113 units)</t>
+  </si>
+  <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>48% Signed (54/113 units)</t>
+  </si>
+  <si>
+    <t>56% Signed (63/113 units)</t>
+  </si>
+  <si>
+    <t>60% Signed (68/113 units)</t>
+  </si>
+  <si>
+    <t>68/113 signed</t>
+  </si>
+  <si>
+    <t>69/113 signed</t>
+  </si>
+  <si>
+    <t>8% Booked (4/48 units)</t>
+  </si>
+  <si>
+    <t>15% Booked (7/48 units)</t>
+  </si>
+  <si>
+    <t>50% Booked (24/48 units)</t>
+  </si>
+  <si>
+    <t>52% Booked (25/48 units)</t>
+  </si>
+  <si>
+    <t>31% Signed (15/48 units)</t>
+  </si>
+  <si>
+    <t>40% Signed (19/48 units)</t>
+  </si>
+  <si>
+    <t>44% Signed (21/48 units)</t>
+  </si>
+  <si>
+    <t>21/48 signed</t>
+  </si>
+  <si>
+    <t>74% Signed (83/99 units)</t>
+  </si>
+  <si>
+    <t>62% Signed (70/113 units)</t>
+  </si>
+  <si>
+    <t>63% Signed (71/113 units)</t>
+  </si>
+  <si>
+    <t>71/113 signed</t>
+  </si>
+  <si>
+    <t>98% Signed (45/46 units)</t>
+  </si>
+  <si>
     <t>20' x 70'</t>
   </si>
   <si>
-    <t>20' x 65'</t>
-  </si>
-  <si>
-    <t>20' x 75'</t>
-  </si>
-  <si>
-    <t>20' x 80'</t>
-  </si>
-  <si>
-    <t>Group A · front-kitchen layout</t>
-  </si>
-  <si>
-    <t>Group B · rear-kitchen layout</t>
-  </si>
-  <si>
-    <t>Latest record</t>
-  </si>
-  <si>
-    <t>19/10/2026</t>
-  </si>
-  <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>Sales Unit · latest</t>
-  </si>
-  <si>
-    <t>74 / 81</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>69 / 113</t>
-  </si>
-  <si>
-    <t>21 / 48</t>
-  </si>
-  <si>
-    <t>71 / 113</t>
-  </si>
-  <si>
-    <t>46 / 46</t>
-  </si>
-  <si>
-    <t>56 / 56</t>
-  </si>
-  <si>
-    <t>24 / 25</t>
-  </si>
-  <si>
-    <t>10 / 25</t>
-  </si>
-  <si>
-    <t>77 / 99</t>
-  </si>
-  <si>
-    <t>111 / 111</t>
-  </si>
-  <si>
-    <t>134 / 138</t>
-  </si>
-  <si>
-    <t>79 / 81</t>
-  </si>
-  <si>
-    <t>23 / 26</t>
-  </si>
-  <si>
-    <t>124 / 126</t>
-  </si>
-  <si>
-    <t>98 / 104</t>
-  </si>
-  <si>
-    <t>29 / 44</t>
-  </si>
-  <si>
-    <t>65 / 85</t>
-  </si>
-  <si>
-    <t>24 / 102</t>
-  </si>
-  <si>
-    <t>45 / 136</t>
-  </si>
-  <si>
-    <t>1 / 27</t>
-  </si>
-  <si>
-    <t>161 / 308</t>
-  </si>
-  <si>
-    <t>34 / 149</t>
-  </si>
-  <si>
-    <t>Sales Status · latest</t>
-  </si>
-  <si>
-    <t>91%</t>
-  </si>
-  <si>
-    <t>Yet to launch</t>
-  </si>
-  <si>
-    <t>61%</t>
-  </si>
-  <si>
-    <t>44%</t>
-  </si>
-  <si>
-    <t>63%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>96%</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>78%</t>
-  </si>
-  <si>
-    <t>97%</t>
-  </si>
-  <si>
-    <t>98%</t>
-  </si>
-  <si>
-    <t>88%</t>
-  </si>
-  <si>
-    <t>94%</t>
-  </si>
-  <si>
-    <t>66%</t>
-  </si>
-  <si>
-    <t>76%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>Yet to sign</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>52%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>Weekly baseline</t>
-  </si>
-  <si>
-    <t>No record 7–14 days earlier</t>
-  </si>
-  <si>
-    <t>Sales Unit · baseline</t>
-  </si>
-  <si>
-    <t>Sales Status · baseline</t>
-  </si>
-  <si>
-    <t>Weekly Change</t>
-  </si>
-  <si>
-    <t>Insufficient weekly history</t>
-  </si>
-  <si>
-    <t>No signed status yet</t>
-  </si>
-  <si>
-    <t>Record Date</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Unit Group / Layout</t>
-  </si>
-  <si>
-    <t>Status Type</t>
-  </si>
-  <si>
-    <t>Signed Units</t>
-  </si>
-  <si>
-    <t>Total Units</t>
-  </si>
-  <si>
-    <t>Signed %</t>
-  </si>
-  <si>
-    <t>Raw Recorded Status</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>17/03/2025</t>
-  </si>
-  <si>
-    <t>Booked</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>11% Booked (9/81 units)</t>
-  </si>
-  <si>
-    <t>Embedded historical record</t>
-  </si>
-  <si>
-    <t>06/10/2025</t>
-  </si>
-  <si>
-    <t>35% Booked (28/81 units)</t>
-  </si>
-  <si>
-    <t>08/06/2026</t>
-  </si>
-  <si>
-    <t>Signed</t>
-  </si>
-  <si>
-    <t>59% Signed (48/81 units)</t>
-  </si>
-  <si>
-    <t>10/07/2026</t>
-  </si>
-  <si>
-    <t>65% Signed (53/81 units)</t>
-  </si>
-  <si>
-    <t>88% Signed (72/81 units)</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>74/81 signed</t>
-  </si>
-  <si>
-    <t>Saved TEDUH record</t>
-  </si>
-  <si>
-    <t>16/10/2026</t>
-  </si>
-  <si>
-    <t>17/10/2026</t>
-  </si>
-  <si>
-    <t>18/10/2026</t>
-  </si>
-  <si>
-    <t>No group details</t>
-  </si>
-  <si>
-    <t>Unclassified</t>
-  </si>
-  <si>
-    <t>No parseable group-level values: Yet to Launch</t>
-  </si>
-  <si>
-    <t>01/08/2024</t>
-  </si>
-  <si>
-    <t>33% Booked (37/113 units)</t>
-  </si>
-  <si>
-    <t>17/10/2024</t>
-  </si>
-  <si>
-    <t>31% Booked (35/113 units)</t>
-  </si>
-  <si>
-    <t>29/11/2024</t>
-  </si>
-  <si>
-    <t>19% Booked (21/113 units)</t>
-  </si>
-  <si>
-    <t>25% Booked (28/113 units)</t>
-  </si>
-  <si>
-    <t>20/08/2025</t>
-  </si>
-  <si>
-    <t>30% Signed (34/113 units)</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
-  </si>
-  <si>
-    <t>33% Signed (37/113 units)</t>
-  </si>
-  <si>
-    <t>27/02/2026</t>
-  </si>
-  <si>
-    <t>48% Signed (54/113 units)</t>
-  </si>
-  <si>
-    <t>56% Signed (63/113 units)</t>
-  </si>
-  <si>
-    <t>60% Signed (68/113 units)</t>
-  </si>
-  <si>
-    <t>68/113 signed</t>
-  </si>
-  <si>
-    <t>69/113 signed</t>
-  </si>
-  <si>
-    <t>8% Booked (4/48 units)</t>
-  </si>
-  <si>
-    <t>15% Booked (7/48 units)</t>
-  </si>
-  <si>
-    <t>50% Booked (24/48 units)</t>
-  </si>
-  <si>
-    <t>52% Booked (25/48 units)</t>
-  </si>
-  <si>
-    <t>31% Signed (15/48 units)</t>
-  </si>
-  <si>
-    <t>40% Signed (19/48 units)</t>
-  </si>
-  <si>
-    <t>44% Signed (21/48 units)</t>
-  </si>
-  <si>
-    <t>21/48 signed</t>
-  </si>
-  <si>
-    <t>74% Signed (83/99 units)</t>
-  </si>
-  <si>
-    <t>62% Signed (70/113 units)</t>
-  </si>
-  <si>
-    <t>63% Signed (71/113 units)</t>
-  </si>
-  <si>
-    <t>71/113 signed</t>
-  </si>
-  <si>
-    <t>98% Signed (45/46 units)</t>
-  </si>
-  <si>
     <t>84% Signed (47/56 units)</t>
   </si>
   <si>
+    <t>Unmapped unit group 3 — verify TEDUH mapping</t>
+  </si>
+  <si>
     <t>52% Signed (13/25 units)</t>
+  </si>
+  <si>
+    <t>Unmapped unit group 4 — verify TEDUH mapping</t>
   </si>
   <si>
     <t>12% Signed (3/25 units)</t>
@@ -1370,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>24</v>
@@ -1385,588 +1409,588 @@
         <v>25</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="U5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="W6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="X6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Y6" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="U7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="T7" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="U7" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="V7" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="X7" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="Y7" s="6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="U8" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="W8" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="X8" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Y8" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="V10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="W10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="X10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="T12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="V12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="W12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="X12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Y12" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2000,36 +2024,36 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>3</v>
@@ -2038,25 +2062,25 @@
         <v>18</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F2" s="11">
         <v>81</v>
       </c>
       <c r="G2" s="13"/>
       <c r="H2" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>3</v>
@@ -2065,25 +2089,25 @@
         <v>18</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F3" s="11">
         <v>81</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>3</v>
@@ -2092,7 +2116,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E4" s="11">
         <v>48</v>
@@ -2104,15 +2128,15 @@
         <v>0.5925925925925926</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>3</v>
@@ -2121,7 +2145,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E5" s="11">
         <v>53</v>
@@ -2133,15 +2157,15 @@
         <v>0.654320987654321</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>3</v>
@@ -2150,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E6" s="11">
         <v>72</v>
@@ -2162,15 +2186,15 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>3</v>
@@ -2179,7 +2203,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E7" s="11">
         <v>74</v>
@@ -2191,15 +2215,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>3</v>
@@ -2208,7 +2232,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E8" s="11">
         <v>74</v>
@@ -2220,15 +2244,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>3</v>
@@ -2237,7 +2261,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E9" s="11">
         <v>74</v>
@@ -2249,15 +2273,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>3</v>
@@ -2266,7 +2290,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E10" s="11">
         <v>74</v>
@@ -2278,15 +2302,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>3</v>
@@ -2295,7 +2319,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E11" s="11">
         <v>74</v>
@@ -2307,102 +2331,102 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>5</v>
@@ -2411,25 +2435,25 @@
         <v>20</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F15" s="11">
         <v>113</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="12" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>5</v>
@@ -2438,25 +2462,25 @@
         <v>20</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F16" s="11">
         <v>113</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>5</v>
@@ -2465,25 +2489,25 @@
         <v>20</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F17" s="11">
         <v>113</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>5</v>
@@ -2492,25 +2516,25 @@
         <v>20</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F18" s="11">
         <v>113</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="12" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>5</v>
@@ -2519,7 +2543,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E19" s="11">
         <v>34</v>
@@ -2531,15 +2555,15 @@
         <v>0.3008849557522124</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>5</v>
@@ -2548,7 +2572,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E20" s="11">
         <v>37</v>
@@ -2560,15 +2584,15 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>5</v>
@@ -2577,7 +2601,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E21" s="11">
         <v>37</v>
@@ -2589,15 +2613,15 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>5</v>
@@ -2606,7 +2630,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E22" s="11">
         <v>54</v>
@@ -2618,15 +2642,15 @@
         <v>0.4778761061946903</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>5</v>
@@ -2635,7 +2659,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E23" s="11">
         <v>63</v>
@@ -2647,15 +2671,15 @@
         <v>0.5575221238938053</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>5</v>
@@ -2664,7 +2688,7 @@
         <v>20</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E24" s="11">
         <v>68</v>
@@ -2676,15 +2700,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>5</v>
@@ -2693,7 +2717,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E25" s="11">
         <v>68</v>
@@ -2705,15 +2729,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>5</v>
@@ -2722,7 +2746,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E26" s="11">
         <v>68</v>
@@ -2734,15 +2758,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>5</v>
@@ -2751,7 +2775,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E27" s="11">
         <v>68</v>
@@ -2763,15 +2787,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>5</v>
@@ -2780,7 +2804,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E28" s="11">
         <v>69</v>
@@ -2792,15 +2816,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>5</v>
@@ -2809,7 +2833,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E29" s="11">
         <v>69</v>
@@ -2821,15 +2845,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>5</v>
@@ -2838,7 +2862,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E30" s="11">
         <v>69</v>
@@ -2850,15 +2874,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>6</v>
@@ -2867,25 +2891,25 @@
         <v>21</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F31" s="11">
         <v>48</v>
       </c>
       <c r="G31" s="13"/>
       <c r="H31" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>6</v>
@@ -2894,25 +2918,25 @@
         <v>21</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F32" s="11">
         <v>48</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>6</v>
@@ -2921,25 +2945,25 @@
         <v>21</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F33" s="11">
         <v>48</v>
       </c>
       <c r="G33" s="13"/>
       <c r="H33" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>6</v>
@@ -2948,25 +2972,25 @@
         <v>21</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F34" s="11">
         <v>48</v>
       </c>
       <c r="G34" s="13"/>
       <c r="H34" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>6</v>
@@ -2975,25 +2999,25 @@
         <v>21</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F35" s="11">
         <v>48</v>
       </c>
       <c r="G35" s="13"/>
       <c r="H35" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>6</v>
@@ -3002,25 +3026,25 @@
         <v>21</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F36" s="11">
         <v>48</v>
       </c>
       <c r="G36" s="13"/>
       <c r="H36" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>6</v>
@@ -3029,7 +3053,7 @@
         <v>21</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E37" s="11">
         <v>15</v>
@@ -3041,15 +3065,15 @@
         <v>0.3125</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>6</v>
@@ -3058,7 +3082,7 @@
         <v>21</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E38" s="11">
         <v>19</v>
@@ -3070,15 +3094,15 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>6</v>
@@ -3087,7 +3111,7 @@
         <v>21</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E39" s="11">
         <v>19</v>
@@ -3099,15 +3123,15 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>6</v>
@@ -3116,7 +3140,7 @@
         <v>21</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E40" s="11">
         <v>21</v>
@@ -3128,15 +3152,15 @@
         <v>0.4375</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>6</v>
@@ -3145,7 +3169,7 @@
         <v>21</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E41" s="11">
         <v>21</v>
@@ -3157,15 +3181,15 @@
         <v>0.4375</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>6</v>
@@ -3174,7 +3198,7 @@
         <v>21</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E42" s="11">
         <v>21</v>
@@ -3186,15 +3210,15 @@
         <v>0.4375</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>6</v>
@@ -3203,7 +3227,7 @@
         <v>21</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E43" s="11">
         <v>21</v>
@@ -3215,15 +3239,15 @@
         <v>0.4375</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>6</v>
@@ -3232,7 +3256,7 @@
         <v>21</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E44" s="11">
         <v>21</v>
@@ -3244,15 +3268,15 @@
         <v>0.4375</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>6</v>
@@ -3261,7 +3285,7 @@
         <v>21</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E45" s="11">
         <v>21</v>
@@ -3273,24 +3297,24 @@
         <v>0.4375</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E46" s="11">
         <v>83</v>
@@ -3302,24 +3326,24 @@
         <v>0.8383838383838383</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E47" s="11">
         <v>70</v>
@@ -3331,24 +3355,24 @@
         <v>0.6194690265486725</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E48" s="11">
         <v>70</v>
@@ -3360,24 +3384,24 @@
         <v>0.6194690265486725</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E49" s="11">
         <v>71</v>
@@ -3389,24 +3413,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E50" s="11">
         <v>71</v>
@@ -3418,24 +3442,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E51" s="11">
         <v>71</v>
@@ -3447,24 +3471,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E52" s="11">
         <v>71</v>
@@ -3476,24 +3500,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E53" s="11">
         <v>71</v>
@@ -3505,24 +3529,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E54" s="11">
         <v>71</v>
@@ -3534,24 +3558,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E55" s="11">
         <v>45</v>
@@ -3563,24 +3587,24 @@
         <v>0.9782608695652174</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E56" s="11">
         <v>47</v>
@@ -3592,24 +3616,24 @@
         <v>0.8392857142857143</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E57" s="11">
         <v>13</v>
@@ -3621,24 +3645,24 @@
         <v>0.52</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E58" s="11">
         <v>3</v>
@@ -3650,24 +3674,24 @@
         <v>0.12</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E59" s="11">
         <v>46</v>
@@ -3679,24 +3703,24 @@
         <v>1</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E60" s="11">
         <v>56</v>
@@ -3708,24 +3732,24 @@
         <v>1</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E61" s="11">
         <v>24</v>
@@ -3737,24 +3761,24 @@
         <v>0.96</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E62" s="11">
         <v>7</v>
@@ -3766,24 +3790,24 @@
         <v>0.28</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E63" s="11">
         <v>46</v>
@@ -3795,24 +3819,24 @@
         <v>1</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E64" s="11">
         <v>56</v>
@@ -3824,24 +3848,24 @@
         <v>1</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E65" s="11">
         <v>24</v>
@@ -3853,24 +3877,24 @@
         <v>0.96</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E66" s="11">
         <v>8</v>
@@ -3882,24 +3906,24 @@
         <v>0.32</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E67" s="11">
         <v>46</v>
@@ -3911,24 +3935,24 @@
         <v>1</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E68" s="11">
         <v>56</v>
@@ -3940,24 +3964,24 @@
         <v>1</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E69" s="11">
         <v>24</v>
@@ -3969,24 +3993,24 @@
         <v>0.96</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E70" s="11">
         <v>10</v>
@@ -3998,24 +4022,24 @@
         <v>0.4</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E71" s="11">
         <v>46</v>
@@ -4027,24 +4051,24 @@
         <v>1</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E72" s="11">
         <v>56</v>
@@ -4056,15 +4080,15 @@
         <v>1</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>8</v>
@@ -4073,7 +4097,7 @@
         <v>24</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E73" s="11">
         <v>24</v>
@@ -4085,15 +4109,15 @@
         <v>0.96</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>8</v>
@@ -4102,7 +4126,7 @@
         <v>25</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E74" s="11">
         <v>10</v>
@@ -4114,24 +4138,24 @@
         <v>0.4</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E75" s="11">
         <v>46</v>
@@ -4143,24 +4167,24 @@
         <v>1</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E76" s="11">
         <v>56</v>
@@ -4172,15 +4196,15 @@
         <v>1</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>8</v>
@@ -4189,7 +4213,7 @@
         <v>24</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E77" s="11">
         <v>24</v>
@@ -4201,15 +4225,15 @@
         <v>0.96</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B78" s="11" t="s">
         <v>8</v>
@@ -4218,7 +4242,7 @@
         <v>25</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E78" s="11">
         <v>10</v>
@@ -4230,24 +4254,24 @@
         <v>0.4</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E79" s="11">
         <v>46</v>
@@ -4259,24 +4283,24 @@
         <v>1</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E80" s="11">
         <v>56</v>
@@ -4288,15 +4312,15 @@
         <v>1</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>8</v>
@@ -4305,7 +4329,7 @@
         <v>24</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E81" s="11">
         <v>24</v>
@@ -4317,15 +4341,15 @@
         <v>0.96</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>8</v>
@@ -4334,7 +4358,7 @@
         <v>25</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E82" s="11">
         <v>10</v>
@@ -4346,24 +4370,24 @@
         <v>0.4</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E83" s="11">
         <v>46</v>
@@ -4375,24 +4399,24 @@
         <v>1</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E84" s="11">
         <v>56</v>
@@ -4404,15 +4428,15 @@
         <v>1</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>8</v>
@@ -4421,7 +4445,7 @@
         <v>24</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E85" s="11">
         <v>24</v>
@@ -4433,15 +4457,15 @@
         <v>0.96</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>8</v>
@@ -4450,7 +4474,7 @@
         <v>25</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E86" s="11">
         <v>10</v>
@@ -4462,24 +4486,24 @@
         <v>0.4</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E87" s="11">
         <v>46</v>
@@ -4491,24 +4515,24 @@
         <v>1</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E88" s="11">
         <v>56</v>
@@ -4520,15 +4544,15 @@
         <v>1</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>8</v>
@@ -4537,7 +4561,7 @@
         <v>24</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E89" s="11">
         <v>24</v>
@@ -4549,15 +4573,15 @@
         <v>0.96</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>8</v>
@@ -4566,7 +4590,7 @@
         <v>25</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E90" s="11">
         <v>10</v>
@@ -4578,24 +4602,24 @@
         <v>0.4</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E91" s="11">
         <v>87</v>
@@ -4607,24 +4631,24 @@
         <v>0.8787878787878788</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E92" s="11">
         <v>77</v>
@@ -4636,24 +4660,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E93" s="11">
         <v>77</v>
@@ -4665,24 +4689,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E94" s="11">
         <v>77</v>
@@ -4694,24 +4718,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E95" s="11">
         <v>77</v>
@@ -4723,24 +4747,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E96" s="11">
         <v>77</v>
@@ -4752,24 +4776,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E97" s="11">
         <v>77</v>
@@ -4781,24 +4805,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E98" s="11">
         <v>77</v>
@@ -4810,24 +4834,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I98" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E99" s="11">
         <v>77</v>
@@ -4839,24 +4863,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H99" s="12" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E100" s="11">
         <v>57</v>
@@ -4868,24 +4892,24 @@
         <v>0.5135135135135135</v>
       </c>
       <c r="H100" s="12" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E101" s="11">
         <v>93</v>
@@ -4897,24 +4921,24 @@
         <v>0.6739130434782609</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E102" s="11">
         <v>44</v>
@@ -4926,24 +4950,24 @@
         <v>0.5432098765432098</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B103" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E103" s="11">
         <v>62</v>
@@ -4955,24 +4979,24 @@
         <v>0.5585585585585585</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E104" s="11">
         <v>98</v>
@@ -4984,24 +5008,24 @@
         <v>0.7101449275362319</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E105" s="11">
         <v>52</v>
@@ -5013,24 +5037,24 @@
         <v>0.6419753086419753</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E106" s="11">
         <v>101</v>
@@ -5042,24 +5066,24 @@
         <v>0.9099099099099099</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B107" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E107" s="11">
         <v>131</v>
@@ -5071,24 +5095,24 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="I107" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E108" s="11">
         <v>78</v>
@@ -5100,24 +5124,24 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I108" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B109" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E109" s="11">
         <v>102</v>
@@ -5129,24 +5153,24 @@
         <v>0.918918918918919</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="I109" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E110" s="11">
         <v>131</v>
@@ -5158,24 +5182,24 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="I110" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E111" s="11">
         <v>78</v>
@@ -5187,24 +5211,24 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I111" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E112" s="11">
         <v>102</v>
@@ -5216,24 +5240,24 @@
         <v>0.918918918918919</v>
       </c>
       <c r="H112" s="12" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="I112" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E113" s="11">
         <v>131</v>
@@ -5245,24 +5269,24 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="I113" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B114" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E114" s="11">
         <v>78</v>
@@ -5274,24 +5298,24 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B115" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E115" s="11">
         <v>111</v>
@@ -5303,24 +5327,24 @@
         <v>1</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="I115" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E116" s="11">
         <v>134</v>
@@ -5332,24 +5356,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H116" s="12" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B117" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E117" s="11">
         <v>79</v>
@@ -5361,24 +5385,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="I117" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E118" s="11">
         <v>111</v>
@@ -5390,24 +5414,24 @@
         <v>1</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I118" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E119" s="11">
         <v>134</v>
@@ -5419,24 +5443,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I119" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B120" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E120" s="11">
         <v>79</v>
@@ -5448,24 +5472,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I120" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E121" s="11">
         <v>111</v>
@@ -5477,24 +5501,24 @@
         <v>1</v>
       </c>
       <c r="H121" s="12" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I121" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B122" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E122" s="11">
         <v>134</v>
@@ -5506,24 +5530,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I122" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E123" s="11">
         <v>79</v>
@@ -5535,24 +5559,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H123" s="12" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I123" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E124" s="11">
         <v>111</v>
@@ -5564,24 +5588,24 @@
         <v>1</v>
       </c>
       <c r="H124" s="12" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I124" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E125" s="11">
         <v>134</v>
@@ -5593,24 +5617,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H125" s="12" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I125" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E126" s="11">
         <v>79</v>
@@ -5622,24 +5646,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H126" s="12" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E127" s="11">
         <v>111</v>
@@ -5651,24 +5675,24 @@
         <v>1</v>
       </c>
       <c r="H127" s="12" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B128" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E128" s="11">
         <v>134</v>
@@ -5680,24 +5704,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H128" s="12" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E129" s="11">
         <v>79</v>
@@ -5709,24 +5733,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B130" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E130" s="11">
         <v>111</v>
@@ -5738,24 +5762,24 @@
         <v>1</v>
       </c>
       <c r="H130" s="12" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E131" s="11">
         <v>134</v>
@@ -5767,24 +5791,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I131" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B132" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E132" s="11">
         <v>79</v>
@@ -5796,53 +5820,53 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I132" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B133" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G133" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I133" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B134" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E134" s="11">
         <v>3</v>
@@ -5854,24 +5878,24 @@
         <v>0.11538461538461539</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I134" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B135" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E135" s="11">
         <v>77</v>
@@ -5883,24 +5907,24 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="I135" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E136" s="11">
         <v>17</v>
@@ -5912,24 +5936,24 @@
         <v>0.16346153846153846</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I136" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E137" s="11">
         <v>17</v>
@@ -5941,24 +5965,24 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="I137" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B138" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E138" s="11">
         <v>111</v>
@@ -5970,24 +5994,24 @@
         <v>0.8809523809523809</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="I138" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E139" s="11">
         <v>71</v>
@@ -5999,24 +6023,24 @@
         <v>0.6826923076923077</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I139" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B140" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E140" s="11">
         <v>17</v>
@@ -6028,24 +6052,24 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="I140" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B141" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E141" s="11">
         <v>116</v>
@@ -6057,24 +6081,24 @@
         <v>0.9206349206349206</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I141" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B142" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E142" s="11">
         <v>89</v>
@@ -6086,24 +6110,24 @@
         <v>0.8557692307692307</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B143" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E143" s="11">
         <v>23</v>
@@ -6115,24 +6139,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="I143" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B144" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E144" s="11">
         <v>124</v>
@@ -6144,24 +6168,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H144" s="12" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B145" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E145" s="11">
         <v>98</v>
@@ -6173,24 +6197,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H145" s="12" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="I145" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E146" s="11">
         <v>23</v>
@@ -6202,24 +6226,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B147" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E147" s="11">
         <v>124</v>
@@ -6231,24 +6255,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H147" s="12" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I147" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B148" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E148" s="11">
         <v>98</v>
@@ -6260,24 +6284,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H148" s="12" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="I148" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E149" s="11">
         <v>23</v>
@@ -6289,24 +6313,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H149" s="12" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="I149" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E150" s="11">
         <v>124</v>
@@ -6318,24 +6342,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H150" s="12" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I150" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E151" s="11">
         <v>98</v>
@@ -6347,24 +6371,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H151" s="12" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="I151" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B152" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E152" s="11">
         <v>23</v>
@@ -6376,24 +6400,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H152" s="12" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="I152" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B153" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E153" s="11">
         <v>124</v>
@@ -6405,24 +6429,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H153" s="12" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I153" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B154" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E154" s="11">
         <v>98</v>
@@ -6434,24 +6458,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H154" s="12" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="I154" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E155" s="11">
         <v>23</v>
@@ -6463,24 +6487,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H155" s="12" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="I155" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B156" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E156" s="11">
         <v>124</v>
@@ -6492,24 +6516,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H156" s="12" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I156" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E157" s="11">
         <v>98</v>
@@ -6521,24 +6545,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H157" s="12" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="I157" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B158" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E158" s="11">
         <v>23</v>
@@ -6550,24 +6574,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H158" s="12" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="I158" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B159" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E159" s="11">
         <v>124</v>
@@ -6579,24 +6603,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H159" s="12" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I159" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B160" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E160" s="11">
         <v>98</v>
@@ -6608,24 +6632,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H160" s="12" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="I160" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B161" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E161" s="11">
         <v>16</v>
@@ -6637,24 +6661,24 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="H161" s="12" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I161" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B162" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E162" s="11">
         <v>39</v>
@@ -6666,24 +6690,24 @@
         <v>0.4588235294117647</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="I162" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B163" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E163" s="11">
         <v>11</v>
@@ -6695,24 +6719,24 @@
         <v>0.10784313725490197</v>
       </c>
       <c r="H163" s="12" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I163" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B164" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E164" s="11">
         <v>29</v>
@@ -6724,24 +6748,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H164" s="12" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="I164" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B165" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E165" s="11">
         <v>63</v>
@@ -6753,24 +6777,24 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H165" s="12" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="I165" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B166" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E166" s="11">
         <v>22</v>
@@ -6782,24 +6806,24 @@
         <v>0.21568627450980393</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="I166" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B167" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E167" s="11">
         <v>29</v>
@@ -6811,24 +6835,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H167" s="12" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I167" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E168" s="11">
         <v>63</v>
@@ -6840,24 +6864,24 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H168" s="12" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="I168" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B169" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E169" s="11">
         <v>23</v>
@@ -6869,24 +6893,24 @@
         <v>0.22549019607843138</v>
       </c>
       <c r="H169" s="12" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="I169" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C170" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E170" s="11">
         <v>29</v>
@@ -6898,24 +6922,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H170" s="12" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I170" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B171" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E171" s="11">
         <v>63</v>
@@ -6927,24 +6951,24 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H171" s="12" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="I171" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B172" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E172" s="11">
         <v>23</v>
@@ -6956,24 +6980,24 @@
         <v>0.22549019607843138</v>
       </c>
       <c r="H172" s="12" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="I172" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B173" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E173" s="11">
         <v>29</v>
@@ -6985,24 +7009,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H173" s="12" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I173" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B174" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E174" s="11">
         <v>65</v>
@@ -7014,24 +7038,24 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H174" s="12" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="I174" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B175" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E175" s="11">
         <v>24</v>
@@ -7043,24 +7067,24 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H175" s="12" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I175" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B176" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E176" s="11">
         <v>29</v>
@@ -7072,24 +7096,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H176" s="12" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I176" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B177" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E177" s="11">
         <v>65</v>
@@ -7101,24 +7125,24 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H177" s="12" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="I177" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B178" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E178" s="11">
         <v>24</v>
@@ -7130,24 +7154,24 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H178" s="12" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I178" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B179" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E179" s="11">
         <v>29</v>
@@ -7159,24 +7183,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H179" s="12" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I179" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B180" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E180" s="11">
         <v>65</v>
@@ -7188,24 +7212,24 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H180" s="12" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="I180" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B181" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E181" s="11">
         <v>24</v>
@@ -7217,111 +7241,111 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H181" s="12" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I181" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B182" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E182" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G182" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H182" s="12" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I182" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B183" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E183" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G183" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H183" s="12" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I183" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E184" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G184" s="11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H184" s="12" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I184" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B185" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E185" s="11">
         <v>24</v>
@@ -7333,24 +7357,24 @@
         <v>0.17647058823529413</v>
       </c>
       <c r="H185" s="12" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="I185" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B186" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E186" s="11">
         <v>30</v>
@@ -7362,24 +7386,24 @@
         <v>0.22058823529411764</v>
       </c>
       <c r="H186" s="12" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="I186" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B187" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E187" s="11">
         <v>45</v>
@@ -7391,24 +7415,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H187" s="12" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="I187" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B188" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E188" s="11">
         <v>45</v>
@@ -7420,24 +7444,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H188" s="12" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="I188" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B189" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E189" s="11">
         <v>45</v>
@@ -7449,24 +7473,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H189" s="12" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="I189" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B190" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E190" s="11">
         <v>45</v>
@@ -7478,24 +7502,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H190" s="12" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="I190" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B191" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E191" s="11">
         <v>45</v>
@@ -7507,24 +7531,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H191" s="12" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="I191" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B192" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E192" s="11">
         <v>45</v>
@@ -7536,24 +7560,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H192" s="12" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="I192" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="11" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B193" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E193" s="11">
         <v>81</v>
@@ -7565,24 +7589,24 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="H193" s="12" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="I193" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B194" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E194" s="11">
         <v>1</v>
@@ -7594,24 +7618,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H194" s="12" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I194" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B195" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E195" s="11">
         <v>84</v>
@@ -7623,24 +7647,24 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="H195" s="12" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="I195" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B196" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E196" s="11">
         <v>0</v>
@@ -7652,24 +7676,24 @@
         <v>0</v>
       </c>
       <c r="H196" s="12" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I196" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B197" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E197" s="11">
         <v>124</v>
@@ -7681,24 +7705,24 @@
         <v>0.656084656084656</v>
       </c>
       <c r="H197" s="12" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="I197" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B198" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E198" s="11">
         <v>0</v>
@@ -7710,24 +7734,24 @@
         <v>0</v>
       </c>
       <c r="H198" s="12" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I198" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B199" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D199" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E199" s="11">
         <v>148</v>
@@ -7739,24 +7763,24 @@
         <v>0.783068783068783</v>
       </c>
       <c r="H199" s="12" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="I199" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B200" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E200" s="11">
         <v>1</v>
@@ -7768,24 +7792,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H200" s="12" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I200" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B201" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E201" s="11">
         <v>154</v>
@@ -7797,24 +7821,24 @@
         <v>0.8148148148148148</v>
       </c>
       <c r="H201" s="12" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I201" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B202" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E202" s="11">
         <v>1</v>
@@ -7826,24 +7850,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H202" s="12" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I202" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B203" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E203" s="11">
         <v>160</v>
@@ -7855,24 +7879,24 @@
         <v>0.5194805194805194</v>
       </c>
       <c r="H203" s="12" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="I203" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B204" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D204" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E204" s="11">
         <v>1</v>
@@ -7884,24 +7908,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H204" s="12" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I204" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B205" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E205" s="11">
         <v>1</v>
@@ -7913,24 +7937,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H205" s="12" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="I205" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D206" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E206" s="11">
         <v>161</v>
@@ -7942,24 +7966,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H206" s="12" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I206" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B207" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E207" s="11">
         <v>1</v>
@@ -7971,24 +7995,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H207" s="12" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="I207" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B208" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D208" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E208" s="11">
         <v>161</v>
@@ -8000,24 +8024,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H208" s="12" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I208" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B209" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E209" s="11">
         <v>1</v>
@@ -8029,24 +8053,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H209" s="12" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="I209" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B210" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E210" s="11">
         <v>161</v>
@@ -8058,24 +8082,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H210" s="12" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I210" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B211" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D211" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E211" s="11">
         <v>1</v>
@@ -8087,24 +8111,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H211" s="12" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="I211" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B212" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E212" s="11">
         <v>161</v>
@@ -8116,24 +8140,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H212" s="12" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I212" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B213" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E213" s="11">
         <v>1</v>
@@ -8145,24 +8169,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H213" s="12" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="I213" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B214" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E214" s="11">
         <v>161</v>
@@ -8174,24 +8198,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H214" s="12" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I214" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B215" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E215" s="11">
         <v>9</v>
@@ -8203,24 +8227,24 @@
         <v>0.06040268456375839</v>
       </c>
       <c r="H215" s="12" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="I215" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D216" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E216" s="11">
         <v>21</v>
@@ -8232,24 +8256,24 @@
         <v>0.14093959731543623</v>
       </c>
       <c r="H216" s="12" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="I216" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B217" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E217" s="11">
         <v>23</v>
@@ -8261,24 +8285,24 @@
         <v>0.15436241610738255</v>
       </c>
       <c r="H217" s="12" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="I217" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D218" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E218" s="11">
         <v>31</v>
@@ -8290,24 +8314,24 @@
         <v>0.2080536912751678</v>
       </c>
       <c r="H218" s="12" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I218" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B219" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D219" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E219" s="11">
         <v>34</v>
@@ -8319,24 +8343,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H219" s="12" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="I219" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B220" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E220" s="11">
         <v>34</v>
@@ -8348,24 +8372,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H220" s="12" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B221" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D221" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E221" s="11">
         <v>34</v>
@@ -8377,24 +8401,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H221" s="12" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I221" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D222" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E222" s="11">
         <v>34</v>
@@ -8406,24 +8430,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H222" s="12" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I222" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B223" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D223" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E223" s="11">
         <v>34</v>
@@ -8435,24 +8459,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H223" s="12" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I223" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D224" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E224" s="11">
         <v>34</v>
@@ -8464,24 +8488,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H224" s="12" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I224" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B225" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C225" s="12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E225" s="11">
         <v>34</v>
@@ -8493,10 +8517,10 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H225" s="12" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I225" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -8517,58 +8541,58 @@
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -18,7 +18,7 @@
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
   <si>
-    <t>Generated from embedded historical records + saved TEDUH records · 19/10/2026</t>
+    <t>Generated from embedded historical records + saved TEDUH records · 20/10/2026</t>
   </si>
   <si>
     <t>RECORD DETAIL</t>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -12,8 +12,74 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="F50" authorId="0">
+      <text>
+        <r>
+          <t>Total units increased from 99 to 113 compared with 06/10/2025. Review whether this reflects a newly released unit scope.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F222" authorId="0">
+      <text>
+        <r>
+          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F225" authorId="0">
+      <text>
+        <r>
+          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F227" authorId="0">
+      <text>
+        <r>
+          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F229" authorId="0">
+      <text>
+        <r>
+          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F231" authorId="0">
+      <text>
+        <r>
+          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F233" authorId="0">
+      <text>
+        <r>
+          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F235" authorId="0">
+      <text>
+        <r>
+          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="258">
   <si>
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
@@ -705,9 +771,6 @@
     <t>45/136 signed</t>
   </si>
   <si>
-    <t>Earlier release scope (189 units)</t>
-  </si>
-  <si>
     <t>25% Signed (81/189 units)</t>
   </si>
   <si>
@@ -783,7 +846,7 @@
     <t>Scope</t>
   </si>
   <si>
-    <t>Birchpark remains four terrace groups and excludes rumah bandar. Sapphire uses the terrace-only comparison scope. Springvale keeps the 27-unit front-kitchen and 308-unit rear-kitchen groups separate.</t>
+    <t>Birchpark remains four terrace groups and excludes rumah bandar. Sapphire uses the terrace-only comparison scope. Springvale Group A remains 27 units. Group B is one continuing historical series: earlier records used 189 total units before the release scope increased to 308; the change is highlighted for review, not split into a new group.</t>
   </si>
   <si>
     <t>OneDrive destination</t>
@@ -796,7 +859,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -835,8 +898,12 @@
       <b/>
       <color rgb="FFB54708"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF8A4B08"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -878,6 +945,11 @@
         <fgColor rgb="FFFFF1D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE4B5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -909,7 +981,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -952,6 +1024,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3590,7 +3665,7 @@
       <c r="E50" s="12">
         <v>70</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="16">
         <v>113</v>
       </c>
       <c r="G50" s="15">
@@ -8280,7 +8355,7 @@
         <v>15</v>
       </c>
       <c r="C212" s="13" t="s">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="D212" s="12" t="s">
         <v>121</v>
@@ -8295,7 +8370,7 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="H212" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I212" s="12" t="s">
         <v>117</v>
@@ -8324,7 +8399,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H213" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I213" s="12" t="s">
         <v>117</v>
@@ -8338,7 +8413,7 @@
         <v>15</v>
       </c>
       <c r="C214" s="13" t="s">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="D214" s="12" t="s">
         <v>121</v>
@@ -8353,7 +8428,7 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="H214" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I214" s="12" t="s">
         <v>117</v>
@@ -8382,7 +8457,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I215" s="12" t="s">
         <v>117</v>
@@ -8396,7 +8471,7 @@
         <v>15</v>
       </c>
       <c r="C216" s="13" t="s">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="D216" s="12" t="s">
         <v>121</v>
@@ -8411,7 +8486,7 @@
         <v>0.656084656084656</v>
       </c>
       <c r="H216" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I216" s="12" t="s">
         <v>117</v>
@@ -8440,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="H217" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I217" s="12" t="s">
         <v>117</v>
@@ -8454,7 +8529,7 @@
         <v>15</v>
       </c>
       <c r="C218" s="13" t="s">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="D218" s="12" t="s">
         <v>121</v>
@@ -8469,7 +8544,7 @@
         <v>0.783068783068783</v>
       </c>
       <c r="H218" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I218" s="12" t="s">
         <v>117</v>
@@ -8498,7 +8573,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H219" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I219" s="12" t="s">
         <v>117</v>
@@ -8512,7 +8587,7 @@
         <v>15</v>
       </c>
       <c r="C220" s="13" t="s">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="D220" s="12" t="s">
         <v>121</v>
@@ -8527,7 +8602,7 @@
         <v>0.8148148148148148</v>
       </c>
       <c r="H220" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I220" s="12" t="s">
         <v>117</v>
@@ -8556,7 +8631,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H221" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I221" s="12" t="s">
         <v>117</v>
@@ -8578,14 +8653,14 @@
       <c r="E222" s="12">
         <v>160</v>
       </c>
-      <c r="F222" s="12">
+      <c r="F222" s="16">
         <v>308</v>
       </c>
       <c r="G222" s="15">
         <v>0.5194805194805194</v>
       </c>
       <c r="H222" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I222" s="12" t="s">
         <v>117</v>
@@ -8614,7 +8689,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H223" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I223" s="12" t="s">
         <v>117</v>
@@ -8643,7 +8718,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H224" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I224" s="12" t="s">
         <v>128</v>
@@ -8665,14 +8740,14 @@
       <c r="E225" s="12">
         <v>161</v>
       </c>
-      <c r="F225" s="12">
+      <c r="F225" s="16">
         <v>308</v>
       </c>
       <c r="G225" s="15">
         <v>0.5227272727272727</v>
       </c>
       <c r="H225" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I225" s="12" t="s">
         <v>128</v>
@@ -8701,7 +8776,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H226" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I226" s="12" t="s">
         <v>128</v>
@@ -8723,14 +8798,14 @@
       <c r="E227" s="12">
         <v>161</v>
       </c>
-      <c r="F227" s="12">
+      <c r="F227" s="16">
         <v>308</v>
       </c>
       <c r="G227" s="15">
         <v>0.5227272727272727</v>
       </c>
       <c r="H227" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I227" s="12" t="s">
         <v>128</v>
@@ -8759,7 +8834,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H228" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I228" s="12" t="s">
         <v>128</v>
@@ -8781,14 +8856,14 @@
       <c r="E229" s="12">
         <v>161</v>
       </c>
-      <c r="F229" s="12">
+      <c r="F229" s="16">
         <v>308</v>
       </c>
       <c r="G229" s="15">
         <v>0.5227272727272727</v>
       </c>
       <c r="H229" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I229" s="12" t="s">
         <v>128</v>
@@ -8817,7 +8892,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H230" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I230" s="12" t="s">
         <v>128</v>
@@ -8839,14 +8914,14 @@
       <c r="E231" s="12">
         <v>161</v>
       </c>
-      <c r="F231" s="12">
+      <c r="F231" s="16">
         <v>308</v>
       </c>
       <c r="G231" s="15">
         <v>0.5227272727272727</v>
       </c>
       <c r="H231" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I231" s="12" t="s">
         <v>128</v>
@@ -8875,7 +8950,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H232" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I232" s="12" t="s">
         <v>128</v>
@@ -8897,14 +8972,14 @@
       <c r="E233" s="12">
         <v>161</v>
       </c>
-      <c r="F233" s="12">
+      <c r="F233" s="16">
         <v>308</v>
       </c>
       <c r="G233" s="15">
         <v>0.5227272727272727</v>
       </c>
       <c r="H233" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I233" s="12" t="s">
         <v>128</v>
@@ -8933,7 +9008,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H234" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I234" s="12" t="s">
         <v>128</v>
@@ -8955,14 +9030,14 @@
       <c r="E235" s="12">
         <v>161</v>
       </c>
-      <c r="F235" s="12">
+      <c r="F235" s="16">
         <v>308</v>
       </c>
       <c r="G235" s="15">
         <v>0.5227272727272727</v>
       </c>
       <c r="H235" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I235" s="12" t="s">
         <v>128</v>
@@ -8991,7 +9066,7 @@
         <v>0.06040268456375839</v>
       </c>
       <c r="H236" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I236" s="12" t="s">
         <v>117</v>
@@ -9020,7 +9095,7 @@
         <v>0.14093959731543623</v>
       </c>
       <c r="H237" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I237" s="12" t="s">
         <v>117</v>
@@ -9049,7 +9124,7 @@
         <v>0.15436241610738255</v>
       </c>
       <c r="H238" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I238" s="12" t="s">
         <v>117</v>
@@ -9078,7 +9153,7 @@
         <v>0.2080536912751678</v>
       </c>
       <c r="H239" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I239" s="12" t="s">
         <v>117</v>
@@ -9107,7 +9182,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H240" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I240" s="12" t="s">
         <v>117</v>
@@ -9136,7 +9211,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H241" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I241" s="12" t="s">
         <v>117</v>
@@ -9165,7 +9240,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H242" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I242" s="12" t="s">
         <v>128</v>
@@ -9194,7 +9269,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H243" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I243" s="12" t="s">
         <v>128</v>
@@ -9223,7 +9298,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H244" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I244" s="12" t="s">
         <v>128</v>
@@ -9252,7 +9327,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H245" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I245" s="12" t="s">
         <v>128</v>
@@ -9281,7 +9356,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H246" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I246" s="12" t="s">
         <v>128</v>
@@ -9310,7 +9385,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H247" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I247" s="12" t="s">
         <v>128</v>
@@ -9320,6 +9395,7 @@
   <autoFilter ref="A1:I247"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9333,59 +9409,59 @@
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="17" t="s">
+    </row>
+    <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="17" t="s">
+    <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="B3" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="B3" s="17" t="s">
+    </row>
+    <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="B4" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="B4" s="17" t="s">
+    </row>
+    <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="17" t="s">
+    <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="B6" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="B6" s="17" t="s">
+    </row>
+    <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="B7" s="18" t="s">
         <v>257</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -12,72 +12,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="F50" authorId="0">
-      <text>
-        <r>
-          <t>Total units increased from 99 to 113 compared with 06/10/2025. Review whether this reflects a newly released unit scope.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F222" authorId="0">
-      <text>
-        <r>
-          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F225" authorId="0">
-      <text>
-        <r>
-          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F227" authorId="0">
-      <text>
-        <r>
-          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F229" authorId="0">
-      <text>
-        <r>
-          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F231" authorId="0">
-      <text>
-        <r>
-          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F233" authorId="0">
-      <text>
-        <r>
-          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F235" authorId="0">
-      <text>
-        <r>
-          <t>Total units increased from 189 to 308 compared with 27/02/2026. Review whether this reflects a newly released unit scope.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="258">
   <si>
@@ -846,7 +780,7 @@
     <t>Scope</t>
   </si>
   <si>
-    <t>Birchpark remains four terrace groups and excludes rumah bandar. Sapphire uses the terrace-only comparison scope. Springvale Group A remains 27 units. Group B is one continuing historical series: earlier records used 189 total units before the release scope increased to 308; the change is highlighted for review, not split into a new group.</t>
+    <t>Birchpark remains four terrace groups and excludes rumah bandar. Sapphire uses the terrace-only comparison scope. Springvale keeps the 27-unit front-kitchen and 308-unit rear-kitchen groups separate.</t>
   </si>
   <si>
     <t>OneDrive destination</t>
@@ -859,7 +793,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -898,12 +832,8 @@
       <b/>
       <color rgb="FFB54708"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FF8A4B08"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -945,11 +875,6 @@
         <fgColor rgb="FFFFF1D6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE4B5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -981,7 +906,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1024,9 +949,6 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3665,7 +3587,7 @@
       <c r="E50" s="12">
         <v>70</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="12">
         <v>113</v>
       </c>
       <c r="G50" s="15">
@@ -8653,7 +8575,7 @@
       <c r="E222" s="12">
         <v>160</v>
       </c>
-      <c r="F222" s="16">
+      <c r="F222" s="12">
         <v>308</v>
       </c>
       <c r="G222" s="15">
@@ -8740,7 +8662,7 @@
       <c r="E225" s="12">
         <v>161</v>
       </c>
-      <c r="F225" s="16">
+      <c r="F225" s="12">
         <v>308</v>
       </c>
       <c r="G225" s="15">
@@ -8798,7 +8720,7 @@
       <c r="E227" s="12">
         <v>161</v>
       </c>
-      <c r="F227" s="16">
+      <c r="F227" s="12">
         <v>308</v>
       </c>
       <c r="G227" s="15">
@@ -8856,7 +8778,7 @@
       <c r="E229" s="12">
         <v>161</v>
       </c>
-      <c r="F229" s="16">
+      <c r="F229" s="12">
         <v>308</v>
       </c>
       <c r="G229" s="15">
@@ -8914,7 +8836,7 @@
       <c r="E231" s="12">
         <v>161</v>
       </c>
-      <c r="F231" s="16">
+      <c r="F231" s="12">
         <v>308</v>
       </c>
       <c r="G231" s="15">
@@ -8972,7 +8894,7 @@
       <c r="E233" s="12">
         <v>161</v>
       </c>
-      <c r="F233" s="16">
+      <c r="F233" s="12">
         <v>308</v>
       </c>
       <c r="G233" s="15">
@@ -9030,7 +8952,7 @@
       <c r="E235" s="12">
         <v>161</v>
       </c>
-      <c r="F235" s="16">
+      <c r="F235" s="12">
         <v>308</v>
       </c>
       <c r="G235" s="15">
@@ -9395,7 +9317,6 @@
   <autoFilter ref="A1:I247"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9409,58 +9330,58 @@
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>257</v>
       </c>
     </row>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="256">
   <si>
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
@@ -69,7 +69,7 @@
     <t>Unit group / layout</t>
   </si>
   <si>
-    <t>Terrace houses</t>
+    <t>20' x 70' / 20' x 72'</t>
   </si>
   <si>
     <t>Overall status</t>
@@ -81,28 +81,16 @@
     <t>22' x 70'</t>
   </si>
   <si>
+    <t>20' x 70'</t>
+  </si>
+  <si>
     <t>20' x 65'</t>
   </si>
   <si>
-    <t>20' x 70'</t>
-  </si>
-  <si>
-    <t>Group 57513</t>
-  </si>
-  <si>
-    <t>Group 57514</t>
-  </si>
-  <si>
-    <t>Group 57515</t>
-  </si>
-  <si>
-    <t>Group 57516</t>
-  </si>
-  <si>
-    <t>Unmapped unit group 3 — verify TEDUH mapping</t>
-  </si>
-  <si>
-    <t>Unmapped unit group 4 — verify TEDUH mapping</t>
+    <t>20' x 75'</t>
+  </si>
+  <si>
+    <t>20' x 80'</t>
   </si>
   <si>
     <t>Group 1</t>
@@ -114,9 +102,6 @@
     <t>Group 3</t>
   </si>
   <si>
-    <t>Rumah teres only</t>
-  </si>
-  <si>
     <t>Group A · front-kitchen layout</t>
   </si>
   <si>
@@ -312,19 +297,28 @@
     <t>Weekly Change</t>
   </si>
   <si>
-    <t>+2 signed</t>
+    <t>+2 signed; +2.5 percentage points</t>
   </si>
   <si>
     <t>No signed status yet</t>
   </si>
   <si>
-    <t>+1 signed</t>
+    <t>+1 signed; +0.9 percentage points</t>
   </si>
   <si>
     <t>No change</t>
   </si>
   <si>
     <t>Insufficient weekly history</t>
+  </si>
+  <si>
+    <t>+2 signed; +2.4 percentage points</t>
+  </si>
+  <si>
+    <t>+2 signed; +2.0 percentage points</t>
+  </si>
+  <si>
+    <t>+1 signed; +0.3 percentage points</t>
   </si>
   <si>
     <t>Record Date</t>
@@ -1299,14 +1293,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="29" width="21" customWidth="1"/>
+    <col min="2" max="34" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1338,8 +1332,13 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1371,8 +1370,13 @@
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1397,43 +1401,48 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="K4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3" t="s">
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="AE4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AF4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3" t="s">
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="48" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -1450,13 +1459,13 @@
         <v>21</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>24</v>
@@ -1465,696 +1474,816 @@
         <v>25</v>
       </c>
       <c r="K5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="N5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="O5" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="AC5" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" ht="38" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="X6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH6" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="T6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="U6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="V6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="W6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="X6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC6" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>41</v>
       </c>
       <c r="I7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="P7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="Q7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="R7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U7" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="V7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="W7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="X7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH7" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="S8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="V8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="W8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="X8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB8" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH8" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="X9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH9" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="6" t="s">
+      <c r="I10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="V10" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="W10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="X10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="R7" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="T7" s="6" t="s">
+      <c r="AB10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="U7" s="6" t="s">
+      <c r="AF10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="V7" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="W7" s="6" t="s">
+      <c r="AG10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="X7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA7" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB7" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC7" s="6" t="s">
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="F11" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="G11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="H11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="J11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="K11" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="L11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="P11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="6" t="s">
+      <c r="Q11" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="R11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="V11" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8" s="6" t="s">
+      <c r="W11" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" s="6" t="s">
+      <c r="X11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA11" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="T8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="U8" s="6" t="s">
+      <c r="AB11" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="V8" s="6" t="s">
+      <c r="AF11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="W8" s="6" t="s">
+      <c r="AG11" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="X8" s="6" t="s">
+      <c r="AH11" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="Y8" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB8" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC8" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="R9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="S9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="U9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="V9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="W9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="X9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y9" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC9" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S10" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="V10" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="W10" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="X10" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z10" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA10" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB10" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC10" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    </row>
+    <row r="12" ht="38" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="S11" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="U11" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="V11" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="W11" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="X11" s="7" t="s">
+      <c r="E12" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="Y11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z11" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA11" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB11" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC11" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="F12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="M12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="R12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="S12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="T12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="V12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="W12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="X12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB12" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="AC12" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="AD12" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG12" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="V12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="W12" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="X12" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y12" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB12" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC12" s="9" t="s">
-        <v>102</v>
+      <c r="AH12" s="9" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:AC5"/>
+  <autoFilter ref="A5:AH5"/>
   <mergeCells count="7">
-    <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="A2:AC2"/>
-    <mergeCell ref="G4:N4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="A2:AH2"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="L4:Q4"/>
+    <mergeCell ref="R4:W4"/>
+    <mergeCell ref="X4:AC4"/>
+    <mergeCell ref="AF4:AG4"/>
   </mergeCells>
   <pageSetup paperSize="8" orientation="landscape" horizontalDpi="300" verticalDpi="300" fitToWidth="2" fitToHeight="0"/>
 </worksheet>
@@ -2176,36 +2305,36 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>3</v>
@@ -2214,25 +2343,25 @@
         <v>18</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F2" s="12">
         <v>81</v>
       </c>
       <c r="G2" s="14"/>
       <c r="H2" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>3</v>
@@ -2241,25 +2370,25 @@
         <v>18</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F3" s="12">
         <v>81</v>
       </c>
       <c r="G3" s="14"/>
       <c r="H3" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>3</v>
@@ -2268,7 +2397,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E4" s="12">
         <v>48</v>
@@ -2280,15 +2409,15 @@
         <v>0.5925925925925926</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>3</v>
@@ -2297,7 +2426,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E5" s="12">
         <v>53</v>
@@ -2309,15 +2438,15 @@
         <v>0.654320987654321</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>3</v>
@@ -2326,7 +2455,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E6" s="12">
         <v>72</v>
@@ -2338,15 +2467,15 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>3</v>
@@ -2355,7 +2484,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E7" s="12">
         <v>74</v>
@@ -2367,15 +2496,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>3</v>
@@ -2384,7 +2513,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E8" s="12">
         <v>74</v>
@@ -2396,15 +2525,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>3</v>
@@ -2413,7 +2542,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E9" s="12">
         <v>74</v>
@@ -2425,15 +2554,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>3</v>
@@ -2442,7 +2571,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E10" s="12">
         <v>74</v>
@@ -2454,15 +2583,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>3</v>
@@ -2471,7 +2600,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E11" s="12">
         <v>74</v>
@@ -2483,15 +2612,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>3</v>
@@ -2500,7 +2629,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E12" s="12">
         <v>74</v>
@@ -2512,102 +2641,102 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="I13" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="I14" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="I15" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>5</v>
@@ -2616,25 +2745,25 @@
         <v>20</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F16" s="12">
         <v>113</v>
       </c>
       <c r="G16" s="14"/>
       <c r="H16" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>5</v>
@@ -2643,25 +2772,25 @@
         <v>20</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F17" s="12">
         <v>113</v>
       </c>
       <c r="G17" s="14"/>
       <c r="H17" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>5</v>
@@ -2670,25 +2799,25 @@
         <v>20</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F18" s="12">
         <v>113</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>5</v>
@@ -2697,25 +2826,25 @@
         <v>20</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F19" s="12">
         <v>113</v>
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>5</v>
@@ -2724,7 +2853,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E20" s="12">
         <v>34</v>
@@ -2736,15 +2865,15 @@
         <v>0.3008849557522124</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>5</v>
@@ -2753,7 +2882,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E21" s="12">
         <v>37</v>
@@ -2765,15 +2894,15 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>5</v>
@@ -2782,7 +2911,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E22" s="12">
         <v>37</v>
@@ -2794,15 +2923,15 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>5</v>
@@ -2811,7 +2940,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E23" s="12">
         <v>54</v>
@@ -2823,15 +2952,15 @@
         <v>0.4778761061946903</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>5</v>
@@ -2840,7 +2969,7 @@
         <v>20</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E24" s="12">
         <v>63</v>
@@ -2852,15 +2981,15 @@
         <v>0.5575221238938053</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>5</v>
@@ -2869,7 +2998,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E25" s="12">
         <v>68</v>
@@ -2881,15 +3010,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>5</v>
@@ -2898,7 +3027,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E26" s="12">
         <v>68</v>
@@ -2910,15 +3039,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>5</v>
@@ -2927,7 +3056,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E27" s="12">
         <v>68</v>
@@ -2939,15 +3068,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>5</v>
@@ -2956,7 +3085,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E28" s="12">
         <v>68</v>
@@ -2968,15 +3097,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>5</v>
@@ -2985,7 +3114,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E29" s="12">
         <v>69</v>
@@ -2997,15 +3126,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>5</v>
@@ -3014,7 +3143,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E30" s="12">
         <v>69</v>
@@ -3026,15 +3155,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>5</v>
@@ -3043,7 +3172,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E31" s="12">
         <v>69</v>
@@ -3055,15 +3184,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>5</v>
@@ -3072,7 +3201,7 @@
         <v>20</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E32" s="12">
         <v>69</v>
@@ -3084,15 +3213,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>6</v>
@@ -3101,25 +3230,25 @@
         <v>21</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F33" s="12">
         <v>48</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>6</v>
@@ -3128,25 +3257,25 @@
         <v>21</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F34" s="12">
         <v>48</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>6</v>
@@ -3155,25 +3284,25 @@
         <v>21</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F35" s="12">
         <v>48</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>6</v>
@@ -3182,25 +3311,25 @@
         <v>21</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F36" s="12">
         <v>48</v>
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>6</v>
@@ -3209,25 +3338,25 @@
         <v>21</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F37" s="12">
         <v>48</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>6</v>
@@ -3236,25 +3365,25 @@
         <v>21</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F38" s="12">
         <v>48</v>
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>6</v>
@@ -3263,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E39" s="12">
         <v>15</v>
@@ -3275,15 +3404,15 @@
         <v>0.3125</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>6</v>
@@ -3292,7 +3421,7 @@
         <v>21</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E40" s="12">
         <v>19</v>
@@ -3304,15 +3433,15 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>6</v>
@@ -3321,7 +3450,7 @@
         <v>21</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E41" s="12">
         <v>19</v>
@@ -3333,15 +3462,15 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>6</v>
@@ -3350,7 +3479,7 @@
         <v>21</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E42" s="12">
         <v>21</v>
@@ -3362,15 +3491,15 @@
         <v>0.4375</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>6</v>
@@ -3379,7 +3508,7 @@
         <v>21</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E43" s="12">
         <v>21</v>
@@ -3391,15 +3520,15 @@
         <v>0.4375</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>6</v>
@@ -3408,7 +3537,7 @@
         <v>21</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E44" s="12">
         <v>21</v>
@@ -3420,15 +3549,15 @@
         <v>0.4375</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>6</v>
@@ -3437,7 +3566,7 @@
         <v>21</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E45" s="12">
         <v>21</v>
@@ -3449,15 +3578,15 @@
         <v>0.4375</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>6</v>
@@ -3466,7 +3595,7 @@
         <v>21</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E46" s="12">
         <v>21</v>
@@ -3478,15 +3607,15 @@
         <v>0.4375</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>6</v>
@@ -3495,7 +3624,7 @@
         <v>21</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E47" s="12">
         <v>21</v>
@@ -3507,15 +3636,15 @@
         <v>0.4375</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>6</v>
@@ -3524,7 +3653,7 @@
         <v>21</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E48" s="12">
         <v>21</v>
@@ -3536,24 +3665,24 @@
         <v>0.4375</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E49" s="12">
         <v>83</v>
@@ -3565,24 +3694,24 @@
         <v>0.8383838383838383</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E50" s="12">
         <v>70</v>
@@ -3594,24 +3723,24 @@
         <v>0.6194690265486725</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E51" s="12">
         <v>70</v>
@@ -3623,24 +3752,24 @@
         <v>0.6194690265486725</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E52" s="12">
         <v>71</v>
@@ -3652,24 +3781,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E53" s="12">
         <v>71</v>
@@ -3681,24 +3810,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E54" s="12">
         <v>71</v>
@@ -3710,24 +3839,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E55" s="12">
         <v>71</v>
@@ -3739,24 +3868,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E56" s="12">
         <v>71</v>
@@ -3768,24 +3897,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E57" s="12">
         <v>71</v>
@@ -3797,24 +3926,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E58" s="12">
         <v>71</v>
@@ -3826,24 +3955,24 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E59" s="12">
         <v>45</v>
@@ -3855,24 +3984,24 @@
         <v>0.9782608695652174</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E60" s="12">
         <v>47</v>
@@ -3884,24 +4013,24 @@
         <v>0.8392857142857143</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E61" s="12">
         <v>13</v>
@@ -3913,24 +4042,24 @@
         <v>0.52</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E62" s="12">
         <v>3</v>
@@ -3942,24 +4071,24 @@
         <v>0.12</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E63" s="12">
         <v>46</v>
@@ -3971,24 +4100,24 @@
         <v>1</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E64" s="12">
         <v>56</v>
@@ -4000,24 +4129,24 @@
         <v>1</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E65" s="12">
         <v>24</v>
@@ -4029,24 +4158,24 @@
         <v>0.96</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E66" s="12">
         <v>7</v>
@@ -4058,24 +4187,24 @@
         <v>0.28</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E67" s="12">
         <v>46</v>
@@ -4087,24 +4216,24 @@
         <v>1</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E68" s="12">
         <v>56</v>
@@ -4116,24 +4245,24 @@
         <v>1</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E69" s="12">
         <v>24</v>
@@ -4145,24 +4274,24 @@
         <v>0.96</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E70" s="12">
         <v>8</v>
@@ -4174,24 +4303,24 @@
         <v>0.32</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E71" s="12">
         <v>46</v>
@@ -4203,24 +4332,24 @@
         <v>1</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E72" s="12">
         <v>56</v>
@@ -4232,24 +4361,24 @@
         <v>1</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E73" s="12">
         <v>24</v>
@@ -4261,24 +4390,24 @@
         <v>0.96</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E74" s="12">
         <v>10</v>
@@ -4290,24 +4419,24 @@
         <v>0.4</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E75" s="12">
         <v>46</v>
@@ -4319,24 +4448,24 @@
         <v>1</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E76" s="12">
         <v>56</v>
@@ -4348,24 +4477,24 @@
         <v>1</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I76" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E77" s="12">
         <v>24</v>
@@ -4377,24 +4506,24 @@
         <v>0.96</v>
       </c>
       <c r="H77" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E78" s="12">
         <v>10</v>
@@ -4406,24 +4535,24 @@
         <v>0.4</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E79" s="12">
         <v>46</v>
@@ -4435,24 +4564,24 @@
         <v>1</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E80" s="12">
         <v>56</v>
@@ -4464,24 +4593,24 @@
         <v>1</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I80" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E81" s="12">
         <v>24</v>
@@ -4493,24 +4622,24 @@
         <v>0.96</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I81" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E82" s="12">
         <v>10</v>
@@ -4522,24 +4651,24 @@
         <v>0.4</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E83" s="12">
         <v>46</v>
@@ -4551,24 +4680,24 @@
         <v>1</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E84" s="12">
         <v>56</v>
@@ -4580,24 +4709,24 @@
         <v>1</v>
       </c>
       <c r="H84" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E85" s="12">
         <v>24</v>
@@ -4609,24 +4738,24 @@
         <v>0.96</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E86" s="12">
         <v>10</v>
@@ -4638,24 +4767,24 @@
         <v>0.4</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I86" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E87" s="12">
         <v>46</v>
@@ -4667,24 +4796,24 @@
         <v>1</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E88" s="12">
         <v>56</v>
@@ -4696,24 +4825,24 @@
         <v>1</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E89" s="12">
         <v>24</v>
@@ -4725,24 +4854,24 @@
         <v>0.96</v>
       </c>
       <c r="H89" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I89" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B90" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E90" s="12">
         <v>10</v>
@@ -4754,24 +4883,24 @@
         <v>0.4</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I90" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E91" s="12">
         <v>46</v>
@@ -4783,24 +4912,24 @@
         <v>1</v>
       </c>
       <c r="H91" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I91" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E92" s="12">
         <v>56</v>
@@ -4812,24 +4941,24 @@
         <v>1</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E93" s="12">
         <v>24</v>
@@ -4841,24 +4970,24 @@
         <v>0.96</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I93" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E94" s="12">
         <v>10</v>
@@ -4870,24 +4999,24 @@
         <v>0.4</v>
       </c>
       <c r="H94" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B95" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E95" s="12">
         <v>46</v>
@@ -4899,24 +5028,24 @@
         <v>1</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B96" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E96" s="12">
         <v>56</v>
@@ -4928,24 +5057,24 @@
         <v>1</v>
       </c>
       <c r="H96" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I96" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B97" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E97" s="12">
         <v>24</v>
@@ -4957,24 +5086,24 @@
         <v>0.96</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I97" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B98" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E98" s="12">
         <v>10</v>
@@ -4986,24 +5115,24 @@
         <v>0.4</v>
       </c>
       <c r="H98" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I98" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B99" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E99" s="12">
         <v>87</v>
@@ -5015,24 +5144,24 @@
         <v>0.8787878787878788</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I99" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B100" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E100" s="12">
         <v>77</v>
@@ -5044,24 +5173,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B101" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E101" s="12">
         <v>77</v>
@@ -5073,24 +5202,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H101" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B102" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E102" s="12">
         <v>77</v>
@@ -5102,24 +5231,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B103" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E103" s="12">
         <v>77</v>
@@ -5131,24 +5260,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I103" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B104" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E104" s="12">
         <v>77</v>
@@ -5160,24 +5289,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B105" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E105" s="12">
         <v>77</v>
@@ -5189,24 +5318,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H105" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B106" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E106" s="12">
         <v>77</v>
@@ -5218,24 +5347,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B107" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E107" s="12">
         <v>77</v>
@@ -5247,24 +5376,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H107" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I107" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E108" s="12">
         <v>77</v>
@@ -5276,24 +5405,24 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B109" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E109" s="12">
         <v>57</v>
@@ -5305,24 +5434,24 @@
         <v>0.5135135135135135</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I109" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B110" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E110" s="12">
         <v>93</v>
@@ -5334,24 +5463,24 @@
         <v>0.6739130434782609</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E111" s="12">
         <v>44</v>
@@ -5363,24 +5492,24 @@
         <v>0.5432098765432098</v>
       </c>
       <c r="H111" s="13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B112" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E112" s="12">
         <v>62</v>
@@ -5392,24 +5521,24 @@
         <v>0.5585585585585585</v>
       </c>
       <c r="H112" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B113" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E113" s="12">
         <v>98</v>
@@ -5421,24 +5550,24 @@
         <v>0.7101449275362319</v>
       </c>
       <c r="H113" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B114" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E114" s="12">
         <v>52</v>
@@ -5450,24 +5579,24 @@
         <v>0.6419753086419753</v>
       </c>
       <c r="H114" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I114" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B115" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E115" s="12">
         <v>101</v>
@@ -5479,24 +5608,24 @@
         <v>0.9099099099099099</v>
       </c>
       <c r="H115" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B116" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E116" s="12">
         <v>131</v>
@@ -5508,24 +5637,24 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B117" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E117" s="12">
         <v>78</v>
@@ -5537,24 +5666,24 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H117" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I117" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B118" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E118" s="12">
         <v>102</v>
@@ -5566,24 +5695,24 @@
         <v>0.918918918918919</v>
       </c>
       <c r="H118" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I118" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B119" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E119" s="12">
         <v>131</v>
@@ -5595,24 +5724,24 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H119" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I119" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B120" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E120" s="12">
         <v>78</v>
@@ -5624,24 +5753,24 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H120" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I120" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B121" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E121" s="12">
         <v>102</v>
@@ -5653,24 +5782,24 @@
         <v>0.918918918918919</v>
       </c>
       <c r="H121" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I121" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B122" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E122" s="12">
         <v>131</v>
@@ -5682,24 +5811,24 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H122" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I122" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B123" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E123" s="12">
         <v>78</v>
@@ -5711,24 +5840,24 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H123" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I123" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B124" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E124" s="12">
         <v>111</v>
@@ -5740,24 +5869,24 @@
         <v>1</v>
       </c>
       <c r="H124" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I124" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B125" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E125" s="12">
         <v>134</v>
@@ -5769,24 +5898,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H125" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I125" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B126" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E126" s="12">
         <v>79</v>
@@ -5798,24 +5927,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H126" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I126" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B127" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E127" s="12">
         <v>111</v>
@@ -5827,24 +5956,24 @@
         <v>1</v>
       </c>
       <c r="H127" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I127" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B128" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E128" s="12">
         <v>134</v>
@@ -5856,24 +5985,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H128" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I128" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B129" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E129" s="12">
         <v>79</v>
@@ -5885,24 +6014,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H129" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I129" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B130" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E130" s="12">
         <v>111</v>
@@ -5914,24 +6043,24 @@
         <v>1</v>
       </c>
       <c r="H130" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I130" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B131" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E131" s="12">
         <v>134</v>
@@ -5943,24 +6072,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H131" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B132" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E132" s="12">
         <v>79</v>
@@ -5972,24 +6101,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H132" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I132" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B133" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E133" s="12">
         <v>111</v>
@@ -6001,24 +6130,24 @@
         <v>1</v>
       </c>
       <c r="H133" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I133" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B134" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E134" s="12">
         <v>134</v>
@@ -6030,24 +6159,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H134" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I134" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B135" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E135" s="12">
         <v>79</v>
@@ -6059,24 +6188,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H135" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I135" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B136" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C136" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E136" s="12">
         <v>111</v>
@@ -6088,24 +6217,24 @@
         <v>1</v>
       </c>
       <c r="H136" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I136" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B137" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E137" s="12">
         <v>134</v>
@@ -6117,24 +6246,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H137" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I137" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B138" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E138" s="12">
         <v>79</v>
@@ -6146,24 +6275,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I138" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B139" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E139" s="12">
         <v>111</v>
@@ -6175,24 +6304,24 @@
         <v>1</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I139" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B140" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C140" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E140" s="12">
         <v>134</v>
@@ -6204,24 +6333,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I140" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B141" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E141" s="12">
         <v>79</v>
@@ -6233,24 +6362,24 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I141" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B142" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E142" s="12">
         <v>111</v>
@@ -6262,24 +6391,24 @@
         <v>1</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I142" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B143" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E143" s="12">
         <v>134</v>
@@ -6291,24 +6420,24 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I143" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B144" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D144" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E144" s="12">
         <v>79</v>
@@ -6320,53 +6449,53 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H144" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I144" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B145" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F145" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G145" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H145" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B146" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E146" s="12">
         <v>3</v>
@@ -6378,24 +6507,24 @@
         <v>0.11538461538461539</v>
       </c>
       <c r="H146" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B147" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E147" s="12">
         <v>77</v>
@@ -6407,24 +6536,24 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="H147" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B148" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E148" s="12">
         <v>17</v>
@@ -6436,24 +6565,24 @@
         <v>0.16346153846153846</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B149" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C149" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E149" s="12">
         <v>17</v>
@@ -6465,24 +6594,24 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="H149" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B150" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E150" s="12">
         <v>111</v>
@@ -6494,24 +6623,24 @@
         <v>0.8809523809523809</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I150" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B151" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E151" s="12">
         <v>71</v>
@@ -6523,24 +6652,24 @@
         <v>0.6826923076923077</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B152" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C152" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E152" s="12">
         <v>17</v>
@@ -6552,24 +6681,24 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="H152" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I152" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B153" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C153" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E153" s="12">
         <v>116</v>
@@ -6581,24 +6710,24 @@
         <v>0.9206349206349206</v>
       </c>
       <c r="H153" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I153" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B154" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C154" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E154" s="12">
         <v>89</v>
@@ -6610,24 +6739,24 @@
         <v>0.8557692307692307</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I154" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B155" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C155" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E155" s="12">
         <v>23</v>
@@ -6639,24 +6768,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H155" s="13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I155" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B156" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E156" s="12">
         <v>124</v>
@@ -6668,24 +6797,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I156" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B157" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E157" s="12">
         <v>98</v>
@@ -6697,24 +6826,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H157" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B158" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C158" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D158" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E158" s="12">
         <v>23</v>
@@ -6726,24 +6855,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I158" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B159" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C159" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D159" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E159" s="12">
         <v>124</v>
@@ -6755,24 +6884,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H159" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I159" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B160" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C160" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E160" s="12">
         <v>98</v>
@@ -6784,24 +6913,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I160" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B161" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C161" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E161" s="12">
         <v>23</v>
@@ -6813,24 +6942,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H161" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I161" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B162" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C162" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E162" s="12">
         <v>124</v>
@@ -6842,24 +6971,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H162" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B163" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C163" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E163" s="12">
         <v>98</v>
@@ -6871,24 +7000,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H163" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B164" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C164" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E164" s="12">
         <v>23</v>
@@ -6900,24 +7029,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H164" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I164" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B165" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C165" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E165" s="12">
         <v>124</v>
@@ -6929,24 +7058,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H165" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I165" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B166" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C166" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E166" s="12">
         <v>98</v>
@@ -6958,24 +7087,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H166" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I166" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B167" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C167" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E167" s="12">
         <v>23</v>
@@ -6987,24 +7116,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H167" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B168" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C168" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D168" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E168" s="12">
         <v>124</v>
@@ -7016,24 +7145,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I168" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B169" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C169" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E169" s="12">
         <v>98</v>
@@ -7045,24 +7174,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H169" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I169" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B170" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E170" s="12">
         <v>23</v>
@@ -7074,24 +7203,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H170" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I170" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B171" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C171" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E171" s="12">
         <v>124</v>
@@ -7103,24 +7232,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H171" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I171" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B172" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C172" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E172" s="12">
         <v>98</v>
@@ -7132,24 +7261,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H172" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I172" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B173" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C173" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E173" s="12">
         <v>23</v>
@@ -7161,24 +7290,24 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H173" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I173" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B174" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C174" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E174" s="12">
         <v>124</v>
@@ -7190,24 +7319,24 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H174" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I174" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B175" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C175" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D175" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E175" s="12">
         <v>98</v>
@@ -7219,24 +7348,24 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H175" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I175" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B176" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C176" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D176" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E176" s="12">
         <v>16</v>
@@ -7248,24 +7377,24 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="H176" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I176" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B177" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C177" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D177" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E177" s="12">
         <v>39</v>
@@ -7277,24 +7406,24 @@
         <v>0.4588235294117647</v>
       </c>
       <c r="H177" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I177" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B178" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C178" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D178" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E178" s="12">
         <v>11</v>
@@ -7306,24 +7435,24 @@
         <v>0.10784313725490197</v>
       </c>
       <c r="H178" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I178" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B179" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C179" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D179" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E179" s="12">
         <v>29</v>
@@ -7335,24 +7464,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H179" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I179" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B180" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C180" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D180" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E180" s="12">
         <v>63</v>
@@ -7364,24 +7493,24 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H180" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I180" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B181" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C181" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D181" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E181" s="12">
         <v>22</v>
@@ -7393,24 +7522,24 @@
         <v>0.21568627450980393</v>
       </c>
       <c r="H181" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I181" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B182" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C182" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D182" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E182" s="12">
         <v>29</v>
@@ -7422,24 +7551,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H182" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I182" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B183" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C183" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D183" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E183" s="12">
         <v>63</v>
@@ -7451,24 +7580,24 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H183" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I183" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B184" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C184" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D184" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E184" s="12">
         <v>23</v>
@@ -7480,24 +7609,24 @@
         <v>0.22549019607843138</v>
       </c>
       <c r="H184" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I184" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B185" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C185" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D185" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E185" s="12">
         <v>29</v>
@@ -7509,24 +7638,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H185" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I185" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B186" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C186" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D186" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E186" s="12">
         <v>63</v>
@@ -7538,24 +7667,24 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H186" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I186" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B187" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C187" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D187" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E187" s="12">
         <v>23</v>
@@ -7567,24 +7696,24 @@
         <v>0.22549019607843138</v>
       </c>
       <c r="H187" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I187" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C188" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D188" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E188" s="12">
         <v>29</v>
@@ -7596,24 +7725,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H188" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C189" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D189" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E189" s="12">
         <v>65</v>
@@ -7625,24 +7754,24 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H189" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C190" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D190" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E190" s="12">
         <v>24</v>
@@ -7654,24 +7783,24 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H190" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C191" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D191" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E191" s="12">
         <v>29</v>
@@ -7683,24 +7812,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H191" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C192" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D192" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E192" s="12">
         <v>65</v>
@@ -7712,24 +7841,24 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H192" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B193" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C193" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D193" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E193" s="12">
         <v>24</v>
@@ -7741,24 +7870,24 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H193" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C194" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D194" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E194" s="12">
         <v>29</v>
@@ -7770,24 +7899,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H194" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C195" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D195" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E195" s="12">
         <v>65</v>
@@ -7799,24 +7928,24 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H195" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C196" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D196" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E196" s="12">
         <v>24</v>
@@ -7828,24 +7957,24 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H196" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C197" s="13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D197" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E197" s="12">
         <v>29</v>
@@ -7857,24 +7986,24 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H197" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C198" s="13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D198" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E198" s="12">
         <v>65</v>
@@ -7886,24 +8015,24 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H198" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B199" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C199" s="13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D199" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E199" s="12">
         <v>24</v>
@@ -7915,111 +8044,111 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H199" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C200" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D200" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E200" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G200" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H200" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C201" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D201" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E201" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G201" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H201" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C202" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D202" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E202" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G202" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H202" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C203" s="13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D203" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E203" s="12">
         <v>24</v>
@@ -8031,24 +8160,24 @@
         <v>0.17647058823529413</v>
       </c>
       <c r="H203" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D204" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E204" s="12">
         <v>30</v>
@@ -8060,24 +8189,24 @@
         <v>0.22058823529411764</v>
       </c>
       <c r="H204" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D205" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E205" s="12">
         <v>45</v>
@@ -8089,24 +8218,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H205" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B206" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C206" s="13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D206" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E206" s="12">
         <v>45</v>
@@ -8118,24 +8247,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H206" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C207" s="13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D207" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E207" s="12">
         <v>45</v>
@@ -8147,24 +8276,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H207" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C208" s="13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D208" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E208" s="12">
         <v>45</v>
@@ -8176,24 +8305,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H208" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C209" s="13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D209" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E209" s="12">
         <v>45</v>
@@ -8205,24 +8334,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H209" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C210" s="13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D210" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E210" s="12">
         <v>45</v>
@@ -8234,24 +8363,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H210" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C211" s="13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D211" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E211" s="12">
         <v>45</v>
@@ -8263,24 +8392,24 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H211" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I211" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B212" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C212" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D212" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E212" s="12">
         <v>81</v>
@@ -8292,24 +8421,24 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="H212" s="13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B213" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C213" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D213" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E213" s="12">
         <v>1</v>
@@ -8321,24 +8450,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H213" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I213" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B214" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C214" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D214" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E214" s="12">
         <v>84</v>
@@ -8350,24 +8479,24 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="H214" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I214" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B215" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C215" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D215" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E215" s="12">
         <v>0</v>
@@ -8379,24 +8508,24 @@
         <v>0</v>
       </c>
       <c r="H215" s="13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I215" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B216" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C216" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D216" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E216" s="12">
         <v>124</v>
@@ -8408,24 +8537,24 @@
         <v>0.656084656084656</v>
       </c>
       <c r="H216" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I216" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B217" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C217" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D217" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E217" s="12">
         <v>0</v>
@@ -8437,24 +8566,24 @@
         <v>0</v>
       </c>
       <c r="H217" s="13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I217" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B218" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C218" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D218" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E218" s="12">
         <v>148</v>
@@ -8466,24 +8595,24 @@
         <v>0.783068783068783</v>
       </c>
       <c r="H218" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I218" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B219" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C219" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D219" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E219" s="12">
         <v>1</v>
@@ -8495,24 +8624,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H219" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I219" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B220" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C220" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D220" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E220" s="12">
         <v>154</v>
@@ -8524,24 +8653,24 @@
         <v>0.8148148148148148</v>
       </c>
       <c r="H220" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I220" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B221" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C221" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D221" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E221" s="12">
         <v>1</v>
@@ -8553,24 +8682,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H221" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I221" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B222" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C222" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D222" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E222" s="12">
         <v>160</v>
@@ -8582,24 +8711,24 @@
         <v>0.5194805194805194</v>
       </c>
       <c r="H222" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B223" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C223" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D223" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E223" s="12">
         <v>1</v>
@@ -8611,24 +8740,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H223" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I223" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B224" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C224" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D224" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E224" s="12">
         <v>1</v>
@@ -8640,24 +8769,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H224" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I224" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B225" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C225" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E225" s="12">
         <v>161</v>
@@ -8669,24 +8798,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H225" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I225" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B226" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C226" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D226" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E226" s="12">
         <v>1</v>
@@ -8698,24 +8827,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H226" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I226" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B227" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C227" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D227" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E227" s="12">
         <v>161</v>
@@ -8727,24 +8856,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H227" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I227" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B228" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C228" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D228" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E228" s="12">
         <v>1</v>
@@ -8756,24 +8885,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H228" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I228" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B229" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C229" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D229" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E229" s="12">
         <v>161</v>
@@ -8785,24 +8914,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H229" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I229" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B230" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C230" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D230" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E230" s="12">
         <v>1</v>
@@ -8814,24 +8943,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H230" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I230" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B231" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C231" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D231" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E231" s="12">
         <v>161</v>
@@ -8843,24 +8972,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H231" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I231" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B232" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C232" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D232" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E232" s="12">
         <v>1</v>
@@ -8872,24 +9001,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H232" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I232" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B233" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C233" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D233" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E233" s="12">
         <v>161</v>
@@ -8901,24 +9030,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H233" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I233" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B234" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C234" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D234" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E234" s="12">
         <v>1</v>
@@ -8930,24 +9059,24 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H234" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I234" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B235" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C235" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D235" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E235" s="12">
         <v>161</v>
@@ -8959,24 +9088,24 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H235" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I235" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B236" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C236" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D236" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E236" s="12">
         <v>9</v>
@@ -8988,24 +9117,24 @@
         <v>0.06040268456375839</v>
       </c>
       <c r="H236" s="13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I236" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B237" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C237" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D237" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E237" s="12">
         <v>21</v>
@@ -9017,24 +9146,24 @@
         <v>0.14093959731543623</v>
       </c>
       <c r="H237" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I237" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B238" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C238" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D238" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E238" s="12">
         <v>23</v>
@@ -9046,24 +9175,24 @@
         <v>0.15436241610738255</v>
       </c>
       <c r="H238" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I238" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B239" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C239" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D239" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E239" s="12">
         <v>31</v>
@@ -9075,24 +9204,24 @@
         <v>0.2080536912751678</v>
       </c>
       <c r="H239" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I239" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B240" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C240" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D240" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E240" s="12">
         <v>34</v>
@@ -9104,24 +9233,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H240" s="13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I240" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B241" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C241" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D241" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E241" s="12">
         <v>34</v>
@@ -9133,24 +9262,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H241" s="13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I241" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B242" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C242" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D242" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E242" s="12">
         <v>34</v>
@@ -9162,24 +9291,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H242" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I242" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B243" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C243" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D243" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E243" s="12">
         <v>34</v>
@@ -9191,24 +9320,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H243" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I243" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B244" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C244" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D244" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E244" s="12">
         <v>34</v>
@@ -9220,24 +9349,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H244" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I244" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B245" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C245" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D245" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E245" s="12">
         <v>34</v>
@@ -9249,24 +9378,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H245" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I245" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B246" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C246" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D246" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E246" s="12">
         <v>34</v>
@@ -9278,24 +9407,24 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H246" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I246" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B247" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C247" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D247" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E247" s="12">
         <v>34</v>
@@ -9307,10 +9436,10 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H247" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I247" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -9331,58 +9460,58 @@
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="254">
   <si>
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
@@ -411,10 +411,7 @@
     <t>No group details</t>
   </si>
   <si>
-    <t>Unclassified</t>
-  </si>
-  <si>
-    <t>No parseable group-level values: Yet to Launch</t>
+    <t>Yet to Launch</t>
   </si>
   <si>
     <t>01/08/2024</t>
@@ -606,9 +603,6 @@
     <t>79/81 signed</t>
   </si>
   <si>
-    <t>No parseable group-level values: Yet to sign</t>
-  </si>
-  <si>
     <t>12% Signed (3/26 units)</t>
   </si>
   <si>
@@ -684,7 +678,7 @@
     <t>24/102 signed</t>
   </si>
   <si>
-    <t>No parseable group-level values: Yet to Sign</t>
+    <t>Yet to Sign</t>
   </si>
   <si>
     <t>18% Signed (24/136 units)</t>
@@ -2658,7 +2652,7 @@
         <v>131</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>113</v>
@@ -2670,7 +2664,7 @@
         <v>113</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>115</v>
@@ -2687,7 +2681,7 @@
         <v>131</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>113</v>
@@ -2699,7 +2693,7 @@
         <v>113</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>115</v>
@@ -2716,7 +2710,7 @@
         <v>131</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>113</v>
@@ -2728,7 +2722,7 @@
         <v>113</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>115</v>
@@ -2736,7 +2730,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>5</v>
@@ -2755,7 +2749,7 @@
       </c>
       <c r="G16" s="14"/>
       <c r="H16" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>115</v>
@@ -2763,7 +2757,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>5</v>
@@ -2782,7 +2776,7 @@
       </c>
       <c r="G17" s="14"/>
       <c r="H17" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>115</v>
@@ -2790,7 +2784,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>5</v>
@@ -2809,7 +2803,7 @@
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>115</v>
@@ -2836,7 +2830,7 @@
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>115</v>
@@ -2844,7 +2838,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>5</v>
@@ -2865,7 +2859,7 @@
         <v>0.3008849557522124</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>115</v>
@@ -2873,7 +2867,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>5</v>
@@ -2894,7 +2888,7 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I21" s="12" t="s">
         <v>115</v>
@@ -2923,7 +2917,7 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>115</v>
@@ -2931,7 +2925,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>5</v>
@@ -2952,7 +2946,7 @@
         <v>0.4778761061946903</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I23" s="12" t="s">
         <v>115</v>
@@ -2981,7 +2975,7 @@
         <v>0.5575221238938053</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>115</v>
@@ -3010,7 +3004,7 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>115</v>
@@ -3039,7 +3033,7 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>115</v>
@@ -3068,7 +3062,7 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I27" s="12" t="s">
         <v>126</v>
@@ -3097,7 +3091,7 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I28" s="12" t="s">
         <v>126</v>
@@ -3126,7 +3120,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I29" s="12" t="s">
         <v>126</v>
@@ -3155,7 +3149,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I30" s="12" t="s">
         <v>126</v>
@@ -3184,7 +3178,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I31" s="12" t="s">
         <v>126</v>
@@ -3213,7 +3207,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I32" s="12" t="s">
         <v>126</v>
@@ -3221,7 +3215,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>6</v>
@@ -3240,7 +3234,7 @@
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I33" s="12" t="s">
         <v>115</v>
@@ -3248,7 +3242,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>6</v>
@@ -3267,7 +3261,7 @@
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I34" s="12" t="s">
         <v>115</v>
@@ -3294,7 +3288,7 @@
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I35" s="12" t="s">
         <v>115</v>
@@ -3302,7 +3296,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>6</v>
@@ -3321,7 +3315,7 @@
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>115</v>
@@ -3329,7 +3323,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>6</v>
@@ -3348,7 +3342,7 @@
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I37" s="12" t="s">
         <v>115</v>
@@ -3375,7 +3369,7 @@
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I38" s="12" t="s">
         <v>115</v>
@@ -3383,7 +3377,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>6</v>
@@ -3404,7 +3398,7 @@
         <v>0.3125</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I39" s="12" t="s">
         <v>115</v>
@@ -3433,7 +3427,7 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I40" s="12" t="s">
         <v>115</v>
@@ -3462,7 +3456,7 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I41" s="12" t="s">
         <v>115</v>
@@ -3491,7 +3485,7 @@
         <v>0.4375</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I42" s="12" t="s">
         <v>115</v>
@@ -3520,7 +3514,7 @@
         <v>0.4375</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I43" s="12" t="s">
         <v>126</v>
@@ -3549,7 +3543,7 @@
         <v>0.4375</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I44" s="12" t="s">
         <v>126</v>
@@ -3578,7 +3572,7 @@
         <v>0.4375</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I45" s="12" t="s">
         <v>126</v>
@@ -3607,7 +3601,7 @@
         <v>0.4375</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I46" s="12" t="s">
         <v>126</v>
@@ -3636,7 +3630,7 @@
         <v>0.4375</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I47" s="12" t="s">
         <v>126</v>
@@ -3665,7 +3659,7 @@
         <v>0.4375</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I48" s="12" t="s">
         <v>126</v>
@@ -3694,7 +3688,7 @@
         <v>0.8383838383838383</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I49" s="12" t="s">
         <v>115</v>
@@ -3723,7 +3717,7 @@
         <v>0.6194690265486725</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I50" s="12" t="s">
         <v>115</v>
@@ -3752,7 +3746,7 @@
         <v>0.6194690265486725</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I51" s="12" t="s">
         <v>115</v>
@@ -3781,7 +3775,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I52" s="12" t="s">
         <v>115</v>
@@ -3810,7 +3804,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>126</v>
@@ -3839,7 +3833,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I54" s="12" t="s">
         <v>126</v>
@@ -3868,7 +3862,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I55" s="12" t="s">
         <v>126</v>
@@ -3897,7 +3891,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I56" s="12" t="s">
         <v>126</v>
@@ -3926,7 +3920,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I57" s="12" t="s">
         <v>126</v>
@@ -3955,7 +3949,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I58" s="12" t="s">
         <v>126</v>
@@ -3984,7 +3978,7 @@
         <v>0.9782608695652174</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I59" s="12" t="s">
         <v>115</v>
@@ -4013,7 +4007,7 @@
         <v>0.8392857142857143</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I60" s="12" t="s">
         <v>115</v>
@@ -4042,7 +4036,7 @@
         <v>0.52</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I61" s="12" t="s">
         <v>115</v>
@@ -4071,7 +4065,7 @@
         <v>0.12</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I62" s="12" t="s">
         <v>115</v>
@@ -4100,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I63" s="12" t="s">
         <v>115</v>
@@ -4129,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>115</v>
@@ -4158,7 +4152,7 @@
         <v>0.96</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>115</v>
@@ -4187,7 +4181,7 @@
         <v>0.28</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I66" s="12" t="s">
         <v>115</v>
@@ -4216,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I67" s="12" t="s">
         <v>115</v>
@@ -4245,7 +4239,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I68" s="12" t="s">
         <v>115</v>
@@ -4274,7 +4268,7 @@
         <v>0.96</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I69" s="12" t="s">
         <v>115</v>
@@ -4303,7 +4297,7 @@
         <v>0.32</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I70" s="12" t="s">
         <v>115</v>
@@ -4332,7 +4326,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I71" s="12" t="s">
         <v>115</v>
@@ -4361,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I72" s="12" t="s">
         <v>115</v>
@@ -4390,7 +4384,7 @@
         <v>0.96</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I73" s="12" t="s">
         <v>115</v>
@@ -4419,7 +4413,7 @@
         <v>0.4</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I74" s="12" t="s">
         <v>115</v>
@@ -4448,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I75" s="12" t="s">
         <v>126</v>
@@ -4477,7 +4471,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I76" s="12" t="s">
         <v>126</v>
@@ -4506,7 +4500,7 @@
         <v>0.96</v>
       </c>
       <c r="H77" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I77" s="12" t="s">
         <v>126</v>
@@ -4535,7 +4529,7 @@
         <v>0.4</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I78" s="12" t="s">
         <v>126</v>
@@ -4564,7 +4558,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I79" s="12" t="s">
         <v>126</v>
@@ -4593,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I80" s="12" t="s">
         <v>126</v>
@@ -4622,7 +4616,7 @@
         <v>0.96</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I81" s="12" t="s">
         <v>126</v>
@@ -4651,7 +4645,7 @@
         <v>0.4</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I82" s="12" t="s">
         <v>126</v>
@@ -4680,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I83" s="12" t="s">
         <v>126</v>
@@ -4709,7 +4703,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I84" s="12" t="s">
         <v>126</v>
@@ -4738,7 +4732,7 @@
         <v>0.96</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I85" s="12" t="s">
         <v>126</v>
@@ -4767,7 +4761,7 @@
         <v>0.4</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I86" s="12" t="s">
         <v>126</v>
@@ -4796,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I87" s="12" t="s">
         <v>126</v>
@@ -4825,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I88" s="12" t="s">
         <v>126</v>
@@ -4854,7 +4848,7 @@
         <v>0.96</v>
       </c>
       <c r="H89" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I89" s="12" t="s">
         <v>126</v>
@@ -4883,7 +4877,7 @@
         <v>0.4</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I90" s="12" t="s">
         <v>126</v>
@@ -4912,7 +4906,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I91" s="12" t="s">
         <v>126</v>
@@ -4941,7 +4935,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I92" s="12" t="s">
         <v>126</v>
@@ -4970,7 +4964,7 @@
         <v>0.96</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I93" s="12" t="s">
         <v>126</v>
@@ -4999,7 +4993,7 @@
         <v>0.4</v>
       </c>
       <c r="H94" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I94" s="12" t="s">
         <v>126</v>
@@ -5028,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I95" s="12" t="s">
         <v>126</v>
@@ -5057,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I96" s="12" t="s">
         <v>126</v>
@@ -5086,7 +5080,7 @@
         <v>0.96</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I97" s="12" t="s">
         <v>126</v>
@@ -5115,7 +5109,7 @@
         <v>0.4</v>
       </c>
       <c r="H98" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I98" s="12" t="s">
         <v>126</v>
@@ -5144,7 +5138,7 @@
         <v>0.8787878787878788</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I99" s="12" t="s">
         <v>115</v>
@@ -5173,7 +5167,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I100" s="12" t="s">
         <v>115</v>
@@ -5202,7 +5196,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H101" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I101" s="12" t="s">
         <v>115</v>
@@ -5231,7 +5225,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I102" s="12" t="s">
         <v>115</v>
@@ -5260,7 +5254,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I103" s="12" t="s">
         <v>126</v>
@@ -5289,7 +5283,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I104" s="12" t="s">
         <v>126</v>
@@ -5318,7 +5312,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H105" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I105" s="12" t="s">
         <v>126</v>
@@ -5347,7 +5341,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I106" s="12" t="s">
         <v>126</v>
@@ -5376,7 +5370,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H107" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I107" s="12" t="s">
         <v>126</v>
@@ -5405,7 +5399,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I108" s="12" t="s">
         <v>126</v>
@@ -5413,7 +5407,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B109" s="12" t="s">
         <v>10</v>
@@ -5434,7 +5428,7 @@
         <v>0.5135135135135135</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I109" s="12" t="s">
         <v>115</v>
@@ -5442,7 +5436,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B110" s="12" t="s">
         <v>10</v>
@@ -5463,7 +5457,7 @@
         <v>0.6739130434782609</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I110" s="12" t="s">
         <v>115</v>
@@ -5471,7 +5465,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>10</v>
@@ -5492,7 +5486,7 @@
         <v>0.5432098765432098</v>
       </c>
       <c r="H111" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I111" s="12" t="s">
         <v>115</v>
@@ -5521,7 +5515,7 @@
         <v>0.5585585585585585</v>
       </c>
       <c r="H112" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I112" s="12" t="s">
         <v>115</v>
@@ -5550,7 +5544,7 @@
         <v>0.7101449275362319</v>
       </c>
       <c r="H113" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I113" s="12" t="s">
         <v>115</v>
@@ -5579,7 +5573,7 @@
         <v>0.6419753086419753</v>
       </c>
       <c r="H114" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I114" s="12" t="s">
         <v>115</v>
@@ -5587,7 +5581,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B115" s="12" t="s">
         <v>10</v>
@@ -5608,7 +5602,7 @@
         <v>0.9099099099099099</v>
       </c>
       <c r="H115" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I115" s="12" t="s">
         <v>115</v>
@@ -5616,7 +5610,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B116" s="12" t="s">
         <v>10</v>
@@ -5637,7 +5631,7 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I116" s="12" t="s">
         <v>115</v>
@@ -5645,7 +5639,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B117" s="12" t="s">
         <v>10</v>
@@ -5666,7 +5660,7 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H117" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I117" s="12" t="s">
         <v>115</v>
@@ -5695,7 +5689,7 @@
         <v>0.918918918918919</v>
       </c>
       <c r="H118" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I118" s="12" t="s">
         <v>115</v>
@@ -5724,7 +5718,7 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H119" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I119" s="12" t="s">
         <v>115</v>
@@ -5753,7 +5747,7 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H120" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I120" s="12" t="s">
         <v>115</v>
@@ -5782,7 +5776,7 @@
         <v>0.918918918918919</v>
       </c>
       <c r="H121" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I121" s="12" t="s">
         <v>115</v>
@@ -5811,7 +5805,7 @@
         <v>0.9492753623188406</v>
       </c>
       <c r="H122" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I122" s="12" t="s">
         <v>115</v>
@@ -5840,7 +5834,7 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="H123" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I123" s="12" t="s">
         <v>115</v>
@@ -5869,7 +5863,7 @@
         <v>1</v>
       </c>
       <c r="H124" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I124" s="12" t="s">
         <v>115</v>
@@ -5898,7 +5892,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H125" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I125" s="12" t="s">
         <v>115</v>
@@ -5927,7 +5921,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H126" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I126" s="12" t="s">
         <v>115</v>
@@ -5956,7 +5950,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I127" s="12" t="s">
         <v>126</v>
@@ -5985,7 +5979,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H128" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I128" s="12" t="s">
         <v>126</v>
@@ -6014,7 +6008,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H129" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I129" s="12" t="s">
         <v>126</v>
@@ -6043,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="H130" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I130" s="12" t="s">
         <v>126</v>
@@ -6072,7 +6066,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H131" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I131" s="12" t="s">
         <v>126</v>
@@ -6101,7 +6095,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H132" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I132" s="12" t="s">
         <v>126</v>
@@ -6130,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I133" s="12" t="s">
         <v>126</v>
@@ -6159,7 +6153,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H134" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I134" s="12" t="s">
         <v>126</v>
@@ -6188,7 +6182,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H135" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I135" s="12" t="s">
         <v>126</v>
@@ -6217,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="H136" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I136" s="12" t="s">
         <v>126</v>
@@ -6246,7 +6240,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H137" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I137" s="12" t="s">
         <v>126</v>
@@ -6275,7 +6269,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I138" s="12" t="s">
         <v>126</v>
@@ -6304,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I139" s="12" t="s">
         <v>126</v>
@@ -6333,7 +6327,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I140" s="12" t="s">
         <v>126</v>
@@ -6362,7 +6356,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I141" s="12" t="s">
         <v>126</v>
@@ -6391,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I142" s="12" t="s">
         <v>126</v>
@@ -6420,7 +6414,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I143" s="12" t="s">
         <v>126</v>
@@ -6449,7 +6443,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H144" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I144" s="12" t="s">
         <v>126</v>
@@ -6466,7 +6460,7 @@
         <v>131</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="E145" s="12" t="s">
         <v>113</v>
@@ -6478,7 +6472,7 @@
         <v>113</v>
       </c>
       <c r="H145" s="13" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="I145" s="12" t="s">
         <v>115</v>
@@ -6486,7 +6480,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B146" s="12" t="s">
         <v>11</v>
@@ -6507,7 +6501,7 @@
         <v>0.11538461538461539</v>
       </c>
       <c r="H146" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I146" s="12" t="s">
         <v>115</v>
@@ -6515,7 +6509,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B147" s="12" t="s">
         <v>11</v>
@@ -6536,7 +6530,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="H147" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I147" s="12" t="s">
         <v>115</v>
@@ -6544,7 +6538,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B148" s="12" t="s">
         <v>11</v>
@@ -6565,7 +6559,7 @@
         <v>0.16346153846153846</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I148" s="12" t="s">
         <v>115</v>
@@ -6594,7 +6588,7 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="H149" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I149" s="12" t="s">
         <v>115</v>
@@ -6623,7 +6617,7 @@
         <v>0.8809523809523809</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I150" s="12" t="s">
         <v>115</v>
@@ -6652,7 +6646,7 @@
         <v>0.6826923076923077</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I151" s="12" t="s">
         <v>115</v>
@@ -6681,7 +6675,7 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="H152" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I152" s="12" t="s">
         <v>115</v>
@@ -6710,7 +6704,7 @@
         <v>0.9206349206349206</v>
       </c>
       <c r="H153" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I153" s="12" t="s">
         <v>115</v>
@@ -6739,7 +6733,7 @@
         <v>0.8557692307692307</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I154" s="12" t="s">
         <v>115</v>
@@ -6768,7 +6762,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H155" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I155" s="12" t="s">
         <v>115</v>
@@ -6797,7 +6791,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I156" s="12" t="s">
         <v>115</v>
@@ -6826,7 +6820,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H157" s="13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I157" s="12" t="s">
         <v>115</v>
@@ -6855,7 +6849,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I158" s="12" t="s">
         <v>126</v>
@@ -6884,7 +6878,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H159" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I159" s="12" t="s">
         <v>126</v>
@@ -6913,7 +6907,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I160" s="12" t="s">
         <v>126</v>
@@ -6942,7 +6936,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H161" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I161" s="12" t="s">
         <v>126</v>
@@ -6971,7 +6965,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H162" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I162" s="12" t="s">
         <v>126</v>
@@ -7000,7 +6994,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H163" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I163" s="12" t="s">
         <v>126</v>
@@ -7029,7 +7023,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H164" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I164" s="12" t="s">
         <v>126</v>
@@ -7058,7 +7052,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H165" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I165" s="12" t="s">
         <v>126</v>
@@ -7087,7 +7081,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H166" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I166" s="12" t="s">
         <v>126</v>
@@ -7116,7 +7110,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H167" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I167" s="12" t="s">
         <v>126</v>
@@ -7145,7 +7139,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I168" s="12" t="s">
         <v>126</v>
@@ -7174,7 +7168,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H169" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I169" s="12" t="s">
         <v>126</v>
@@ -7203,7 +7197,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H170" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I170" s="12" t="s">
         <v>126</v>
@@ -7232,7 +7226,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H171" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I171" s="12" t="s">
         <v>126</v>
@@ -7261,7 +7255,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H172" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I172" s="12" t="s">
         <v>126</v>
@@ -7290,7 +7284,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H173" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I173" s="12" t="s">
         <v>126</v>
@@ -7319,7 +7313,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H174" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I174" s="12" t="s">
         <v>126</v>
@@ -7348,7 +7342,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H175" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I175" s="12" t="s">
         <v>126</v>
@@ -7377,7 +7371,7 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="H176" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I176" s="12" t="s">
         <v>115</v>
@@ -7406,7 +7400,7 @@
         <v>0.4588235294117647</v>
       </c>
       <c r="H177" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I177" s="12" t="s">
         <v>115</v>
@@ -7435,7 +7429,7 @@
         <v>0.10784313725490197</v>
       </c>
       <c r="H178" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I178" s="12" t="s">
         <v>115</v>
@@ -7464,7 +7458,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H179" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I179" s="12" t="s">
         <v>115</v>
@@ -7493,7 +7487,7 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H180" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I180" s="12" t="s">
         <v>115</v>
@@ -7522,7 +7516,7 @@
         <v>0.21568627450980393</v>
       </c>
       <c r="H181" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I181" s="12" t="s">
         <v>115</v>
@@ -7551,7 +7545,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H182" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I182" s="12" t="s">
         <v>126</v>
@@ -7580,7 +7574,7 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H183" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I183" s="12" t="s">
         <v>126</v>
@@ -7609,7 +7603,7 @@
         <v>0.22549019607843138</v>
       </c>
       <c r="H184" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I184" s="12" t="s">
         <v>126</v>
@@ -7638,7 +7632,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H185" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I185" s="12" t="s">
         <v>126</v>
@@ -7667,7 +7661,7 @@
         <v>0.7411764705882353</v>
       </c>
       <c r="H186" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I186" s="12" t="s">
         <v>126</v>
@@ -7696,7 +7690,7 @@
         <v>0.22549019607843138</v>
       </c>
       <c r="H187" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I187" s="12" t="s">
         <v>126</v>
@@ -7725,7 +7719,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H188" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I188" s="12" t="s">
         <v>126</v>
@@ -7754,7 +7748,7 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H189" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I189" s="12" t="s">
         <v>126</v>
@@ -7783,7 +7777,7 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H190" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I190" s="12" t="s">
         <v>126</v>
@@ -7812,7 +7806,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H191" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I191" s="12" t="s">
         <v>126</v>
@@ -7841,7 +7835,7 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H192" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I192" s="12" t="s">
         <v>126</v>
@@ -7870,7 +7864,7 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H193" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I193" s="12" t="s">
         <v>126</v>
@@ -7899,7 +7893,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H194" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I194" s="12" t="s">
         <v>126</v>
@@ -7928,7 +7922,7 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H195" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I195" s="12" t="s">
         <v>126</v>
@@ -7957,7 +7951,7 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H196" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I196" s="12" t="s">
         <v>126</v>
@@ -7986,7 +7980,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H197" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I197" s="12" t="s">
         <v>126</v>
@@ -8015,7 +8009,7 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="H198" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I198" s="12" t="s">
         <v>126</v>
@@ -8044,7 +8038,7 @@
         <v>0.23529411764705882</v>
       </c>
       <c r="H199" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I199" s="12" t="s">
         <v>126</v>
@@ -8061,7 +8055,7 @@
         <v>131</v>
       </c>
       <c r="D200" s="12" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="E200" s="12" t="s">
         <v>113</v>
@@ -8073,7 +8067,7 @@
         <v>113</v>
       </c>
       <c r="H200" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I200" s="12" t="s">
         <v>115</v>
@@ -8090,7 +8084,7 @@
         <v>131</v>
       </c>
       <c r="D201" s="12" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="E201" s="12" t="s">
         <v>113</v>
@@ -8102,7 +8096,7 @@
         <v>113</v>
       </c>
       <c r="H201" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I201" s="12" t="s">
         <v>115</v>
@@ -8119,7 +8113,7 @@
         <v>131</v>
       </c>
       <c r="D202" s="12" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="E202" s="12" t="s">
         <v>113</v>
@@ -8131,7 +8125,7 @@
         <v>113</v>
       </c>
       <c r="H202" s="13" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="I202" s="12" t="s">
         <v>115</v>
@@ -8160,7 +8154,7 @@
         <v>0.17647058823529413</v>
       </c>
       <c r="H203" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I203" s="12" t="s">
         <v>115</v>
@@ -8189,7 +8183,7 @@
         <v>0.22058823529411764</v>
       </c>
       <c r="H204" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I204" s="12" t="s">
         <v>115</v>
@@ -8218,7 +8212,7 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H205" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I205" s="12" t="s">
         <v>115</v>
@@ -8247,7 +8241,7 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H206" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I206" s="12" t="s">
         <v>126</v>
@@ -8276,7 +8270,7 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H207" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I207" s="12" t="s">
         <v>126</v>
@@ -8305,7 +8299,7 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H208" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I208" s="12" t="s">
         <v>126</v>
@@ -8334,7 +8328,7 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H209" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I209" s="12" t="s">
         <v>126</v>
@@ -8363,7 +8357,7 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H210" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I210" s="12" t="s">
         <v>126</v>
@@ -8392,7 +8386,7 @@
         <v>0.33088235294117646</v>
       </c>
       <c r="H211" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I211" s="12" t="s">
         <v>126</v>
@@ -8400,7 +8394,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B212" s="12" t="s">
         <v>15</v>
@@ -8421,7 +8415,7 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="H212" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I212" s="12" t="s">
         <v>115</v>
@@ -8429,7 +8423,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B213" s="12" t="s">
         <v>15</v>
@@ -8450,7 +8444,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H213" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I213" s="12" t="s">
         <v>115</v>
@@ -8479,7 +8473,7 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="H214" s="13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I214" s="12" t="s">
         <v>115</v>
@@ -8508,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I215" s="12" t="s">
         <v>115</v>
@@ -8516,7 +8510,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B216" s="12" t="s">
         <v>15</v>
@@ -8537,7 +8531,7 @@
         <v>0.656084656084656</v>
       </c>
       <c r="H216" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I216" s="12" t="s">
         <v>115</v>
@@ -8545,7 +8539,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B217" s="12" t="s">
         <v>15</v>
@@ -8566,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="H217" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I217" s="12" t="s">
         <v>115</v>
@@ -8595,7 +8589,7 @@
         <v>0.783068783068783</v>
       </c>
       <c r="H218" s="13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I218" s="12" t="s">
         <v>115</v>
@@ -8624,7 +8618,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H219" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I219" s="12" t="s">
         <v>115</v>
@@ -8653,7 +8647,7 @@
         <v>0.8148148148148148</v>
       </c>
       <c r="H220" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I220" s="12" t="s">
         <v>115</v>
@@ -8682,7 +8676,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H221" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I221" s="12" t="s">
         <v>115</v>
@@ -8711,7 +8705,7 @@
         <v>0.5194805194805194</v>
       </c>
       <c r="H222" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I222" s="12" t="s">
         <v>115</v>
@@ -8740,7 +8734,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H223" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I223" s="12" t="s">
         <v>115</v>
@@ -8769,7 +8763,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H224" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I224" s="12" t="s">
         <v>126</v>
@@ -8798,7 +8792,7 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H225" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I225" s="12" t="s">
         <v>126</v>
@@ -8827,7 +8821,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H226" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I226" s="12" t="s">
         <v>126</v>
@@ -8856,7 +8850,7 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H227" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I227" s="12" t="s">
         <v>126</v>
@@ -8885,7 +8879,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H228" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I228" s="12" t="s">
         <v>126</v>
@@ -8914,7 +8908,7 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H229" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I229" s="12" t="s">
         <v>126</v>
@@ -8943,7 +8937,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H230" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I230" s="12" t="s">
         <v>126</v>
@@ -8972,7 +8966,7 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H231" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I231" s="12" t="s">
         <v>126</v>
@@ -9001,7 +8995,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H232" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I232" s="12" t="s">
         <v>126</v>
@@ -9030,7 +9024,7 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H233" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I233" s="12" t="s">
         <v>126</v>
@@ -9059,7 +9053,7 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H234" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I234" s="12" t="s">
         <v>126</v>
@@ -9088,7 +9082,7 @@
         <v>0.5227272727272727</v>
       </c>
       <c r="H235" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I235" s="12" t="s">
         <v>126</v>
@@ -9117,7 +9111,7 @@
         <v>0.06040268456375839</v>
       </c>
       <c r="H236" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I236" s="12" t="s">
         <v>115</v>
@@ -9125,7 +9119,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B237" s="12" t="s">
         <v>16</v>
@@ -9146,7 +9140,7 @@
         <v>0.14093959731543623</v>
       </c>
       <c r="H237" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I237" s="12" t="s">
         <v>115</v>
@@ -9175,7 +9169,7 @@
         <v>0.15436241610738255</v>
       </c>
       <c r="H238" s="13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I238" s="12" t="s">
         <v>115</v>
@@ -9204,7 +9198,7 @@
         <v>0.2080536912751678</v>
       </c>
       <c r="H239" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I239" s="12" t="s">
         <v>115</v>
@@ -9233,7 +9227,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H240" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I240" s="12" t="s">
         <v>115</v>
@@ -9262,7 +9256,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H241" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I241" s="12" t="s">
         <v>115</v>
@@ -9291,7 +9285,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H242" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I242" s="12" t="s">
         <v>126</v>
@@ -9320,7 +9314,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H243" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I243" s="12" t="s">
         <v>126</v>
@@ -9349,7 +9343,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H244" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I244" s="12" t="s">
         <v>126</v>
@@ -9378,7 +9372,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H245" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I245" s="12" t="s">
         <v>126</v>
@@ -9407,7 +9401,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H246" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I246" s="12" t="s">
         <v>126</v>
@@ -9436,7 +9430,7 @@
         <v>0.22818791946308725</v>
       </c>
       <c r="H247" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I247" s="12" t="s">
         <v>126</v>
@@ -9460,10 +9454,10 @@
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9471,23 +9465,23 @@
         <v>80</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9495,23 +9489,23 @@
         <v>93</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="263">
   <si>
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
   <si>
-    <t>Generated from embedded historical records + saved TEDUH records · 22/10/2026</t>
+    <t>Generated from embedded historical records + saved TEDUH records · 23/10/2026</t>
   </si>
   <si>
     <t>RECORD DETAIL</t>
@@ -111,310 +111,313 @@
     <t>Latest record</t>
   </si>
   <si>
+    <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>Sales Unit · latest</t>
+  </si>
+  <si>
+    <t>74 / 81</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>69 / 113</t>
+  </si>
+  <si>
+    <t>22 / 48</t>
+  </si>
+  <si>
+    <t>71 / 113</t>
+  </si>
+  <si>
+    <t>46 / 46</t>
+  </si>
+  <si>
+    <t>56 / 56</t>
+  </si>
+  <si>
+    <t>25 / 25</t>
+  </si>
+  <si>
+    <t>10 / 25</t>
+  </si>
+  <si>
+    <t>77 / 99</t>
+  </si>
+  <si>
+    <t>111 / 111</t>
+  </si>
+  <si>
+    <t>134 / 138</t>
+  </si>
+  <si>
+    <t>79 / 81</t>
+  </si>
+  <si>
+    <t>23 / 26</t>
+  </si>
+  <si>
+    <t>124 / 126</t>
+  </si>
+  <si>
+    <t>98 / 104</t>
+  </si>
+  <si>
+    <t>29 / 44</t>
+  </si>
+  <si>
+    <t>66 / 85</t>
+  </si>
+  <si>
+    <t>25 / 102</t>
+  </si>
+  <si>
+    <t>45 / 136</t>
+  </si>
+  <si>
+    <t>1 / 27</t>
+  </si>
+  <si>
+    <t>161 / 346</t>
+  </si>
+  <si>
+    <t>34 / 149</t>
+  </si>
+  <si>
+    <t>Sales Status · latest</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>Yet to launch</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>46%</t>
+  </si>
+  <si>
+    <t>63%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>78%</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>98%</t>
+  </si>
+  <si>
+    <t>88%</t>
+  </si>
+  <si>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>66%</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>Yet to sign</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>4%</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>23%</t>
+  </si>
+  <si>
+    <t>Weekly baseline</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>No record 7–14 days earlier</t>
+  </si>
+  <si>
+    <t>Sales Unit · baseline</t>
+  </si>
+  <si>
+    <t>68 / 113</t>
+  </si>
+  <si>
+    <t>21 / 48</t>
+  </si>
+  <si>
+    <t>24 / 25</t>
+  </si>
+  <si>
+    <t>63 / 85</t>
+  </si>
+  <si>
+    <t>23 / 102</t>
+  </si>
+  <si>
+    <t>161 / 308</t>
+  </si>
+  <si>
+    <t>Sales Status · baseline</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>44%</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>74%</t>
+  </si>
+  <si>
+    <t>52%</t>
+  </si>
+  <si>
+    <t>Weekly Change</t>
+  </si>
+  <si>
+    <t>No change</t>
+  </si>
+  <si>
+    <t>No signed status yet</t>
+  </si>
+  <si>
+    <t>+1 signed; +0.9 percentage points</t>
+  </si>
+  <si>
+    <t>+1 signed; +2.1 percentage points</t>
+  </si>
+  <si>
+    <t>+1 signed; +4.0 percentage points</t>
+  </si>
+  <si>
+    <t>Insufficient weekly history</t>
+  </si>
+  <si>
+    <t>+3 signed; +3.5 percentage points</t>
+  </si>
+  <si>
+    <t>+2 signed; +2.0 percentage points</t>
+  </si>
+  <si>
+    <t>⚠ Scope changed (308 → 346); recalculated: 0 signed change; -5.7 percentage points</t>
+  </si>
+  <si>
+    <t>Record Date</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Unit Group / Layout</t>
+  </si>
+  <si>
+    <t>Status Type</t>
+  </si>
+  <si>
+    <t>Signed Units</t>
+  </si>
+  <si>
+    <t>Total Units</t>
+  </si>
+  <si>
+    <t>Signed %</t>
+  </si>
+  <si>
+    <t>Raw Recorded Status</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>17/03/2025</t>
+  </si>
+  <si>
+    <t>Booked</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>11% Booked (9/81 units)</t>
+  </si>
+  <si>
+    <t>Embedded historical record</t>
+  </si>
+  <si>
+    <t>06/10/2025</t>
+  </si>
+  <si>
+    <t>35% Booked (28/81 units)</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>Signed</t>
+  </si>
+  <si>
+    <t>59% Signed (48/81 units)</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>65% Signed (53/81 units)</t>
+  </si>
+  <si>
+    <t>88% Signed (72/81 units)</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>74/81 signed</t>
+  </si>
+  <si>
+    <t>Saved TEDUH record</t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>18/10/2026</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>21/10/2026</t>
+  </si>
+  <si>
     <t>22/10/2026</t>
-  </si>
-  <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>Sales Unit · latest</t>
-  </si>
-  <si>
-    <t>74 / 81</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>69 / 113</t>
-  </si>
-  <si>
-    <t>22 / 48</t>
-  </si>
-  <si>
-    <t>71 / 113</t>
-  </si>
-  <si>
-    <t>46 / 46</t>
-  </si>
-  <si>
-    <t>56 / 56</t>
-  </si>
-  <si>
-    <t>25 / 25</t>
-  </si>
-  <si>
-    <t>10 / 25</t>
-  </si>
-  <si>
-    <t>77 / 99</t>
-  </si>
-  <si>
-    <t>111 / 111</t>
-  </si>
-  <si>
-    <t>134 / 138</t>
-  </si>
-  <si>
-    <t>79 / 81</t>
-  </si>
-  <si>
-    <t>23 / 26</t>
-  </si>
-  <si>
-    <t>124 / 126</t>
-  </si>
-  <si>
-    <t>98 / 104</t>
-  </si>
-  <si>
-    <t>29 / 44</t>
-  </si>
-  <si>
-    <t>66 / 85</t>
-  </si>
-  <si>
-    <t>25 / 102</t>
-  </si>
-  <si>
-    <t>45 / 136</t>
-  </si>
-  <si>
-    <t>1 / 27</t>
-  </si>
-  <si>
-    <t>161 / 346</t>
-  </si>
-  <si>
-    <t>34 / 149</t>
-  </si>
-  <si>
-    <t>Sales Status · latest</t>
-  </si>
-  <si>
-    <t>91%</t>
-  </si>
-  <si>
-    <t>Yet to launch</t>
-  </si>
-  <si>
-    <t>61%</t>
-  </si>
-  <si>
-    <t>46%</t>
-  </si>
-  <si>
-    <t>63%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>78%</t>
-  </si>
-  <si>
-    <t>97%</t>
-  </si>
-  <si>
-    <t>98%</t>
-  </si>
-  <si>
-    <t>88%</t>
-  </si>
-  <si>
-    <t>94%</t>
-  </si>
-  <si>
-    <t>66%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>Yet to sign</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>47%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>Weekly baseline</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>No record 7–14 days earlier</t>
-  </si>
-  <si>
-    <t>Sales Unit · baseline</t>
-  </si>
-  <si>
-    <t>68 / 113</t>
-  </si>
-  <si>
-    <t>21 / 48</t>
-  </si>
-  <si>
-    <t>24 / 25</t>
-  </si>
-  <si>
-    <t>63 / 85</t>
-  </si>
-  <si>
-    <t>23 / 102</t>
-  </si>
-  <si>
-    <t>161 / 308</t>
-  </si>
-  <si>
-    <t>Sales Status · baseline</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>44%</t>
-  </si>
-  <si>
-    <t>96%</t>
-  </si>
-  <si>
-    <t>74%</t>
-  </si>
-  <si>
-    <t>52%</t>
-  </si>
-  <si>
-    <t>Weekly Change</t>
-  </si>
-  <si>
-    <t>No change</t>
-  </si>
-  <si>
-    <t>No signed status yet</t>
-  </si>
-  <si>
-    <t>+1 signed; +0.9 percentage points</t>
-  </si>
-  <si>
-    <t>+1 signed; +2.1 percentage points</t>
-  </si>
-  <si>
-    <t>+1 signed; +4.0 percentage points</t>
-  </si>
-  <si>
-    <t>Insufficient weekly history</t>
-  </si>
-  <si>
-    <t>+3 signed; +3.5 percentage points</t>
-  </si>
-  <si>
-    <t>+2 signed; +2.0 percentage points</t>
-  </si>
-  <si>
-    <t>⚠ Scope changed (308 → 346); recalculated: 0 signed change; -5.7 percentage points</t>
-  </si>
-  <si>
-    <t>Record Date</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Unit Group / Layout</t>
-  </si>
-  <si>
-    <t>Status Type</t>
-  </si>
-  <si>
-    <t>Signed Units</t>
-  </si>
-  <si>
-    <t>Total Units</t>
-  </si>
-  <si>
-    <t>Signed %</t>
-  </si>
-  <si>
-    <t>Raw Recorded Status</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>17/03/2025</t>
-  </si>
-  <si>
-    <t>Booked</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>11% Booked (9/81 units)</t>
-  </si>
-  <si>
-    <t>Embedded historical record</t>
-  </si>
-  <si>
-    <t>06/10/2025</t>
-  </si>
-  <si>
-    <t>35% Booked (28/81 units)</t>
-  </si>
-  <si>
-    <t>08/06/2026</t>
-  </si>
-  <si>
-    <t>Signed</t>
-  </si>
-  <si>
-    <t>59% Signed (48/81 units)</t>
-  </si>
-  <si>
-    <t>10/07/2026</t>
-  </si>
-  <si>
-    <t>65% Signed (53/81 units)</t>
-  </si>
-  <si>
-    <t>88% Signed (72/81 units)</t>
-  </si>
-  <si>
-    <t>74/81 signed</t>
-  </si>
-  <si>
-    <t>Saved TEDUH record</t>
-  </si>
-  <si>
-    <t>16/10/2026</t>
-  </si>
-  <si>
-    <t>17/10/2026</t>
-  </si>
-  <si>
-    <t>18/10/2026</t>
-  </si>
-  <si>
-    <t>19/10/2026</t>
-  </si>
-  <si>
-    <t>20/10/2026</t>
-  </si>
-  <si>
-    <t>21/10/2026</t>
   </si>
   <si>
     <t>No group details</t>
@@ -2309,7 +2312,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I291"/>
+  <dimension ref="A1:I313"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2493,7 +2496,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>3</v>
@@ -2514,15 +2517,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>3</v>
@@ -2543,10 +2546,10 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -2572,10 +2575,10 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2601,10 +2604,10 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2630,10 +2633,10 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2659,10 +2662,10 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2688,15 +2691,15 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>3</v>
@@ -2717,50 +2720,50 @@
         <v>0.9135802469135802</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="E15" s="12">
+        <v>74</v>
+      </c>
+      <c r="F15" s="12">
+        <v>81</v>
+      </c>
+      <c r="G15" s="15">
+        <v>0.9135802469135802</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>60</v>
@@ -2775,7 +2778,7 @@
         <v>115</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>117</v>
@@ -2783,13 +2786,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>60</v>
@@ -2804,7 +2807,7 @@
         <v>115</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>117</v>
@@ -2812,26 +2815,28 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="12">
-        <v>113</v>
-      </c>
-      <c r="G18" s="14"/>
+      <c r="F18" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="H18" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>117</v>
@@ -2839,7 +2844,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>5</v>
@@ -2858,7 +2863,7 @@
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>117</v>
@@ -2866,7 +2871,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>5</v>
@@ -2885,7 +2890,7 @@
       </c>
       <c r="G20" s="14"/>
       <c r="H20" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>117</v>
@@ -2893,7 +2898,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>5</v>
@@ -2920,7 +2925,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>5</v>
@@ -2929,19 +2934,17 @@
         <v>20</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E22" s="12">
-        <v>34</v>
+        <v>114</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="F22" s="12">
         <v>113</v>
       </c>
-      <c r="G22" s="15">
-        <v>0.3008849557522124</v>
-      </c>
+      <c r="G22" s="14"/>
       <c r="H22" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>117</v>
@@ -2949,7 +2952,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>5</v>
@@ -2961,16 +2964,16 @@
         <v>121</v>
       </c>
       <c r="E23" s="12">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F23" s="12">
         <v>113</v>
       </c>
       <c r="G23" s="15">
-        <v>0.3274336283185841</v>
+        <v>0.3008849557522124</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I23" s="12" t="s">
         <v>117</v>
@@ -2978,7 +2981,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>5</v>
@@ -2999,7 +3002,7 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>117</v>
@@ -3007,7 +3010,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>5</v>
@@ -3019,16 +3022,16 @@
         <v>121</v>
       </c>
       <c r="E25" s="12">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F25" s="12">
         <v>113</v>
       </c>
       <c r="G25" s="15">
-        <v>0.4778761061946903</v>
+        <v>0.3274336283185841</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>117</v>
@@ -3036,7 +3039,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>5</v>
@@ -3048,13 +3051,13 @@
         <v>121</v>
       </c>
       <c r="E26" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F26" s="12">
         <v>113</v>
       </c>
       <c r="G26" s="15">
-        <v>0.5575221238938053</v>
+        <v>0.4778761061946903</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>149</v>
@@ -3065,7 +3068,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>5</v>
@@ -3077,13 +3080,13 @@
         <v>121</v>
       </c>
       <c r="E27" s="12">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F27" s="12">
         <v>113</v>
       </c>
       <c r="G27" s="15">
-        <v>0.6017699115044248</v>
+        <v>0.5575221238938053</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>150</v>
@@ -3094,7 +3097,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>5</v>
@@ -3115,7 +3118,7 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I28" s="12" t="s">
         <v>117</v>
@@ -3123,7 +3126,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>5</v>
@@ -3147,12 +3150,12 @@
         <v>151</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>5</v>
@@ -3173,15 +3176,15 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>5</v>
@@ -3193,24 +3196,24 @@
         <v>121</v>
       </c>
       <c r="E31" s="12">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F31" s="12">
         <v>113</v>
       </c>
       <c r="G31" s="15">
-        <v>0.6106194690265486</v>
+        <v>0.6017699115044248</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>152</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>5</v>
@@ -3231,15 +3234,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>5</v>
@@ -3260,15 +3263,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>5</v>
@@ -3289,15 +3292,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>5</v>
@@ -3318,15 +3321,15 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>5</v>
@@ -3347,69 +3350,73 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="E37" s="12">
+        <v>69</v>
       </c>
       <c r="F37" s="12">
-        <v>48</v>
-      </c>
-      <c r="G37" s="14"/>
+        <v>113</v>
+      </c>
+      <c r="G37" s="15">
+        <v>0.6106194690265486</v>
+      </c>
       <c r="H37" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="E38" s="12">
+        <v>69</v>
       </c>
       <c r="F38" s="12">
-        <v>48</v>
-      </c>
-      <c r="G38" s="14"/>
+        <v>113</v>
+      </c>
+      <c r="G38" s="15">
+        <v>0.6106194690265486</v>
+      </c>
       <c r="H38" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>6</v>
@@ -3436,7 +3443,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>6</v>
@@ -3463,7 +3470,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>6</v>
@@ -3482,7 +3489,7 @@
       </c>
       <c r="G41" s="14"/>
       <c r="H41" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I41" s="12" t="s">
         <v>117</v>
@@ -3490,7 +3497,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>6</v>
@@ -3517,7 +3524,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>6</v>
@@ -3526,17 +3533,15 @@
         <v>21</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E43" s="12">
-        <v>15</v>
+        <v>114</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="F43" s="12">
         <v>48</v>
       </c>
-      <c r="G43" s="15">
-        <v>0.3125</v>
-      </c>
+      <c r="G43" s="14"/>
       <c r="H43" s="13" t="s">
         <v>157</v>
       </c>
@@ -3546,7 +3551,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>6</v>
@@ -3555,19 +3560,17 @@
         <v>21</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E44" s="12">
-        <v>19</v>
+        <v>114</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="F44" s="12">
         <v>48</v>
       </c>
-      <c r="G44" s="15">
-        <v>0.3958333333333333</v>
-      </c>
+      <c r="G44" s="14"/>
       <c r="H44" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I44" s="12" t="s">
         <v>117</v>
@@ -3575,7 +3578,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>6</v>
@@ -3587,13 +3590,13 @@
         <v>121</v>
       </c>
       <c r="E45" s="12">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F45" s="12">
         <v>48</v>
       </c>
       <c r="G45" s="15">
-        <v>0.3958333333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="H45" s="13" t="s">
         <v>158</v>
@@ -3604,7 +3607,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>6</v>
@@ -3616,13 +3619,13 @@
         <v>121</v>
       </c>
       <c r="E46" s="12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F46" s="12">
         <v>48</v>
       </c>
       <c r="G46" s="15">
-        <v>0.4375</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>159</v>
@@ -3633,7 +3636,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>6</v>
@@ -3645,24 +3648,24 @@
         <v>121</v>
       </c>
       <c r="E47" s="12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F47" s="12">
         <v>48</v>
       </c>
       <c r="G47" s="15">
-        <v>0.4375</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>6</v>
@@ -3686,12 +3689,12 @@
         <v>160</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>6</v>
@@ -3712,15 +3715,15 @@
         <v>0.4375</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>6</v>
@@ -3741,15 +3744,15 @@
         <v>0.4375</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>6</v>
@@ -3770,15 +3773,15 @@
         <v>0.4375</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>6</v>
@@ -3799,15 +3802,15 @@
         <v>0.4375</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>6</v>
@@ -3819,24 +3822,24 @@
         <v>121</v>
       </c>
       <c r="E53" s="12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F53" s="12">
         <v>48</v>
       </c>
       <c r="G53" s="15">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="H53" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>6</v>
@@ -3848,111 +3851,111 @@
         <v>121</v>
       </c>
       <c r="E54" s="12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F54" s="12">
         <v>48</v>
       </c>
       <c r="G54" s="15">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="H54" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E55" s="12">
         <v>22</v>
       </c>
-      <c r="D55" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E55" s="12">
-        <v>83</v>
-      </c>
       <c r="F55" s="12">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="G55" s="15">
-        <v>0.8383838383838383</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H55" s="13" t="s">
         <v>162</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" s="12">
         <v>22</v>
       </c>
-      <c r="D56" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E56" s="12">
-        <v>70</v>
-      </c>
       <c r="F56" s="12">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G56" s="15">
-        <v>0.6194690265486725</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C57" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="12">
         <v>22</v>
       </c>
-      <c r="D57" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E57" s="12">
-        <v>70</v>
-      </c>
       <c r="F57" s="12">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G57" s="15">
-        <v>0.6194690265486725</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>7</v>
@@ -3964,16 +3967,16 @@
         <v>121</v>
       </c>
       <c r="E58" s="12">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F58" s="12">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G58" s="15">
-        <v>0.6283185840707964</v>
+        <v>0.8383838383838383</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I58" s="12" t="s">
         <v>117</v>
@@ -3981,7 +3984,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>7</v>
@@ -3993,24 +3996,24 @@
         <v>121</v>
       </c>
       <c r="E59" s="12">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F59" s="12">
         <v>113</v>
       </c>
       <c r="G59" s="15">
-        <v>0.6283185840707964</v>
+        <v>0.6194690265486725</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>7</v>
@@ -4022,24 +4025,24 @@
         <v>121</v>
       </c>
       <c r="E60" s="12">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F60" s="12">
         <v>113</v>
       </c>
       <c r="G60" s="15">
-        <v>0.6283185840707964</v>
+        <v>0.6194690265486725</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>7</v>
@@ -4063,12 +4066,12 @@
         <v>165</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>7</v>
@@ -4089,15 +4092,15 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>7</v>
@@ -4118,15 +4121,15 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>7</v>
@@ -4147,15 +4150,15 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>7</v>
@@ -4176,15 +4179,15 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>7</v>
@@ -4205,47 +4208,47 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E67" s="12">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="F67" s="12">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="G67" s="15">
-        <v>0.9782608695652174</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H67" s="13" t="s">
         <v>166</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>22</v>
@@ -4254,82 +4257,82 @@
         <v>121</v>
       </c>
       <c r="E68" s="12">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F68" s="12">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="G68" s="15">
-        <v>0.8392857142857143</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D69" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E69" s="12">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F69" s="12">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G69" s="15">
-        <v>0.52</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D70" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E70" s="12">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="F70" s="12">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G70" s="15">
-        <v>0.12</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>8</v>
@@ -4341,16 +4344,16 @@
         <v>121</v>
       </c>
       <c r="E71" s="12">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F71" s="12">
         <v>46</v>
       </c>
       <c r="G71" s="15">
-        <v>1</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I71" s="12" t="s">
         <v>117</v>
@@ -4358,7 +4361,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>8</v>
@@ -4370,16 +4373,16 @@
         <v>121</v>
       </c>
       <c r="E72" s="12">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F72" s="12">
         <v>56</v>
       </c>
       <c r="G72" s="15">
-        <v>1</v>
+        <v>0.8392857142857143</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I72" s="12" t="s">
         <v>117</v>
@@ -4387,7 +4390,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>8</v>
@@ -4399,16 +4402,16 @@
         <v>121</v>
       </c>
       <c r="E73" s="12">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F73" s="12">
         <v>25</v>
       </c>
       <c r="G73" s="15">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I73" s="12" t="s">
         <v>117</v>
@@ -4416,7 +4419,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>8</v>
@@ -4428,16 +4431,16 @@
         <v>121</v>
       </c>
       <c r="E74" s="12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F74" s="12">
         <v>25</v>
       </c>
       <c r="G74" s="15">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I74" s="12" t="s">
         <v>117</v>
@@ -4445,7 +4448,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>8</v>
@@ -4466,7 +4469,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I75" s="12" t="s">
         <v>117</v>
@@ -4474,7 +4477,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>8</v>
@@ -4495,7 +4498,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I76" s="12" t="s">
         <v>117</v>
@@ -4503,7 +4506,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>8</v>
@@ -4524,7 +4527,7 @@
         <v>0.96</v>
       </c>
       <c r="H77" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I77" s="12" t="s">
         <v>117</v>
@@ -4532,7 +4535,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>8</v>
@@ -4544,13 +4547,13 @@
         <v>121</v>
       </c>
       <c r="E78" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F78" s="12">
         <v>25</v>
       </c>
       <c r="G78" s="15">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H78" s="13" t="s">
         <v>174</v>
@@ -4561,7 +4564,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>8</v>
@@ -4582,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I79" s="12" t="s">
         <v>117</v>
@@ -4590,7 +4593,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>8</v>
@@ -4611,7 +4614,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I80" s="12" t="s">
         <v>117</v>
@@ -4619,7 +4622,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>8</v>
@@ -4640,7 +4643,7 @@
         <v>0.96</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I81" s="12" t="s">
         <v>117</v>
@@ -4648,7 +4651,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>8</v>
@@ -4660,13 +4663,13 @@
         <v>121</v>
       </c>
       <c r="E82" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F82" s="12">
         <v>25</v>
       </c>
       <c r="G82" s="15">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="H82" s="13" t="s">
         <v>175</v>
@@ -4677,7 +4680,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>8</v>
@@ -4698,15 +4701,15 @@
         <v>1</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>8</v>
@@ -4727,15 +4730,15 @@
         <v>1</v>
       </c>
       <c r="H84" s="13" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>8</v>
@@ -4756,15 +4759,15 @@
         <v>0.96</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>8</v>
@@ -4785,15 +4788,15 @@
         <v>0.4</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I86" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>8</v>
@@ -4814,15 +4817,15 @@
         <v>1</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>8</v>
@@ -4843,15 +4846,15 @@
         <v>1</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>8</v>
@@ -4872,15 +4875,15 @@
         <v>0.96</v>
       </c>
       <c r="H89" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I89" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B90" s="12" t="s">
         <v>8</v>
@@ -4901,15 +4904,15 @@
         <v>0.4</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I90" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>8</v>
@@ -4930,15 +4933,15 @@
         <v>1</v>
       </c>
       <c r="H91" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I91" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>8</v>
@@ -4959,15 +4962,15 @@
         <v>1</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>8</v>
@@ -4988,15 +4991,15 @@
         <v>0.96</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I93" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>8</v>
@@ -5017,15 +5020,15 @@
         <v>0.4</v>
       </c>
       <c r="H94" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B95" s="12" t="s">
         <v>8</v>
@@ -5046,15 +5049,15 @@
         <v>1</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B96" s="12" t="s">
         <v>8</v>
@@ -5075,15 +5078,15 @@
         <v>1</v>
       </c>
       <c r="H96" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I96" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B97" s="12" t="s">
         <v>8</v>
@@ -5104,15 +5107,15 @@
         <v>0.96</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I97" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B98" s="12" t="s">
         <v>8</v>
@@ -5133,15 +5136,15 @@
         <v>0.4</v>
       </c>
       <c r="H98" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I98" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B99" s="12" t="s">
         <v>8</v>
@@ -5162,15 +5165,15 @@
         <v>1</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I99" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B100" s="12" t="s">
         <v>8</v>
@@ -5191,15 +5194,15 @@
         <v>1</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B101" s="12" t="s">
         <v>8</v>
@@ -5220,15 +5223,15 @@
         <v>0.96</v>
       </c>
       <c r="H101" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B102" s="12" t="s">
         <v>8</v>
@@ -5249,15 +5252,15 @@
         <v>0.4</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B103" s="12" t="s">
         <v>8</v>
@@ -5278,15 +5281,15 @@
         <v>1</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I103" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B104" s="12" t="s">
         <v>8</v>
@@ -5307,15 +5310,15 @@
         <v>1</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B105" s="12" t="s">
         <v>8</v>
@@ -5336,15 +5339,15 @@
         <v>0.96</v>
       </c>
       <c r="H105" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B106" s="12" t="s">
         <v>8</v>
@@ -5365,15 +5368,15 @@
         <v>0.4</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B107" s="12" t="s">
         <v>8</v>
@@ -5394,15 +5397,15 @@
         <v>1</v>
       </c>
       <c r="H107" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I107" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>8</v>
@@ -5423,15 +5426,15 @@
         <v>1</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B109" s="12" t="s">
         <v>8</v>
@@ -5443,24 +5446,24 @@
         <v>121</v>
       </c>
       <c r="E109" s="12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F109" s="12">
         <v>25</v>
       </c>
       <c r="G109" s="15">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I109" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B110" s="12" t="s">
         <v>8</v>
@@ -5481,15 +5484,15 @@
         <v>0.4</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>8</v>
@@ -5510,15 +5513,15 @@
         <v>1</v>
       </c>
       <c r="H111" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="B112" s="12" t="s">
         <v>8</v>
@@ -5539,15 +5542,15 @@
         <v>1</v>
       </c>
       <c r="H112" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="B113" s="12" t="s">
         <v>8</v>
@@ -5568,15 +5571,15 @@
         <v>1</v>
       </c>
       <c r="H113" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="B114" s="12" t="s">
         <v>8</v>
@@ -5597,247 +5600,247 @@
         <v>0.4</v>
       </c>
       <c r="H114" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I114" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E115" s="12">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="F115" s="12">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="G115" s="15">
-        <v>0.8787878787878788</v>
+        <v>1</v>
       </c>
       <c r="H115" s="13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D116" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E116" s="12">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F116" s="12">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="G116" s="15">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D117" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E117" s="12">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F117" s="12">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G117" s="15">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H117" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I117" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D118" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E118" s="12">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F118" s="12">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G118" s="15">
-        <v>0.7777777777777778</v>
+        <v>0.4</v>
       </c>
       <c r="H118" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I118" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E119" s="12">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="F119" s="12">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="G119" s="15">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H119" s="13" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I119" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D120" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E120" s="12">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F120" s="12">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="G120" s="15">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H120" s="13" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I120" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D121" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E121" s="12">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F121" s="12">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G121" s="15">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H121" s="13" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I121" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D122" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E122" s="12">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F122" s="12">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G122" s="15">
-        <v>0.7777777777777778</v>
+        <v>0.4</v>
       </c>
       <c r="H122" s="13" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I122" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B123" s="12" t="s">
         <v>9</v>
@@ -5849,24 +5852,24 @@
         <v>121</v>
       </c>
       <c r="E123" s="12">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F123" s="12">
         <v>99</v>
       </c>
       <c r="G123" s="15">
-        <v>0.7777777777777778</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="H123" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I123" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B124" s="12" t="s">
         <v>9</v>
@@ -5890,12 +5893,12 @@
         <v>183</v>
       </c>
       <c r="I124" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B125" s="12" t="s">
         <v>9</v>
@@ -5919,12 +5922,12 @@
         <v>183</v>
       </c>
       <c r="I125" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B126" s="12" t="s">
         <v>9</v>
@@ -5948,273 +5951,273 @@
         <v>183</v>
       </c>
       <c r="I126" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E127" s="12">
+        <v>77</v>
+      </c>
+      <c r="F127" s="12">
+        <v>99</v>
+      </c>
+      <c r="G127" s="15">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="H127" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="B127" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C127" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E127" s="12">
-        <v>57</v>
-      </c>
-      <c r="F127" s="12">
-        <v>111</v>
-      </c>
-      <c r="G127" s="15">
-        <v>0.5135135135135135</v>
-      </c>
-      <c r="H127" s="13" t="s">
-        <v>185</v>
-      </c>
       <c r="I127" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E128" s="12">
+        <v>77</v>
+      </c>
+      <c r="F128" s="12">
+        <v>99</v>
+      </c>
+      <c r="G128" s="15">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="H128" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="B128" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C128" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D128" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E128" s="12">
-        <v>93</v>
-      </c>
-      <c r="F128" s="12">
-        <v>138</v>
-      </c>
-      <c r="G128" s="15">
-        <v>0.6739130434782609</v>
-      </c>
-      <c r="H128" s="13" t="s">
-        <v>186</v>
-      </c>
       <c r="I128" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E129" s="12">
+        <v>77</v>
+      </c>
+      <c r="F129" s="12">
+        <v>99</v>
+      </c>
+      <c r="G129" s="15">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="H129" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="B129" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C129" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D129" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E129" s="12">
-        <v>44</v>
-      </c>
-      <c r="F129" s="12">
-        <v>81</v>
-      </c>
-      <c r="G129" s="15">
-        <v>0.5432098765432098</v>
-      </c>
-      <c r="H129" s="13" t="s">
-        <v>187</v>
-      </c>
       <c r="I129" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D130" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E130" s="12">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F130" s="12">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G130" s="15">
-        <v>0.5585585585585585</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H130" s="13" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I130" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D131" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E131" s="12">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F131" s="12">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="G131" s="15">
-        <v>0.7101449275362319</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H131" s="13" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D132" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E132" s="12">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="F132" s="12">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G132" s="15">
-        <v>0.6419753086419753</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H132" s="13" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I132" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D133" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E133" s="12">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="F133" s="12">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G133" s="15">
-        <v>0.9099099099099099</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H133" s="13" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I133" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D134" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E134" s="12">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="F134" s="12">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="G134" s="15">
-        <v>0.9492753623188406</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H134" s="13" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="I134" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D135" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E135" s="12">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F135" s="12">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G135" s="15">
-        <v>0.9629629629629629</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H135" s="13" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="I135" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="B136" s="12" t="s">
         <v>10</v>
@@ -6226,16 +6229,16 @@
         <v>121</v>
       </c>
       <c r="E136" s="12">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="F136" s="12">
         <v>111</v>
       </c>
       <c r="G136" s="15">
-        <v>0.918918918918919</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="H136" s="13" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I136" s="12" t="s">
         <v>117</v>
@@ -6243,7 +6246,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="B137" s="12" t="s">
         <v>10</v>
@@ -6255,16 +6258,16 @@
         <v>121</v>
       </c>
       <c r="E137" s="12">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="F137" s="12">
         <v>138</v>
       </c>
       <c r="G137" s="15">
-        <v>0.9492753623188406</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="H137" s="13" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I137" s="12" t="s">
         <v>117</v>
@@ -6272,7 +6275,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="B138" s="12" t="s">
         <v>10</v>
@@ -6284,16 +6287,16 @@
         <v>121</v>
       </c>
       <c r="E138" s="12">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F138" s="12">
         <v>81</v>
       </c>
       <c r="G138" s="15">
-        <v>0.9629629629629629</v>
+        <v>0.5432098765432098</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I138" s="12" t="s">
         <v>117</v>
@@ -6301,7 +6304,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B139" s="12" t="s">
         <v>10</v>
@@ -6313,16 +6316,16 @@
         <v>121</v>
       </c>
       <c r="E139" s="12">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F139" s="12">
         <v>111</v>
       </c>
       <c r="G139" s="15">
-        <v>0.918918918918919</v>
+        <v>0.5585585585585585</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I139" s="12" t="s">
         <v>117</v>
@@ -6330,7 +6333,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B140" s="12" t="s">
         <v>10</v>
@@ -6342,16 +6345,16 @@
         <v>121</v>
       </c>
       <c r="E140" s="12">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="F140" s="12">
         <v>138</v>
       </c>
       <c r="G140" s="15">
-        <v>0.9492753623188406</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I140" s="12" t="s">
         <v>117</v>
@@ -6359,7 +6362,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B141" s="12" t="s">
         <v>10</v>
@@ -6371,16 +6374,16 @@
         <v>121</v>
       </c>
       <c r="E141" s="12">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="F141" s="12">
         <v>81</v>
       </c>
       <c r="G141" s="15">
-        <v>0.9629629629629629</v>
+        <v>0.6419753086419753</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I141" s="12" t="s">
         <v>117</v>
@@ -6388,7 +6391,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>33</v>
+        <v>148</v>
       </c>
       <c r="B142" s="12" t="s">
         <v>10</v>
@@ -6400,16 +6403,16 @@
         <v>121</v>
       </c>
       <c r="E142" s="12">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F142" s="12">
         <v>111</v>
       </c>
       <c r="G142" s="15">
-        <v>1</v>
+        <v>0.9099099099099099</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I142" s="12" t="s">
         <v>117</v>
@@ -6417,7 +6420,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>33</v>
+        <v>148</v>
       </c>
       <c r="B143" s="12" t="s">
         <v>10</v>
@@ -6429,16 +6432,16 @@
         <v>121</v>
       </c>
       <c r="E143" s="12">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F143" s="12">
         <v>138</v>
       </c>
       <c r="G143" s="15">
-        <v>0.9710144927536232</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I143" s="12" t="s">
         <v>117</v>
@@ -6446,7 +6449,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>33</v>
+        <v>148</v>
       </c>
       <c r="B144" s="12" t="s">
         <v>10</v>
@@ -6458,16 +6461,16 @@
         <v>121</v>
       </c>
       <c r="E144" s="12">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F144" s="12">
         <v>81</v>
       </c>
       <c r="G144" s="15">
-        <v>0.9753086419753086</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H144" s="13" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I144" s="12" t="s">
         <v>117</v>
@@ -6475,7 +6478,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="B145" s="12" t="s">
         <v>10</v>
@@ -6487,24 +6490,24 @@
         <v>121</v>
       </c>
       <c r="E145" s="12">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F145" s="12">
         <v>111</v>
       </c>
       <c r="G145" s="15">
-        <v>1</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="H145" s="13" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="B146" s="12" t="s">
         <v>10</v>
@@ -6516,24 +6519,24 @@
         <v>121</v>
       </c>
       <c r="E146" s="12">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F146" s="12">
         <v>138</v>
       </c>
       <c r="G146" s="15">
-        <v>0.9710144927536232</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H146" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="B147" s="12" t="s">
         <v>10</v>
@@ -6545,24 +6548,24 @@
         <v>121</v>
       </c>
       <c r="E147" s="12">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F147" s="12">
         <v>81</v>
       </c>
       <c r="G147" s="15">
-        <v>0.9753086419753086</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H147" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B148" s="12" t="s">
         <v>10</v>
@@ -6574,24 +6577,24 @@
         <v>121</v>
       </c>
       <c r="E148" s="12">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F148" s="12">
         <v>111</v>
       </c>
       <c r="G148" s="15">
-        <v>1</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="12" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B149" s="12" t="s">
         <v>10</v>
@@ -6603,24 +6606,24 @@
         <v>121</v>
       </c>
       <c r="E149" s="12">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F149" s="12">
         <v>138</v>
       </c>
       <c r="G149" s="15">
-        <v>0.9710144927536232</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H149" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B150" s="12" t="s">
         <v>10</v>
@@ -6632,24 +6635,24 @@
         <v>121</v>
       </c>
       <c r="E150" s="12">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F150" s="12">
         <v>81</v>
       </c>
       <c r="G150" s="15">
-        <v>0.9753086419753086</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I150" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="B151" s="12" t="s">
         <v>10</v>
@@ -6670,15 +6673,15 @@
         <v>1</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="B152" s="12" t="s">
         <v>10</v>
@@ -6699,15 +6702,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H152" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I152" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="B153" s="12" t="s">
         <v>10</v>
@@ -6728,15 +6731,15 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H153" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I153" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B154" s="12" t="s">
         <v>10</v>
@@ -6757,15 +6760,15 @@
         <v>1</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I154" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B155" s="12" t="s">
         <v>10</v>
@@ -6786,15 +6789,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H155" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I155" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B156" s="12" t="s">
         <v>10</v>
@@ -6815,15 +6818,15 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I156" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="12" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="B157" s="12" t="s">
         <v>10</v>
@@ -6844,15 +6847,15 @@
         <v>1</v>
       </c>
       <c r="H157" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="B158" s="12" t="s">
         <v>10</v>
@@ -6873,15 +6876,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I158" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="B159" s="12" t="s">
         <v>10</v>
@@ -6902,15 +6905,15 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H159" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I159" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B160" s="12" t="s">
         <v>10</v>
@@ -6931,15 +6934,15 @@
         <v>1</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I160" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B161" s="12" t="s">
         <v>10</v>
@@ -6960,15 +6963,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H161" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I161" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B162" s="12" t="s">
         <v>10</v>
@@ -6989,15 +6992,15 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H162" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B163" s="12" t="s">
         <v>10</v>
@@ -7018,15 +7021,15 @@
         <v>1</v>
       </c>
       <c r="H163" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B164" s="12" t="s">
         <v>10</v>
@@ -7047,15 +7050,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H164" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I164" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B165" s="12" t="s">
         <v>10</v>
@@ -7076,15 +7079,15 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H165" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I165" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="B166" s="12" t="s">
         <v>10</v>
@@ -7105,15 +7108,15 @@
         <v>1</v>
       </c>
       <c r="H166" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I166" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="B167" s="12" t="s">
         <v>10</v>
@@ -7134,15 +7137,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H167" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="B168" s="12" t="s">
         <v>10</v>
@@ -7163,384 +7166,384 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I168" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C169" s="13" t="s">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E169" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F169" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="G169" s="12" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="E169" s="12">
+        <v>111</v>
+      </c>
+      <c r="F169" s="12">
+        <v>111</v>
+      </c>
+      <c r="G169" s="15">
+        <v>1</v>
       </c>
       <c r="H169" s="13" t="s">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="I169" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D170" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E170" s="12">
-        <v>3</v>
+        <v>134</v>
       </c>
       <c r="F170" s="12">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G170" s="15">
-        <v>0.11538461538461539</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H170" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I170" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C171" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D171" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E171" s="12">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F171" s="12">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G171" s="15">
-        <v>0.6111111111111112</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H171" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I171" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C172" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D172" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E172" s="12">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="F172" s="12">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G172" s="15">
-        <v>0.16346153846153846</v>
+        <v>1</v>
       </c>
       <c r="H172" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I172" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C173" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D173" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E173" s="12">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="F173" s="12">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G173" s="15">
-        <v>0.6538461538461539</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H173" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I173" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C174" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D174" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E174" s="12">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="F174" s="12">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G174" s="15">
-        <v>0.8809523809523809</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H174" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I174" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C175" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D175" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E175" s="12">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="F175" s="12">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G175" s="15">
-        <v>0.6826923076923077</v>
+        <v>1</v>
       </c>
       <c r="H175" s="13" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="I175" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C176" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D176" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E176" s="12">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="F176" s="12">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G176" s="15">
-        <v>0.6538461538461539</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H176" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I176" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="12" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C177" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D177" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E177" s="12">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="F177" s="12">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G177" s="15">
-        <v>0.9206349206349206</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H177" s="13" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="I177" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C178" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D178" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E178" s="12">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="F178" s="12">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G178" s="15">
-        <v>0.8557692307692307</v>
+        <v>1</v>
       </c>
       <c r="H178" s="13" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="I178" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C179" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D179" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E179" s="12">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="F179" s="12">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G179" s="15">
-        <v>0.8846153846153846</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H179" s="13" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="I179" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C180" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D180" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E180" s="12">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="F180" s="12">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G180" s="15">
-        <v>0.9841269841269841</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H180" s="13" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="I180" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="12" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="B181" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C181" s="13" t="s">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="D181" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E181" s="12">
-        <v>98</v>
-      </c>
-      <c r="F181" s="12">
-        <v>104</v>
-      </c>
-      <c r="G181" s="15">
-        <v>0.9423076923076923</v>
+        <v>73</v>
+      </c>
+      <c r="E181" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G181" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="H181" s="13" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="I181" s="12" t="s">
         <v>117</v>
@@ -7548,7 +7551,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="B182" s="12" t="s">
         <v>11</v>
@@ -7560,24 +7563,24 @@
         <v>121</v>
       </c>
       <c r="E182" s="12">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F182" s="12">
         <v>26</v>
       </c>
       <c r="G182" s="15">
-        <v>0.8846153846153846</v>
+        <v>0.11538461538461539</v>
       </c>
       <c r="H182" s="13" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="I182" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="12" t="s">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="B183" s="12" t="s">
         <v>11</v>
@@ -7589,24 +7592,24 @@
         <v>121</v>
       </c>
       <c r="E183" s="12">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="F183" s="12">
         <v>126</v>
       </c>
       <c r="G183" s="15">
-        <v>0.9841269841269841</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="H183" s="13" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="I183" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="B184" s="12" t="s">
         <v>11</v>
@@ -7618,24 +7621,24 @@
         <v>121</v>
       </c>
       <c r="E184" s="12">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="F184" s="12">
         <v>104</v>
       </c>
       <c r="G184" s="15">
-        <v>0.9423076923076923</v>
+        <v>0.16346153846153846</v>
       </c>
       <c r="H184" s="13" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="I184" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B185" s="12" t="s">
         <v>11</v>
@@ -7647,24 +7650,24 @@
         <v>121</v>
       </c>
       <c r="E185" s="12">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F185" s="12">
         <v>26</v>
       </c>
       <c r="G185" s="15">
-        <v>0.8846153846153846</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="H185" s="13" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="I185" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B186" s="12" t="s">
         <v>11</v>
@@ -7676,24 +7679,24 @@
         <v>121</v>
       </c>
       <c r="E186" s="12">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="F186" s="12">
         <v>126</v>
       </c>
       <c r="G186" s="15">
-        <v>0.9841269841269841</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="H186" s="13" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="I186" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B187" s="12" t="s">
         <v>11</v>
@@ -7705,24 +7708,24 @@
         <v>121</v>
       </c>
       <c r="E187" s="12">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="F187" s="12">
         <v>104</v>
       </c>
       <c r="G187" s="15">
-        <v>0.9423076923076923</v>
+        <v>0.6826923076923077</v>
       </c>
       <c r="H187" s="13" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I187" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>11</v>
@@ -7734,24 +7737,24 @@
         <v>121</v>
       </c>
       <c r="E188" s="12">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F188" s="12">
         <v>26</v>
       </c>
       <c r="G188" s="15">
-        <v>0.8846153846153846</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="H188" s="13" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="12" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>11</v>
@@ -7763,24 +7766,24 @@
         <v>121</v>
       </c>
       <c r="E189" s="12">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F189" s="12">
         <v>126</v>
       </c>
       <c r="G189" s="15">
-        <v>0.9841269841269841</v>
+        <v>0.9206349206349206</v>
       </c>
       <c r="H189" s="13" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>11</v>
@@ -7792,24 +7795,24 @@
         <v>121</v>
       </c>
       <c r="E190" s="12">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F190" s="12">
         <v>104</v>
       </c>
       <c r="G190" s="15">
-        <v>0.9423076923076923</v>
+        <v>0.8557692307692307</v>
       </c>
       <c r="H190" s="13" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="12" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>11</v>
@@ -7830,15 +7833,15 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H191" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="12" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>11</v>
@@ -7859,15 +7862,15 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H192" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="12" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="B193" s="12" t="s">
         <v>11</v>
@@ -7888,15 +7891,15 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H193" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>11</v>
@@ -7917,15 +7920,15 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H194" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>11</v>
@@ -7946,15 +7949,15 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H195" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>11</v>
@@ -7975,15 +7978,15 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H196" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="12" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>11</v>
@@ -8004,15 +8007,15 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H197" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>11</v>
@@ -8033,15 +8036,15 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H198" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="12" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="B199" s="12" t="s">
         <v>11</v>
@@ -8062,15 +8065,15 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H199" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>11</v>
@@ -8091,15 +8094,15 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H200" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>11</v>
@@ -8120,15 +8123,15 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H201" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>11</v>
@@ -8149,15 +8152,15 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H202" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="12" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>11</v>
@@ -8178,15 +8181,15 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H203" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="12" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>11</v>
@@ -8207,15 +8210,15 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H204" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="12" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>11</v>
@@ -8236,18 +8239,18 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H205" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="12" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C206" s="13" t="s">
         <v>20</v>
@@ -8256,27 +8259,27 @@
         <v>121</v>
       </c>
       <c r="E206" s="12">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F206" s="12">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G206" s="15">
-        <v>0.36363636363636365</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H206" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="12" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C207" s="13" t="s">
         <v>23</v>
@@ -8285,27 +8288,27 @@
         <v>121</v>
       </c>
       <c r="E207" s="12">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="F207" s="12">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G207" s="15">
-        <v>0.4588235294117647</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H207" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B208" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C208" s="13" t="s">
         <v>22</v>
@@ -8314,27 +8317,27 @@
         <v>121</v>
       </c>
       <c r="E208" s="12">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="F208" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G208" s="15">
-        <v>0.10784313725490197</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H208" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="12" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C209" s="13" t="s">
         <v>20</v>
@@ -8343,27 +8346,27 @@
         <v>121</v>
       </c>
       <c r="E209" s="12">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F209" s="12">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G209" s="15">
-        <v>0.6590909090909091</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H209" s="13" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="B210" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C210" s="13" t="s">
         <v>23</v>
@@ -8372,27 +8375,27 @@
         <v>121</v>
       </c>
       <c r="E210" s="12">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F210" s="12">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G210" s="15">
-        <v>0.7411764705882353</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H210" s="13" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="12" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="B211" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C211" s="13" t="s">
         <v>22</v>
@@ -8401,27 +8404,27 @@
         <v>121</v>
       </c>
       <c r="E211" s="12">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="F211" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G211" s="15">
-        <v>0.21568627450980393</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H211" s="13" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="I211" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="B212" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C212" s="13" t="s">
         <v>20</v>
@@ -8430,27 +8433,27 @@
         <v>121</v>
       </c>
       <c r="E212" s="12">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F212" s="12">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G212" s="15">
-        <v>0.6590909090909091</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H212" s="13" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="12" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="B213" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C213" s="13" t="s">
         <v>23</v>
@@ -8459,27 +8462,27 @@
         <v>121</v>
       </c>
       <c r="E213" s="12">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F213" s="12">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G213" s="15">
-        <v>0.7411764705882353</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H213" s="13" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I213" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="B214" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C214" s="13" t="s">
         <v>22</v>
@@ -8488,27 +8491,27 @@
         <v>121</v>
       </c>
       <c r="E214" s="12">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="F214" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G214" s="15">
-        <v>0.22549019607843138</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H214" s="13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I214" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="12" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B215" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C215" s="13" t="s">
         <v>20</v>
@@ -8517,27 +8520,27 @@
         <v>121</v>
       </c>
       <c r="E215" s="12">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F215" s="12">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G215" s="15">
-        <v>0.6590909090909091</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H215" s="13" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I215" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C216" s="13" t="s">
         <v>23</v>
@@ -8546,27 +8549,27 @@
         <v>121</v>
       </c>
       <c r="E216" s="12">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F216" s="12">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G216" s="15">
-        <v>0.7411764705882353</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H216" s="13" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I216" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="12" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B217" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C217" s="13" t="s">
         <v>22</v>
@@ -8575,27 +8578,27 @@
         <v>121</v>
       </c>
       <c r="E217" s="12">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="F217" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G217" s="15">
-        <v>0.22549019607843138</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H217" s="13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I217" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="B218" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C218" s="13" t="s">
         <v>20</v>
@@ -8604,27 +8607,27 @@
         <v>121</v>
       </c>
       <c r="E218" s="12">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F218" s="12">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G218" s="15">
-        <v>0.6590909090909091</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H218" s="13" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I218" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="12" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C219" s="13" t="s">
         <v>23</v>
@@ -8633,27 +8636,27 @@
         <v>121</v>
       </c>
       <c r="E219" s="12">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="F219" s="12">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G219" s="15">
-        <v>0.7647058823529411</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H219" s="13" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="I219" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="B220" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C220" s="13" t="s">
         <v>22</v>
@@ -8662,24 +8665,24 @@
         <v>121</v>
       </c>
       <c r="E220" s="12">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="F220" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G220" s="15">
-        <v>0.23529411764705882</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H220" s="13" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="I220" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="12" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B221" s="12" t="s">
         <v>12</v>
@@ -8691,24 +8694,24 @@
         <v>121</v>
       </c>
       <c r="E221" s="12">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F221" s="12">
         <v>44</v>
       </c>
       <c r="G221" s="15">
-        <v>0.6590909090909091</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="H221" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I221" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B222" s="12" t="s">
         <v>12</v>
@@ -8720,24 +8723,24 @@
         <v>121</v>
       </c>
       <c r="E222" s="12">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F222" s="12">
         <v>85</v>
       </c>
       <c r="G222" s="15">
-        <v>0.7647058823529411</v>
+        <v>0.4588235294117647</v>
       </c>
       <c r="H222" s="13" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="12" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B223" s="12" t="s">
         <v>12</v>
@@ -8749,24 +8752,24 @@
         <v>121</v>
       </c>
       <c r="E223" s="12">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F223" s="12">
         <v>102</v>
       </c>
       <c r="G223" s="15">
-        <v>0.23529411764705882</v>
+        <v>0.10784313725490197</v>
       </c>
       <c r="H223" s="13" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="I223" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="B224" s="12" t="s">
         <v>12</v>
@@ -8787,15 +8790,15 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H224" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I224" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="12" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="B225" s="12" t="s">
         <v>12</v>
@@ -8807,24 +8810,24 @@
         <v>121</v>
       </c>
       <c r="E225" s="12">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F225" s="12">
         <v>85</v>
       </c>
       <c r="G225" s="15">
-        <v>0.7647058823529411</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="H225" s="13" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="I225" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="B226" s="12" t="s">
         <v>12</v>
@@ -8836,24 +8839,24 @@
         <v>121</v>
       </c>
       <c r="E226" s="12">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F226" s="12">
         <v>102</v>
       </c>
       <c r="G226" s="15">
-        <v>0.23529411764705882</v>
+        <v>0.21568627450980393</v>
       </c>
       <c r="H226" s="13" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I226" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B227" s="12" t="s">
         <v>12</v>
@@ -8874,15 +8877,15 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H227" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I227" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B228" s="12" t="s">
         <v>12</v>
@@ -8894,24 +8897,24 @@
         <v>121</v>
       </c>
       <c r="E228" s="12">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F228" s="12">
         <v>85</v>
       </c>
       <c r="G228" s="15">
-        <v>0.7647058823529411</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="H228" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I228" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B229" s="12" t="s">
         <v>12</v>
@@ -8923,24 +8926,24 @@
         <v>121</v>
       </c>
       <c r="E229" s="12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F229" s="12">
         <v>102</v>
       </c>
       <c r="G229" s="15">
-        <v>0.23529411764705882</v>
+        <v>0.22549019607843138</v>
       </c>
       <c r="H229" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I229" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="B230" s="12" t="s">
         <v>12</v>
@@ -8961,15 +8964,15 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H230" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I230" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="12" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="B231" s="12" t="s">
         <v>12</v>
@@ -8981,24 +8984,24 @@
         <v>121</v>
       </c>
       <c r="E231" s="12">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F231" s="12">
         <v>85</v>
       </c>
       <c r="G231" s="15">
-        <v>0.7647058823529411</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="H231" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I231" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="B232" s="12" t="s">
         <v>12</v>
@@ -9010,24 +9013,24 @@
         <v>121</v>
       </c>
       <c r="E232" s="12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F232" s="12">
         <v>102</v>
       </c>
       <c r="G232" s="15">
-        <v>0.24509803921568626</v>
+        <v>0.22549019607843138</v>
       </c>
       <c r="H232" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I232" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="12" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="B233" s="12" t="s">
         <v>12</v>
@@ -9048,15 +9051,15 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H233" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I233" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="12" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="B234" s="12" t="s">
         <v>12</v>
@@ -9068,24 +9071,24 @@
         <v>121</v>
       </c>
       <c r="E234" s="12">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F234" s="12">
         <v>85</v>
       </c>
       <c r="G234" s="15">
-        <v>0.7764705882352941</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="H234" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I234" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="12" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="B235" s="12" t="s">
         <v>12</v>
@@ -9097,172 +9100,172 @@
         <v>121</v>
       </c>
       <c r="E235" s="12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F235" s="12">
         <v>102</v>
       </c>
       <c r="G235" s="15">
-        <v>0.24509803921568626</v>
+        <v>0.23529411764705882</v>
       </c>
       <c r="H235" s="13" t="s">
         <v>226</v>
       </c>
       <c r="I235" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B236" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C236" s="13" t="s">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="D236" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E236" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F236" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="G236" s="12" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="E236" s="12">
+        <v>29</v>
+      </c>
+      <c r="F236" s="12">
+        <v>44</v>
+      </c>
+      <c r="G236" s="15">
+        <v>0.6590909090909091</v>
       </c>
       <c r="H236" s="13" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="I236" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="12" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="B237" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C237" s="13" t="s">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="D237" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E237" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F237" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="G237" s="12" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="E237" s="12">
+        <v>65</v>
+      </c>
+      <c r="F237" s="12">
+        <v>85</v>
+      </c>
+      <c r="G237" s="15">
+        <v>0.7647058823529411</v>
       </c>
       <c r="H237" s="13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I237" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B238" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C238" s="13" t="s">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="D238" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E238" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F238" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="G238" s="12" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="E238" s="12">
+        <v>24</v>
+      </c>
+      <c r="F238" s="12">
+        <v>102</v>
+      </c>
+      <c r="G238" s="15">
+        <v>0.23529411764705882</v>
       </c>
       <c r="H238" s="13" t="s">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="I238" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="12" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B239" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C239" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D239" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E239" s="12">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F239" s="12">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G239" s="15">
-        <v>0.17647058823529413</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H239" s="13" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="I239" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="12" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B240" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C240" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D240" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E240" s="12">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F240" s="12">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="G240" s="15">
-        <v>0.22058823529411764</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="H240" s="13" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I240" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="12" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="B241" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C241" s="13" t="s">
         <v>22</v>
@@ -9271,85 +9274,85 @@
         <v>121</v>
       </c>
       <c r="E241" s="12">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F241" s="12">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="G241" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.23529411764705882</v>
       </c>
       <c r="H241" s="13" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I241" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="12" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="B242" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C242" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D242" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E242" s="12">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F242" s="12">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G242" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H242" s="13" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="I242" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B243" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C243" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D243" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E243" s="12">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="F243" s="12">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="G243" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="H243" s="13" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="I243" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B244" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C244" s="13" t="s">
         <v>22</v>
@@ -9358,85 +9361,85 @@
         <v>121</v>
       </c>
       <c r="E244" s="12">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F244" s="12">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="G244" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.23529411764705882</v>
       </c>
       <c r="H244" s="13" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="I244" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B245" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C245" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D245" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E245" s="12">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F245" s="12">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G245" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H245" s="13" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="I245" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B246" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C246" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D246" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E246" s="12">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="F246" s="12">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="G246" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="H246" s="13" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="I246" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B247" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C247" s="13" t="s">
         <v>22</v>
@@ -9445,219 +9448,219 @@
         <v>121</v>
       </c>
       <c r="E247" s="12">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F247" s="12">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="G247" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.24509803921568626</v>
       </c>
       <c r="H247" s="13" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I247" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B248" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C248" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D248" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E248" s="12">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F248" s="12">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G248" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H248" s="13" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="I248" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="12" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="B249" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C249" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D249" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E249" s="12">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F249" s="12">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="G249" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="H249" s="13" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I249" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="12" t="s">
-        <v>184</v>
+        <v>134</v>
       </c>
       <c r="B250" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C250" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D250" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E250" s="12">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="F250" s="12">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="G250" s="15">
-        <v>0.42857142857142855</v>
+        <v>0.24509803921568626</v>
       </c>
       <c r="H250" s="13" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="I250" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="12" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="B251" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C251" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D251" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E251" s="12">
         <v>29</v>
       </c>
-      <c r="D251" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E251" s="12">
-        <v>1</v>
-      </c>
       <c r="F251" s="12">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G251" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H251" s="13" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="I251" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="12" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="B252" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C252" s="13" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D252" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E252" s="12">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F252" s="12">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="G252" s="15">
-        <v>0.4444444444444444</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="H252" s="13" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I252" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="12" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="B253" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C253" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D253" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E253" s="12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F253" s="12">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="G253" s="15">
-        <v>0</v>
+        <v>0.24509803921568626</v>
       </c>
       <c r="H253" s="13" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I253" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="12" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="B254" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C254" s="13" t="s">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="D254" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E254" s="12">
-        <v>124</v>
-      </c>
-      <c r="F254" s="12">
-        <v>189</v>
-      </c>
-      <c r="G254" s="15">
-        <v>0.656084656084656</v>
+        <v>73</v>
+      </c>
+      <c r="E254" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F254" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G254" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="H254" s="13" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I254" s="12" t="s">
         <v>117</v>
@@ -9665,28 +9668,28 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="12" t="s">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="B255" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C255" s="13" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="D255" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E255" s="12">
-        <v>0</v>
-      </c>
-      <c r="F255" s="12">
-        <v>27</v>
-      </c>
-      <c r="G255" s="15">
-        <v>0</v>
+        <v>73</v>
+      </c>
+      <c r="E255" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F255" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G255" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="H255" s="13" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="I255" s="12" t="s">
         <v>117</v>
@@ -9694,28 +9697,28 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B256" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C256" s="13" t="s">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="D256" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E256" s="12">
-        <v>148</v>
-      </c>
-      <c r="F256" s="12">
-        <v>189</v>
-      </c>
-      <c r="G256" s="15">
-        <v>0.783068783068783</v>
+        <v>73</v>
+      </c>
+      <c r="E256" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F256" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G256" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="H256" s="13" t="s">
-        <v>238</v>
+        <v>73</v>
       </c>
       <c r="I256" s="12" t="s">
         <v>117</v>
@@ -9726,25 +9729,25 @@
         <v>120</v>
       </c>
       <c r="B257" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C257" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D257" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E257" s="12">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F257" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G257" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.17647058823529413</v>
       </c>
       <c r="H257" s="13" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I257" s="12" t="s">
         <v>117</v>
@@ -9755,25 +9758,25 @@
         <v>123</v>
       </c>
       <c r="B258" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C258" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D258" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E258" s="12">
         <v>30</v>
       </c>
-      <c r="D258" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E258" s="12">
-        <v>154</v>
-      </c>
       <c r="F258" s="12">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="G258" s="15">
-        <v>0.8148148148148148</v>
+        <v>0.22058823529411764</v>
       </c>
       <c r="H258" s="13" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I258" s="12" t="s">
         <v>117</v>
@@ -9781,28 +9784,28 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="12" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="B259" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C259" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D259" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E259" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F259" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G259" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H259" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I259" s="12" t="s">
         <v>117</v>
@@ -9810,268 +9813,268 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="12" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="B260" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C260" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D260" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E260" s="12">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="F260" s="12">
-        <v>308</v>
+        <v>136</v>
       </c>
       <c r="G260" s="15">
-        <v>0.5194805194805194</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H260" s="13" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="I260" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="12" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="B261" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C261" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D261" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E261" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F261" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G261" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H261" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I261" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="B262" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C262" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D262" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E262" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F262" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G262" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H262" s="13" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I262" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="12" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="B263" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C263" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D263" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E263" s="12">
-        <v>161</v>
+        <v>45</v>
       </c>
       <c r="F263" s="12">
-        <v>308</v>
+        <v>136</v>
       </c>
       <c r="G263" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H263" s="13" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="I263" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B264" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C264" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D264" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E264" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F264" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G264" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H264" s="13" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I264" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B265" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C265" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D265" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E265" s="12">
-        <v>161</v>
+        <v>45</v>
       </c>
       <c r="F265" s="12">
-        <v>308</v>
+        <v>136</v>
       </c>
       <c r="G265" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H265" s="13" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="I265" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B266" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C266" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D266" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E266" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F266" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G266" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H266" s="13" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I266" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B267" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C267" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D267" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E267" s="12">
-        <v>161</v>
+        <v>45</v>
       </c>
       <c r="F267" s="12">
-        <v>308</v>
+        <v>136</v>
       </c>
       <c r="G267" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H267" s="13" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="I267" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="B268" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C268" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D268" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E268" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F268" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G268" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H268" s="13" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I268" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="12" t="s">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="B269" s="12" t="s">
         <v>15</v>
@@ -10083,24 +10086,24 @@
         <v>121</v>
       </c>
       <c r="E269" s="12">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="F269" s="12">
-        <v>308</v>
+        <v>189</v>
       </c>
       <c r="G269" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="H269" s="13" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="I269" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="12" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="B270" s="12" t="s">
         <v>15</v>
@@ -10121,15 +10124,15 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H270" s="13" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I270" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="12" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B271" s="12" t="s">
         <v>15</v>
@@ -10141,24 +10144,24 @@
         <v>121</v>
       </c>
       <c r="E271" s="12">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="F271" s="12">
-        <v>308</v>
+        <v>189</v>
       </c>
       <c r="G271" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="H271" s="13" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I271" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B272" s="12" t="s">
         <v>15</v>
@@ -10170,24 +10173,24 @@
         <v>121</v>
       </c>
       <c r="E272" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F272" s="12">
         <v>27</v>
       </c>
       <c r="G272" s="15">
-        <v>0.037037037037037035</v>
+        <v>0</v>
       </c>
       <c r="H272" s="13" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="I272" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="12" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="B273" s="12" t="s">
         <v>15</v>
@@ -10199,24 +10202,24 @@
         <v>121</v>
       </c>
       <c r="E273" s="12">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="F273" s="12">
-        <v>308</v>
+        <v>189</v>
       </c>
       <c r="G273" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.656084656084656</v>
       </c>
       <c r="H273" s="13" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="I273" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="B274" s="12" t="s">
         <v>15</v>
@@ -10228,24 +10231,24 @@
         <v>121</v>
       </c>
       <c r="E274" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F274" s="12">
         <v>27</v>
       </c>
       <c r="G274" s="15">
-        <v>0.037037037037037035</v>
+        <v>0</v>
       </c>
       <c r="H274" s="13" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="I274" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="12" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B275" s="12" t="s">
         <v>15</v>
@@ -10257,24 +10260,24 @@
         <v>121</v>
       </c>
       <c r="E275" s="12">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="F275" s="12">
-        <v>346</v>
+        <v>189</v>
       </c>
       <c r="G275" s="15">
-        <v>0.4653179190751445</v>
+        <v>0.783068783068783</v>
       </c>
       <c r="H275" s="13" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I275" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="12" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="B276" s="12" t="s">
         <v>15</v>
@@ -10295,15 +10298,15 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H276" s="13" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I276" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="12" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="B277" s="12" t="s">
         <v>15</v>
@@ -10315,45 +10318,45 @@
         <v>121</v>
       </c>
       <c r="E277" s="12">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F277" s="12">
-        <v>346</v>
+        <v>189</v>
       </c>
       <c r="G277" s="15">
-        <v>0.4653179190751445</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="H277" s="13" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I277" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B278" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C278" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D278" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E278" s="12">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F278" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G278" s="15">
-        <v>0.06040268456375839</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H278" s="13" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I278" s="12" t="s">
         <v>117</v>
@@ -10361,28 +10364,28 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="12" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
       <c r="B279" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C279" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D279" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E279" s="12">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="F279" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G279" s="15">
-        <v>0.14093959731543623</v>
+        <v>0.5194805194805194</v>
       </c>
       <c r="H279" s="13" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I279" s="12" t="s">
         <v>117</v>
@@ -10390,28 +10393,28 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="12" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="B280" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C280" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D280" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E280" s="12">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F280" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G280" s="15">
-        <v>0.15436241610738255</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H280" s="13" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="I280" s="12" t="s">
         <v>117</v>
@@ -10419,89 +10422,89 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="12" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B281" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C281" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D281" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E281" s="12">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F281" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G281" s="15">
-        <v>0.2080536912751678</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H281" s="13" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I281" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B282" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C282" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D282" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E282" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F282" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G282" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H282" s="13" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I282" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="12" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="B283" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C283" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D283" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E283" s="12">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F283" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G283" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H283" s="13" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I283" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
@@ -10509,57 +10512,57 @@
         <v>79</v>
       </c>
       <c r="B284" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C284" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D284" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E284" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F284" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G284" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H284" s="13" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I284" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B285" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C285" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D285" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E285" s="12">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F285" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G285" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H285" s="13" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I285" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
@@ -10567,28 +10570,28 @@
         <v>129</v>
       </c>
       <c r="B286" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C286" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D286" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E286" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F286" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G286" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H286" s="13" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I286" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
@@ -10596,148 +10599,786 @@
         <v>130</v>
       </c>
       <c r="B287" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C287" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D287" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E287" s="12">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F287" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G287" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H287" s="13" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I287" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B288" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C288" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D288" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E288" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F288" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G288" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H288" s="13" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I288" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B289" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C289" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D289" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E289" s="12">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F289" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G289" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H289" s="13" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I289" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B290" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C290" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D290" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E290" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F290" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G290" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H290" s="13" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I290" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B291" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C291" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D291" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E291" s="12">
+        <v>1</v>
+      </c>
+      <c r="F291" s="12">
+        <v>27</v>
+      </c>
+      <c r="G291" s="15">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H291" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="I291" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B292" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C292" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D292" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E292" s="12">
+        <v>161</v>
+      </c>
+      <c r="F292" s="12">
+        <v>308</v>
+      </c>
+      <c r="G292" s="15">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="H292" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="I292" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B293" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C293" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D293" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E293" s="12">
+        <v>1</v>
+      </c>
+      <c r="F293" s="12">
+        <v>27</v>
+      </c>
+      <c r="G293" s="15">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H293" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="I293" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C294" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D294" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E294" s="12">
+        <v>161</v>
+      </c>
+      <c r="F294" s="12">
+        <v>346</v>
+      </c>
+      <c r="G294" s="15">
+        <v>0.4653179190751445</v>
+      </c>
+      <c r="H294" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I294" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B295" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C295" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D295" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E295" s="12">
+        <v>1</v>
+      </c>
+      <c r="F295" s="12">
+        <v>27</v>
+      </c>
+      <c r="G295" s="15">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H295" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="I295" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B296" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C296" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D296" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E296" s="12">
+        <v>161</v>
+      </c>
+      <c r="F296" s="12">
+        <v>346</v>
+      </c>
+      <c r="G296" s="15">
+        <v>0.4653179190751445</v>
+      </c>
+      <c r="H296" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I296" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B291" s="12" t="s">
+      <c r="B297" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C297" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D297" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E297" s="12">
+        <v>1</v>
+      </c>
+      <c r="F297" s="12">
+        <v>27</v>
+      </c>
+      <c r="G297" s="15">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H297" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="I297" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B298" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C298" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D298" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E298" s="12">
+        <v>161</v>
+      </c>
+      <c r="F298" s="12">
+        <v>346</v>
+      </c>
+      <c r="G298" s="15">
+        <v>0.4653179190751445</v>
+      </c>
+      <c r="H298" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I298" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B299" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C291" s="13" t="s">
+      <c r="C299" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D291" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E291" s="12">
+      <c r="D299" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E299" s="12">
+        <v>9</v>
+      </c>
+      <c r="F299" s="12">
+        <v>149</v>
+      </c>
+      <c r="G299" s="15">
+        <v>0.06040268456375839</v>
+      </c>
+      <c r="H299" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I299" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B300" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C300" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D300" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E300" s="12">
+        <v>21</v>
+      </c>
+      <c r="F300" s="12">
+        <v>149</v>
+      </c>
+      <c r="G300" s="15">
+        <v>0.14093959731543623</v>
+      </c>
+      <c r="H300" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="I300" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B301" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C301" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D301" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E301" s="12">
+        <v>23</v>
+      </c>
+      <c r="F301" s="12">
+        <v>149</v>
+      </c>
+      <c r="G301" s="15">
+        <v>0.15436241610738255</v>
+      </c>
+      <c r="H301" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="I301" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B302" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C302" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D302" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E302" s="12">
+        <v>31</v>
+      </c>
+      <c r="F302" s="12">
+        <v>149</v>
+      </c>
+      <c r="G302" s="15">
+        <v>0.2080536912751678</v>
+      </c>
+      <c r="H302" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="I302" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B303" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C303" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D303" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E303" s="12">
         <v>34</v>
       </c>
-      <c r="F291" s="12">
+      <c r="F303" s="12">
         <v>149</v>
       </c>
-      <c r="G291" s="15">
+      <c r="G303" s="15">
         <v>0.22818791946308725</v>
       </c>
-      <c r="H291" s="13" t="s">
+      <c r="H303" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="I291" s="12" t="s">
-        <v>127</v>
+      <c r="I303" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B304" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C304" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D304" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E304" s="12">
+        <v>34</v>
+      </c>
+      <c r="F304" s="12">
+        <v>149</v>
+      </c>
+      <c r="G304" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H304" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="I304" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B305" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C305" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D305" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E305" s="12">
+        <v>34</v>
+      </c>
+      <c r="F305" s="12">
+        <v>149</v>
+      </c>
+      <c r="G305" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H305" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I305" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B306" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C306" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D306" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E306" s="12">
+        <v>34</v>
+      </c>
+      <c r="F306" s="12">
+        <v>149</v>
+      </c>
+      <c r="G306" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H306" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I306" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B307" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C307" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D307" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E307" s="12">
+        <v>34</v>
+      </c>
+      <c r="F307" s="12">
+        <v>149</v>
+      </c>
+      <c r="G307" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H307" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I307" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B308" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C308" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D308" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E308" s="12">
+        <v>34</v>
+      </c>
+      <c r="F308" s="12">
+        <v>149</v>
+      </c>
+      <c r="G308" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H308" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I308" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B309" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C309" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D309" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E309" s="12">
+        <v>34</v>
+      </c>
+      <c r="F309" s="12">
+        <v>149</v>
+      </c>
+      <c r="G309" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H309" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I309" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B310" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C310" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D310" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E310" s="12">
+        <v>34</v>
+      </c>
+      <c r="F310" s="12">
+        <v>149</v>
+      </c>
+      <c r="G310" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H310" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I310" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B311" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C311" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D311" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E311" s="12">
+        <v>34</v>
+      </c>
+      <c r="F311" s="12">
+        <v>149</v>
+      </c>
+      <c r="G311" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H311" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I311" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B312" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C312" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D312" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E312" s="12">
+        <v>34</v>
+      </c>
+      <c r="F312" s="12">
+        <v>149</v>
+      </c>
+      <c r="G312" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H312" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I312" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B313" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C313" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D313" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E313" s="12">
+        <v>34</v>
+      </c>
+      <c r="F313" s="12">
+        <v>149</v>
+      </c>
+      <c r="G313" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H313" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I313" s="12" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I291"/>
+  <autoFilter ref="A1:I313"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -10754,10 +11395,10 @@
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -10765,23 +11406,23 @@
         <v>78</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -10789,23 +11430,23 @@
         <v>94</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/Broga_Competitor_Sales_Analysis.xlsx
+++ b/Broga_Competitor_Sales_Analysis.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="266">
   <si>
     <t>BROGA COMPETITOR SALES ANALYSIS</t>
   </si>
   <si>
-    <t>Generated from embedded historical records + saved TEDUH records · 24/10/2026</t>
+    <t>Generated from embedded historical records + saved TEDUH records · 25/10/2026</t>
   </si>
   <si>
     <t>RECORD DETAIL</t>
@@ -111,313 +111,316 @@
     <t>Latest record</t>
   </si>
   <si>
+    <t>25/10/2026</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>Sales Unit · latest</t>
+  </si>
+  <si>
+    <t>74 / 81</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>69 / 113</t>
+  </si>
+  <si>
+    <t>22 / 48</t>
+  </si>
+  <si>
+    <t>71 / 113</t>
+  </si>
+  <si>
+    <t>46 / 46</t>
+  </si>
+  <si>
+    <t>56 / 56</t>
+  </si>
+  <si>
+    <t>25 / 25</t>
+  </si>
+  <si>
+    <t>10 / 25</t>
+  </si>
+  <si>
+    <t>77 / 99</t>
+  </si>
+  <si>
+    <t>111 / 111</t>
+  </si>
+  <si>
+    <t>134 / 138</t>
+  </si>
+  <si>
+    <t>79 / 81</t>
+  </si>
+  <si>
+    <t>23 / 26</t>
+  </si>
+  <si>
+    <t>124 / 126</t>
+  </si>
+  <si>
+    <t>98 / 104</t>
+  </si>
+  <si>
+    <t>29 / 44</t>
+  </si>
+  <si>
+    <t>67 / 85</t>
+  </si>
+  <si>
+    <t>26 / 102</t>
+  </si>
+  <si>
+    <t>45 / 136</t>
+  </si>
+  <si>
+    <t>1 / 27</t>
+  </si>
+  <si>
+    <t>161 / 346</t>
+  </si>
+  <si>
+    <t>34 / 149</t>
+  </si>
+  <si>
+    <t>Sales Status · latest</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>Yet to launch</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>46%</t>
+  </si>
+  <si>
+    <t>63%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>78%</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>98%</t>
+  </si>
+  <si>
+    <t>88%</t>
+  </si>
+  <si>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>66%</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>Yet to sign</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>4%</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>23%</t>
+  </si>
+  <si>
+    <t>Weekly baseline</t>
+  </si>
+  <si>
+    <t>18/10/2026</t>
+  </si>
+  <si>
+    <t>No record 7–14 days earlier</t>
+  </si>
+  <si>
+    <t>Sales Unit · baseline</t>
+  </si>
+  <si>
+    <t>21 / 48</t>
+  </si>
+  <si>
+    <t>24 / 25</t>
+  </si>
+  <si>
+    <t>65 / 85</t>
+  </si>
+  <si>
+    <t>24 / 102</t>
+  </si>
+  <si>
+    <t>161 / 308</t>
+  </si>
+  <si>
+    <t>Sales Status · baseline</t>
+  </si>
+  <si>
+    <t>44%</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>76%</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>52%</t>
+  </si>
+  <si>
+    <t>Weekly Change</t>
+  </si>
+  <si>
+    <t>No change</t>
+  </si>
+  <si>
+    <t>No signed status yet</t>
+  </si>
+  <si>
+    <t>+1 signed; +2.1 percentage points</t>
+  </si>
+  <si>
+    <t>+1 signed; +4.0 percentage points</t>
+  </si>
+  <si>
+    <t>Insufficient weekly history</t>
+  </si>
+  <si>
+    <t>+2 signed; +2.4 percentage points</t>
+  </si>
+  <si>
+    <t>+2 signed; +2.0 percentage points</t>
+  </si>
+  <si>
+    <t>⚠ Scope changed (308 → 346); recalculated: 0 signed change; -5.7 percentage points</t>
+  </si>
+  <si>
+    <t>Record Date</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Unit Group / Layout</t>
+  </si>
+  <si>
+    <t>Status Type</t>
+  </si>
+  <si>
+    <t>Signed Units</t>
+  </si>
+  <si>
+    <t>Total Units</t>
+  </si>
+  <si>
+    <t>Signed %</t>
+  </si>
+  <si>
+    <t>Raw Recorded Status</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>17/03/2025</t>
+  </si>
+  <si>
+    <t>Booked</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>11% Booked (9/81 units)</t>
+  </si>
+  <si>
+    <t>Embedded historical record</t>
+  </si>
+  <si>
+    <t>06/10/2025</t>
+  </si>
+  <si>
+    <t>35% Booked (28/81 units)</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>Signed</t>
+  </si>
+  <si>
+    <t>59% Signed (48/81 units)</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>65% Signed (53/81 units)</t>
+  </si>
+  <si>
+    <t>88% Signed (72/81 units)</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>74/81 signed</t>
+  </si>
+  <si>
+    <t>Saved TEDUH record</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>21/10/2026</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
+  </si>
+  <si>
     <t>24/10/2026</t>
-  </si>
-  <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>Sales Unit · latest</t>
-  </si>
-  <si>
-    <t>74 / 81</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>69 / 113</t>
-  </si>
-  <si>
-    <t>22 / 48</t>
-  </si>
-  <si>
-    <t>71 / 113</t>
-  </si>
-  <si>
-    <t>46 / 46</t>
-  </si>
-  <si>
-    <t>56 / 56</t>
-  </si>
-  <si>
-    <t>25 / 25</t>
-  </si>
-  <si>
-    <t>10 / 25</t>
-  </si>
-  <si>
-    <t>77 / 99</t>
-  </si>
-  <si>
-    <t>111 / 111</t>
-  </si>
-  <si>
-    <t>134 / 138</t>
-  </si>
-  <si>
-    <t>79 / 81</t>
-  </si>
-  <si>
-    <t>23 / 26</t>
-  </si>
-  <si>
-    <t>124 / 126</t>
-  </si>
-  <si>
-    <t>98 / 104</t>
-  </si>
-  <si>
-    <t>29 / 44</t>
-  </si>
-  <si>
-    <t>67 / 85</t>
-  </si>
-  <si>
-    <t>26 / 102</t>
-  </si>
-  <si>
-    <t>45 / 136</t>
-  </si>
-  <si>
-    <t>1 / 27</t>
-  </si>
-  <si>
-    <t>161 / 346</t>
-  </si>
-  <si>
-    <t>34 / 149</t>
-  </si>
-  <si>
-    <t>Sales Status · latest</t>
-  </si>
-  <si>
-    <t>91%</t>
-  </si>
-  <si>
-    <t>Yet to launch</t>
-  </si>
-  <si>
-    <t>61%</t>
-  </si>
-  <si>
-    <t>46%</t>
-  </si>
-  <si>
-    <t>63%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>78%</t>
-  </si>
-  <si>
-    <t>97%</t>
-  </si>
-  <si>
-    <t>98%</t>
-  </si>
-  <si>
-    <t>88%</t>
-  </si>
-  <si>
-    <t>94%</t>
-  </si>
-  <si>
-    <t>66%</t>
-  </si>
-  <si>
-    <t>79%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>Yet to sign</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>47%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>Weekly baseline</t>
-  </si>
-  <si>
-    <t>17/10/2026</t>
-  </si>
-  <si>
-    <t>No record 7–14 days earlier</t>
-  </si>
-  <si>
-    <t>Sales Unit · baseline</t>
-  </si>
-  <si>
-    <t>21 / 48</t>
-  </si>
-  <si>
-    <t>24 / 25</t>
-  </si>
-  <si>
-    <t>65 / 85</t>
-  </si>
-  <si>
-    <t>24 / 102</t>
-  </si>
-  <si>
-    <t>161 / 308</t>
-  </si>
-  <si>
-    <t>Sales Status · baseline</t>
-  </si>
-  <si>
-    <t>44%</t>
-  </si>
-  <si>
-    <t>96%</t>
-  </si>
-  <si>
-    <t>76%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>52%</t>
-  </si>
-  <si>
-    <t>Weekly Change</t>
-  </si>
-  <si>
-    <t>No change</t>
-  </si>
-  <si>
-    <t>No signed status yet</t>
-  </si>
-  <si>
-    <t>+1 signed; +2.1 percentage points</t>
-  </si>
-  <si>
-    <t>+1 signed; +4.0 percentage points</t>
-  </si>
-  <si>
-    <t>Insufficient weekly history</t>
-  </si>
-  <si>
-    <t>+2 signed; +2.4 percentage points</t>
-  </si>
-  <si>
-    <t>+2 signed; +2.0 percentage points</t>
-  </si>
-  <si>
-    <t>⚠ Scope changed (308 → 346); recalculated: 0 signed change; -5.7 percentage points</t>
-  </si>
-  <si>
-    <t>Record Date</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Unit Group / Layout</t>
-  </si>
-  <si>
-    <t>Status Type</t>
-  </si>
-  <si>
-    <t>Signed Units</t>
-  </si>
-  <si>
-    <t>Total Units</t>
-  </si>
-  <si>
-    <t>Signed %</t>
-  </si>
-  <si>
-    <t>Raw Recorded Status</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>17/03/2025</t>
-  </si>
-  <si>
-    <t>Booked</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>11% Booked (9/81 units)</t>
-  </si>
-  <si>
-    <t>Embedded historical record</t>
-  </si>
-  <si>
-    <t>06/10/2025</t>
-  </si>
-  <si>
-    <t>35% Booked (28/81 units)</t>
-  </si>
-  <si>
-    <t>08/06/2026</t>
-  </si>
-  <si>
-    <t>Signed</t>
-  </si>
-  <si>
-    <t>59% Signed (48/81 units)</t>
-  </si>
-  <si>
-    <t>10/07/2026</t>
-  </si>
-  <si>
-    <t>65% Signed (53/81 units)</t>
-  </si>
-  <si>
-    <t>88% Signed (72/81 units)</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>74/81 signed</t>
-  </si>
-  <si>
-    <t>Saved TEDUH record</t>
-  </si>
-  <si>
-    <t>16/10/2026</t>
-  </si>
-  <si>
-    <t>18/10/2026</t>
-  </si>
-  <si>
-    <t>19/10/2026</t>
-  </si>
-  <si>
-    <t>20/10/2026</t>
-  </si>
-  <si>
-    <t>21/10/2026</t>
-  </si>
-  <si>
-    <t>22/10/2026</t>
-  </si>
-  <si>
-    <t>23/10/2026</t>
   </si>
   <si>
     <t>No group details</t>
@@ -2318,7 +2321,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I335"/>
+  <dimension ref="A1:I357"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2560,7 +2563,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>3</v>
@@ -2589,7 +2592,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>3</v>
@@ -2763,7 +2766,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>3</v>
@@ -2792,42 +2795,42 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
+      </c>
+      <c r="E17" s="12">
+        <v>74</v>
+      </c>
+      <c r="F17" s="12">
+        <v>81</v>
+      </c>
+      <c r="G17" s="15">
+        <v>0.9135802469135802</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>60</v>
@@ -2842,7 +2845,7 @@
         <v>114</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>116</v>
@@ -2850,13 +2853,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>60</v>
@@ -2871,7 +2874,7 @@
         <v>114</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>116</v>
@@ -2879,26 +2882,28 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F20" s="12">
-        <v>113</v>
-      </c>
-      <c r="G20" s="14"/>
+      <c r="F20" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>114</v>
+      </c>
       <c r="H20" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>116</v>
@@ -2906,7 +2911,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>5</v>
@@ -2925,7 +2930,7 @@
       </c>
       <c r="G21" s="14"/>
       <c r="H21" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I21" s="12" t="s">
         <v>116</v>
@@ -2933,7 +2938,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>5</v>
@@ -2952,7 +2957,7 @@
       </c>
       <c r="G22" s="14"/>
       <c r="H22" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>116</v>
@@ -2960,7 +2965,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>5</v>
@@ -2987,7 +2992,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>5</v>
@@ -2996,19 +3001,17 @@
         <v>20</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E24" s="12">
-        <v>34</v>
+        <v>113</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="F24" s="12">
         <v>113</v>
       </c>
-      <c r="G24" s="15">
-        <v>0.3008849557522124</v>
-      </c>
+      <c r="G24" s="14"/>
       <c r="H24" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>116</v>
@@ -3016,7 +3019,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>5</v>
@@ -3028,16 +3031,16 @@
         <v>120</v>
       </c>
       <c r="E25" s="12">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F25" s="12">
         <v>113</v>
       </c>
       <c r="G25" s="15">
-        <v>0.3274336283185841</v>
+        <v>0.3008849557522124</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>116</v>
@@ -3045,7 +3048,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>5</v>
@@ -3066,7 +3069,7 @@
         <v>0.3274336283185841</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>116</v>
@@ -3074,7 +3077,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>5</v>
@@ -3086,16 +3089,16 @@
         <v>120</v>
       </c>
       <c r="E27" s="12">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F27" s="12">
         <v>113</v>
       </c>
       <c r="G27" s="15">
-        <v>0.4778761061946903</v>
+        <v>0.3274336283185841</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I27" s="12" t="s">
         <v>116</v>
@@ -3103,7 +3106,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>5</v>
@@ -3115,13 +3118,13 @@
         <v>120</v>
       </c>
       <c r="E28" s="12">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F28" s="12">
         <v>113</v>
       </c>
       <c r="G28" s="15">
-        <v>0.5575221238938053</v>
+        <v>0.4778761061946903</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>150</v>
@@ -3132,7 +3135,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>5</v>
@@ -3144,13 +3147,13 @@
         <v>120</v>
       </c>
       <c r="E29" s="12">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F29" s="12">
         <v>113</v>
       </c>
       <c r="G29" s="15">
-        <v>0.6017699115044248</v>
+        <v>0.5575221238938053</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>151</v>
@@ -3161,7 +3164,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>5</v>
@@ -3182,7 +3185,7 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I30" s="12" t="s">
         <v>116</v>
@@ -3190,7 +3193,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>5</v>
@@ -3214,12 +3217,12 @@
         <v>152</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>5</v>
@@ -3240,7 +3243,7 @@
         <v>0.6017699115044248</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I32" s="12" t="s">
         <v>127</v>
@@ -3248,7 +3251,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>5</v>
@@ -3260,13 +3263,13 @@
         <v>120</v>
       </c>
       <c r="E33" s="12">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F33" s="12">
         <v>113</v>
       </c>
       <c r="G33" s="15">
-        <v>0.6106194690265486</v>
+        <v>0.6017699115044248</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>153</v>
@@ -3298,7 +3301,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I34" s="12" t="s">
         <v>127</v>
@@ -3306,7 +3309,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>5</v>
@@ -3327,7 +3330,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I35" s="12" t="s">
         <v>127</v>
@@ -3335,7 +3338,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>5</v>
@@ -3356,7 +3359,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>127</v>
@@ -3364,7 +3367,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>5</v>
@@ -3385,7 +3388,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I37" s="12" t="s">
         <v>127</v>
@@ -3393,7 +3396,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>5</v>
@@ -3414,7 +3417,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I38" s="12" t="s">
         <v>127</v>
@@ -3422,7 +3425,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>5</v>
@@ -3443,7 +3446,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I39" s="12" t="s">
         <v>127</v>
@@ -3451,7 +3454,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>5</v>
@@ -3472,7 +3475,7 @@
         <v>0.6106194690265486</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I40" s="12" t="s">
         <v>127</v>
@@ -3480,61 +3483,65 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D41" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" s="12">
+        <v>69</v>
+      </c>
+      <c r="F41" s="12">
         <v>113</v>
       </c>
-      <c r="E41" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="F41" s="12">
-        <v>48</v>
-      </c>
-      <c r="G41" s="14"/>
+      <c r="G41" s="15">
+        <v>0.6106194690265486</v>
+      </c>
       <c r="H41" s="13" t="s">
         <v>154</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D42" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" s="12">
+        <v>69</v>
+      </c>
+      <c r="F42" s="12">
         <v>113</v>
       </c>
-      <c r="E42" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="F42" s="12">
-        <v>48</v>
-      </c>
-      <c r="G42" s="14"/>
+      <c r="G42" s="15">
+        <v>0.6106194690265486</v>
+      </c>
       <c r="H42" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>6</v>
@@ -3561,7 +3568,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>6</v>
@@ -3588,7 +3595,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>6</v>
@@ -3607,7 +3614,7 @@
       </c>
       <c r="G45" s="14"/>
       <c r="H45" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I45" s="12" t="s">
         <v>116</v>
@@ -3615,7 +3622,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>6</v>
@@ -3642,7 +3649,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>6</v>
@@ -3651,17 +3658,15 @@
         <v>21</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E47" s="12">
-        <v>15</v>
+        <v>113</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="F47" s="12">
         <v>48</v>
       </c>
-      <c r="G47" s="15">
-        <v>0.3125</v>
-      </c>
+      <c r="G47" s="14"/>
       <c r="H47" s="13" t="s">
         <v>158</v>
       </c>
@@ -3671,7 +3676,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>6</v>
@@ -3680,19 +3685,17 @@
         <v>21</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E48" s="12">
-        <v>19</v>
+        <v>113</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="F48" s="12">
         <v>48</v>
       </c>
-      <c r="G48" s="15">
-        <v>0.3958333333333333</v>
-      </c>
+      <c r="G48" s="14"/>
       <c r="H48" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I48" s="12" t="s">
         <v>116</v>
@@ -3700,7 +3703,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>6</v>
@@ -3712,13 +3715,13 @@
         <v>120</v>
       </c>
       <c r="E49" s="12">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F49" s="12">
         <v>48</v>
       </c>
       <c r="G49" s="15">
-        <v>0.3958333333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>159</v>
@@ -3729,7 +3732,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>6</v>
@@ -3741,13 +3744,13 @@
         <v>120</v>
       </c>
       <c r="E50" s="12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F50" s="12">
         <v>48</v>
       </c>
       <c r="G50" s="15">
-        <v>0.4375</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>160</v>
@@ -3758,7 +3761,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>6</v>
@@ -3770,24 +3773,24 @@
         <v>120</v>
       </c>
       <c r="E51" s="12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F51" s="12">
         <v>48</v>
       </c>
       <c r="G51" s="15">
-        <v>0.4375</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>6</v>
@@ -3811,12 +3814,12 @@
         <v>161</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>6</v>
@@ -3837,7 +3840,7 @@
         <v>0.4375</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>127</v>
@@ -3845,7 +3848,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>6</v>
@@ -3866,7 +3869,7 @@
         <v>0.4375</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I54" s="12" t="s">
         <v>127</v>
@@ -3874,7 +3877,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>6</v>
@@ -3895,7 +3898,7 @@
         <v>0.4375</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I55" s="12" t="s">
         <v>127</v>
@@ -3903,7 +3906,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>6</v>
@@ -3924,7 +3927,7 @@
         <v>0.4375</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I56" s="12" t="s">
         <v>127</v>
@@ -3932,7 +3935,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>6</v>
@@ -3944,13 +3947,13 @@
         <v>120</v>
       </c>
       <c r="E57" s="12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F57" s="12">
         <v>48</v>
       </c>
       <c r="G57" s="15">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>162</v>
@@ -3961,7 +3964,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>6</v>
@@ -3973,13 +3976,13 @@
         <v>120</v>
       </c>
       <c r="E58" s="12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F58" s="12">
         <v>48</v>
       </c>
       <c r="G58" s="15">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="H58" s="13" t="s">
         <v>162</v>
@@ -3990,7 +3993,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>6</v>
@@ -4011,7 +4014,7 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I59" s="12" t="s">
         <v>127</v>
@@ -4019,7 +4022,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>6</v>
@@ -4040,7 +4043,7 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I60" s="12" t="s">
         <v>127</v>
@@ -4048,94 +4051,94 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C61" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E61" s="12">
         <v>22</v>
       </c>
-      <c r="D61" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E61" s="12">
-        <v>83</v>
-      </c>
       <c r="F61" s="12">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="G61" s="15">
-        <v>0.8383838383838383</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H61" s="13" t="s">
         <v>163</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C62" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E62" s="12">
         <v>22</v>
       </c>
-      <c r="D62" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E62" s="12">
-        <v>70</v>
-      </c>
       <c r="F62" s="12">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G62" s="15">
-        <v>0.6194690265486725</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C63" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E63" s="12">
         <v>22</v>
       </c>
-      <c r="D63" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E63" s="12">
-        <v>70</v>
-      </c>
       <c r="F63" s="12">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G63" s="15">
-        <v>0.6194690265486725</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>7</v>
@@ -4147,16 +4150,16 @@
         <v>120</v>
       </c>
       <c r="E64" s="12">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F64" s="12">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G64" s="15">
-        <v>0.6283185840707964</v>
+        <v>0.8383838383838383</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>116</v>
@@ -4164,7 +4167,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>7</v>
@@ -4176,24 +4179,24 @@
         <v>120</v>
       </c>
       <c r="E65" s="12">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F65" s="12">
         <v>113</v>
       </c>
       <c r="G65" s="15">
-        <v>0.6283185840707964</v>
+        <v>0.6194690265486725</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>7</v>
@@ -4205,24 +4208,24 @@
         <v>120</v>
       </c>
       <c r="E66" s="12">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F66" s="12">
         <v>113</v>
       </c>
       <c r="G66" s="15">
-        <v>0.6283185840707964</v>
+        <v>0.6194690265486725</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>7</v>
@@ -4246,12 +4249,12 @@
         <v>166</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>7</v>
@@ -4272,7 +4275,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I68" s="12" t="s">
         <v>127</v>
@@ -4280,7 +4283,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>7</v>
@@ -4301,7 +4304,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I69" s="12" t="s">
         <v>127</v>
@@ -4309,7 +4312,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>7</v>
@@ -4330,7 +4333,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I70" s="12" t="s">
         <v>127</v>
@@ -4338,7 +4341,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>7</v>
@@ -4359,7 +4362,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I71" s="12" t="s">
         <v>127</v>
@@ -4367,7 +4370,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>7</v>
@@ -4388,7 +4391,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I72" s="12" t="s">
         <v>127</v>
@@ -4396,7 +4399,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>7</v>
@@ -4417,7 +4420,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I73" s="12" t="s">
         <v>127</v>
@@ -4425,7 +4428,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>7</v>
@@ -4446,7 +4449,7 @@
         <v>0.6283185840707964</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I74" s="12" t="s">
         <v>127</v>
@@ -4454,39 +4457,39 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D75" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E75" s="12">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="F75" s="12">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="G75" s="15">
-        <v>0.9782608695652174</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H75" s="13" t="s">
         <v>167</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C76" s="13" t="s">
         <v>22</v>
@@ -4495,82 +4498,82 @@
         <v>120</v>
       </c>
       <c r="E76" s="12">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F76" s="12">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="G76" s="15">
-        <v>0.8392857142857143</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I76" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D77" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E77" s="12">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F77" s="12">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G77" s="15">
-        <v>0.52</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H77" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D78" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E78" s="12">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="F78" s="12">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G78" s="15">
-        <v>0.12</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>8</v>
@@ -4582,16 +4585,16 @@
         <v>120</v>
       </c>
       <c r="E79" s="12">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F79" s="12">
         <v>46</v>
       </c>
       <c r="G79" s="15">
-        <v>1</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I79" s="12" t="s">
         <v>116</v>
@@ -4599,7 +4602,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>8</v>
@@ -4611,16 +4614,16 @@
         <v>120</v>
       </c>
       <c r="E80" s="12">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F80" s="12">
         <v>56</v>
       </c>
       <c r="G80" s="15">
-        <v>1</v>
+        <v>0.8392857142857143</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I80" s="12" t="s">
         <v>116</v>
@@ -4628,7 +4631,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>8</v>
@@ -4640,16 +4643,16 @@
         <v>120</v>
       </c>
       <c r="E81" s="12">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F81" s="12">
         <v>25</v>
       </c>
       <c r="G81" s="15">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I81" s="12" t="s">
         <v>116</v>
@@ -4657,7 +4660,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>8</v>
@@ -4669,16 +4672,16 @@
         <v>120</v>
       </c>
       <c r="E82" s="12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F82" s="12">
         <v>25</v>
       </c>
       <c r="G82" s="15">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I82" s="12" t="s">
         <v>116</v>
@@ -4686,7 +4689,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>8</v>
@@ -4707,7 +4710,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I83" s="12" t="s">
         <v>116</v>
@@ -4715,7 +4718,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>8</v>
@@ -4736,7 +4739,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I84" s="12" t="s">
         <v>116</v>
@@ -4744,7 +4747,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>8</v>
@@ -4765,7 +4768,7 @@
         <v>0.96</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I85" s="12" t="s">
         <v>116</v>
@@ -4773,7 +4776,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>8</v>
@@ -4785,13 +4788,13 @@
         <v>120</v>
       </c>
       <c r="E86" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F86" s="12">
         <v>25</v>
       </c>
       <c r="G86" s="15">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H86" s="13" t="s">
         <v>175</v>
@@ -4802,7 +4805,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>8</v>
@@ -4823,7 +4826,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I87" s="12" t="s">
         <v>116</v>
@@ -4831,7 +4834,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>8</v>
@@ -4852,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I88" s="12" t="s">
         <v>116</v>
@@ -4860,7 +4863,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>8</v>
@@ -4881,7 +4884,7 @@
         <v>0.96</v>
       </c>
       <c r="H89" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I89" s="12" t="s">
         <v>116</v>
@@ -4889,7 +4892,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="B90" s="12" t="s">
         <v>8</v>
@@ -4901,13 +4904,13 @@
         <v>120</v>
       </c>
       <c r="E90" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F90" s="12">
         <v>25</v>
       </c>
       <c r="G90" s="15">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="H90" s="13" t="s">
         <v>176</v>
@@ -4918,7 +4921,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>8</v>
@@ -4939,15 +4942,15 @@
         <v>1</v>
       </c>
       <c r="H91" s="13" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I91" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>8</v>
@@ -4968,15 +4971,15 @@
         <v>1</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>8</v>
@@ -4997,15 +5000,15 @@
         <v>0.96</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I93" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>8</v>
@@ -5026,15 +5029,15 @@
         <v>0.4</v>
       </c>
       <c r="H94" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B95" s="12" t="s">
         <v>8</v>
@@ -5055,7 +5058,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I95" s="12" t="s">
         <v>127</v>
@@ -5063,7 +5066,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B96" s="12" t="s">
         <v>8</v>
@@ -5084,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I96" s="12" t="s">
         <v>127</v>
@@ -5092,7 +5095,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B97" s="12" t="s">
         <v>8</v>
@@ -5113,7 +5116,7 @@
         <v>0.96</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I97" s="12" t="s">
         <v>127</v>
@@ -5121,7 +5124,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B98" s="12" t="s">
         <v>8</v>
@@ -5142,7 +5145,7 @@
         <v>0.4</v>
       </c>
       <c r="H98" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I98" s="12" t="s">
         <v>127</v>
@@ -5150,7 +5153,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="B99" s="12" t="s">
         <v>8</v>
@@ -5171,7 +5174,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I99" s="12" t="s">
         <v>127</v>
@@ -5179,7 +5182,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="B100" s="12" t="s">
         <v>8</v>
@@ -5200,7 +5203,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I100" s="12" t="s">
         <v>127</v>
@@ -5208,7 +5211,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="B101" s="12" t="s">
         <v>8</v>
@@ -5229,7 +5232,7 @@
         <v>0.96</v>
       </c>
       <c r="H101" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I101" s="12" t="s">
         <v>127</v>
@@ -5237,7 +5240,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="B102" s="12" t="s">
         <v>8</v>
@@ -5258,7 +5261,7 @@
         <v>0.4</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I102" s="12" t="s">
         <v>127</v>
@@ -5287,7 +5290,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I103" s="12" t="s">
         <v>127</v>
@@ -5316,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I104" s="12" t="s">
         <v>127</v>
@@ -5345,7 +5348,7 @@
         <v>0.96</v>
       </c>
       <c r="H105" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I105" s="12" t="s">
         <v>127</v>
@@ -5374,7 +5377,7 @@
         <v>0.4</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I106" s="12" t="s">
         <v>127</v>
@@ -5382,7 +5385,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="B107" s="12" t="s">
         <v>8</v>
@@ -5403,7 +5406,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I107" s="12" t="s">
         <v>127</v>
@@ -5411,7 +5414,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>8</v>
@@ -5432,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I108" s="12" t="s">
         <v>127</v>
@@ -5440,7 +5443,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="B109" s="12" t="s">
         <v>8</v>
@@ -5461,7 +5464,7 @@
         <v>0.96</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I109" s="12" t="s">
         <v>127</v>
@@ -5469,7 +5472,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="B110" s="12" t="s">
         <v>8</v>
@@ -5490,7 +5493,7 @@
         <v>0.4</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I110" s="12" t="s">
         <v>127</v>
@@ -5498,7 +5501,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>8</v>
@@ -5519,7 +5522,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I111" s="12" t="s">
         <v>127</v>
@@ -5527,7 +5530,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B112" s="12" t="s">
         <v>8</v>
@@ -5548,7 +5551,7 @@
         <v>1</v>
       </c>
       <c r="H112" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I112" s="12" t="s">
         <v>127</v>
@@ -5556,7 +5559,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B113" s="12" t="s">
         <v>8</v>
@@ -5577,7 +5580,7 @@
         <v>0.96</v>
       </c>
       <c r="H113" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I113" s="12" t="s">
         <v>127</v>
@@ -5585,7 +5588,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B114" s="12" t="s">
         <v>8</v>
@@ -5606,7 +5609,7 @@
         <v>0.4</v>
       </c>
       <c r="H114" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I114" s="12" t="s">
         <v>127</v>
@@ -5614,7 +5617,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B115" s="12" t="s">
         <v>8</v>
@@ -5635,7 +5638,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I115" s="12" t="s">
         <v>127</v>
@@ -5643,7 +5646,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B116" s="12" t="s">
         <v>8</v>
@@ -5664,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I116" s="12" t="s">
         <v>127</v>
@@ -5672,7 +5675,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B117" s="12" t="s">
         <v>8</v>
@@ -5684,16 +5687,16 @@
         <v>120</v>
       </c>
       <c r="E117" s="12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F117" s="12">
         <v>25</v>
       </c>
       <c r="G117" s="15">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H117" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I117" s="12" t="s">
         <v>127</v>
@@ -5701,7 +5704,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B118" s="12" t="s">
         <v>8</v>
@@ -5722,7 +5725,7 @@
         <v>0.4</v>
       </c>
       <c r="H118" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I118" s="12" t="s">
         <v>127</v>
@@ -5730,7 +5733,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B119" s="12" t="s">
         <v>8</v>
@@ -5751,7 +5754,7 @@
         <v>1</v>
       </c>
       <c r="H119" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I119" s="12" t="s">
         <v>127</v>
@@ -5759,7 +5762,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B120" s="12" t="s">
         <v>8</v>
@@ -5780,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I120" s="12" t="s">
         <v>127</v>
@@ -5788,7 +5791,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B121" s="12" t="s">
         <v>8</v>
@@ -5809,7 +5812,7 @@
         <v>1</v>
       </c>
       <c r="H121" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I121" s="12" t="s">
         <v>127</v>
@@ -5817,7 +5820,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B122" s="12" t="s">
         <v>8</v>
@@ -5838,7 +5841,7 @@
         <v>0.4</v>
       </c>
       <c r="H122" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I122" s="12" t="s">
         <v>127</v>
@@ -5846,7 +5849,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B123" s="12" t="s">
         <v>8</v>
@@ -5867,7 +5870,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I123" s="12" t="s">
         <v>127</v>
@@ -5875,7 +5878,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B124" s="12" t="s">
         <v>8</v>
@@ -5896,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="H124" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I124" s="12" t="s">
         <v>127</v>
@@ -5904,7 +5907,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B125" s="12" t="s">
         <v>8</v>
@@ -5925,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I125" s="12" t="s">
         <v>127</v>
@@ -5933,7 +5936,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B126" s="12" t="s">
         <v>8</v>
@@ -5954,7 +5957,7 @@
         <v>0.4</v>
       </c>
       <c r="H126" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I126" s="12" t="s">
         <v>127</v>
@@ -5962,7 +5965,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="B127" s="12" t="s">
         <v>8</v>
@@ -5983,7 +5986,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I127" s="12" t="s">
         <v>127</v>
@@ -5991,7 +5994,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="B128" s="12" t="s">
         <v>8</v>
@@ -6012,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I128" s="12" t="s">
         <v>127</v>
@@ -6020,7 +6023,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="B129" s="12" t="s">
         <v>8</v>
@@ -6041,7 +6044,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I129" s="12" t="s">
         <v>127</v>
@@ -6049,7 +6052,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="B130" s="12" t="s">
         <v>8</v>
@@ -6070,7 +6073,7 @@
         <v>0.4</v>
       </c>
       <c r="H130" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I130" s="12" t="s">
         <v>127</v>
@@ -6078,144 +6081,144 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D131" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E131" s="12">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="F131" s="12">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="G131" s="15">
-        <v>0.8787878787878788</v>
+        <v>1</v>
       </c>
       <c r="H131" s="13" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D132" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E132" s="12">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F132" s="12">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="G132" s="15">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H132" s="13" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I132" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D133" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E133" s="12">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F133" s="12">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G133" s="15">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H133" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I133" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D134" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E134" s="12">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F134" s="12">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G134" s="15">
-        <v>0.7777777777777778</v>
+        <v>0.4</v>
       </c>
       <c r="H134" s="13" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I134" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D135" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E135" s="12">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="F135" s="12">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="G135" s="15">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H135" s="13" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I135" s="12" t="s">
         <v>127</v>
@@ -6223,28 +6226,28 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C136" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D136" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E136" s="12">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F136" s="12">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="G136" s="15">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H136" s="13" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I136" s="12" t="s">
         <v>127</v>
@@ -6252,28 +6255,28 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D137" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E137" s="12">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F137" s="12">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G137" s="15">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="H137" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I137" s="12" t="s">
         <v>127</v>
@@ -6281,28 +6284,28 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D138" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E138" s="12">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F138" s="12">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G138" s="15">
-        <v>0.7777777777777778</v>
+        <v>0.4</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I138" s="12" t="s">
         <v>127</v>
@@ -6310,7 +6313,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B139" s="12" t="s">
         <v>9</v>
@@ -6322,24 +6325,24 @@
         <v>120</v>
       </c>
       <c r="E139" s="12">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F139" s="12">
         <v>99</v>
       </c>
       <c r="G139" s="15">
-        <v>0.7777777777777778</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I139" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B140" s="12" t="s">
         <v>9</v>
@@ -6363,12 +6366,12 @@
         <v>184</v>
       </c>
       <c r="I140" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B141" s="12" t="s">
         <v>9</v>
@@ -6392,12 +6395,12 @@
         <v>184</v>
       </c>
       <c r="I141" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c r="B142" s="12" t="s">
         <v>9</v>
@@ -6421,12 +6424,12 @@
         <v>184</v>
       </c>
       <c r="I142" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B143" s="12" t="s">
         <v>9</v>
@@ -6447,7 +6450,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I143" s="12" t="s">
         <v>127</v>
@@ -6455,7 +6458,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="B144" s="12" t="s">
         <v>9</v>
@@ -6476,7 +6479,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="H144" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I144" s="12" t="s">
         <v>127</v>
@@ -6484,268 +6487,268 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E145" s="12">
+        <v>77</v>
+      </c>
+      <c r="F145" s="12">
+        <v>99</v>
+      </c>
+      <c r="G145" s="15">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="H145" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="B145" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C145" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D145" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E145" s="12">
-        <v>57</v>
-      </c>
-      <c r="F145" s="12">
-        <v>111</v>
-      </c>
-      <c r="G145" s="15">
-        <v>0.5135135135135135</v>
-      </c>
-      <c r="H145" s="13" t="s">
-        <v>186</v>
-      </c>
       <c r="I145" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E146" s="12">
+        <v>77</v>
+      </c>
+      <c r="F146" s="12">
+        <v>99</v>
+      </c>
+      <c r="G146" s="15">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="H146" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="B146" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C146" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D146" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E146" s="12">
-        <v>93</v>
-      </c>
-      <c r="F146" s="12">
-        <v>138</v>
-      </c>
-      <c r="G146" s="15">
-        <v>0.6739130434782609</v>
-      </c>
-      <c r="H146" s="13" t="s">
-        <v>187</v>
-      </c>
       <c r="I146" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B147" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E147" s="12">
+        <v>77</v>
+      </c>
+      <c r="F147" s="12">
+        <v>99</v>
+      </c>
+      <c r="G147" s="15">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="H147" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="B147" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C147" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D147" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E147" s="12">
-        <v>44</v>
-      </c>
-      <c r="F147" s="12">
-        <v>81</v>
-      </c>
-      <c r="G147" s="15">
-        <v>0.5432098765432098</v>
-      </c>
-      <c r="H147" s="13" t="s">
-        <v>188</v>
-      </c>
       <c r="I147" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D148" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E148" s="12">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F148" s="12">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G148" s="15">
-        <v>0.5585585585585585</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="12" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C149" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D149" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E149" s="12">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F149" s="12">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="G149" s="15">
-        <v>0.7101449275362319</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H149" s="13" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D150" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E150" s="12">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="F150" s="12">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G150" s="15">
-        <v>0.6419753086419753</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I150" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D151" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E151" s="12">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="F151" s="12">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G151" s="15">
-        <v>0.9099099099099099</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C152" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D152" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E152" s="12">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="F152" s="12">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="G152" s="15">
-        <v>0.9492753623188406</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H152" s="13" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="I152" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C153" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D153" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E153" s="12">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F153" s="12">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G153" s="15">
-        <v>0.9629629629629629</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H153" s="13" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I153" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="B154" s="12" t="s">
         <v>10</v>
@@ -6757,16 +6760,16 @@
         <v>120</v>
       </c>
       <c r="E154" s="12">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="F154" s="12">
         <v>111</v>
       </c>
       <c r="G154" s="15">
-        <v>0.918918918918919</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="I154" s="12" t="s">
         <v>116</v>
@@ -6774,7 +6777,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="B155" s="12" t="s">
         <v>10</v>
@@ -6786,16 +6789,16 @@
         <v>120</v>
       </c>
       <c r="E155" s="12">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="F155" s="12">
         <v>138</v>
       </c>
       <c r="G155" s="15">
-        <v>0.9492753623188406</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="H155" s="13" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I155" s="12" t="s">
         <v>116</v>
@@ -6803,7 +6806,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="B156" s="12" t="s">
         <v>10</v>
@@ -6815,16 +6818,16 @@
         <v>120</v>
       </c>
       <c r="E156" s="12">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F156" s="12">
         <v>81</v>
       </c>
       <c r="G156" s="15">
-        <v>0.9629629629629629</v>
+        <v>0.5432098765432098</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I156" s="12" t="s">
         <v>116</v>
@@ -6832,7 +6835,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B157" s="12" t="s">
         <v>10</v>
@@ -6844,16 +6847,16 @@
         <v>120</v>
       </c>
       <c r="E157" s="12">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F157" s="12">
         <v>111</v>
       </c>
       <c r="G157" s="15">
-        <v>0.918918918918919</v>
+        <v>0.5585585585585585</v>
       </c>
       <c r="H157" s="13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I157" s="12" t="s">
         <v>116</v>
@@ -6861,7 +6864,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B158" s="12" t="s">
         <v>10</v>
@@ -6873,16 +6876,16 @@
         <v>120</v>
       </c>
       <c r="E158" s="12">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="F158" s="12">
         <v>138</v>
       </c>
       <c r="G158" s="15">
-        <v>0.9492753623188406</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I158" s="12" t="s">
         <v>116</v>
@@ -6890,7 +6893,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B159" s="12" t="s">
         <v>10</v>
@@ -6902,16 +6905,16 @@
         <v>120</v>
       </c>
       <c r="E159" s="12">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="F159" s="12">
         <v>81</v>
       </c>
       <c r="G159" s="15">
-        <v>0.9629629629629629</v>
+        <v>0.6419753086419753</v>
       </c>
       <c r="H159" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I159" s="12" t="s">
         <v>116</v>
@@ -6919,7 +6922,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="B160" s="12" t="s">
         <v>10</v>
@@ -6931,16 +6934,16 @@
         <v>120</v>
       </c>
       <c r="E160" s="12">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F160" s="12">
         <v>111</v>
       </c>
       <c r="G160" s="15">
-        <v>1</v>
+        <v>0.9099099099099099</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I160" s="12" t="s">
         <v>116</v>
@@ -6948,7 +6951,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="B161" s="12" t="s">
         <v>10</v>
@@ -6960,16 +6963,16 @@
         <v>120</v>
       </c>
       <c r="E161" s="12">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F161" s="12">
         <v>138</v>
       </c>
       <c r="G161" s="15">
-        <v>0.9710144927536232</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H161" s="13" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I161" s="12" t="s">
         <v>116</v>
@@ -6977,7 +6980,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="B162" s="12" t="s">
         <v>10</v>
@@ -6989,16 +6992,16 @@
         <v>120</v>
       </c>
       <c r="E162" s="12">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F162" s="12">
         <v>81</v>
       </c>
       <c r="G162" s="15">
-        <v>0.9753086419753086</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H162" s="13" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I162" s="12" t="s">
         <v>116</v>
@@ -7006,7 +7009,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B163" s="12" t="s">
         <v>10</v>
@@ -7018,24 +7021,24 @@
         <v>120</v>
       </c>
       <c r="E163" s="12">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F163" s="12">
         <v>111</v>
       </c>
       <c r="G163" s="15">
-        <v>1</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="H163" s="13" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B164" s="12" t="s">
         <v>10</v>
@@ -7047,24 +7050,24 @@
         <v>120</v>
       </c>
       <c r="E164" s="12">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F164" s="12">
         <v>138</v>
       </c>
       <c r="G164" s="15">
-        <v>0.9710144927536232</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H164" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I164" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B165" s="12" t="s">
         <v>10</v>
@@ -7076,24 +7079,24 @@
         <v>120</v>
       </c>
       <c r="E165" s="12">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F165" s="12">
         <v>81</v>
       </c>
       <c r="G165" s="15">
-        <v>0.9753086419753086</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H165" s="13" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="I165" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B166" s="12" t="s">
         <v>10</v>
@@ -7105,24 +7108,24 @@
         <v>120</v>
       </c>
       <c r="E166" s="12">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F166" s="12">
         <v>111</v>
       </c>
       <c r="G166" s="15">
-        <v>1</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="H166" s="13" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I166" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B167" s="12" t="s">
         <v>10</v>
@@ -7134,24 +7137,24 @@
         <v>120</v>
       </c>
       <c r="E167" s="12">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F167" s="12">
         <v>138</v>
       </c>
       <c r="G167" s="15">
-        <v>0.9710144927536232</v>
+        <v>0.9492753623188406</v>
       </c>
       <c r="H167" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B168" s="12" t="s">
         <v>10</v>
@@ -7163,24 +7166,24 @@
         <v>120</v>
       </c>
       <c r="E168" s="12">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F168" s="12">
         <v>81</v>
       </c>
       <c r="G168" s="15">
-        <v>0.9753086419753086</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="I168" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B169" s="12" t="s">
         <v>10</v>
@@ -7201,15 +7204,15 @@
         <v>1</v>
       </c>
       <c r="H169" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I169" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B170" s="12" t="s">
         <v>10</v>
@@ -7230,15 +7233,15 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H170" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I170" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B171" s="12" t="s">
         <v>10</v>
@@ -7259,15 +7262,15 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H171" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I171" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B172" s="12" t="s">
         <v>10</v>
@@ -7288,7 +7291,7 @@
         <v>1</v>
       </c>
       <c r="H172" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I172" s="12" t="s">
         <v>127</v>
@@ -7296,7 +7299,7 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B173" s="12" t="s">
         <v>10</v>
@@ -7317,7 +7320,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H173" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I173" s="12" t="s">
         <v>127</v>
@@ -7325,7 +7328,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B174" s="12" t="s">
         <v>10</v>
@@ -7346,7 +7349,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H174" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I174" s="12" t="s">
         <v>127</v>
@@ -7354,7 +7357,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B175" s="12" t="s">
         <v>10</v>
@@ -7375,7 +7378,7 @@
         <v>1</v>
       </c>
       <c r="H175" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I175" s="12" t="s">
         <v>127</v>
@@ -7383,7 +7386,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B176" s="12" t="s">
         <v>10</v>
@@ -7404,7 +7407,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H176" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I176" s="12" t="s">
         <v>127</v>
@@ -7412,7 +7415,7 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B177" s="12" t="s">
         <v>10</v>
@@ -7433,7 +7436,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H177" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I177" s="12" t="s">
         <v>127</v>
@@ -7441,7 +7444,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B178" s="12" t="s">
         <v>10</v>
@@ -7462,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I178" s="12" t="s">
         <v>127</v>
@@ -7470,7 +7473,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B179" s="12" t="s">
         <v>10</v>
@@ -7491,7 +7494,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H179" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I179" s="12" t="s">
         <v>127</v>
@@ -7499,7 +7502,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B180" s="12" t="s">
         <v>10</v>
@@ -7520,7 +7523,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H180" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I180" s="12" t="s">
         <v>127</v>
@@ -7528,7 +7531,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="12" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="B181" s="12" t="s">
         <v>10</v>
@@ -7549,7 +7552,7 @@
         <v>1</v>
       </c>
       <c r="H181" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I181" s="12" t="s">
         <v>127</v>
@@ -7557,7 +7560,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="B182" s="12" t="s">
         <v>10</v>
@@ -7578,7 +7581,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H182" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I182" s="12" t="s">
         <v>127</v>
@@ -7586,7 +7589,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="12" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="B183" s="12" t="s">
         <v>10</v>
@@ -7607,7 +7610,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H183" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I183" s="12" t="s">
         <v>127</v>
@@ -7615,7 +7618,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B184" s="12" t="s">
         <v>10</v>
@@ -7636,7 +7639,7 @@
         <v>1</v>
       </c>
       <c r="H184" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I184" s="12" t="s">
         <v>127</v>
@@ -7644,7 +7647,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B185" s="12" t="s">
         <v>10</v>
@@ -7665,7 +7668,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H185" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I185" s="12" t="s">
         <v>127</v>
@@ -7673,7 +7676,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B186" s="12" t="s">
         <v>10</v>
@@ -7694,7 +7697,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H186" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I186" s="12" t="s">
         <v>127</v>
@@ -7702,7 +7705,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B187" s="12" t="s">
         <v>10</v>
@@ -7723,7 +7726,7 @@
         <v>1</v>
       </c>
       <c r="H187" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I187" s="12" t="s">
         <v>127</v>
@@ -7731,7 +7734,7 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>10</v>
@@ -7752,7 +7755,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H188" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I188" s="12" t="s">
         <v>127</v>
@@ -7760,7 +7763,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>10</v>
@@ -7781,7 +7784,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H189" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I189" s="12" t="s">
         <v>127</v>
@@ -7789,7 +7792,7 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>10</v>
@@ -7810,7 +7813,7 @@
         <v>1</v>
       </c>
       <c r="H190" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I190" s="12" t="s">
         <v>127</v>
@@ -7818,7 +7821,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="12" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>10</v>
@@ -7839,7 +7842,7 @@
         <v>0.9710144927536232</v>
       </c>
       <c r="H191" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I191" s="12" t="s">
         <v>127</v>
@@ -7847,7 +7850,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="12" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>10</v>
@@ -7868,7 +7871,7 @@
         <v>0.9753086419753086</v>
       </c>
       <c r="H192" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I192" s="12" t="s">
         <v>127</v>
@@ -7876,376 +7879,376 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="12" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B193" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C193" s="13" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="D193" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E193" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="F193" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="G193" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
+      </c>
+      <c r="E193" s="12">
+        <v>111</v>
+      </c>
+      <c r="F193" s="12">
+        <v>111</v>
+      </c>
+      <c r="G193" s="15">
+        <v>1</v>
       </c>
       <c r="H193" s="13" t="s">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C194" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D194" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E194" s="12">
-        <v>3</v>
+        <v>134</v>
       </c>
       <c r="F194" s="12">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G194" s="15">
-        <v>0.11538461538461539</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H194" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="12" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B195" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C195" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D195" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E195" s="12">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F195" s="12">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G195" s="15">
-        <v>0.6111111111111112</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H195" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="12" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C196" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D196" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E196" s="12">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="F196" s="12">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G196" s="15">
-        <v>0.16346153846153846</v>
+        <v>1</v>
       </c>
       <c r="H196" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="12" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B197" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C197" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D197" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E197" s="12">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="F197" s="12">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G197" s="15">
-        <v>0.6538461538461539</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H197" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C198" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D198" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E198" s="12">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="F198" s="12">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G198" s="15">
-        <v>0.8809523809523809</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H198" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="12" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B199" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C199" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D199" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E199" s="12">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="F199" s="12">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G199" s="15">
-        <v>0.6826923076923077</v>
+        <v>1</v>
       </c>
       <c r="H199" s="13" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C200" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D200" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E200" s="12">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="F200" s="12">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G200" s="15">
-        <v>0.6538461538461539</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H200" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="12" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B201" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C201" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D201" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E201" s="12">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="F201" s="12">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G201" s="15">
-        <v>0.9206349206349206</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H201" s="13" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="12" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="B202" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C202" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D202" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E202" s="12">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="F202" s="12">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G202" s="15">
-        <v>0.8557692307692307</v>
+        <v>1</v>
       </c>
       <c r="H202" s="13" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B203" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C203" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D203" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E203" s="12">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="F203" s="12">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="G203" s="15">
-        <v>0.8846153846153846</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="H203" s="13" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B204" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D204" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E204" s="12">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="F204" s="12">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G204" s="15">
-        <v>0.9841269841269841</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="H204" s="13" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="12" t="s">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="B205" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="D205" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E205" s="12">
-        <v>98</v>
-      </c>
-      <c r="F205" s="12">
-        <v>104</v>
-      </c>
-      <c r="G205" s="15">
-        <v>0.9423076923076923</v>
+        <v>74</v>
+      </c>
+      <c r="E205" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F205" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G205" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="H205" s="13" t="s">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="I205" s="12" t="s">
         <v>116</v>
@@ -8253,7 +8256,7 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="12" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="B206" s="12" t="s">
         <v>11</v>
@@ -8265,24 +8268,24 @@
         <v>120</v>
       </c>
       <c r="E206" s="12">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F206" s="12">
         <v>26</v>
       </c>
       <c r="G206" s="15">
-        <v>0.8846153846153846</v>
+        <v>0.11538461538461539</v>
       </c>
       <c r="H206" s="13" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="12" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>11</v>
@@ -8294,24 +8297,24 @@
         <v>120</v>
       </c>
       <c r="E207" s="12">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="F207" s="12">
         <v>126</v>
       </c>
       <c r="G207" s="15">
-        <v>0.9841269841269841</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="H207" s="13" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>11</v>
@@ -8323,24 +8326,24 @@
         <v>120</v>
       </c>
       <c r="E208" s="12">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="F208" s="12">
         <v>104</v>
       </c>
       <c r="G208" s="15">
-        <v>0.9423076923076923</v>
+        <v>0.16346153846153846</v>
       </c>
       <c r="H208" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="12" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>11</v>
@@ -8352,24 +8355,24 @@
         <v>120</v>
       </c>
       <c r="E209" s="12">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F209" s="12">
         <v>26</v>
       </c>
       <c r="G209" s="15">
-        <v>0.8846153846153846</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="H209" s="13" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>11</v>
@@ -8381,24 +8384,24 @@
         <v>120</v>
       </c>
       <c r="E210" s="12">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="F210" s="12">
         <v>126</v>
       </c>
       <c r="G210" s="15">
-        <v>0.9841269841269841</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="H210" s="13" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="12" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>11</v>
@@ -8410,24 +8413,24 @@
         <v>120</v>
       </c>
       <c r="E211" s="12">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="F211" s="12">
         <v>104</v>
       </c>
       <c r="G211" s="15">
-        <v>0.9423076923076923</v>
+        <v>0.6826923076923077</v>
       </c>
       <c r="H211" s="13" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="I211" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="B212" s="12" t="s">
         <v>11</v>
@@ -8439,24 +8442,24 @@
         <v>120</v>
       </c>
       <c r="E212" s="12">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F212" s="12">
         <v>26</v>
       </c>
       <c r="G212" s="15">
-        <v>0.8846153846153846</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="H212" s="13" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="12" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="B213" s="12" t="s">
         <v>11</v>
@@ -8468,24 +8471,24 @@
         <v>120</v>
       </c>
       <c r="E213" s="12">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F213" s="12">
         <v>126</v>
       </c>
       <c r="G213" s="15">
-        <v>0.9841269841269841</v>
+        <v>0.9206349206349206</v>
       </c>
       <c r="H213" s="13" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I213" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="B214" s="12" t="s">
         <v>11</v>
@@ -8497,24 +8500,24 @@
         <v>120</v>
       </c>
       <c r="E214" s="12">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F214" s="12">
         <v>104</v>
       </c>
       <c r="G214" s="15">
-        <v>0.9423076923076923</v>
+        <v>0.8557692307692307</v>
       </c>
       <c r="H214" s="13" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I214" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="12" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="B215" s="12" t="s">
         <v>11</v>
@@ -8535,15 +8538,15 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H215" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I215" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="B216" s="12" t="s">
         <v>11</v>
@@ -8564,15 +8567,15 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H216" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I216" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="12" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="B217" s="12" t="s">
         <v>11</v>
@@ -8593,15 +8596,15 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H217" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I217" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B218" s="12" t="s">
         <v>11</v>
@@ -8622,7 +8625,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H218" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I218" s="12" t="s">
         <v>127</v>
@@ -8630,7 +8633,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B219" s="12" t="s">
         <v>11</v>
@@ -8651,7 +8654,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H219" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I219" s="12" t="s">
         <v>127</v>
@@ -8659,7 +8662,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B220" s="12" t="s">
         <v>11</v>
@@ -8680,7 +8683,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H220" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I220" s="12" t="s">
         <v>127</v>
@@ -8688,7 +8691,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B221" s="12" t="s">
         <v>11</v>
@@ -8709,7 +8712,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H221" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I221" s="12" t="s">
         <v>127</v>
@@ -8717,7 +8720,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B222" s="12" t="s">
         <v>11</v>
@@ -8738,7 +8741,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H222" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I222" s="12" t="s">
         <v>127</v>
@@ -8746,7 +8749,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B223" s="12" t="s">
         <v>11</v>
@@ -8767,7 +8770,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H223" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I223" s="12" t="s">
         <v>127</v>
@@ -8775,7 +8778,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B224" s="12" t="s">
         <v>11</v>
@@ -8796,7 +8799,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H224" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I224" s="12" t="s">
         <v>127</v>
@@ -8804,7 +8807,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B225" s="12" t="s">
         <v>11</v>
@@ -8825,7 +8828,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H225" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I225" s="12" t="s">
         <v>127</v>
@@ -8833,7 +8836,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B226" s="12" t="s">
         <v>11</v>
@@ -8854,7 +8857,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H226" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I226" s="12" t="s">
         <v>127</v>
@@ -8862,7 +8865,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="12" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="B227" s="12" t="s">
         <v>11</v>
@@ -8883,7 +8886,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H227" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I227" s="12" t="s">
         <v>127</v>
@@ -8891,7 +8894,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="B228" s="12" t="s">
         <v>11</v>
@@ -8912,7 +8915,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H228" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I228" s="12" t="s">
         <v>127</v>
@@ -8920,7 +8923,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="12" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="B229" s="12" t="s">
         <v>11</v>
@@ -8941,7 +8944,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H229" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I229" s="12" t="s">
         <v>127</v>
@@ -8949,7 +8952,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B230" s="12" t="s">
         <v>11</v>
@@ -8970,7 +8973,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H230" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I230" s="12" t="s">
         <v>127</v>
@@ -8978,7 +8981,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B231" s="12" t="s">
         <v>11</v>
@@ -8999,7 +9002,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H231" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I231" s="12" t="s">
         <v>127</v>
@@ -9007,7 +9010,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B232" s="12" t="s">
         <v>11</v>
@@ -9028,7 +9031,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H232" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I232" s="12" t="s">
         <v>127</v>
@@ -9036,7 +9039,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="12" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="B233" s="12" t="s">
         <v>11</v>
@@ -9057,7 +9060,7 @@
         <v>0.8846153846153846</v>
       </c>
       <c r="H233" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I233" s="12" t="s">
         <v>127</v>
@@ -9065,7 +9068,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="12" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="B234" s="12" t="s">
         <v>11</v>
@@ -9086,7 +9089,7 @@
         <v>0.9841269841269841</v>
       </c>
       <c r="H234" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I234" s="12" t="s">
         <v>127</v>
@@ -9094,7 +9097,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="12" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="B235" s="12" t="s">
         <v>11</v>
@@ -9115,7 +9118,7 @@
         <v>0.9423076923076923</v>
       </c>
       <c r="H235" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I235" s="12" t="s">
         <v>127</v>
@@ -9123,10 +9126,10 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B236" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C236" s="13" t="s">
         <v>20</v>
@@ -9135,27 +9138,27 @@
         <v>120</v>
       </c>
       <c r="E236" s="12">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F236" s="12">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G236" s="15">
-        <v>0.36363636363636365</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H236" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I236" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="12" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B237" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C237" s="13" t="s">
         <v>23</v>
@@ -9164,27 +9167,27 @@
         <v>120</v>
       </c>
       <c r="E237" s="12">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="F237" s="12">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G237" s="15">
-        <v>0.4588235294117647</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H237" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I237" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B238" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C238" s="13" t="s">
         <v>22</v>
@@ -9193,27 +9196,27 @@
         <v>120</v>
       </c>
       <c r="E238" s="12">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="F238" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G238" s="15">
-        <v>0.10784313725490197</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H238" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I238" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="12" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="B239" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C239" s="13" t="s">
         <v>20</v>
@@ -9222,27 +9225,27 @@
         <v>120</v>
       </c>
       <c r="E239" s="12">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F239" s="12">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G239" s="15">
-        <v>0.6590909090909091</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H239" s="13" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I239" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="12" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="B240" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C240" s="13" t="s">
         <v>23</v>
@@ -9251,27 +9254,27 @@
         <v>120</v>
       </c>
       <c r="E240" s="12">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F240" s="12">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G240" s="15">
-        <v>0.7411764705882353</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H240" s="13" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="I240" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="12" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="B241" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C241" s="13" t="s">
         <v>22</v>
@@ -9280,27 +9283,27 @@
         <v>120</v>
       </c>
       <c r="E241" s="12">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="F241" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G241" s="15">
-        <v>0.21568627450980393</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H241" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I241" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="12" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B242" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C242" s="13" t="s">
         <v>20</v>
@@ -9309,16 +9312,16 @@
         <v>120</v>
       </c>
       <c r="E242" s="12">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F242" s="12">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G242" s="15">
-        <v>0.6590909090909091</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H242" s="13" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I242" s="12" t="s">
         <v>127</v>
@@ -9326,10 +9329,10 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="12" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B243" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C243" s="13" t="s">
         <v>23</v>
@@ -9338,16 +9341,16 @@
         <v>120</v>
       </c>
       <c r="E243" s="12">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F243" s="12">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G243" s="15">
-        <v>0.7411764705882353</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H243" s="13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I243" s="12" t="s">
         <v>127</v>
@@ -9355,10 +9358,10 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="12" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B244" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C244" s="13" t="s">
         <v>22</v>
@@ -9367,16 +9370,16 @@
         <v>120</v>
       </c>
       <c r="E244" s="12">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="F244" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G244" s="15">
-        <v>0.22549019607843138</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H244" s="13" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="I244" s="12" t="s">
         <v>127</v>
@@ -9384,10 +9387,10 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="12" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B245" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C245" s="13" t="s">
         <v>20</v>
@@ -9396,16 +9399,16 @@
         <v>120</v>
       </c>
       <c r="E245" s="12">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F245" s="12">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G245" s="15">
-        <v>0.6590909090909091</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H245" s="13" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I245" s="12" t="s">
         <v>127</v>
@@ -9413,10 +9416,10 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="12" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B246" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C246" s="13" t="s">
         <v>23</v>
@@ -9425,16 +9428,16 @@
         <v>120</v>
       </c>
       <c r="E246" s="12">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F246" s="12">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G246" s="15">
-        <v>0.7411764705882353</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H246" s="13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I246" s="12" t="s">
         <v>127</v>
@@ -9442,10 +9445,10 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="12" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B247" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C247" s="13" t="s">
         <v>22</v>
@@ -9454,16 +9457,16 @@
         <v>120</v>
       </c>
       <c r="E247" s="12">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="F247" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G247" s="15">
-        <v>0.22549019607843138</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H247" s="13" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="I247" s="12" t="s">
         <v>127</v>
@@ -9471,10 +9474,10 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="12" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="B248" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C248" s="13" t="s">
         <v>20</v>
@@ -9483,16 +9486,16 @@
         <v>120</v>
       </c>
       <c r="E248" s="12">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F248" s="12">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G248" s="15">
-        <v>0.6590909090909091</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="H248" s="13" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I248" s="12" t="s">
         <v>127</v>
@@ -9500,10 +9503,10 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="12" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="B249" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C249" s="13" t="s">
         <v>23</v>
@@ -9512,16 +9515,16 @@
         <v>120</v>
       </c>
       <c r="E249" s="12">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="F249" s="12">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G249" s="15">
-        <v>0.7647058823529411</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="H249" s="13" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="I249" s="12" t="s">
         <v>127</v>
@@ -9529,10 +9532,10 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="12" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="B250" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C250" s="13" t="s">
         <v>22</v>
@@ -9541,16 +9544,16 @@
         <v>120</v>
       </c>
       <c r="E250" s="12">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="F250" s="12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G250" s="15">
-        <v>0.23529411764705882</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="H250" s="13" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="I250" s="12" t="s">
         <v>127</v>
@@ -9558,7 +9561,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="12" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B251" s="12" t="s">
         <v>12</v>
@@ -9570,24 +9573,24 @@
         <v>120</v>
       </c>
       <c r="E251" s="12">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F251" s="12">
         <v>44</v>
       </c>
       <c r="G251" s="15">
-        <v>0.6590909090909091</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="H251" s="13" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I251" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="12" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B252" s="12" t="s">
         <v>12</v>
@@ -9599,24 +9602,24 @@
         <v>120</v>
       </c>
       <c r="E252" s="12">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F252" s="12">
         <v>85</v>
       </c>
       <c r="G252" s="15">
-        <v>0.7647058823529411</v>
+        <v>0.4588235294117647</v>
       </c>
       <c r="H252" s="13" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="I252" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="12" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B253" s="12" t="s">
         <v>12</v>
@@ -9628,24 +9631,24 @@
         <v>120</v>
       </c>
       <c r="E253" s="12">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F253" s="12">
         <v>102</v>
       </c>
       <c r="G253" s="15">
-        <v>0.23529411764705882</v>
+        <v>0.10784313725490197</v>
       </c>
       <c r="H253" s="13" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="I253" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="12" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="B254" s="12" t="s">
         <v>12</v>
@@ -9666,15 +9669,15 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H254" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I254" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="12" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="B255" s="12" t="s">
         <v>12</v>
@@ -9686,24 +9689,24 @@
         <v>120</v>
       </c>
       <c r="E255" s="12">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F255" s="12">
         <v>85</v>
       </c>
       <c r="G255" s="15">
-        <v>0.7647058823529411</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="H255" s="13" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I255" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="12" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="B256" s="12" t="s">
         <v>12</v>
@@ -9715,24 +9718,24 @@
         <v>120</v>
       </c>
       <c r="E256" s="12">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F256" s="12">
         <v>102</v>
       </c>
       <c r="G256" s="15">
-        <v>0.23529411764705882</v>
+        <v>0.21568627450980393</v>
       </c>
       <c r="H256" s="13" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I256" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B257" s="12" t="s">
         <v>12</v>
@@ -9753,7 +9756,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H257" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I257" s="12" t="s">
         <v>127</v>
@@ -9761,7 +9764,7 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B258" s="12" t="s">
         <v>12</v>
@@ -9773,16 +9776,16 @@
         <v>120</v>
       </c>
       <c r="E258" s="12">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F258" s="12">
         <v>85</v>
       </c>
       <c r="G258" s="15">
-        <v>0.7647058823529411</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="H258" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I258" s="12" t="s">
         <v>127</v>
@@ -9790,7 +9793,7 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B259" s="12" t="s">
         <v>12</v>
@@ -9802,16 +9805,16 @@
         <v>120</v>
       </c>
       <c r="E259" s="12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F259" s="12">
         <v>102</v>
       </c>
       <c r="G259" s="15">
-        <v>0.23529411764705882</v>
+        <v>0.22549019607843138</v>
       </c>
       <c r="H259" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I259" s="12" t="s">
         <v>127</v>
@@ -9819,7 +9822,7 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B260" s="12" t="s">
         <v>12</v>
@@ -9840,7 +9843,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H260" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I260" s="12" t="s">
         <v>127</v>
@@ -9848,7 +9851,7 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B261" s="12" t="s">
         <v>12</v>
@@ -9860,16 +9863,16 @@
         <v>120</v>
       </c>
       <c r="E261" s="12">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F261" s="12">
         <v>85</v>
       </c>
       <c r="G261" s="15">
-        <v>0.7647058823529411</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="H261" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I261" s="12" t="s">
         <v>127</v>
@@ -9877,7 +9880,7 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B262" s="12" t="s">
         <v>12</v>
@@ -9889,16 +9892,16 @@
         <v>120</v>
       </c>
       <c r="E262" s="12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F262" s="12">
         <v>102</v>
       </c>
       <c r="G262" s="15">
-        <v>0.24509803921568626</v>
+        <v>0.22549019607843138</v>
       </c>
       <c r="H262" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I262" s="12" t="s">
         <v>127</v>
@@ -9906,7 +9909,7 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B263" s="12" t="s">
         <v>12</v>
@@ -9927,7 +9930,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H263" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I263" s="12" t="s">
         <v>127</v>
@@ -9935,7 +9938,7 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B264" s="12" t="s">
         <v>12</v>
@@ -9947,16 +9950,16 @@
         <v>120</v>
       </c>
       <c r="E264" s="12">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F264" s="12">
         <v>85</v>
       </c>
       <c r="G264" s="15">
-        <v>0.7764705882352941</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="H264" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I264" s="12" t="s">
         <v>127</v>
@@ -9964,7 +9967,7 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B265" s="12" t="s">
         <v>12</v>
@@ -9976,13 +9979,13 @@
         <v>120</v>
       </c>
       <c r="E265" s="12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F265" s="12">
         <v>102</v>
       </c>
       <c r="G265" s="15">
-        <v>0.24509803921568626</v>
+        <v>0.23529411764705882</v>
       </c>
       <c r="H265" s="13" t="s">
         <v>227</v>
@@ -9993,7 +9996,7 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="B266" s="12" t="s">
         <v>12</v>
@@ -10014,7 +10017,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H266" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I266" s="12" t="s">
         <v>127</v>
@@ -10022,7 +10025,7 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="12" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="B267" s="12" t="s">
         <v>12</v>
@@ -10034,16 +10037,16 @@
         <v>120</v>
       </c>
       <c r="E267" s="12">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F267" s="12">
         <v>85</v>
       </c>
       <c r="G267" s="15">
-        <v>0.7764705882352941</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="H267" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I267" s="12" t="s">
         <v>127</v>
@@ -10051,7 +10054,7 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="B268" s="12" t="s">
         <v>12</v>
@@ -10063,13 +10066,13 @@
         <v>120</v>
       </c>
       <c r="E268" s="12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F268" s="12">
         <v>102</v>
       </c>
       <c r="G268" s="15">
-        <v>0.24509803921568626</v>
+        <v>0.23529411764705882</v>
       </c>
       <c r="H268" s="13" t="s">
         <v>227</v>
@@ -10080,7 +10083,7 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="12" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="B269" s="12" t="s">
         <v>12</v>
@@ -10101,7 +10104,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="H269" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I269" s="12" t="s">
         <v>127</v>
@@ -10109,7 +10112,7 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="12" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="B270" s="12" t="s">
         <v>12</v>
@@ -10121,16 +10124,16 @@
         <v>120</v>
       </c>
       <c r="E270" s="12">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F270" s="12">
         <v>85</v>
       </c>
       <c r="G270" s="15">
-        <v>0.788235294117647</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="H270" s="13" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I270" s="12" t="s">
         <v>127</v>
@@ -10138,7 +10141,7 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="12" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="B271" s="12" t="s">
         <v>12</v>
@@ -10150,16 +10153,16 @@
         <v>120</v>
       </c>
       <c r="E271" s="12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F271" s="12">
         <v>102</v>
       </c>
       <c r="G271" s="15">
-        <v>0.2549019607843137</v>
+        <v>0.23529411764705882</v>
       </c>
       <c r="H271" s="13" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I271" s="12" t="s">
         <v>127</v>
@@ -10167,155 +10170,155 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B272" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C272" s="13" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="D272" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E272" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="F272" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="G272" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
+      </c>
+      <c r="E272" s="12">
+        <v>29</v>
+      </c>
+      <c r="F272" s="12">
+        <v>44</v>
+      </c>
+      <c r="G272" s="15">
+        <v>0.6590909090909091</v>
       </c>
       <c r="H272" s="13" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I272" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="12" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="B273" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C273" s="13" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="D273" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E273" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="F273" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="G273" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
+      </c>
+      <c r="E273" s="12">
+        <v>65</v>
+      </c>
+      <c r="F273" s="12">
+        <v>85</v>
+      </c>
+      <c r="G273" s="15">
+        <v>0.7647058823529411</v>
       </c>
       <c r="H273" s="13" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I273" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B274" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C274" s="13" t="s">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="D274" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E274" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="F274" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="G274" s="12" t="s">
-        <v>114</v>
+        <v>120</v>
+      </c>
+      <c r="E274" s="12">
+        <v>24</v>
+      </c>
+      <c r="F274" s="12">
+        <v>102</v>
+      </c>
+      <c r="G274" s="15">
+        <v>0.23529411764705882</v>
       </c>
       <c r="H274" s="13" t="s">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="I274" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="12" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B275" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C275" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D275" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E275" s="12">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F275" s="12">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G275" s="15">
-        <v>0.17647058823529413</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H275" s="13" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="I275" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="12" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B276" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C276" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D276" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E276" s="12">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F276" s="12">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="G276" s="15">
-        <v>0.22058823529411764</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="H276" s="13" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="I276" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="12" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="B277" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C277" s="13" t="s">
         <v>22</v>
@@ -10324,45 +10327,45 @@
         <v>120</v>
       </c>
       <c r="E277" s="12">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F277" s="12">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="G277" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.24509803921568626</v>
       </c>
       <c r="H277" s="13" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="I277" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B278" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C278" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D278" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E278" s="12">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F278" s="12">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G278" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H278" s="13" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="I278" s="12" t="s">
         <v>127</v>
@@ -10370,28 +10373,28 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B279" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C279" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D279" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E279" s="12">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F279" s="12">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="G279" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="H279" s="13" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="I279" s="12" t="s">
         <v>127</v>
@@ -10399,10 +10402,10 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="12" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="B280" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C280" s="13" t="s">
         <v>22</v>
@@ -10411,16 +10414,16 @@
         <v>120</v>
       </c>
       <c r="E280" s="12">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F280" s="12">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="G280" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.24509803921568626</v>
       </c>
       <c r="H280" s="13" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I280" s="12" t="s">
         <v>127</v>
@@ -10428,28 +10431,28 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B281" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C281" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D281" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E281" s="12">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F281" s="12">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G281" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H281" s="13" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="I281" s="12" t="s">
         <v>127</v>
@@ -10457,28 +10460,28 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B282" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C282" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D282" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E282" s="12">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F282" s="12">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="G282" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="H282" s="13" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="I282" s="12" t="s">
         <v>127</v>
@@ -10486,10 +10489,10 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B283" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C283" s="13" t="s">
         <v>22</v>
@@ -10498,16 +10501,16 @@
         <v>120</v>
       </c>
       <c r="E283" s="12">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F283" s="12">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="G283" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.24509803921568626</v>
       </c>
       <c r="H283" s="13" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I283" s="12" t="s">
         <v>127</v>
@@ -10515,28 +10518,28 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B284" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C284" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D284" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E284" s="12">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F284" s="12">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G284" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H284" s="13" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="I284" s="12" t="s">
         <v>127</v>
@@ -10544,28 +10547,28 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B285" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C285" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D285" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E285" s="12">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="F285" s="12">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="G285" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.788235294117647</v>
       </c>
       <c r="H285" s="13" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I285" s="12" t="s">
         <v>127</v>
@@ -10573,10 +10576,10 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B286" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C286" s="13" t="s">
         <v>22</v>
@@ -10585,16 +10588,16 @@
         <v>120</v>
       </c>
       <c r="E286" s="12">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F286" s="12">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="G286" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.2549019607843137</v>
       </c>
       <c r="H286" s="13" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I286" s="12" t="s">
         <v>127</v>
@@ -10605,25 +10608,25 @@
         <v>32</v>
       </c>
       <c r="B287" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C287" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D287" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E287" s="12">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F287" s="12">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G287" s="15">
-        <v>0.33088235294117646</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="H287" s="13" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="I287" s="12" t="s">
         <v>127</v>
@@ -10631,86 +10634,86 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
-        <v>185</v>
+        <v>32</v>
       </c>
       <c r="B288" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C288" s="13" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D288" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E288" s="12">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F288" s="12">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="G288" s="15">
-        <v>0.42857142857142855</v>
+        <v>0.788235294117647</v>
       </c>
       <c r="H288" s="13" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="I288" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="12" t="s">
-        <v>185</v>
+        <v>32</v>
       </c>
       <c r="B289" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C289" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D289" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E289" s="12">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="F289" s="12">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="G289" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.2549019607843137</v>
       </c>
       <c r="H289" s="13" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="I289" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B290" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C290" s="13" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="D290" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E290" s="12">
-        <v>84</v>
-      </c>
-      <c r="F290" s="12">
-        <v>189</v>
-      </c>
-      <c r="G290" s="15">
-        <v>0.4444444444444444</v>
+        <v>74</v>
+      </c>
+      <c r="E290" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F290" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G290" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="H290" s="13" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I290" s="12" t="s">
         <v>116</v>
@@ -10718,28 +10721,28 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="12" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="B291" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C291" s="13" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="D291" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E291" s="12">
-        <v>0</v>
-      </c>
-      <c r="F291" s="12">
-        <v>27</v>
-      </c>
-      <c r="G291" s="15">
-        <v>0</v>
+        <v>74</v>
+      </c>
+      <c r="E291" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F291" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G291" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="H291" s="13" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="I291" s="12" t="s">
         <v>116</v>
@@ -10747,28 +10750,28 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="12" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="B292" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C292" s="13" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="D292" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E292" s="12">
-        <v>124</v>
-      </c>
-      <c r="F292" s="12">
-        <v>189</v>
-      </c>
-      <c r="G292" s="15">
-        <v>0.656084656084656</v>
+        <v>74</v>
+      </c>
+      <c r="E292" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F292" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G292" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="H292" s="13" t="s">
-        <v>240</v>
+        <v>74</v>
       </c>
       <c r="I292" s="12" t="s">
         <v>116</v>
@@ -10776,28 +10779,28 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="12" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="B293" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C293" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D293" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E293" s="12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F293" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G293" s="15">
-        <v>0</v>
+        <v>0.17647058823529413</v>
       </c>
       <c r="H293" s="13" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="I293" s="12" t="s">
         <v>116</v>
@@ -10805,28 +10808,28 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B294" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C294" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D294" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E294" s="12">
         <v>30</v>
       </c>
-      <c r="D294" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E294" s="12">
-        <v>148</v>
-      </c>
       <c r="F294" s="12">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="G294" s="15">
-        <v>0.783068783068783</v>
+        <v>0.22058823529411764</v>
       </c>
       <c r="H294" s="13" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="I294" s="12" t="s">
         <v>116</v>
@@ -10834,28 +10837,28 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="12" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="B295" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C295" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D295" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E295" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F295" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G295" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H295" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I295" s="12" t="s">
         <v>116</v>
@@ -10863,144 +10866,144 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B296" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C296" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D296" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E296" s="12">
-        <v>154</v>
+        <v>45</v>
       </c>
       <c r="F296" s="12">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="G296" s="15">
-        <v>0.8148148148148148</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H296" s="13" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I296" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="12" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B297" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C297" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D297" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E297" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F297" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G297" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H297" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I297" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="12" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="B298" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C298" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D298" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E298" s="12">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="F298" s="12">
-        <v>308</v>
+        <v>136</v>
       </c>
       <c r="G298" s="15">
-        <v>0.5194805194805194</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H298" s="13" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I298" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="12" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="B299" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C299" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D299" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E299" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F299" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G299" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H299" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I299" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B300" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C300" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D300" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E300" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F300" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G300" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H300" s="13" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I300" s="12" t="s">
         <v>127</v>
@@ -11008,28 +11011,28 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="12" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B301" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C301" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D301" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E301" s="12">
-        <v>161</v>
+        <v>45</v>
       </c>
       <c r="F301" s="12">
-        <v>308</v>
+        <v>136</v>
       </c>
       <c r="G301" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H301" s="13" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="I301" s="12" t="s">
         <v>127</v>
@@ -11037,28 +11040,28 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B302" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C302" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D302" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E302" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F302" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G302" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H302" s="13" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I302" s="12" t="s">
         <v>127</v>
@@ -11066,28 +11069,28 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B303" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C303" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D303" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E303" s="12">
-        <v>161</v>
+        <v>45</v>
       </c>
       <c r="F303" s="12">
-        <v>308</v>
+        <v>136</v>
       </c>
       <c r="G303" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H303" s="13" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="I303" s="12" t="s">
         <v>127</v>
@@ -11095,28 +11098,28 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="12" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="B304" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C304" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D304" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E304" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F304" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G304" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H304" s="13" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I304" s="12" t="s">
         <v>127</v>
@@ -11124,28 +11127,28 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="12" t="s">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="B305" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C305" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D305" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E305" s="12">
-        <v>161</v>
+        <v>45</v>
       </c>
       <c r="F305" s="12">
-        <v>308</v>
+        <v>136</v>
       </c>
       <c r="G305" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H305" s="13" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="I305" s="12" t="s">
         <v>127</v>
@@ -11153,28 +11156,28 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="12" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="B306" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C306" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D306" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E306" s="12">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F306" s="12">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G306" s="15">
-        <v>0.037037037037037035</v>
+        <v>0.33088235294117646</v>
       </c>
       <c r="H306" s="13" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I306" s="12" t="s">
         <v>127</v>
@@ -11182,7 +11185,7 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="12" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="B307" s="12" t="s">
         <v>15</v>
@@ -11194,24 +11197,24 @@
         <v>120</v>
       </c>
       <c r="E307" s="12">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="F307" s="12">
-        <v>308</v>
+        <v>189</v>
       </c>
       <c r="G307" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="H307" s="13" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I307" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="12" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="B308" s="12" t="s">
         <v>15</v>
@@ -11232,15 +11235,15 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H308" s="13" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I308" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="12" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B309" s="12" t="s">
         <v>15</v>
@@ -11252,24 +11255,24 @@
         <v>120</v>
       </c>
       <c r="E309" s="12">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="F309" s="12">
-        <v>308</v>
+        <v>189</v>
       </c>
       <c r="G309" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="H309" s="13" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="I309" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="12" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B310" s="12" t="s">
         <v>15</v>
@@ -11281,24 +11284,24 @@
         <v>120</v>
       </c>
       <c r="E310" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F310" s="12">
         <v>27</v>
       </c>
       <c r="G310" s="15">
-        <v>0.037037037037037035</v>
+        <v>0</v>
       </c>
       <c r="H310" s="13" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I310" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="12" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="B311" s="12" t="s">
         <v>15</v>
@@ -11310,24 +11313,24 @@
         <v>120</v>
       </c>
       <c r="E311" s="12">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="F311" s="12">
-        <v>308</v>
+        <v>189</v>
       </c>
       <c r="G311" s="15">
-        <v>0.5227272727272727</v>
+        <v>0.656084656084656</v>
       </c>
       <c r="H311" s="13" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I311" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="12" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="B312" s="12" t="s">
         <v>15</v>
@@ -11339,24 +11342,24 @@
         <v>120</v>
       </c>
       <c r="E312" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F312" s="12">
         <v>27</v>
       </c>
       <c r="G312" s="15">
-        <v>0.037037037037037035</v>
+        <v>0</v>
       </c>
       <c r="H312" s="13" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I312" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="12" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B313" s="12" t="s">
         <v>15</v>
@@ -11368,24 +11371,24 @@
         <v>120</v>
       </c>
       <c r="E313" s="12">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="F313" s="12">
-        <v>346</v>
+        <v>189</v>
       </c>
       <c r="G313" s="15">
-        <v>0.4653179190751445</v>
+        <v>0.783068783068783</v>
       </c>
       <c r="H313" s="13" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I313" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="12" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B314" s="12" t="s">
         <v>15</v>
@@ -11406,15 +11409,15 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H314" s="13" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I314" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="12" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B315" s="12" t="s">
         <v>15</v>
@@ -11426,24 +11429,24 @@
         <v>120</v>
       </c>
       <c r="E315" s="12">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F315" s="12">
-        <v>346</v>
+        <v>189</v>
       </c>
       <c r="G315" s="15">
-        <v>0.4653179190751445</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="H315" s="13" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I315" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="12" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B316" s="12" t="s">
         <v>15</v>
@@ -11464,15 +11467,15 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H316" s="13" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I316" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="12" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="B317" s="12" t="s">
         <v>15</v>
@@ -11484,24 +11487,24 @@
         <v>120</v>
       </c>
       <c r="E317" s="12">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F317" s="12">
-        <v>346</v>
+        <v>308</v>
       </c>
       <c r="G317" s="15">
-        <v>0.4653179190751445</v>
+        <v>0.5194805194805194</v>
       </c>
       <c r="H317" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I317" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B318" s="12" t="s">
         <v>15</v>
@@ -11522,36 +11525,36 @@
         <v>0.037037037037037035</v>
       </c>
       <c r="H318" s="13" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I318" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="12" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="B319" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C319" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D319" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E319" s="12">
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="F319" s="12">
-        <v>346</v>
+        <v>27</v>
       </c>
       <c r="G319" s="15">
-        <v>0.4653179190751445</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H319" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I319" s="12" t="s">
         <v>127</v>
@@ -11559,202 +11562,202 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="12" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B320" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C320" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D320" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E320" s="12">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="F320" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G320" s="15">
-        <v>0.06040268456375839</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H320" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I320" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="12" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B321" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C321" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D321" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E321" s="12">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F321" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G321" s="15">
-        <v>0.14093959731543623</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H321" s="13" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I321" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" s="12" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B322" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C322" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D322" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E322" s="12">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="F322" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G322" s="15">
-        <v>0.15436241610738255</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H322" s="13" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I322" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="12" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B323" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C323" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D323" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E323" s="12">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F323" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G323" s="15">
-        <v>0.2080536912751678</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H323" s="13" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I323" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" s="12" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B324" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C324" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D324" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E324" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F324" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G324" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H324" s="13" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I324" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" s="12" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="B325" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C325" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D325" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E325" s="12">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F325" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G325" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H325" s="13" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="I325" s="12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" s="12" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="B326" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C326" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D326" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E326" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F326" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G326" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H326" s="13" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I326" s="12" t="s">
         <v>127</v>
@@ -11762,28 +11765,28 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B327" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C327" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D327" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E327" s="12">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F327" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G327" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H327" s="13" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="I327" s="12" t="s">
         <v>127</v>
@@ -11791,28 +11794,28 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="12" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="B328" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C328" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D328" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E328" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F328" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G328" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H328" s="13" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I328" s="12" t="s">
         <v>127</v>
@@ -11820,28 +11823,28 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B329" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C329" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D329" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E329" s="12">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F329" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G329" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H329" s="13" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="I329" s="12" t="s">
         <v>127</v>
@@ -11849,28 +11852,28 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B330" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C330" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D330" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E330" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F330" s="12">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="G330" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H330" s="13" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I330" s="12" t="s">
         <v>127</v>
@@ -11878,28 +11881,28 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B331" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C331" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D331" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E331" s="12">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F331" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G331" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H331" s="13" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="I331" s="12" t="s">
         <v>127</v>
@@ -11910,25 +11913,25 @@
         <v>132</v>
       </c>
       <c r="B332" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C332" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D332" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E332" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F332" s="12">
-        <v>149</v>
+        <v>346</v>
       </c>
       <c r="G332" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.4653179190751445</v>
       </c>
       <c r="H332" s="13" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I332" s="12" t="s">
         <v>127</v>
@@ -11939,25 +11942,25 @@
         <v>133</v>
       </c>
       <c r="B333" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C333" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D333" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E333" s="12">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F333" s="12">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="G333" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="H333" s="13" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="I333" s="12" t="s">
         <v>127</v>
@@ -11965,28 +11968,28 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B334" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C334" s="13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D334" s="12" t="s">
         <v>120</v>
       </c>
       <c r="E334" s="12">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="F334" s="12">
-        <v>149</v>
+        <v>346</v>
       </c>
       <c r="G334" s="15">
-        <v>0.22818791946308725</v>
+        <v>0.4653179190751445</v>
       </c>
       <c r="H334" s="13" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I334" s="12" t="s">
         <v>127</v>
@@ -11994,35 +11997,673 @@
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B335" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C335" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D335" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E335" s="12">
+        <v>1</v>
+      </c>
+      <c r="F335" s="12">
+        <v>27</v>
+      </c>
+      <c r="G335" s="15">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H335" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I335" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B336" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C336" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D336" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E336" s="12">
+        <v>161</v>
+      </c>
+      <c r="F336" s="12">
+        <v>346</v>
+      </c>
+      <c r="G336" s="15">
+        <v>0.4653179190751445</v>
+      </c>
+      <c r="H336" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="I336" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B337" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C337" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D337" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E337" s="12">
+        <v>1</v>
+      </c>
+      <c r="F337" s="12">
+        <v>27</v>
+      </c>
+      <c r="G337" s="15">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H337" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I337" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B338" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C338" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D338" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E338" s="12">
+        <v>161</v>
+      </c>
+      <c r="F338" s="12">
+        <v>346</v>
+      </c>
+      <c r="G338" s="15">
+        <v>0.4653179190751445</v>
+      </c>
+      <c r="H338" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="I338" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B335" s="12" t="s">
+      <c r="B339" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C339" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D339" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E339" s="12">
+        <v>1</v>
+      </c>
+      <c r="F339" s="12">
+        <v>27</v>
+      </c>
+      <c r="G339" s="15">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="H339" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I339" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B340" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C340" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D340" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E340" s="12">
+        <v>161</v>
+      </c>
+      <c r="F340" s="12">
+        <v>346</v>
+      </c>
+      <c r="G340" s="15">
+        <v>0.4653179190751445</v>
+      </c>
+      <c r="H340" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="I340" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B341" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C335" s="13" t="s">
+      <c r="C341" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D335" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E335" s="12">
+      <c r="D341" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E341" s="12">
+        <v>9</v>
+      </c>
+      <c r="F341" s="12">
+        <v>149</v>
+      </c>
+      <c r="G341" s="15">
+        <v>0.06040268456375839</v>
+      </c>
+      <c r="H341" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="I341" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B342" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C342" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D342" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E342" s="12">
+        <v>21</v>
+      </c>
+      <c r="F342" s="12">
+        <v>149</v>
+      </c>
+      <c r="G342" s="15">
+        <v>0.14093959731543623</v>
+      </c>
+      <c r="H342" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="I342" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B343" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C343" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D343" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E343" s="12">
+        <v>23</v>
+      </c>
+      <c r="F343" s="12">
+        <v>149</v>
+      </c>
+      <c r="G343" s="15">
+        <v>0.15436241610738255</v>
+      </c>
+      <c r="H343" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I343" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B344" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C344" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D344" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E344" s="12">
+        <v>31</v>
+      </c>
+      <c r="F344" s="12">
+        <v>149</v>
+      </c>
+      <c r="G344" s="15">
+        <v>0.2080536912751678</v>
+      </c>
+      <c r="H344" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="I344" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B345" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C345" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D345" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E345" s="12">
         <v>34</v>
       </c>
-      <c r="F335" s="12">
+      <c r="F345" s="12">
         <v>149</v>
       </c>
-      <c r="G335" s="15">
+      <c r="G345" s="15">
         <v>0.22818791946308725</v>
       </c>
-      <c r="H335" s="13" t="s">
+      <c r="H345" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="I335" s="12" t="s">
+      <c r="I345" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B346" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C346" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D346" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E346" s="12">
+        <v>34</v>
+      </c>
+      <c r="F346" s="12">
+        <v>149</v>
+      </c>
+      <c r="G346" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H346" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="I346" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B347" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C347" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D347" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E347" s="12">
+        <v>34</v>
+      </c>
+      <c r="F347" s="12">
+        <v>149</v>
+      </c>
+      <c r="G347" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H347" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I347" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B348" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C348" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D348" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E348" s="12">
+        <v>34</v>
+      </c>
+      <c r="F348" s="12">
+        <v>149</v>
+      </c>
+      <c r="G348" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H348" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I348" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B349" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C349" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D349" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E349" s="12">
+        <v>34</v>
+      </c>
+      <c r="F349" s="12">
+        <v>149</v>
+      </c>
+      <c r="G349" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H349" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I349" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B350" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C350" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D350" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E350" s="12">
+        <v>34</v>
+      </c>
+      <c r="F350" s="12">
+        <v>149</v>
+      </c>
+      <c r="G350" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H350" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I350" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B351" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C351" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D351" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E351" s="12">
+        <v>34</v>
+      </c>
+      <c r="F351" s="12">
+        <v>149</v>
+      </c>
+      <c r="G351" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H351" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I351" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B352" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C352" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D352" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E352" s="12">
+        <v>34</v>
+      </c>
+      <c r="F352" s="12">
+        <v>149</v>
+      </c>
+      <c r="G352" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H352" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I352" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B353" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C353" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D353" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E353" s="12">
+        <v>34</v>
+      </c>
+      <c r="F353" s="12">
+        <v>149</v>
+      </c>
+      <c r="G353" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H353" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I353" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B354" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C354" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D354" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E354" s="12">
+        <v>34</v>
+      </c>
+      <c r="F354" s="12">
+        <v>149</v>
+      </c>
+      <c r="G354" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H354" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I354" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B355" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C355" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D355" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E355" s="12">
+        <v>34</v>
+      </c>
+      <c r="F355" s="12">
+        <v>149</v>
+      </c>
+      <c r="G355" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H355" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I355" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B356" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C356" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D356" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E356" s="12">
+        <v>34</v>
+      </c>
+      <c r="F356" s="12">
+        <v>149</v>
+      </c>
+      <c r="G356" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H356" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I356" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B357" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C357" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D357" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E357" s="12">
+        <v>34</v>
+      </c>
+      <c r="F357" s="12">
+        <v>149</v>
+      </c>
+      <c r="G357" s="15">
+        <v>0.22818791946308725</v>
+      </c>
+      <c r="H357" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I357" s="12" t="s">
         <v>127</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I335"/>
+  <autoFilter ref="A1:I357"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -12039,10 +12680,10 @@
   <sheetData>
     <row r="1" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -12050,23 +12691,23 @@
         <v>79</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -12074,23 +12715,23 @@
         <v>94</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
